--- a/luban-excels/bak/xlsx/Items.xlsx
+++ b/luban-excels/bak/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="717">
   <si>
     <t>##var</t>
   </si>
@@ -313,87 +313,96 @@
     <t>Dog</t>
   </si>
   <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>初始拥有</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Red\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Red.png</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>黑柴</t>
+  </si>
+  <si>
+    <t>神话</t>
+  </si>
+  <si>
+    <t>装扮盲盒产出</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Black\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Black.png</t>
+  </si>
+  <si>
+    <t>Cream</t>
+  </si>
+  <si>
+    <t>白柴</t>
+  </si>
+  <si>
+    <t>史诗</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Cream\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Cream.png</t>
+  </si>
+  <si>
+    <t>Sesame</t>
+  </si>
+  <si>
+    <t>胡麻柴</t>
+  </si>
+  <si>
+    <t>传说</t>
+  </si>
+  <si>
+    <t>v1\Shiba\Sesame\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_Sesame.png</t>
+  </si>
+  <si>
+    <t>Thin Red</t>
+  </si>
+  <si>
+    <t>瘦赤柴</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_ThinRed.png</t>
+  </si>
+  <si>
+    <t>Unshaven Red</t>
+  </si>
+  <si>
+    <t>胡渣赤柴</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Shiba_UnshavenRed.png</t>
+  </si>
+  <si>
+    <t>Thin Black</t>
+  </si>
+  <si>
+    <t>瘦黑柴</t>
+  </si>
+  <si>
     <t>稀有</t>
   </si>
   <si>
-    <t>初始拥有</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Red\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_Red.png</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>黑柴</t>
-  </si>
-  <si>
-    <t>装扮盲盒产出</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Black\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_Black.png</t>
-  </si>
-  <si>
-    <t>Cream</t>
-  </si>
-  <si>
-    <t>白柴</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Cream\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_Cream.png</t>
-  </si>
-  <si>
-    <t>Sesame</t>
-  </si>
-  <si>
-    <t>胡麻柴</t>
-  </si>
-  <si>
-    <t>v1\Shiba\Sesame\</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_Sesame.png</t>
-  </si>
-  <si>
-    <t>Thin Red</t>
-  </si>
-  <si>
-    <t>瘦赤柴</t>
-  </si>
-  <si>
-    <t>史诗</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_ThinRed.png</t>
-  </si>
-  <si>
-    <t>Unshaven Red</t>
-  </si>
-  <si>
-    <t>胡渣赤柴</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Shiba_UnshavenRed.png</t>
-  </si>
-  <si>
-    <t>Thin Black</t>
-  </si>
-  <si>
-    <t>瘦黑柴</t>
-  </si>
-  <si>
     <t>v1\ItemIcon\Shiba_ThinBlack.png</t>
   </si>
   <si>
@@ -421,9 +430,6 @@
     <t>胡渣白柴</t>
   </si>
   <si>
-    <t>传说</t>
-  </si>
-  <si>
     <t>v1\ItemIcon\Shiba_UnshavenCream.png</t>
   </si>
   <si>
@@ -454,7 +460,7 @@
     <t>Headwear</t>
   </si>
   <si>
-    <t>普通</t>
+    <t>优秀</t>
   </si>
   <si>
     <t>v1\Headwear\Beret_Green.png</t>
@@ -1474,148 +1480,154 @@
     <t>小狗本体</t>
   </si>
   <si>
+    <t>Mythic</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>在全部国家隐藏</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
+    <t>小狗头部装饰</t>
+  </si>
+  <si>
     <t>Legendary</t>
   </si>
   <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>在全部国家隐藏</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>默认</t>
-  </si>
-  <si>
-    <t>小狗头部装饰</t>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>沙特阿拉伯</t>
+  </si>
+  <si>
+    <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
+  </si>
+  <si>
+    <t>Serious</t>
+  </si>
+  <si>
+    <t>严肃</t>
+  </si>
+  <si>
+    <t>小狗眼部装饰</t>
   </si>
   <si>
     <t>Epic</t>
   </si>
   <si>
-    <t>SA</t>
-  </si>
-  <si>
-    <t>沙特阿拉伯</t>
-  </si>
-  <si>
-    <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
-  </si>
-  <si>
-    <t>Serious</t>
-  </si>
-  <si>
-    <t>严肃</t>
-  </si>
-  <si>
-    <t>小狗眼部装饰</t>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>阿联酋</t>
+  </si>
+  <si>
+    <t>United Arab Emirates赌博/宗教/酒精/色情</t>
+  </si>
+  <si>
+    <t>Bored</t>
+  </si>
+  <si>
+    <t>无聊</t>
+  </si>
+  <si>
+    <t>手臂层的装饰</t>
   </si>
   <si>
     <t>Rare</t>
   </si>
   <si>
-    <t>AE</t>
-  </si>
-  <si>
-    <t>阿联酋</t>
-  </si>
-  <si>
-    <t>United Arab Emirates赌博/宗教/酒精/色情</t>
-  </si>
-  <si>
-    <t>Bored</t>
-  </si>
-  <si>
-    <t>无聊</t>
-  </si>
-  <si>
-    <t>手臂层的装饰</t>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>伊朗</t>
+  </si>
+  <si>
+    <t>Iran宗教/进化论/赌博/政治/西方文化</t>
+  </si>
+  <si>
+    <t>Wink</t>
+  </si>
+  <si>
+    <t>媚眼</t>
+  </si>
+  <si>
+    <t>玩家手臂衣服</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>巴基斯坦</t>
+  </si>
+  <si>
+    <t>Pakistan国家形象/政治</t>
+  </si>
+  <si>
+    <t>Excited</t>
+  </si>
+  <si>
+    <t>兴奋</t>
+  </si>
+  <si>
+    <t>桌布</t>
   </si>
   <si>
     <t>Common</t>
   </si>
   <si>
-    <t>IR</t>
-  </si>
-  <si>
-    <t>伊朗</t>
-  </si>
-  <si>
-    <t>Iran宗教/进化论/赌博/政治/西方文化</t>
-  </si>
-  <si>
-    <t>Wink</t>
-  </si>
-  <si>
-    <t>媚眼</t>
-  </si>
-  <si>
-    <t>玩家手臂衣服</t>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>马来西亚</t>
+  </si>
+  <si>
+    <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
+  </si>
+  <si>
+    <t>Starstruck</t>
+  </si>
+  <si>
+    <t>崇拜</t>
+  </si>
+  <si>
+    <t>背景</t>
   </si>
   <si>
     <t>Special1</t>
   </si>
   <si>
-    <t>PK</t>
-  </si>
-  <si>
-    <t>巴基斯坦</t>
-  </si>
-  <si>
-    <t>Pakistan国家形象/政治</t>
-  </si>
-  <si>
-    <t>Excited</t>
-  </si>
-  <si>
-    <t>兴奋</t>
-  </si>
-  <si>
-    <t>桌布</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>印尼</t>
+  </si>
+  <si>
+    <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
+  </si>
+  <si>
+    <t>Silent</t>
+  </si>
+  <si>
+    <t>沉默</t>
+  </si>
+  <si>
+    <t>玩家手部装饰</t>
   </si>
   <si>
     <t>Special2</t>
   </si>
   <si>
     <t>特殊2</t>
-  </si>
-  <si>
-    <t>MY</t>
-  </si>
-  <si>
-    <t>马来西亚</t>
-  </si>
-  <si>
-    <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
-  </si>
-  <si>
-    <t>Starstruck</t>
-  </si>
-  <si>
-    <t>崇拜</t>
-  </si>
-  <si>
-    <t>背景</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>印尼</t>
-  </si>
-  <si>
-    <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
-  </si>
-  <si>
-    <t>Silent</t>
-  </si>
-  <si>
-    <t>沉默</t>
-  </si>
-  <si>
-    <t>玩家手部装饰</t>
   </si>
   <si>
     <t>RU</t>
@@ -1970,28 +1982,7 @@
     <t>权重</t>
   </si>
   <si>
-    <t>标准盲盒：普通</t>
-  </si>
-  <si>
-    <t>标准盲盒：稀有</t>
-  </si>
-  <si>
-    <t>标准盲盒：史诗</t>
-  </si>
-  <si>
-    <t>标准盲盒：传说</t>
-  </si>
-  <si>
-    <t>新手盲盒：普通</t>
-  </si>
-  <si>
-    <t>新手盲盒：稀有</t>
-  </si>
-  <si>
-    <t>新手盲盒：史诗</t>
-  </si>
-  <si>
-    <t>新手盲盒：传说</t>
+    <t>新手盲盒概率会高一点</t>
   </si>
   <si>
     <t>测试活动盲盒：特殊1</t>
@@ -2003,7 +1994,10 @@
     <t>StartRarity</t>
   </si>
   <si>
-    <t>MiddleRarity</t>
+    <t>MiddleRarity1</t>
+  </si>
+  <si>
+    <t>MiddleRarity2</t>
   </si>
   <si>
     <t>FinalRarity</t>
@@ -2042,7 +2036,7 @@
     <t>初始品质</t>
   </si>
   <si>
-    <t>过程品质</t>
+    <t>过程品质1</t>
   </si>
   <si>
     <t>最终品质</t>
@@ -2051,7 +2045,7 @@
     <t>是否提前结束</t>
   </si>
   <si>
-    <t>连升2品</t>
+    <t>连升2</t>
   </si>
   <si>
     <t>BlindBoxSpritePath</t>
@@ -2063,6 +2057,9 @@
     <t>BlindBoxGlowPath</t>
   </si>
   <si>
+    <t>BlindBoxBackgroundColor</t>
+  </si>
+  <si>
     <t>BlindBoxBackgroundPath</t>
   </si>
   <si>
@@ -2079,6 +2076,9 @@
   </si>
   <si>
     <t>可选</t>
+  </si>
+  <si>
+    <t>16进制颜色代码</t>
   </si>
   <si>
     <t>开盲盒环节，该品质出现时，播放的音效。
@@ -2094,6 +2094,9 @@
     <t>盲盒发光图</t>
   </si>
   <si>
+    <t>背景颜色</t>
+  </si>
+  <si>
     <t>盲盒背景图</t>
   </si>
   <si>
@@ -2103,31 +2106,55 @@
     <t>升品特效路径</t>
   </si>
   <si>
+    <t>UI\BlindBox\BlindBox_Mythic_Closed.png</t>
+  </si>
+  <si>
+    <t>UI\BlindBox\BlindBox_General_Shadow.png</t>
+  </si>
+  <si>
+    <t>e3504a</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
     <t>UI\BlindBox\BlindBox_Legendary_Closed.png</t>
   </si>
   <si>
-    <t>UI\BlindBox\BlindBox_General_Shadow.png</t>
+    <t>f0b811</t>
+  </si>
+  <si>
+    <t>do</t>
+  </si>
+  <si>
+    <t>UI\BlindBox\BlindBox_Epic_Closed.png</t>
+  </si>
+  <si>
+    <t>b574f0</t>
   </si>
   <si>
     <t>si</t>
   </si>
   <si>
-    <t>UI\BlindBox\BlindBox_Epic_Closed.png</t>
+    <t>UI\BlindBox\BlindBox_Rare_Closed.png</t>
+  </si>
+  <si>
+    <t>0f7edc</t>
   </si>
   <si>
     <t>sol</t>
   </si>
   <si>
-    <t>UI\BlindBox\BlindBox_Rare_Closed.png</t>
-  </si>
-  <si>
-    <t>mi</t>
+    <t>UI\BlindBox\BlindBox_Uncommon_Closed.png</t>
+  </si>
+  <si>
+    <t>68c68c</t>
   </si>
   <si>
     <t>UI\BlindBox\BlindBox_Common_Closed.png</t>
   </si>
   <si>
-    <t>do</t>
+    <t>e4bf8f</t>
   </si>
   <si>
     <t>实际上特殊品质的盲盒没有显示图片的机会</t>
@@ -2158,9 +2185,6 @@
   </si>
   <si>
     <t>Theme</t>
-  </si>
-  <si>
-    <t>Card</t>
   </si>
   <si>
     <t>CanUnequip</t>
@@ -2799,7 +2823,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2820,6 +2844,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2879,7 +2909,49 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="23">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="-0.25"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="-0.25"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3073,25 +3145,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="11"/>
+      <tableStyleElement type="totalRow" dxfId="10"/>
+      <tableStyleElement type="firstColumn" dxfId="9"/>
+      <tableStyleElement type="lastColumn" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="22"/>
+      <tableStyleElement type="totalRow" dxfId="21"/>
+      <tableStyleElement type="firstRowStripe" dxfId="20"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="19"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="18"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="16"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="15"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="14"/>
+      <tableStyleElement type="pageFieldValues" dxfId="13"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3591,7 +3663,7 @@
       <c r="J3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="8"/>
+      <c r="K3" s="10"/>
       <c r="L3" s="1" t="s">
         <v>46</v>
       </c>
@@ -3823,7 +3895,7 @@
         <v>89</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I6">
         <v>200</v>
@@ -3832,7 +3904,7 @@
         <v>200</v>
       </c>
       <c r="K6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -3847,10 +3919,10 @@
         <v>400</v>
       </c>
       <c r="S6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U6">
         <v>1002</v>
@@ -3882,16 +3954,16 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
         <v>89</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I7">
         <v>200</v>
@@ -3900,7 +3972,7 @@
         <v>200</v>
       </c>
       <c r="K7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -3915,10 +3987,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="U7">
         <v>1003</v>
@@ -3950,16 +4022,16 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
         <v>89</v>
       </c>
       <c r="H8" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="I8">
         <v>200</v>
@@ -3968,7 +4040,7 @@
         <v>200</v>
       </c>
       <c r="K8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -3983,10 +4055,10 @@
         <v>400</v>
       </c>
       <c r="S8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="U8">
         <v>1004</v>
@@ -4018,16 +4090,16 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
         <v>89</v>
       </c>
       <c r="H9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -4036,7 +4108,7 @@
         <v>100</v>
       </c>
       <c r="K9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -4054,7 +4126,7 @@
         <v>92</v>
       </c>
       <c r="T9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="U9">
         <v>1005</v>
@@ -4086,16 +4158,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
         <v>89</v>
       </c>
       <c r="H10" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -4104,7 +4176,7 @@
         <v>100</v>
       </c>
       <c r="K10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -4122,7 +4194,7 @@
         <v>92</v>
       </c>
       <c r="T10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="U10">
         <v>1006</v>
@@ -4154,16 +4226,16 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
         <v>89</v>
       </c>
       <c r="H11" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -4172,7 +4244,7 @@
         <v>100</v>
       </c>
       <c r="K11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -4187,10 +4259,10 @@
         <v>200</v>
       </c>
       <c r="S11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T11" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="U11">
         <v>1007</v>
@@ -4222,16 +4294,16 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
         <v>89</v>
       </c>
       <c r="H12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -4240,7 +4312,7 @@
         <v>100</v>
       </c>
       <c r="K12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -4255,10 +4327,10 @@
         <v>200</v>
       </c>
       <c r="S12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="U12">
         <v>1008</v>
@@ -4290,16 +4362,16 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
         <v>89</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -4308,7 +4380,7 @@
         <v>100</v>
       </c>
       <c r="K13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -4323,10 +4395,10 @@
         <v>200</v>
       </c>
       <c r="S13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="U13">
         <v>1009</v>
@@ -4358,16 +4430,16 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E14" t="s">
         <v>89</v>
       </c>
       <c r="H14" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -4376,7 +4448,7 @@
         <v>100</v>
       </c>
       <c r="K14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -4391,10 +4463,10 @@
         <v>200</v>
       </c>
       <c r="S14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="T14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="U14">
         <v>1010</v>
@@ -4426,16 +4498,16 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s">
         <v>89</v>
       </c>
       <c r="H15" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -4444,7 +4516,7 @@
         <v>100</v>
       </c>
       <c r="K15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -4459,10 +4531,10 @@
         <v>200</v>
       </c>
       <c r="S15" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="U15">
         <v>1011</v>
@@ -4494,16 +4566,16 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
         <v>89</v>
       </c>
       <c r="H16" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -4512,7 +4584,7 @@
         <v>100</v>
       </c>
       <c r="K16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
@@ -4527,10 +4599,10 @@
         <v>200</v>
       </c>
       <c r="S16" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="U16">
         <v>1012</v>
@@ -4567,16 +4639,16 @@
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I18">
         <v>300</v>
@@ -4585,7 +4657,7 @@
         <v>300</v>
       </c>
       <c r="K18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -4600,10 +4672,10 @@
         <v>300</v>
       </c>
       <c r="S18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="T18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="W18">
         <v>0</v>
@@ -4632,16 +4704,16 @@
         <v>2002</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H19" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I19">
         <v>300</v>
@@ -4650,7 +4722,7 @@
         <v>300</v>
       </c>
       <c r="K19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -4665,10 +4737,10 @@
         <v>300</v>
       </c>
       <c r="S19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="T19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="W19">
         <v>0</v>
@@ -4697,16 +4769,16 @@
         <v>2003</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E20" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H20" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I20">
         <v>300</v>
@@ -4715,7 +4787,7 @@
         <v>300</v>
       </c>
       <c r="K20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -4730,10 +4802,10 @@
         <v>300</v>
       </c>
       <c r="S20" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="T20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="W20">
         <v>0</v>
@@ -4762,16 +4834,16 @@
         <v>2004</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H21" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I21">
         <v>300</v>
@@ -4780,7 +4852,7 @@
         <v>300</v>
       </c>
       <c r="K21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -4795,10 +4867,10 @@
         <v>300</v>
       </c>
       <c r="S21" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="T21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="W21">
         <v>0</v>
@@ -4827,16 +4899,16 @@
         <v>2005</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H22" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I22">
         <v>300</v>
@@ -4845,7 +4917,7 @@
         <v>300</v>
       </c>
       <c r="K22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -4860,10 +4932,10 @@
         <v>300</v>
       </c>
       <c r="S22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="T22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="W22">
         <v>0</v>
@@ -4892,16 +4964,16 @@
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H23" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I23">
         <v>300</v>
@@ -4910,7 +4982,7 @@
         <v>300</v>
       </c>
       <c r="K23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -4925,10 +4997,10 @@
         <v>300</v>
       </c>
       <c r="S23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T23" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="W23">
         <v>0</v>
@@ -4957,16 +5029,16 @@
         <v>2007</v>
       </c>
       <c r="C24" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H24" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I24">
         <v>300</v>
@@ -4975,7 +5047,7 @@
         <v>300</v>
       </c>
       <c r="K24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -4990,10 +5062,10 @@
         <v>300</v>
       </c>
       <c r="S24" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="T24" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="W24">
         <v>0</v>
@@ -5022,16 +5094,16 @@
         <v>2008</v>
       </c>
       <c r="C25" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D25" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E25" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H25" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I25">
         <v>300</v>
@@ -5040,7 +5112,7 @@
         <v>300</v>
       </c>
       <c r="K25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -5055,10 +5127,10 @@
         <v>300</v>
       </c>
       <c r="S25" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="T25" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="W25">
         <v>0</v>
@@ -5087,16 +5159,16 @@
         <v>2009</v>
       </c>
       <c r="C26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E26" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I26">
         <v>300</v>
@@ -5105,7 +5177,7 @@
         <v>300</v>
       </c>
       <c r="K26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -5120,10 +5192,10 @@
         <v>300</v>
       </c>
       <c r="S26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="T26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="W26">
         <v>0</v>
@@ -5152,16 +5224,16 @@
         <v>2010</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E27" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H27" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I27">
         <v>300</v>
@@ -5170,7 +5242,7 @@
         <v>300</v>
       </c>
       <c r="K27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -5185,10 +5257,10 @@
         <v>300</v>
       </c>
       <c r="S27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="T27" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="W27">
         <v>0</v>
@@ -5217,16 +5289,16 @@
         <v>3001</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D28" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E28" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H28" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I28">
         <v>300</v>
@@ -5235,7 +5307,7 @@
         <v>300</v>
       </c>
       <c r="K28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -5250,10 +5322,10 @@
         <v>300</v>
       </c>
       <c r="S28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="T28" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="W28">
         <v>0</v>
@@ -5282,16 +5354,16 @@
         <v>3002</v>
       </c>
       <c r="C29" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D29" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E29" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H29" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I29">
         <v>300</v>
@@ -5300,7 +5372,7 @@
         <v>300</v>
       </c>
       <c r="K29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
@@ -5315,10 +5387,10 @@
         <v>300</v>
       </c>
       <c r="S29" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="T29" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="W29">
         <v>0</v>
@@ -5347,16 +5419,16 @@
         <v>3003</v>
       </c>
       <c r="C30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E30" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H30" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I30">
         <v>300</v>
@@ -5365,7 +5437,7 @@
         <v>300</v>
       </c>
       <c r="K30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -5380,10 +5452,10 @@
         <v>300</v>
       </c>
       <c r="S30" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="T30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="W30">
         <v>0</v>
@@ -5412,16 +5484,16 @@
         <v>3004</v>
       </c>
       <c r="C31" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D31" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E31" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H31" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I31">
         <v>300</v>
@@ -5430,7 +5502,7 @@
         <v>300</v>
       </c>
       <c r="K31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
@@ -5445,10 +5517,10 @@
         <v>300</v>
       </c>
       <c r="S31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T31" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="W31">
         <v>0</v>
@@ -5477,16 +5549,16 @@
         <v>3005</v>
       </c>
       <c r="C32" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E32" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H32" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I32">
         <v>300</v>
@@ -5495,7 +5567,7 @@
         <v>300</v>
       </c>
       <c r="K32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -5510,10 +5582,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="T32" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="W32">
         <v>0</v>
@@ -5542,19 +5614,19 @@
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F33" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H33" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5578,10 +5650,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="T33" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="W33">
         <v>0</v>
@@ -5610,19 +5682,19 @@
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D34" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E34" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F34" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H34" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -5646,10 +5718,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T34" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="W34">
         <v>0</v>
@@ -5678,19 +5750,19 @@
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D35" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E35" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F35" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H35" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -5714,10 +5786,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="T35" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="W35">
         <v>0</v>
@@ -5746,19 +5818,19 @@
         <v>4004</v>
       </c>
       <c r="C36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D36" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E36" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F36" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H36" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -5782,10 +5854,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="T36" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="W36">
         <v>0</v>
@@ -5814,16 +5886,16 @@
         <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D37" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E37" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H37" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I37">
         <v>300</v>
@@ -5832,7 +5904,7 @@
         <v>300</v>
       </c>
       <c r="K37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -5847,10 +5919,10 @@
         <v>300</v>
       </c>
       <c r="S37" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="T37" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="W37">
         <v>0</v>
@@ -5879,16 +5951,16 @@
         <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H38" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I38">
         <v>300</v>
@@ -5897,7 +5969,7 @@
         <v>300</v>
       </c>
       <c r="K38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -5912,10 +5984,10 @@
         <v>300</v>
       </c>
       <c r="S38" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="T38" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="W38">
         <v>0</v>
@@ -5944,16 +6016,16 @@
         <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E39" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H39" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I39">
         <v>300</v>
@@ -5962,7 +6034,7 @@
         <v>300</v>
       </c>
       <c r="K39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
@@ -5977,10 +6049,10 @@
         <v>300</v>
       </c>
       <c r="S39" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="T39" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="W39">
         <v>0</v>
@@ -6009,16 +6081,16 @@
         <v>5004</v>
       </c>
       <c r="C40" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E40" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H40" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I40">
         <v>300</v>
@@ -6027,7 +6099,7 @@
         <v>300</v>
       </c>
       <c r="K40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -6042,10 +6114,10 @@
         <v>300</v>
       </c>
       <c r="S40" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="T40" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="W40">
         <v>0</v>
@@ -6074,16 +6146,16 @@
         <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E41" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H41" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I41">
         <v>300</v>
@@ -6092,7 +6164,7 @@
         <v>300</v>
       </c>
       <c r="K41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
@@ -6107,10 +6179,10 @@
         <v>300</v>
       </c>
       <c r="S41" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="T41" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="W41">
         <v>0</v>
@@ -6139,16 +6211,16 @@
         <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D42" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E42" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H42" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I42">
         <v>300</v>
@@ -6157,7 +6229,7 @@
         <v>300</v>
       </c>
       <c r="K42" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
@@ -6172,10 +6244,10 @@
         <v>300</v>
       </c>
       <c r="S42" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="T42" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="W42">
         <v>0</v>
@@ -6204,16 +6276,16 @@
         <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H43" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I43">
         <v>300</v>
@@ -6222,7 +6294,7 @@
         <v>300</v>
       </c>
       <c r="K43" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
@@ -6237,10 +6309,10 @@
         <v>300</v>
       </c>
       <c r="S43" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T43" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="W43">
         <v>0</v>
@@ -6269,16 +6341,16 @@
         <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D44" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E44" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H44" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I44">
         <v>300</v>
@@ -6287,7 +6359,7 @@
         <v>300</v>
       </c>
       <c r="K44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
@@ -6302,10 +6374,10 @@
         <v>300</v>
       </c>
       <c r="S44" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="T44" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="W44">
         <v>0</v>
@@ -6334,16 +6406,16 @@
         <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D45" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E45" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H45" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I45">
         <v>300</v>
@@ -6367,10 +6439,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="T45" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="W45">
         <v>0</v>
@@ -6399,16 +6471,16 @@
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D46" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E46" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H46" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I46">
         <v>300</v>
@@ -6417,7 +6489,7 @@
         <v>300</v>
       </c>
       <c r="K46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -6432,10 +6504,10 @@
         <v>300</v>
       </c>
       <c r="S46" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="T46" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="W46">
         <v>0</v>
@@ -6464,16 +6536,16 @@
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D47" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E47" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H47" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I47">
         <v>300</v>
@@ -6482,7 +6554,7 @@
         <v>300</v>
       </c>
       <c r="K47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
@@ -6497,10 +6569,10 @@
         <v>300</v>
       </c>
       <c r="S47" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="T47" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="W47">
         <v>0</v>
@@ -6529,16 +6601,16 @@
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D48" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E48" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H48" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I48">
         <v>300</v>
@@ -6547,7 +6619,7 @@
         <v>300</v>
       </c>
       <c r="K48" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -6562,10 +6634,10 @@
         <v>300</v>
       </c>
       <c r="S48" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="T48" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="W48">
         <v>0</v>
@@ -6594,16 +6666,16 @@
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E49" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H49" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I49">
         <v>300</v>
@@ -6612,7 +6684,7 @@
         <v>300</v>
       </c>
       <c r="K49" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -6627,10 +6699,10 @@
         <v>300</v>
       </c>
       <c r="S49" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="T49" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="W49">
         <v>0</v>
@@ -6659,16 +6731,16 @@
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D50" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E50" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H50" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I50">
         <v>300</v>
@@ -6677,7 +6749,7 @@
         <v>300</v>
       </c>
       <c r="K50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
@@ -6692,10 +6764,10 @@
         <v>300</v>
       </c>
       <c r="S50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="T50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="W50">
         <v>0</v>
@@ -6724,16 +6796,16 @@
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D51" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E51" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H51" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I51">
         <v>300</v>
@@ -6742,7 +6814,7 @@
         <v>300</v>
       </c>
       <c r="K51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
@@ -6757,10 +6829,10 @@
         <v>300</v>
       </c>
       <c r="S51" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="T51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="W51">
         <v>0</v>
@@ -6789,16 +6861,16 @@
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D52" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E52" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H52" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I52">
         <v>300</v>
@@ -6807,7 +6879,7 @@
         <v>300</v>
       </c>
       <c r="K52" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -6822,10 +6894,10 @@
         <v>300</v>
       </c>
       <c r="S52" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="T52" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="W52">
         <v>0</v>
@@ -6854,16 +6926,16 @@
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D53" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E53" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H53" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I53">
         <v>300</v>
@@ -6872,7 +6944,7 @@
         <v>300</v>
       </c>
       <c r="K53" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -6887,10 +6959,10 @@
         <v>300</v>
       </c>
       <c r="S53" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="T53" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="W53">
         <v>0</v>
@@ -6919,16 +6991,16 @@
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D54" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E54" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H54" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I54">
         <v>300</v>
@@ -6937,7 +7009,7 @@
         <v>300</v>
       </c>
       <c r="K54" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
@@ -6952,10 +7024,10 @@
         <v>300</v>
       </c>
       <c r="S54" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="T54" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="W54">
         <v>0</v>
@@ -6984,16 +7056,16 @@
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D55" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E55" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H55" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I55">
         <v>300</v>
@@ -7002,7 +7074,7 @@
         <v>300</v>
       </c>
       <c r="K55" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -7017,10 +7089,10 @@
         <v>300</v>
       </c>
       <c r="S55" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="T55" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="W55">
         <v>0</v>
@@ -7049,16 +7121,16 @@
         <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D56" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E56" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H56" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I56">
         <v>300</v>
@@ -7067,7 +7139,7 @@
         <v>300</v>
       </c>
       <c r="K56" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
@@ -7082,10 +7154,10 @@
         <v>300</v>
       </c>
       <c r="S56" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="T56" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="W56">
         <v>0</v>
@@ -7114,16 +7186,16 @@
         <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D57" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E57" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H57" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I57">
         <v>300</v>
@@ -7132,7 +7204,7 @@
         <v>300</v>
       </c>
       <c r="K57" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -7147,10 +7219,10 @@
         <v>300</v>
       </c>
       <c r="S57" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="T57" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="W57">
         <v>0</v>
@@ -7179,16 +7251,16 @@
         <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D58" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E58" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H58" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I58">
         <v>300</v>
@@ -7197,7 +7269,7 @@
         <v>300</v>
       </c>
       <c r="K58" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
@@ -7212,10 +7284,10 @@
         <v>300</v>
       </c>
       <c r="S58" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="T58" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="W58">
         <v>0</v>
@@ -7244,16 +7316,16 @@
         <v>7004</v>
       </c>
       <c r="C59" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D59" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E59" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H59" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I59">
         <v>300</v>
@@ -7277,10 +7349,10 @@
         <v>0</v>
       </c>
       <c r="S59" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="T59" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="W59">
         <v>0</v>
@@ -7309,16 +7381,16 @@
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D60" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E60" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H60" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I60">
         <v>300</v>
@@ -7327,7 +7399,7 @@
         <v>300</v>
       </c>
       <c r="K60" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -7342,10 +7414,10 @@
         <v>300</v>
       </c>
       <c r="S60" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="T60" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="W60">
         <v>0</v>
@@ -7374,16 +7446,16 @@
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D61" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E61" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H61" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I61">
         <v>300</v>
@@ -7392,7 +7464,7 @@
         <v>300</v>
       </c>
       <c r="K61" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -7407,10 +7479,10 @@
         <v>300</v>
       </c>
       <c r="S61" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="T61" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="W61">
         <v>0</v>
@@ -7439,16 +7511,16 @@
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D62" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E62" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H62" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I62">
         <v>300</v>
@@ -7457,7 +7529,7 @@
         <v>300</v>
       </c>
       <c r="K62" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
@@ -7472,10 +7544,10 @@
         <v>300</v>
       </c>
       <c r="S62" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="T62" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="W62">
         <v>0</v>
@@ -7504,16 +7576,16 @@
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E63" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H63" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="I63">
         <v>300</v>
@@ -7522,7 +7594,7 @@
         <v>300</v>
       </c>
       <c r="K63" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L63" t="b">
         <v>0</v>
@@ -7537,10 +7609,10 @@
         <v>300</v>
       </c>
       <c r="S63" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="T63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="W63">
         <v>0</v>
@@ -7569,16 +7641,16 @@
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E64" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H64" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I64">
         <v>300</v>
@@ -7587,7 +7659,7 @@
         <v>300</v>
       </c>
       <c r="K64" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
@@ -7602,10 +7674,10 @@
         <v>300</v>
       </c>
       <c r="S64" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="T64" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="W64">
         <v>0</v>
@@ -7634,16 +7706,16 @@
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D65" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E65" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H65" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="I65">
         <v>300</v>
@@ -7652,7 +7724,7 @@
         <v>300</v>
       </c>
       <c r="K65" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
@@ -7667,10 +7739,10 @@
         <v>300</v>
       </c>
       <c r="S65" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="T65" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="W65">
         <v>0</v>
@@ -7699,16 +7771,16 @@
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D66" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E66" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H66" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I66">
         <v>300</v>
@@ -7717,7 +7789,7 @@
         <v>300</v>
       </c>
       <c r="K66" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
@@ -7732,10 +7804,10 @@
         <v>300</v>
       </c>
       <c r="S66" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="T66" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="W66">
         <v>0</v>
@@ -7764,16 +7836,16 @@
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D67" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E67" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H67" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I67">
         <v>300</v>
@@ -7782,7 +7854,7 @@
         <v>300</v>
       </c>
       <c r="K67" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
@@ -7797,10 +7869,10 @@
         <v>300</v>
       </c>
       <c r="S67" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T67" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="W67">
         <v>0</v>
@@ -7829,16 +7901,16 @@
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D68" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E68" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H68" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I68">
         <v>300</v>
@@ -7847,7 +7919,7 @@
         <v>300</v>
       </c>
       <c r="K68" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
@@ -7862,10 +7934,10 @@
         <v>300</v>
       </c>
       <c r="S68" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="T68" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="W68">
         <v>0</v>
@@ -7894,16 +7966,16 @@
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D69" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E69" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H69" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I69">
         <v>300</v>
@@ -7912,7 +7984,7 @@
         <v>300</v>
       </c>
       <c r="K69" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -7927,10 +7999,10 @@
         <v>300</v>
       </c>
       <c r="S69" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="T69" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W69">
         <v>0</v>
@@ -7959,16 +8031,16 @@
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D70" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E70" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H70" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I70">
         <v>300</v>
@@ -7977,7 +8049,7 @@
         <v>300</v>
       </c>
       <c r="K70" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
@@ -7992,10 +8064,10 @@
         <v>300</v>
       </c>
       <c r="S70" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="T70" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="W70">
         <v>0</v>
@@ -8024,16 +8096,16 @@
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D71" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E71" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H71" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I71">
         <v>300</v>
@@ -8042,7 +8114,7 @@
         <v>300</v>
       </c>
       <c r="K71" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
@@ -8057,10 +8129,10 @@
         <v>300</v>
       </c>
       <c r="S71" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="T71" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="W71">
         <v>0</v>
@@ -8089,16 +8161,16 @@
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D72" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E72" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H72" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I72">
         <v>300</v>
@@ -8107,7 +8179,7 @@
         <v>300</v>
       </c>
       <c r="K72" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
@@ -8122,10 +8194,10 @@
         <v>300</v>
       </c>
       <c r="S72" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="T72" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="W72">
         <v>0</v>
@@ -8154,16 +8226,16 @@
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D73" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E73" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H73" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I73">
         <v>300</v>
@@ -8172,7 +8244,7 @@
         <v>300</v>
       </c>
       <c r="K73" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
@@ -8187,10 +8259,10 @@
         <v>300</v>
       </c>
       <c r="S73" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="T73" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="W73">
         <v>0</v>
@@ -8219,16 +8291,16 @@
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D74" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E74" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H74" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I74">
         <v>300</v>
@@ -8237,7 +8309,7 @@
         <v>300</v>
       </c>
       <c r="K74" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -8252,10 +8324,10 @@
         <v>300</v>
       </c>
       <c r="S74" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="T74" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="W74">
         <v>0</v>
@@ -8284,16 +8356,16 @@
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D75" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E75" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H75" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I75">
         <v>300</v>
@@ -8302,7 +8374,7 @@
         <v>300</v>
       </c>
       <c r="K75" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
@@ -8317,10 +8389,10 @@
         <v>300</v>
       </c>
       <c r="S75" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="T75" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="W75">
         <v>0</v>
@@ -8349,16 +8421,16 @@
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D76" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E76" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H76" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I76">
         <v>300</v>
@@ -8367,7 +8439,7 @@
         <v>300</v>
       </c>
       <c r="K76" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -8382,10 +8454,10 @@
         <v>300</v>
       </c>
       <c r="S76" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="T76" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="W76">
         <v>0</v>
@@ -8414,16 +8486,16 @@
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D77" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E77" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H77" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I77">
         <v>300</v>
@@ -8432,7 +8504,7 @@
         <v>300</v>
       </c>
       <c r="K77" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -8447,10 +8519,10 @@
         <v>300</v>
       </c>
       <c r="S77" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="T77" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="W77">
         <v>0</v>
@@ -8479,16 +8551,16 @@
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D78" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E78" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H78" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I78">
         <v>300</v>
@@ -8497,7 +8569,7 @@
         <v>300</v>
       </c>
       <c r="K78" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -8512,10 +8584,10 @@
         <v>300</v>
       </c>
       <c r="S78" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="T78" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W78">
         <v>0</v>
@@ -8544,16 +8616,16 @@
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D79" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E79" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H79" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I79">
         <v>300</v>
@@ -8562,7 +8634,7 @@
         <v>300</v>
       </c>
       <c r="K79" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
@@ -8577,10 +8649,10 @@
         <v>300</v>
       </c>
       <c r="S79" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="T79" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="W79">
         <v>0</v>
@@ -8609,16 +8681,16 @@
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D80" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E80" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H80" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I80">
         <v>300</v>
@@ -8627,7 +8699,7 @@
         <v>300</v>
       </c>
       <c r="K80" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -8642,10 +8714,10 @@
         <v>300</v>
       </c>
       <c r="S80" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="T80" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="W80">
         <v>0</v>
@@ -8674,16 +8746,16 @@
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D81" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E81" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H81" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I81">
         <v>300</v>
@@ -8692,7 +8764,7 @@
         <v>300</v>
       </c>
       <c r="K81" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L81" t="b">
         <v>0</v>
@@ -8707,10 +8779,10 @@
         <v>300</v>
       </c>
       <c r="S81" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="T81" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="W81">
         <v>0</v>
@@ -8739,16 +8811,16 @@
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D82" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E82" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H82" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I82">
         <v>300</v>
@@ -8757,7 +8829,7 @@
         <v>300</v>
       </c>
       <c r="K82" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
@@ -8772,10 +8844,10 @@
         <v>300</v>
       </c>
       <c r="S82" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="T82" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="W82">
         <v>0</v>
@@ -8804,16 +8876,16 @@
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D83" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E83" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H83" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I83">
         <v>300</v>
@@ -8822,7 +8894,7 @@
         <v>300</v>
       </c>
       <c r="K83" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L83" t="b">
         <v>0</v>
@@ -8837,10 +8909,10 @@
         <v>300</v>
       </c>
       <c r="S83" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="T83" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="W83">
         <v>0</v>
@@ -8869,16 +8941,16 @@
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D84" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E84" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H84" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="I84">
         <v>300</v>
@@ -8887,7 +8959,7 @@
         <v>300</v>
       </c>
       <c r="K84" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -8902,10 +8974,10 @@
         <v>300</v>
       </c>
       <c r="S84" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="T84" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="W84">
         <v>0</v>
@@ -8934,16 +9006,16 @@
         <v>9001</v>
       </c>
       <c r="C85" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D85" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E85" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H85" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I85">
         <v>200</v>
@@ -8952,7 +9024,7 @@
         <v>300</v>
       </c>
       <c r="K85" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -8970,10 +9042,10 @@
         <v>300</v>
       </c>
       <c r="S85" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="T85" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="W85">
         <v>0</v>
@@ -9002,22 +9074,22 @@
         <v>9002</v>
       </c>
       <c r="C86" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D86" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E86" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F86" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G86">
         <v>9009</v>
       </c>
       <c r="H86" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I86">
         <v>200</v>
@@ -9026,7 +9098,7 @@
         <v>300</v>
       </c>
       <c r="K86" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
@@ -9044,13 +9116,13 @@
         <v>300</v>
       </c>
       <c r="S86" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="T86" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="V86" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W86">
         <v>0</v>
@@ -9079,22 +9151,22 @@
         <v>9003</v>
       </c>
       <c r="C87" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D87" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E87" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F87" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G87">
         <v>9009</v>
       </c>
       <c r="H87" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I87">
         <v>200</v>
@@ -9103,7 +9175,7 @@
         <v>300</v>
       </c>
       <c r="K87" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
@@ -9121,13 +9193,13 @@
         <v>300</v>
       </c>
       <c r="S87" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="T87" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="V87" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W87">
         <v>0</v>
@@ -9156,22 +9228,22 @@
         <v>9004</v>
       </c>
       <c r="C88" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D88" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E88" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F88" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G88">
         <v>9009</v>
       </c>
       <c r="H88" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I88">
         <v>200</v>
@@ -9180,7 +9252,7 @@
         <v>300</v>
       </c>
       <c r="K88" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
@@ -9198,13 +9270,13 @@
         <v>300</v>
       </c>
       <c r="S88" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="T88" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="V88" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W88">
         <v>0</v>
@@ -9233,22 +9305,22 @@
         <v>9005</v>
       </c>
       <c r="C89" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D89" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E89" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F89" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G89">
         <v>9009</v>
       </c>
       <c r="H89" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I89">
         <v>200</v>
@@ -9257,7 +9329,7 @@
         <v>300</v>
       </c>
       <c r="K89" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L89" t="b">
         <v>0</v>
@@ -9275,13 +9347,13 @@
         <v>300</v>
       </c>
       <c r="S89" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="T89" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="V89" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W89">
         <v>0</v>
@@ -9310,22 +9382,22 @@
         <v>9006</v>
       </c>
       <c r="C90" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D90" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E90" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F90" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G90">
         <v>9009</v>
       </c>
       <c r="H90" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I90">
         <v>200</v>
@@ -9334,7 +9406,7 @@
         <v>300</v>
       </c>
       <c r="K90" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -9352,13 +9424,13 @@
         <v>300</v>
       </c>
       <c r="S90" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="T90" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="V90" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W90">
         <v>0</v>
@@ -9387,22 +9459,22 @@
         <v>9007</v>
       </c>
       <c r="C91" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D91" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E91" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F91" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G91">
         <v>9009</v>
       </c>
       <c r="H91" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I91">
         <v>200</v>
@@ -9411,7 +9483,7 @@
         <v>300</v>
       </c>
       <c r="K91" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L91" t="b">
         <v>0</v>
@@ -9429,13 +9501,13 @@
         <v>300</v>
       </c>
       <c r="S91" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="T91" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="V91" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W91">
         <v>0</v>
@@ -9464,22 +9536,22 @@
         <v>9008</v>
       </c>
       <c r="C92" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D92" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E92" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F92" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G92">
         <v>9009</v>
       </c>
       <c r="H92" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I92">
         <v>200</v>
@@ -9488,7 +9560,7 @@
         <v>300</v>
       </c>
       <c r="K92" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
@@ -9506,13 +9578,13 @@
         <v>300</v>
       </c>
       <c r="S92" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="T92" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="V92" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W92">
         <v>0</v>
@@ -9541,16 +9613,16 @@
         <v>9009</v>
       </c>
       <c r="C93" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D93" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E93" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H93" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="I93">
         <v>200</v>
@@ -9559,7 +9631,7 @@
         <v>300</v>
       </c>
       <c r="K93" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L93" t="b">
         <v>1</v>
@@ -9577,13 +9649,13 @@
         <v>300</v>
       </c>
       <c r="S93" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="T93" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="V93" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W93">
         <v>0</v>
@@ -9612,22 +9684,22 @@
         <v>9010</v>
       </c>
       <c r="C94" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D94" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E94" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F94" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G94">
         <v>9009</v>
       </c>
       <c r="H94" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I94">
         <v>200</v>
@@ -9636,7 +9708,7 @@
         <v>300</v>
       </c>
       <c r="K94" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
@@ -9654,10 +9726,10 @@
         <v>300</v>
       </c>
       <c r="S94" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="T94" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="W94">
         <v>0</v>
@@ -9686,22 +9758,22 @@
         <v>9011</v>
       </c>
       <c r="C95" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D95" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E95" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F95" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G95">
         <v>9009</v>
       </c>
       <c r="H95" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I95">
         <v>200</v>
@@ -9710,7 +9782,7 @@
         <v>300</v>
       </c>
       <c r="K95" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
@@ -9728,13 +9800,13 @@
         <v>300</v>
       </c>
       <c r="S95" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="T95" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="V95" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="W95">
         <v>0</v>
@@ -9763,16 +9835,16 @@
         <v>10001</v>
       </c>
       <c r="C96" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D96" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E96" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H96" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I96">
         <v>300</v>
@@ -9796,10 +9868,10 @@
         <v>0</v>
       </c>
       <c r="S96" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="T96" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="W96">
         <v>0</v>
@@ -9828,16 +9900,16 @@
         <v>11001</v>
       </c>
       <c r="C97" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D97" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E97" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="H97" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I97">
         <v>300</v>
@@ -9861,13 +9933,13 @@
         <v>0</v>
       </c>
       <c r="S97" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="T97" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="V97" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="W97">
         <v>0</v>
@@ -9896,19 +9968,19 @@
         <v>11002</v>
       </c>
       <c r="C98" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D98" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E98" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G98">
         <v>11001</v>
       </c>
       <c r="H98" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="I98">
         <v>300</v>
@@ -9932,10 +10004,10 @@
         <v>0</v>
       </c>
       <c r="S98" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="T98" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="W98">
         <v>0</v>
@@ -9964,16 +10036,16 @@
         <v>92005</v>
       </c>
       <c r="C99" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D99" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E99" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H99" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I99">
         <v>100</v>
@@ -9982,7 +10054,7 @@
         <v>300</v>
       </c>
       <c r="K99" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
@@ -9995,13 +10067,13 @@
       </c>
       <c r="R99" s="2"/>
       <c r="S99" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="T99" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="V99" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="W99">
         <v>0</v>
@@ -10030,16 +10102,16 @@
         <v>91012</v>
       </c>
       <c r="C100" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D100" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E100" t="s">
         <v>89</v>
       </c>
       <c r="H100" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I100">
         <v>100</v>
@@ -10048,7 +10120,7 @@
         <v>100</v>
       </c>
       <c r="K100" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L100" t="b">
         <v>0</v>
@@ -10061,16 +10133,16 @@
       </c>
       <c r="R100" s="2"/>
       <c r="S100" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T100" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="U100">
         <v>1012</v>
       </c>
       <c r="V100" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="W100">
         <v>0</v>
@@ -10095,9 +10167,29 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="H$1:H$1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"普通"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"神话"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"优秀"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"稀有"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"史诗"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"传说"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H100">
-      <formula1>枚举示例!$F$2:$F$7</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H83 H85:H100">
+      <formula1>枚举示例!$F$2:$F$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K16 K18:K100">
       <formula1>枚举示例!$C$18:$C$23</formula1>
@@ -10382,10 +10474,10 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -10414,10 +10506,10 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -10446,10 +10538,10 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -10478,10 +10570,10 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -10510,10 +10602,10 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -10542,10 +10634,10 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -10574,10 +10666,10 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -10606,10 +10698,10 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -10638,10 +10730,10 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -10670,10 +10762,10 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -10707,10 +10799,10 @@
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -10739,10 +10831,10 @@
         <v>2002</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -10771,10 +10863,10 @@
         <v>2003</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -10803,10 +10895,10 @@
         <v>2004</v>
       </c>
       <c r="C21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -10835,10 +10927,10 @@
         <v>2005</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -10867,10 +10959,10 @@
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -10899,10 +10991,10 @@
         <v>2007</v>
       </c>
       <c r="C24" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -10931,10 +11023,10 @@
         <v>2008</v>
       </c>
       <c r="C25" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D25" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -10963,10 +11055,10 @@
         <v>2009</v>
       </c>
       <c r="C26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -10995,10 +11087,10 @@
         <v>2010</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -11027,10 +11119,10 @@
         <v>3001</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D28" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -11059,10 +11151,10 @@
         <v>3002</v>
       </c>
       <c r="C29" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D29" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -11091,10 +11183,10 @@
         <v>3003</v>
       </c>
       <c r="C30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -11123,10 +11215,10 @@
         <v>3004</v>
       </c>
       <c r="C31" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D31" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -11155,10 +11247,10 @@
         <v>3005</v>
       </c>
       <c r="C32" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D32" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -11187,10 +11279,10 @@
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -11219,10 +11311,10 @@
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D34" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -11251,10 +11343,10 @@
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D35" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -11283,10 +11375,10 @@
         <v>4004</v>
       </c>
       <c r="C36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D36" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -11315,10 +11407,10 @@
         <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D37" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -11347,10 +11439,10 @@
         <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D38" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -11379,10 +11471,10 @@
         <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -11411,10 +11503,10 @@
         <v>5004</v>
       </c>
       <c r="C40" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D40" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -11443,10 +11535,10 @@
         <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -11475,10 +11567,10 @@
         <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D42" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -11507,10 +11599,10 @@
         <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -11539,10 +11631,10 @@
         <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D44" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -11571,10 +11663,10 @@
         <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D45" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -11603,10 +11695,10 @@
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D46" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -11635,10 +11727,10 @@
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D47" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -11667,10 +11759,10 @@
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D48" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -11699,10 +11791,10 @@
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -11731,10 +11823,10 @@
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D50" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -11763,10 +11855,10 @@
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D51" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -11795,10 +11887,10 @@
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D52" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -11827,10 +11919,10 @@
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D53" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -11859,10 +11951,10 @@
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D54" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -11891,10 +11983,10 @@
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D55" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -11923,10 +12015,10 @@
         <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D56" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -11955,10 +12047,10 @@
         <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D57" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -11987,10 +12079,10 @@
         <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D58" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -12019,10 +12111,10 @@
         <v>7004</v>
       </c>
       <c r="C59" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D59" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -12051,10 +12143,10 @@
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D60" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -12083,10 +12175,10 @@
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D61" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -12115,10 +12207,10 @@
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D62" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -12147,10 +12239,10 @@
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -12179,10 +12271,10 @@
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -12211,10 +12303,10 @@
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D65" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -12243,10 +12335,10 @@
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D66" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -12275,10 +12367,10 @@
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D67" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -12307,10 +12399,10 @@
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D68" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -12339,10 +12431,10 @@
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D69" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -12371,10 +12463,10 @@
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D70" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -12403,10 +12495,10 @@
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D71" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -12435,10 +12527,10 @@
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D72" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -12467,10 +12559,10 @@
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D73" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -12499,10 +12591,10 @@
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D74" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -12531,10 +12623,10 @@
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D75" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -12563,10 +12655,10 @@
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D76" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -12595,10 +12687,10 @@
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D77" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -12627,10 +12719,10 @@
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D78" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -12659,10 +12751,10 @@
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D79" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -12691,10 +12783,10 @@
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D80" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -12723,10 +12815,10 @@
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D81" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -12755,10 +12847,10 @@
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D82" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -12787,10 +12879,10 @@
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D83" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -12819,10 +12911,10 @@
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D84" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -12851,10 +12943,10 @@
         <v>9001</v>
       </c>
       <c r="C85" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D85" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -12883,10 +12975,10 @@
         <v>9002</v>
       </c>
       <c r="C86" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D86" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -12915,10 +13007,10 @@
         <v>9003</v>
       </c>
       <c r="C87" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D87" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -12947,10 +13039,10 @@
         <v>9004</v>
       </c>
       <c r="C88" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D88" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -12979,10 +13071,10 @@
         <v>9005</v>
       </c>
       <c r="C89" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D89" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -13011,10 +13103,10 @@
         <v>9006</v>
       </c>
       <c r="C90" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D90" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -13043,10 +13135,10 @@
         <v>9007</v>
       </c>
       <c r="C91" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D91" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -13075,10 +13167,10 @@
         <v>9008</v>
       </c>
       <c r="C92" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D92" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -13107,10 +13199,10 @@
         <v>9009</v>
       </c>
       <c r="C93" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D93" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -13139,10 +13231,10 @@
         <v>9010</v>
       </c>
       <c r="C94" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D94" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -13171,10 +13263,10 @@
         <v>9011</v>
       </c>
       <c r="C95" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D95" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -13203,10 +13295,10 @@
         <v>10001</v>
       </c>
       <c r="C96" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D96" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -13235,10 +13327,10 @@
         <v>11001</v>
       </c>
       <c r="C97" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D97" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -13267,10 +13359,10 @@
         <v>11002</v>
       </c>
       <c r="C98" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D98" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -13299,10 +13391,10 @@
         <v>92005</v>
       </c>
       <c r="C99" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D99" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -13331,10 +13423,10 @@
         <v>91012</v>
       </c>
       <c r="C100" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D100" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -13380,328 +13472,340 @@
         <v>89</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>126</v>
+        <v>478</v>
+      </c>
+      <c r="E2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F2" t="s">
+        <v>97</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J2" s="6">
         <v>1</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" spans="2:16">
       <c r="B3" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J3" s="6">
         <v>2</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" spans="2:16">
       <c r="B4" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J4" s="6">
         <v>4</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="2:16">
       <c r="B5" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="J5" s="6">
         <v>8</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="2:16">
       <c r="B6" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>472</v>
+        <v>505</v>
+      </c>
+      <c r="E6" t="s">
+        <v>506</v>
+      </c>
+      <c r="F6" t="s">
+        <v>139</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J6" s="6">
         <v>16</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" spans="2:16">
       <c r="B7" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>512</v>
+        <v>90</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J7" s="6">
         <v>32</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8" spans="2:16">
       <c r="B8" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>474</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J8" s="6">
         <v>64</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>528</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="J9" s="6">
         <v>128</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="J10" s="6">
         <v>256</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="J11" s="6">
         <v>512</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="J12" s="6">
         <v>1024</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="H13" s="6" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="J13" s="6">
         <v>2048</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="6" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>91</v>
@@ -13709,42 +13813,42 @@
     </row>
     <row r="19" spans="2:3">
       <c r="B19" s="6" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="6" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" s="6" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="6" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="B23" s="6" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
   </sheetData>
@@ -13785,34 +13889,34 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="E1" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="F1" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="G1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H1" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="I1" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="J1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="K1" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="L1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="M1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -13826,10 +13930,10 @@
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="E2" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F2" t="s">
         <v>31</v>
@@ -13838,7 +13942,7 @@
         <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="I2" t="s">
         <v>37</v>
@@ -13861,81 +13965,81 @@
         <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="4" s="7" customFormat="1" spans="1:13">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="4" s="9" customFormat="1" spans="1:13">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>578</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="B4" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="C4" s="9" t="s">
         <v>581</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="D4" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>583</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="F4" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="G4" s="9" t="s">
         <v>585</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="H4" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="I4" s="9" t="s">
         <v>587</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13943,13 +14047,13 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F5">
         <v>1000</v>
@@ -13981,13 +14085,13 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F6">
         <v>1000</v>
@@ -14019,13 +14123,13 @@
         <v>2001</v>
       </c>
       <c r="C7" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F7">
         <v>1000</v>
@@ -14057,13 +14161,13 @@
         <v>3001</v>
       </c>
       <c r="C8" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D8" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -14136,31 +14240,31 @@
         <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E1" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="F1" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="G1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="H1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="I1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="J1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="K1" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="L1" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -14207,31 +14311,31 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -14242,37 +14346,37 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D4" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="E4" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="F4" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="G4" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="H4" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="I4" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J4" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="K4" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="L4" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="M4" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -14310,7 +14414,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -14348,7 +14452,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -14386,7 +14490,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -14424,7 +14528,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -14462,7 +14566,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -14500,7 +14604,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -14538,7 +14642,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -14576,7 +14680,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -14614,7 +14718,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -14652,7 +14756,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -14690,7 +14794,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -14728,7 +14832,7 @@
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -14766,7 +14870,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -14804,7 +14908,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -14816,17 +14920,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7.08333333333333" customWidth="1"/>
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="7.25" customWidth="1"/>
     <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="6" max="6" width="11.0833333333333" style="7" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14837,16 +14942,16 @@
         <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="E1" t="s">
-        <v>637</v>
-      </c>
-      <c r="F1" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>641</v>
+      </c>
+      <c r="G1" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -14862,29 +14967,30 @@
       <c r="E2" t="s">
         <v>31</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="66" customHeight="1" spans="1:7">
+    <row r="3" s="1" customFormat="1" ht="66" customHeight="1" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>643</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -14892,22 +14998,22 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D4" t="s">
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>640</v>
-      </c>
-      <c r="F4" t="s">
-        <v>584</v>
+        <v>644</v>
       </c>
       <c r="G4" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>588</v>
+      </c>
+      <c r="H4" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="B5">
         <v>100101</v>
       </c>
@@ -14915,19 +15021,20 @@
         <v>1001</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="E5">
-        <v>7000</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <f>E5/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="B6">
         <v>100102</v>
       </c>
@@ -14935,19 +15042,20 @@
         <v>1001</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="E6">
-        <v>2200</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>6700</v>
+      </c>
+      <c r="F6" s="7">
+        <f>E6/10000</f>
+        <v>0.67</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="B7">
         <v>100103</v>
       </c>
@@ -14955,19 +15063,20 @@
         <v>1001</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E7">
-        <v>700</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>2200</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" ref="F7:F17" si="0">E7/10000</f>
+        <v>0.22</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="B8">
         <v>100104</v>
       </c>
@@ -14975,211 +15084,351 @@
         <v>1001</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="E8">
-        <v>100</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
+        <v>900</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" si="0"/>
+        <v>0.09</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9">
+        <v>100105</v>
+      </c>
+      <c r="C9">
+        <v>1001</v>
+      </c>
+      <c r="D9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9">
+        <v>180</v>
+      </c>
+      <c r="F9" s="7">
+        <f t="shared" si="0"/>
+        <v>0.018</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10">
+        <v>100106</v>
+      </c>
+      <c r="C10">
+        <v>1001</v>
+      </c>
+      <c r="D10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10">
+        <v>20</v>
+      </c>
+      <c r="F10" s="7">
+        <f t="shared" si="0"/>
+        <v>0.002</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10">
+      <c r="F11" s="7">
+        <f>SUM(F5:F10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12">
         <v>100201</v>
-      </c>
-      <c r="C10">
-        <v>1002</v>
-      </c>
-      <c r="D10" t="s">
-        <v>137</v>
-      </c>
-      <c r="E10">
-        <v>5000</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="B11">
-        <v>100202</v>
-      </c>
-      <c r="C11">
-        <v>1002</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11">
-        <v>3000</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12">
-        <v>100203</v>
       </c>
       <c r="C12">
         <v>1002</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E12">
-        <v>1700</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>0</v>
+      </c>
+      <c r="F12" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="B13">
-        <v>100204</v>
+        <v>100202</v>
       </c>
       <c r="C13">
         <v>1002</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E13">
-        <v>300</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
+        <v>3700</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" si="0"/>
+        <v>0.37</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="B14">
+        <v>100203</v>
+      </c>
+      <c r="C14">
+        <v>1002</v>
+      </c>
+      <c r="D14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14">
+        <v>4200</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" si="0"/>
+        <v>0.42</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="B15">
+        <v>100204</v>
+      </c>
+      <c r="C15">
+        <v>1002</v>
+      </c>
+      <c r="D15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15">
+        <v>1700</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="0"/>
+        <v>0.17</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="B16">
+        <v>100205</v>
+      </c>
+      <c r="C16">
+        <v>1002</v>
+      </c>
+      <c r="D16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16">
+        <v>380</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" si="0"/>
+        <v>0.038</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="B17">
+        <v>100206</v>
+      </c>
+      <c r="C17">
+        <v>1002</v>
+      </c>
+      <c r="D17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="0"/>
+        <v>0.002</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="B15">
+      <c r="F18" s="7">
+        <f>SUM(F12:F17)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="B19">
         <v>200101</v>
       </c>
-      <c r="C15">
+      <c r="C19">
         <v>2001</v>
       </c>
-      <c r="D15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15">
+      <c r="D19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="B20">
+        <v>200102</v>
+      </c>
+      <c r="C20">
+        <v>2001</v>
+      </c>
+      <c r="D20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20">
         <v>3000</v>
       </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="B16">
-        <v>200102</v>
-      </c>
-      <c r="C16">
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="B21">
+        <v>200103</v>
+      </c>
+      <c r="C21">
         <v>2001</v>
       </c>
-      <c r="D16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16">
+      <c r="D21" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21">
         <v>7000</v>
       </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="B17">
-        <v>200103</v>
-      </c>
-      <c r="C17">
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="B22">
+        <v>200104</v>
+      </c>
+      <c r="C22">
         <v>2001</v>
       </c>
-      <c r="D17" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="B18">
-        <v>200104</v>
-      </c>
-      <c r="C18">
+      <c r="D22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="B23">
+        <v>200105</v>
+      </c>
+      <c r="C23">
         <v>2001</v>
       </c>
-      <c r="D18" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
+      <c r="D23" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="B24">
+        <v>200106</v>
+      </c>
+      <c r="C24">
+        <v>2001</v>
+      </c>
+      <c r="D24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="B20">
+    <row r="26" spans="1:8">
+      <c r="B26">
         <v>300101</v>
       </c>
-      <c r="C20">
+      <c r="C26">
         <v>3001</v>
       </c>
-      <c r="D20" t="s">
-        <v>472</v>
-      </c>
-      <c r="E20">
+      <c r="D26" t="s">
+        <v>474</v>
+      </c>
+      <c r="E26">
         <v>100</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" t="s">
-        <v>649</v>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -15191,7 +15440,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -15199,14 +15448,14 @@
     <col min="3" max="3" width="10.4166666666667" customWidth="1"/>
     <col min="4" max="4" width="7.91666666666667" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="9.25" customWidth="1"/>
-    <col min="7" max="7" width="12.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="8.41666666666667" customWidth="1"/>
-    <col min="9" max="9" width="11.6666666666667" customWidth="1"/>
-    <col min="10" max="10" width="8.83333333333333" customWidth="1"/>
+    <col min="6" max="7" width="13.5" customWidth="1"/>
+    <col min="8" max="8" width="12.25" customWidth="1"/>
+    <col min="9" max="9" width="8.41666666666667" customWidth="1"/>
+    <col min="10" max="10" width="11.6666666666667" customWidth="1"/>
+    <col min="11" max="11" width="8.83333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15214,28 +15463,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>647</v>
+      </c>
+      <c r="D1" t="s">
+        <v>641</v>
+      </c>
+      <c r="E1" t="s">
+        <v>648</v>
+      </c>
+      <c r="F1" t="s">
+        <v>649</v>
+      </c>
+      <c r="G1" t="s">
         <v>650</v>
       </c>
-      <c r="D1" t="s">
-        <v>637</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>651</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
+        <v>563</v>
+      </c>
+      <c r="J1" t="s">
         <v>652</v>
       </c>
-      <c r="G1" t="s">
-        <v>653</v>
-      </c>
-      <c r="H1" t="s">
-        <v>559</v>
-      </c>
-      <c r="I1" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -15258,42 +15510,48 @@
         <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="69" customHeight="1" spans="1:10">
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="69" customHeight="1" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -15301,155 +15559,170 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
+        <v>660</v>
+      </c>
+      <c r="D4" t="s">
+        <v>661</v>
+      </c>
+      <c r="E4" t="s">
         <v>662</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>663</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>663</v>
+      </c>
+      <c r="H4" t="s">
         <v>664</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
+        <v>588</v>
+      </c>
+      <c r="J4" t="s">
         <v>665</v>
       </c>
-      <c r="G4" t="s">
-        <v>666</v>
-      </c>
-      <c r="H4" t="s">
-        <v>584</v>
-      </c>
-      <c r="I4" t="s">
-        <v>667</v>
-      </c>
-      <c r="J4" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B5">
         <v>100401</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="D5">
         <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F5" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="G5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
+        <v>90</v>
+      </c>
+      <c r="H5" t="s">
+        <v>90</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C6" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D6" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E6" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F6" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G6" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H6" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="I6" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>653</v>
+      </c>
+      <c r="J6" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B7">
         <v>100501</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="D7">
         <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="G7" t="s">
         <v>90</v>
       </c>
-      <c r="H7" t="b">
-        <v>1</v>
+      <c r="H7" t="s">
+        <v>139</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B8">
         <v>100502</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="D8">
         <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F8" t="s">
         <v>90</v>
       </c>
       <c r="G8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
+        <v>139</v>
+      </c>
+      <c r="H8" t="s">
+        <v>139</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B9">
         <v>100503</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -15458,431 +15731,844 @@
         <v>90</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="G9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
+        <v>139</v>
+      </c>
+      <c r="H9" t="s">
+        <v>139</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="I10" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>653</v>
+      </c>
+      <c r="J10" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B11">
         <v>100601</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D11">
         <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
         <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>110</v>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
+        <v>139</v>
+      </c>
+      <c r="H11" t="s">
+        <v>119</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B12">
         <v>100602</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D12">
         <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
+        <v>139</v>
+      </c>
+      <c r="H12" t="s">
+        <v>119</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B13">
         <v>100603</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D13">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
         <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="G13" t="s">
-        <v>110</v>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
+        <v>119</v>
+      </c>
+      <c r="H13" t="s">
+        <v>119</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>655</v>
-      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="B14">
         <v>100604</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F14" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
+        <v>119</v>
+      </c>
+      <c r="H14" t="s">
+        <v>119</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
       </c>
-      <c r="J14" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C15" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D15" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E15" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F15" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G15" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H15" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="I15" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>653</v>
+      </c>
+      <c r="J15" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B16">
         <v>100701</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D16">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="G16" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
+        <v>119</v>
+      </c>
+      <c r="H16" t="s">
+        <v>103</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
       </c>
-      <c r="J16" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B17">
         <v>100702</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F17" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="G17" t="s">
-        <v>126</v>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
+        <v>119</v>
+      </c>
+      <c r="H17" t="s">
+        <v>103</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
       </c>
-      <c r="J17" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B18">
         <v>100703</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
         <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="G18" t="s">
-        <v>126</v>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
+        <v>139</v>
+      </c>
+      <c r="H18" t="s">
+        <v>103</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B19">
         <v>100704</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D19">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="F19" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G19" t="s">
-        <v>126</v>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
+        <v>103</v>
+      </c>
+      <c r="H19" t="s">
+        <v>103</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C20" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D20" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E20" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F20" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G20" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H20" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="I20" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>653</v>
+      </c>
+      <c r="J20" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B21">
         <v>100801</v>
       </c>
       <c r="C21" t="s">
-        <v>472</v>
+        <v>108</v>
       </c>
       <c r="D21">
+        <v>37</v>
+      </c>
+      <c r="E21" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>653</v>
+      </c>
+      <c r="B22">
+        <v>100802</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22">
+        <v>55</v>
+      </c>
+      <c r="E22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" t="s">
+        <v>139</v>
+      </c>
+      <c r="G22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H22" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>653</v>
+      </c>
+      <c r="B23">
+        <v>100803</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23" t="s">
+        <v>119</v>
+      </c>
+      <c r="F23" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>653</v>
+      </c>
+      <c r="B24">
+        <v>100804</v>
+      </c>
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>139</v>
+      </c>
+      <c r="F24" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" t="s">
+        <v>103</v>
+      </c>
+      <c r="H24" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>653</v>
+      </c>
+      <c r="C25" t="s">
+        <v>653</v>
+      </c>
+      <c r="D25" t="s">
+        <v>653</v>
+      </c>
+      <c r="E25" t="s">
+        <v>653</v>
+      </c>
+      <c r="F25" t="s">
+        <v>653</v>
+      </c>
+      <c r="G25" t="s">
+        <v>653</v>
+      </c>
+      <c r="H25" t="s">
+        <v>653</v>
+      </c>
+      <c r="I25" t="s">
+        <v>653</v>
+      </c>
+      <c r="J25" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>653</v>
+      </c>
+      <c r="B26">
+        <v>100901</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" t="s">
+        <v>108</v>
+      </c>
+      <c r="H26" t="s">
+        <v>97</v>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>653</v>
+      </c>
+      <c r="B27">
+        <v>100902</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" t="s">
+        <v>108</v>
+      </c>
+      <c r="H27" t="s">
+        <v>97</v>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>653</v>
+      </c>
+      <c r="B28">
+        <v>100903</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28">
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>119</v>
+      </c>
+      <c r="F28" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" t="s">
+        <v>108</v>
+      </c>
+      <c r="H28" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>653</v>
+      </c>
+      <c r="B29">
+        <v>100904</v>
+      </c>
+      <c r="C29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29">
+        <v>25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" t="s">
+        <v>119</v>
+      </c>
+      <c r="G29" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s">
+        <v>653</v>
+      </c>
+      <c r="C30" t="s">
+        <v>653</v>
+      </c>
+      <c r="D30" t="s">
+        <v>653</v>
+      </c>
+      <c r="E30" t="s">
+        <v>653</v>
+      </c>
+      <c r="F30" t="s">
+        <v>653</v>
+      </c>
+      <c r="G30" t="s">
+        <v>653</v>
+      </c>
+      <c r="H30" t="s">
+        <v>653</v>
+      </c>
+      <c r="I30" t="s">
+        <v>653</v>
+      </c>
+      <c r="J30" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>653</v>
+      </c>
+      <c r="B31">
+        <v>200101</v>
+      </c>
+      <c r="C31" t="s">
+        <v>474</v>
+      </c>
+      <c r="D31">
         <v>100</v>
       </c>
-      <c r="E21" t="s">
-        <v>472</v>
-      </c>
-      <c r="F21" t="s">
-        <v>472</v>
-      </c>
-      <c r="G21" t="s">
-        <v>472</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>655</v>
-      </c>
-      <c r="B22">
-        <v>100901</v>
-      </c>
-      <c r="C22" t="s">
-        <v>512</v>
-      </c>
-      <c r="D22">
+      <c r="E31" t="s">
+        <v>474</v>
+      </c>
+      <c r="F31" t="s">
+        <v>474</v>
+      </c>
+      <c r="G31" t="s">
+        <v>474</v>
+      </c>
+      <c r="H31" t="s">
+        <v>474</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>653</v>
+      </c>
+      <c r="B32">
+        <v>200201</v>
+      </c>
+      <c r="C32" t="s">
+        <v>528</v>
+      </c>
+      <c r="D32">
         <v>100</v>
       </c>
-      <c r="E22" t="s">
-        <v>512</v>
-      </c>
-      <c r="F22" t="s">
-        <v>512</v>
-      </c>
-      <c r="G22" t="s">
-        <v>512</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="B23" t="s">
-        <v>655</v>
-      </c>
-      <c r="C23" t="s">
-        <v>655</v>
-      </c>
-      <c r="D23" t="s">
-        <v>655</v>
-      </c>
-      <c r="E23" t="s">
-        <v>655</v>
-      </c>
-      <c r="F23" t="s">
-        <v>655</v>
-      </c>
-      <c r="G23" t="s">
-        <v>655</v>
-      </c>
-      <c r="H23" t="s">
-        <v>655</v>
-      </c>
-      <c r="I23" t="s">
-        <v>655</v>
+      <c r="E32" t="s">
+        <v>528</v>
+      </c>
+      <c r="F32" t="s">
+        <v>528</v>
+      </c>
+      <c r="G32" t="s">
+        <v>528</v>
+      </c>
+      <c r="H32" t="s">
+        <v>528</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33" t="s">
+        <v>653</v>
+      </c>
+      <c r="C33" t="s">
+        <v>653</v>
+      </c>
+      <c r="D33" t="s">
+        <v>653</v>
+      </c>
+      <c r="E33" t="s">
+        <v>653</v>
+      </c>
+      <c r="F33" t="s">
+        <v>653</v>
+      </c>
+      <c r="G33" t="s">
+        <v>653</v>
+      </c>
+      <c r="H33" t="s">
+        <v>653</v>
+      </c>
+      <c r="I33" t="s">
+        <v>653</v>
+      </c>
+      <c r="J33" t="s">
+        <v>653</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E1:H24 E30:H1048576">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+      <formula>"神话"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
+      <formula>"优秀"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
+      <formula>"稀有"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+      <formula>"史诗"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
+      <formula>"传说"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E$1:H$1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"普通"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25:H29">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"传说"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"史诗"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"稀有"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"优秀"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"神话"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -15891,7 +16577,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -15901,13 +16587,14 @@
     <col min="5" max="5" width="39.75" customWidth="1"/>
     <col min="6" max="6" width="38.5" customWidth="1"/>
     <col min="7" max="7" width="16.4166666666667" customWidth="1"/>
-    <col min="8" max="8" width="22.5833333333333" customWidth="1"/>
-    <col min="9" max="9" width="6.16666666666667" customWidth="1"/>
-    <col min="10" max="10" width="19.8333333333333" customWidth="1"/>
-    <col min="11" max="11" width="16.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="23.5" customWidth="1"/>
+    <col min="9" max="9" width="22.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="6.16666666666667" customWidth="1"/>
+    <col min="11" max="11" width="19.8333333333333" customWidth="1"/>
+    <col min="12" max="12" width="16.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -15921,25 +16608,28 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
+        <v>667</v>
+      </c>
+      <c r="F1" t="s">
+        <v>668</v>
+      </c>
+      <c r="G1" t="s">
         <v>669</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>670</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>671</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>672</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>673</v>
       </c>
-      <c r="K1" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
@@ -15964,36 +16654,42 @@
       <c r="H2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" t="s">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
       <c r="K2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:11">
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:12">
       <c r="A3" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>677</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -16019,133 +16715,200 @@
         <v>682</v>
       </c>
       <c r="I4" t="s">
-        <v>621</v>
+        <v>683</v>
       </c>
       <c r="J4" t="s">
-        <v>683</v>
+        <v>625</v>
       </c>
       <c r="K4" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>126</v>
+      <c r="C5" t="s">
+        <v>479</v>
+      </c>
+      <c r="D5" t="s">
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F5" t="s">
-        <v>686</v>
-      </c>
-      <c r="J5" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="H5" t="s">
+        <v>688</v>
+      </c>
+      <c r="K5" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F6" t="s">
-        <v>686</v>
-      </c>
-      <c r="J6" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>687</v>
+      </c>
+      <c r="H6" t="s">
+        <v>691</v>
+      </c>
+      <c r="K6" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F7" t="s">
-        <v>686</v>
-      </c>
-      <c r="J7" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>687</v>
+      </c>
+      <c r="H7" t="s">
+        <v>694</v>
+      </c>
+      <c r="K7" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="F8" t="s">
-        <v>686</v>
-      </c>
-      <c r="J8" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>687</v>
+      </c>
+      <c r="H8" t="s">
+        <v>697</v>
+      </c>
+      <c r="K8" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>472</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="F9" t="s">
-        <v>686</v>
-      </c>
-      <c r="I9" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>687</v>
+      </c>
+      <c r="H9" t="s">
+        <v>700</v>
+      </c>
+      <c r="K9" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>512</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
+        <v>701</v>
+      </c>
+      <c r="F10" t="s">
+        <v>687</v>
+      </c>
+      <c r="H10" t="s">
+        <v>702</v>
+      </c>
+      <c r="K10" t="s">
         <v>692</v>
       </c>
-      <c r="F10" t="s">
-        <v>686</v>
-      </c>
-      <c r="I10" t="s">
-        <v>694</v>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="B11">
+        <v>2001</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="E11" t="s">
+        <v>701</v>
+      </c>
+      <c r="F11" t="s">
+        <v>687</v>
+      </c>
+      <c r="H11" t="s">
+        <v>702</v>
+      </c>
+      <c r="J11" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="B12">
+        <v>2002</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="E12" t="s">
+        <v>701</v>
+      </c>
+      <c r="F12" t="s">
+        <v>687</v>
+      </c>
+      <c r="H12" t="s">
+        <v>702</v>
+      </c>
+      <c r="J12" t="s">
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -16157,7 +16920,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="13.5" customWidth="1"/>
@@ -16173,10 +16936,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="D1" t="s">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -16193,7 +16956,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -16210,10 +16973,10 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="E3" t="s">
-        <v>699</v>
+        <v>708</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -16235,10 +16998,10 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -16249,10 +17012,10 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -16263,10 +17026,10 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="D7" t="s">
-        <v>199</v>
+        <v>369</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -16274,62 +17037,70 @@
     </row>
     <row r="8" spans="1:5">
       <c r="D8" t="s">
-        <v>367</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:5">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>712</v>
+      </c>
       <c r="D9" t="s">
-        <v>217</v>
+        <v>252</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="B10">
-        <v>1005</v>
-      </c>
-      <c r="C10" t="s">
-        <v>703</v>
-      </c>
       <c r="D10" t="s">
-        <v>411</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:5">
+      <c r="B11">
+        <v>1006</v>
+      </c>
+      <c r="C11" t="s">
+        <v>413</v>
+      </c>
       <c r="D11" t="s">
-        <v>250</v>
+        <v>413</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="D12" t="s">
-        <v>295</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="B13">
-        <v>1006</v>
-      </c>
-      <c r="C13" t="s">
-        <v>704</v>
-      </c>
       <c r="D13" t="s">
-        <v>459</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" t="s">
-        <v>464</v>
-      </c>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4">
+      <c r="C21" s="6"/>
+    </row>
+    <row r="22" spans="3:4">
+      <c r="C22" s="6"/>
     </row>
     <row r="23" spans="3:4">
       <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
     </row>
     <row r="24" spans="3:4">
       <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="3:4">
       <c r="C25" s="6"/>
@@ -16354,14 +17125,6 @@
     <row r="30" spans="3:4">
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
-    </row>
-    <row r="31" spans="3:4">
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-    </row>
-    <row r="32" spans="3:4">
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16388,7 +17151,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -16410,7 +17173,7 @@
         <v>59</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -16423,7 +17186,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="B6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -16431,7 +17194,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="B7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -16439,7 +17202,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="B8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
@@ -16447,7 +17210,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="B9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -16455,7 +17218,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="B10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -16463,7 +17226,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="B11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
@@ -16471,7 +17234,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="B12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
@@ -16479,7 +17242,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="B13" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -16487,7 +17250,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="B14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
@@ -16495,7 +17258,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="B15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>

--- a/luban-excels/bak/xlsx/Items.xlsx
+++ b/luban-excels/bak/xlsx/Items.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="798">
   <si>
     <t>##var</t>
   </si>
@@ -673,10 +673,10 @@
     <t>v1\ItemIcon\Eyewear_Sunglasses_Blade.png</t>
   </si>
   <si>
-    <t>Male A</t>
-  </si>
-  <si>
-    <t>男性手臂A</t>
+    <t>Type 1</t>
+  </si>
+  <si>
+    <t>手臂颜色类型1</t>
   </si>
   <si>
     <t>Arm</t>
@@ -685,46 +685,70 @@
     <t>全球</t>
   </si>
   <si>
-    <t>v1\Player\Arm\MaleA.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Hand_MaleA.png</t>
-  </si>
-  <si>
-    <t>Male B</t>
-  </si>
-  <si>
-    <t>男性手臂B</t>
-  </si>
-  <si>
-    <t>v1\Player\Arm\MaleB.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Hand_MaleB.png</t>
-  </si>
-  <si>
-    <t>Male C</t>
-  </si>
-  <si>
-    <t>男性手臂C</t>
-  </si>
-  <si>
-    <t>v1\Player\Arm\MaleC.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Hand_MaleC.png</t>
-  </si>
-  <si>
-    <t>Male D</t>
-  </si>
-  <si>
-    <t>男性手臂D</t>
-  </si>
-  <si>
-    <t>v1\Player\Arm\MaleD.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Hand_MaleD.png</t>
+    <t>v1\Player\Arm\Type1.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Arm_Type1.png</t>
+  </si>
+  <si>
+    <t>Type 2</t>
+  </si>
+  <si>
+    <t>手臂颜色类型2</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\Type2.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Arm_Type2.png</t>
+  </si>
+  <si>
+    <t>Type 3</t>
+  </si>
+  <si>
+    <t>手臂颜色类型3</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\Type3.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Arm_Type3.png</t>
+  </si>
+  <si>
+    <t>Type 4</t>
+  </si>
+  <si>
+    <t>手臂颜色类型4</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\Type4.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Arm_Type4.png</t>
+  </si>
+  <si>
+    <t>Type 5</t>
+  </si>
+  <si>
+    <t>手臂颜色类型5</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\Type5.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Arm_Type5.png</t>
+  </si>
+  <si>
+    <t>Type 6</t>
+  </si>
+  <si>
+    <t>手臂颜色类型6</t>
+  </si>
+  <si>
+    <t>v1\Player\Arm\Type6.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\Arm_Type6.png</t>
   </si>
   <si>
     <t>Baseball Jacket Black</t>
@@ -1213,10 +1237,13 @@
     <t>锚纹身</t>
   </si>
   <si>
-    <t>v1\Player\Surface\AnchorTattoo.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_AnchorTattoo.png</t>
+    <t>BodyDecoration</t>
+  </si>
+  <si>
+    <t>v1\Player\BodyDecoration\AnchorTattoo.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\BodyDecoration_AnchorTattoo.png</t>
   </si>
   <si>
     <t>Canine D88</t>
@@ -1261,10 +1288,10 @@
     <t>体毛</t>
   </si>
   <si>
-    <t>v1\Player\Surface\Hair.png</t>
-  </si>
-  <si>
-    <t>v1\ItemIcon\Accessory_Hair.png</t>
+    <t>v1\Player\BodyDecoration\Hair.png</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\BodyDecoration_Hair.png</t>
   </si>
   <si>
     <t>Royal Mariner Onyx</t>
@@ -1754,6 +1781,9 @@
   </si>
   <si>
     <t>Syria国际制裁/政治/宗教</t>
+  </si>
+  <si>
+    <t>体表装饰</t>
   </si>
   <si>
     <t>CU</t>
@@ -2262,9 +2292,15 @@
     <t>CanUnequip</t>
   </si>
   <si>
+    <t>DefaultItemId</t>
+  </si>
+  <si>
     <t>可脱光吗</t>
   </si>
   <si>
+    <t>默认穿戴物品id</t>
+  </si>
+  <si>
     <t>瘦芝麻柴</t>
   </si>
   <si>
@@ -2272,6 +2308,30 @@
   </si>
   <si>
     <t>Lucky</t>
+  </si>
+  <si>
+    <t>Male A</t>
+  </si>
+  <si>
+    <t>男性手臂A</t>
+  </si>
+  <si>
+    <t>Male B</t>
+  </si>
+  <si>
+    <t>男性手臂B</t>
+  </si>
+  <si>
+    <t>Male C</t>
+  </si>
+  <si>
+    <t>男性手臂C</t>
+  </si>
+  <si>
+    <t>Male D</t>
+  </si>
+  <si>
+    <t>男性手臂D</t>
   </si>
   <si>
     <t>Full Tilt Like</t>
@@ -2392,10 +2452,15 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -2876,16 +2941,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2894,119 +2956,122 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3033,6 +3098,9 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3607,12 +3675,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH105"/>
+  <dimension ref="A1:AH107"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="20.4166666666667" customWidth="1"/>
     <col min="4" max="4" width="20.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="11.4166666666667" customWidth="1"/>
+    <col min="5" max="5" width="14.6666666666667" customWidth="1"/>
     <col min="6" max="6" width="27.4166666666667" customWidth="1"/>
     <col min="7" max="7" width="17.5833333333333" customWidth="1"/>
     <col min="10" max="12" width="14.3333333333333" customWidth="1"/>
@@ -3852,7 +3920,7 @@
       <c r="J3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="10"/>
+      <c r="L3" s="11"/>
       <c r="M3" s="1" t="s">
         <v>47</v>
       </c>
@@ -4519,7 +4587,7 @@
         <v>110</v>
       </c>
       <c r="I12">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4536,10 +4604,10 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="9">
         <v>100</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="9">
         <v>200</v>
       </c>
       <c r="T12" t="s">
@@ -6391,7 +6459,7 @@
     </row>
     <row r="39" spans="2:30">
       <c r="B39">
-        <v>5001</v>
+        <v>4005</v>
       </c>
       <c r="C39" t="s">
         <v>228</v>
@@ -6400,40 +6468,43 @@
         <v>229</v>
       </c>
       <c r="E39" t="s">
+        <v>212</v>
+      </c>
+      <c r="F39" t="s">
+        <v>213</v>
+      </c>
+      <c r="H39" t="s">
+        <v>92</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="s">
+        <v>93</v>
+      </c>
+      <c r="M39" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="T39" t="s">
         <v>230</v>
       </c>
-      <c r="H39" t="s">
-        <v>141</v>
-      </c>
-      <c r="I39">
-        <v>300</v>
-      </c>
-      <c r="J39">
-        <v>300</v>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="s">
-        <v>100</v>
-      </c>
-      <c r="M39" t="b">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>1001</v>
-      </c>
-      <c r="O39">
-        <v>300</v>
-      </c>
-      <c r="P39">
-        <v>300</v>
-      </c>
-      <c r="T39" t="s">
+      <c r="U39" t="s">
         <v>231</v>
-      </c>
-      <c r="U39" t="s">
-        <v>232</v>
       </c>
       <c r="X39">
         <v>0</v>
@@ -6459,49 +6530,52 @@
     </row>
     <row r="40" spans="2:30">
       <c r="B40">
-        <v>5002</v>
+        <v>4006</v>
       </c>
       <c r="C40" t="s">
+        <v>232</v>
+      </c>
+      <c r="D40" t="s">
         <v>233</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
+        <v>212</v>
+      </c>
+      <c r="F40" t="s">
+        <v>213</v>
+      </c>
+      <c r="H40" t="s">
+        <v>92</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
+        <v>93</v>
+      </c>
+      <c r="M40" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="T40" t="s">
         <v>234</v>
       </c>
-      <c r="E40" t="s">
-        <v>230</v>
-      </c>
-      <c r="H40" t="s">
-        <v>105</v>
-      </c>
-      <c r="I40">
-        <v>300</v>
-      </c>
-      <c r="J40">
-        <v>300</v>
-      </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" t="s">
-        <v>100</v>
-      </c>
-      <c r="M40" t="b">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>1001</v>
-      </c>
-      <c r="O40">
-        <v>300</v>
-      </c>
-      <c r="P40">
-        <v>300</v>
-      </c>
-      <c r="T40" t="s">
+      <c r="U40" t="s">
         <v>235</v>
-      </c>
-      <c r="U40" t="s">
-        <v>236</v>
       </c>
       <c r="X40">
         <v>0</v>
@@ -6527,19 +6601,19 @@
     </row>
     <row r="41" spans="2:30">
       <c r="B41">
-        <v>5003</v>
+        <v>5001</v>
       </c>
       <c r="C41" t="s">
+        <v>236</v>
+      </c>
+      <c r="D41" t="s">
         <v>237</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>238</v>
       </c>
-      <c r="E41" t="s">
-        <v>230</v>
-      </c>
       <c r="H41" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I41">
         <v>300</v>
@@ -6595,7 +6669,7 @@
     </row>
     <row r="42" spans="2:30">
       <c r="B42">
-        <v>5004</v>
+        <v>5002</v>
       </c>
       <c r="C42" t="s">
         <v>241</v>
@@ -6604,7 +6678,7 @@
         <v>242</v>
       </c>
       <c r="E42" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H42" t="s">
         <v>105</v>
@@ -6663,7 +6737,7 @@
     </row>
     <row r="43" spans="2:30">
       <c r="B43">
-        <v>5005</v>
+        <v>5003</v>
       </c>
       <c r="C43" t="s">
         <v>245</v>
@@ -6672,10 +6746,10 @@
         <v>246</v>
       </c>
       <c r="E43" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H43" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="I43">
         <v>300</v>
@@ -6731,7 +6805,7 @@
     </row>
     <row r="44" spans="2:30">
       <c r="B44">
-        <v>5006</v>
+        <v>5004</v>
       </c>
       <c r="C44" t="s">
         <v>249</v>
@@ -6740,10 +6814,10 @@
         <v>250</v>
       </c>
       <c r="E44" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H44" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="I44">
         <v>300</v>
@@ -6799,7 +6873,7 @@
     </row>
     <row r="45" spans="2:30">
       <c r="B45">
-        <v>5007</v>
+        <v>5005</v>
       </c>
       <c r="C45" t="s">
         <v>253</v>
@@ -6808,10 +6882,10 @@
         <v>254</v>
       </c>
       <c r="E45" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H45" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="I45">
         <v>300</v>
@@ -6867,7 +6941,7 @@
     </row>
     <row r="46" spans="2:30">
       <c r="B46">
-        <v>5008</v>
+        <v>5006</v>
       </c>
       <c r="C46" t="s">
         <v>257</v>
@@ -6876,7 +6950,7 @@
         <v>258</v>
       </c>
       <c r="E46" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H46" t="s">
         <v>141</v>
@@ -6935,7 +7009,7 @@
     </row>
     <row r="47" spans="2:30">
       <c r="B47">
-        <v>6001</v>
+        <v>5007</v>
       </c>
       <c r="C47" t="s">
         <v>261</v>
@@ -6944,55 +7018,40 @@
         <v>262</v>
       </c>
       <c r="E47" t="s">
+        <v>238</v>
+      </c>
+      <c r="H47" t="s">
+        <v>121</v>
+      </c>
+      <c r="I47">
+        <v>300</v>
+      </c>
+      <c r="J47">
+        <v>300</v>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="s">
+        <v>100</v>
+      </c>
+      <c r="M47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>1001</v>
+      </c>
+      <c r="O47">
+        <v>300</v>
+      </c>
+      <c r="P47">
+        <v>300</v>
+      </c>
+      <c r="T47" t="s">
         <v>263</v>
       </c>
-      <c r="F47" t="s">
-        <v>162</v>
-      </c>
-      <c r="G47" t="s">
-        <v>162</v>
-      </c>
-      <c r="H47" t="s">
-        <v>92</v>
-      </c>
-      <c r="I47">
-        <v>300</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" t="s">
-        <v>93</v>
-      </c>
-      <c r="M47" t="b">
-        <v>1</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>162</v>
-      </c>
-      <c r="R47" t="s">
-        <v>162</v>
-      </c>
-      <c r="S47" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="T47" t="s">
+      <c r="U47" t="s">
         <v>264</v>
-      </c>
-      <c r="U47" t="s">
-        <v>265</v>
       </c>
       <c r="X47">
         <v>0</v>
@@ -7018,25 +7077,19 @@
     </row>
     <row r="48" spans="2:30">
       <c r="B48">
-        <v>6002</v>
+        <v>5008</v>
       </c>
       <c r="C48" t="s">
+        <v>265</v>
+      </c>
+      <c r="D48" t="s">
         <v>266</v>
       </c>
-      <c r="D48" t="s">
-        <v>267</v>
-      </c>
       <c r="E48" t="s">
-        <v>263</v>
-      </c>
-      <c r="F48" t="s">
-        <v>162</v>
-      </c>
-      <c r="G48" t="s">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="H48" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I48">
         <v>300</v>
@@ -7062,20 +7115,11 @@
       <c r="P48">
         <v>300</v>
       </c>
-      <c r="Q48" t="s">
-        <v>162</v>
-      </c>
-      <c r="R48" t="s">
-        <v>162</v>
-      </c>
-      <c r="S48" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="T48" t="s">
+        <v>267</v>
+      </c>
+      <c r="U48" t="s">
         <v>268</v>
-      </c>
-      <c r="U48" t="s">
-        <v>269</v>
       </c>
       <c r="X48">
         <v>0</v>
@@ -7101,17 +7145,17 @@
     </row>
     <row r="49" spans="2:30">
       <c r="B49">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="C49" t="s">
+        <v>269</v>
+      </c>
+      <c r="D49" t="s">
         <v>270</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>271</v>
       </c>
-      <c r="E49" t="s">
-        <v>263</v>
-      </c>
       <c r="F49" t="s">
         <v>162</v>
       </c>
@@ -7119,31 +7163,31 @@
         <v>162</v>
       </c>
       <c r="H49" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="I49">
         <v>300</v>
       </c>
       <c r="J49">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
       </c>
       <c r="L49" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="M49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="s">
         <v>162</v>
@@ -7184,7 +7228,7 @@
     </row>
     <row r="50" spans="2:30">
       <c r="B50">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="C50" t="s">
         <v>274</v>
@@ -7193,7 +7237,7 @@
         <v>275</v>
       </c>
       <c r="E50" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F50" t="s">
         <v>162</v>
@@ -7267,7 +7311,7 @@
     </row>
     <row r="51" spans="2:30">
       <c r="B51">
-        <v>6005</v>
+        <v>6003</v>
       </c>
       <c r="C51" t="s">
         <v>278</v>
@@ -7276,7 +7320,7 @@
         <v>279</v>
       </c>
       <c r="E51" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F51" t="s">
         <v>162</v>
@@ -7350,7 +7394,7 @@
     </row>
     <row r="52" spans="2:30">
       <c r="B52">
-        <v>6006</v>
+        <v>6004</v>
       </c>
       <c r="C52" t="s">
         <v>282</v>
@@ -7359,7 +7403,7 @@
         <v>283</v>
       </c>
       <c r="E52" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F52" t="s">
         <v>162</v>
@@ -7433,7 +7477,7 @@
     </row>
     <row r="53" spans="2:30">
       <c r="B53">
-        <v>6007</v>
+        <v>6005</v>
       </c>
       <c r="C53" t="s">
         <v>286</v>
@@ -7442,7 +7486,7 @@
         <v>287</v>
       </c>
       <c r="E53" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F53" t="s">
         <v>162</v>
@@ -7451,7 +7495,7 @@
         <v>162</v>
       </c>
       <c r="H53" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="I53">
         <v>300</v>
@@ -7516,7 +7560,7 @@
     </row>
     <row r="54" spans="2:30">
       <c r="B54">
-        <v>6008</v>
+        <v>6006</v>
       </c>
       <c r="C54" t="s">
         <v>290</v>
@@ -7525,7 +7569,7 @@
         <v>291</v>
       </c>
       <c r="E54" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F54" t="s">
         <v>162</v>
@@ -7534,7 +7578,7 @@
         <v>162</v>
       </c>
       <c r="H54" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I54">
         <v>300</v>
@@ -7599,7 +7643,7 @@
     </row>
     <row r="55" spans="2:30">
       <c r="B55">
-        <v>6009</v>
+        <v>6007</v>
       </c>
       <c r="C55" t="s">
         <v>294</v>
@@ -7608,7 +7652,7 @@
         <v>295</v>
       </c>
       <c r="E55" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F55" t="s">
         <v>162</v>
@@ -7617,7 +7661,7 @@
         <v>162</v>
       </c>
       <c r="H55" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="I55">
         <v>300</v>
@@ -7682,7 +7726,7 @@
     </row>
     <row r="56" spans="2:30">
       <c r="B56">
-        <v>6010</v>
+        <v>6008</v>
       </c>
       <c r="C56" t="s">
         <v>298</v>
@@ -7691,7 +7735,7 @@
         <v>299</v>
       </c>
       <c r="E56" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F56" t="s">
         <v>162</v>
@@ -7765,7 +7809,7 @@
     </row>
     <row r="57" spans="2:30">
       <c r="B57">
-        <v>6011</v>
+        <v>6009</v>
       </c>
       <c r="C57" t="s">
         <v>302</v>
@@ -7774,7 +7818,7 @@
         <v>303</v>
       </c>
       <c r="E57" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F57" t="s">
         <v>162</v>
@@ -7783,7 +7827,7 @@
         <v>162</v>
       </c>
       <c r="H57" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="I57">
         <v>300</v>
@@ -7848,7 +7892,7 @@
     </row>
     <row r="58" spans="2:30">
       <c r="B58">
-        <v>7001</v>
+        <v>6010</v>
       </c>
       <c r="C58" t="s">
         <v>306</v>
@@ -7857,7 +7901,13 @@
         <v>307</v>
       </c>
       <c r="E58" t="s">
-        <v>308</v>
+        <v>271</v>
+      </c>
+      <c r="F58" t="s">
+        <v>162</v>
+      </c>
+      <c r="G58" t="s">
+        <v>162</v>
       </c>
       <c r="H58" t="s">
         <v>141</v>
@@ -7886,11 +7936,20 @@
       <c r="P58">
         <v>300</v>
       </c>
+      <c r="Q58" t="s">
+        <v>162</v>
+      </c>
+      <c r="R58" t="s">
+        <v>162</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="T58" t="s">
+        <v>308</v>
+      </c>
+      <c r="U58" t="s">
         <v>309</v>
-      </c>
-      <c r="U58" t="s">
-        <v>310</v>
       </c>
       <c r="X58">
         <v>0</v>
@@ -7916,19 +7975,25 @@
     </row>
     <row r="59" spans="2:30">
       <c r="B59">
-        <v>7002</v>
+        <v>6011</v>
       </c>
       <c r="C59" t="s">
+        <v>310</v>
+      </c>
+      <c r="D59" t="s">
         <v>311</v>
       </c>
-      <c r="D59" t="s">
-        <v>312</v>
-      </c>
       <c r="E59" t="s">
-        <v>308</v>
+        <v>271</v>
+      </c>
+      <c r="F59" t="s">
+        <v>162</v>
+      </c>
+      <c r="G59" t="s">
+        <v>162</v>
       </c>
       <c r="H59" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I59">
         <v>300</v>
@@ -7954,11 +8019,20 @@
       <c r="P59">
         <v>300</v>
       </c>
+      <c r="Q59" t="s">
+        <v>162</v>
+      </c>
+      <c r="R59" t="s">
+        <v>162</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="T59" t="s">
+        <v>312</v>
+      </c>
+      <c r="U59" t="s">
         <v>313</v>
-      </c>
-      <c r="U59" t="s">
-        <v>314</v>
       </c>
       <c r="X59">
         <v>0</v>
@@ -7984,16 +8058,16 @@
     </row>
     <row r="60" spans="2:30">
       <c r="B60">
-        <v>7003</v>
+        <v>7001</v>
       </c>
       <c r="C60" t="s">
+        <v>314</v>
+      </c>
+      <c r="D60" t="s">
         <v>315</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>316</v>
-      </c>
-      <c r="E60" t="s">
-        <v>308</v>
       </c>
       <c r="H60" t="s">
         <v>141</v>
@@ -8052,7 +8126,7 @@
     </row>
     <row r="61" spans="2:30">
       <c r="B61">
-        <v>7004</v>
+        <v>7002</v>
       </c>
       <c r="C61" t="s">
         <v>319</v>
@@ -8061,34 +8135,34 @@
         <v>320</v>
       </c>
       <c r="E61" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="H61" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I61">
         <v>300</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K61" t="b">
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="M61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T61" t="s">
         <v>321</v>
@@ -8120,7 +8194,7 @@
     </row>
     <row r="62" spans="2:30">
       <c r="B62">
-        <v>7005</v>
+        <v>7003</v>
       </c>
       <c r="C62" t="s">
         <v>323</v>
@@ -8129,7 +8203,7 @@
         <v>324</v>
       </c>
       <c r="E62" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="H62" t="s">
         <v>141</v>
@@ -8188,7 +8262,7 @@
     </row>
     <row r="63" spans="2:30">
       <c r="B63">
-        <v>7006</v>
+        <v>7004</v>
       </c>
       <c r="C63" t="s">
         <v>327</v>
@@ -8197,34 +8271,34 @@
         <v>328</v>
       </c>
       <c r="E63" t="s">
-        <v>308</v>
-      </c>
-      <c r="H63" t="s">
-        <v>141</v>
+        <v>316</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="I63">
         <v>300</v>
       </c>
       <c r="J63">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="M63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="T63" t="s">
         <v>329</v>
@@ -8256,7 +8330,7 @@
     </row>
     <row r="64" spans="2:30">
       <c r="B64">
-        <v>7007</v>
+        <v>7005</v>
       </c>
       <c r="C64" t="s">
         <v>331</v>
@@ -8265,10 +8339,10 @@
         <v>332</v>
       </c>
       <c r="E64" t="s">
-        <v>308</v>
-      </c>
-      <c r="H64" t="s">
-        <v>141</v>
+        <v>316</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="I64">
         <v>300</v>
@@ -8324,7 +8398,7 @@
     </row>
     <row r="65" spans="1:34">
       <c r="B65">
-        <v>7008</v>
+        <v>7006</v>
       </c>
       <c r="C65" t="s">
         <v>335</v>
@@ -8333,16 +8407,10 @@
         <v>336</v>
       </c>
       <c r="E65" t="s">
-        <v>308</v>
-      </c>
-      <c r="F65" t="s">
-        <v>162</v>
-      </c>
-      <c r="G65" t="s">
-        <v>162</v>
-      </c>
-      <c r="H65" t="s">
-        <v>110</v>
+        <v>316</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="I65">
         <v>300</v>
@@ -8368,15 +8436,6 @@
       <c r="P65">
         <v>300</v>
       </c>
-      <c r="Q65" t="s">
-        <v>162</v>
-      </c>
-      <c r="R65" t="s">
-        <v>162</v>
-      </c>
-      <c r="S65" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="T65" t="s">
         <v>337</v>
       </c>
@@ -8407,7 +8466,7 @@
     </row>
     <row r="66" spans="1:34">
       <c r="B66">
-        <v>7009</v>
+        <v>7007</v>
       </c>
       <c r="C66" t="s">
         <v>339</v>
@@ -8416,16 +8475,10 @@
         <v>340</v>
       </c>
       <c r="E66" t="s">
-        <v>308</v>
-      </c>
-      <c r="F66" t="s">
-        <v>162</v>
-      </c>
-      <c r="G66" t="s">
-        <v>162</v>
+        <v>316</v>
       </c>
       <c r="H66" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I66">
         <v>300</v>
@@ -8451,15 +8504,6 @@
       <c r="P66">
         <v>300</v>
       </c>
-      <c r="Q66" t="s">
-        <v>162</v>
-      </c>
-      <c r="R66" t="s">
-        <v>162</v>
-      </c>
-      <c r="S66" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="T66" t="s">
         <v>341</v>
       </c>
@@ -8490,7 +8534,7 @@
     </row>
     <row r="67" spans="1:34">
       <c r="B67">
-        <v>7010</v>
+        <v>7008</v>
       </c>
       <c r="C67" t="s">
         <v>343</v>
@@ -8499,7 +8543,7 @@
         <v>344</v>
       </c>
       <c r="E67" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F67" t="s">
         <v>162</v>
@@ -8508,7 +8552,7 @@
         <v>162</v>
       </c>
       <c r="H67" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="I67">
         <v>300</v>
@@ -8573,7 +8617,7 @@
     </row>
     <row r="68" spans="1:34">
       <c r="B68">
-        <v>7011</v>
+        <v>7009</v>
       </c>
       <c r="C68" t="s">
         <v>347</v>
@@ -8582,7 +8626,7 @@
         <v>348</v>
       </c>
       <c r="E68" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F68" t="s">
         <v>162</v>
@@ -8656,7 +8700,7 @@
     </row>
     <row r="69" spans="1:34">
       <c r="B69">
-        <v>7012</v>
+        <v>7010</v>
       </c>
       <c r="C69" t="s">
         <v>351</v>
@@ -8665,7 +8709,7 @@
         <v>352</v>
       </c>
       <c r="E69" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F69" t="s">
         <v>162</v>
@@ -8674,7 +8718,7 @@
         <v>162</v>
       </c>
       <c r="H69" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="I69">
         <v>300</v>
@@ -8739,7 +8783,7 @@
     </row>
     <row r="70" spans="1:34">
       <c r="B70">
-        <v>7013</v>
+        <v>7011</v>
       </c>
       <c r="C70" t="s">
         <v>355</v>
@@ -8748,7 +8792,7 @@
         <v>356</v>
       </c>
       <c r="E70" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F70" t="s">
         <v>162</v>
@@ -8822,7 +8866,7 @@
     </row>
     <row r="71" spans="1:34">
       <c r="B71">
-        <v>7014</v>
+        <v>7012</v>
       </c>
       <c r="C71" t="s">
         <v>359</v>
@@ -8831,7 +8875,7 @@
         <v>360</v>
       </c>
       <c r="E71" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F71" t="s">
         <v>162</v>
@@ -8840,7 +8884,7 @@
         <v>162</v>
       </c>
       <c r="H71" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I71">
         <v>300</v>
@@ -8905,7 +8949,7 @@
     </row>
     <row r="72" spans="1:34">
       <c r="B72">
-        <v>7015</v>
+        <v>7013</v>
       </c>
       <c r="C72" t="s">
         <v>363</v>
@@ -8914,7 +8958,7 @@
         <v>364</v>
       </c>
       <c r="E72" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F72" t="s">
         <v>162</v>
@@ -8923,7 +8967,7 @@
         <v>162</v>
       </c>
       <c r="H72" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I72">
         <v>300</v>
@@ -8988,7 +9032,7 @@
     </row>
     <row r="73" spans="1:34">
       <c r="B73">
-        <v>7016</v>
+        <v>7014</v>
       </c>
       <c r="C73" t="s">
         <v>367</v>
@@ -8997,7 +9041,7 @@
         <v>368</v>
       </c>
       <c r="E73" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F73" t="s">
         <v>162</v>
@@ -9006,7 +9050,7 @@
         <v>162</v>
       </c>
       <c r="H73" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I73">
         <v>300</v>
@@ -9071,7 +9115,7 @@
     </row>
     <row r="74" spans="1:34">
       <c r="B74">
-        <v>7017</v>
+        <v>7015</v>
       </c>
       <c r="C74" t="s">
         <v>371</v>
@@ -9080,7 +9124,7 @@
         <v>372</v>
       </c>
       <c r="E74" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F74" t="s">
         <v>162</v>
@@ -9089,7 +9133,7 @@
         <v>162</v>
       </c>
       <c r="H74" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="I74">
         <v>300</v>
@@ -9154,7 +9198,7 @@
     </row>
     <row r="75" spans="1:34">
       <c r="B75">
-        <v>7018</v>
+        <v>7016</v>
       </c>
       <c r="C75" t="s">
         <v>375</v>
@@ -9163,10 +9207,16 @@
         <v>376</v>
       </c>
       <c r="E75" t="s">
-        <v>308</v>
+        <v>316</v>
+      </c>
+      <c r="F75" t="s">
+        <v>162</v>
+      </c>
+      <c r="G75" t="s">
+        <v>162</v>
       </c>
       <c r="H75" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I75">
         <v>300</v>
@@ -9192,6 +9242,15 @@
       <c r="P75">
         <v>300</v>
       </c>
+      <c r="Q75" t="s">
+        <v>162</v>
+      </c>
+      <c r="R75" t="s">
+        <v>162</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="T75" t="s">
         <v>377</v>
       </c>
@@ -9221,11 +9280,8 @@
       </c>
     </row>
     <row r="76" spans="1:34">
-      <c r="A76" t="s">
-        <v>162</v>
-      </c>
       <c r="B76">
-        <v>7019</v>
+        <v>7017</v>
       </c>
       <c r="C76" t="s">
         <v>379</v>
@@ -9234,7 +9290,7 @@
         <v>380</v>
       </c>
       <c r="E76" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="F76" t="s">
         <v>162</v>
@@ -9284,12 +9340,6 @@
       <c r="U76" t="s">
         <v>382</v>
       </c>
-      <c r="V76" t="s">
-        <v>162</v>
-      </c>
-      <c r="W76" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="X76">
         <v>0</v>
       </c>
@@ -9310,23 +9360,11 @@
       </c>
       <c r="AD76" t="b">
         <v>0</v>
-      </c>
-      <c r="AE76" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF76" t="s">
-        <v>162</v>
-      </c>
-      <c r="AG76" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH76" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="77" spans="1:34">
       <c r="B77">
-        <v>8001</v>
+        <v>7018</v>
       </c>
       <c r="C77" t="s">
         <v>383</v>
@@ -9335,16 +9373,10 @@
         <v>384</v>
       </c>
       <c r="E77" t="s">
-        <v>385</v>
-      </c>
-      <c r="F77" t="s">
-        <v>162</v>
-      </c>
-      <c r="G77" t="s">
-        <v>162</v>
+        <v>316</v>
       </c>
       <c r="H77" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I77">
         <v>300</v>
@@ -9370,55 +9402,49 @@
       <c r="P77">
         <v>300</v>
       </c>
-      <c r="Q77" t="s">
-        <v>162</v>
-      </c>
-      <c r="R77" t="s">
-        <v>162</v>
-      </c>
-      <c r="S77" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="T77" t="s">
+        <v>385</v>
+      </c>
+      <c r="U77" t="s">
         <v>386</v>
       </c>
-      <c r="U77" t="s">
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:34">
+      <c r="A78" t="s">
+        <v>162</v>
+      </c>
+      <c r="B78">
+        <v>7019</v>
+      </c>
+      <c r="C78" t="s">
         <v>387</v>
       </c>
-      <c r="X77">
-        <v>0</v>
-      </c>
-      <c r="Y77" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:34">
-      <c r="B78">
-        <v>8002</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>388</v>
       </c>
-      <c r="D78" t="s">
-        <v>389</v>
-      </c>
       <c r="E78" t="s">
-        <v>385</v>
+        <v>316</v>
       </c>
       <c r="F78" t="s">
         <v>162</v>
@@ -9427,7 +9453,7 @@
         <v>162</v>
       </c>
       <c r="H78" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="I78">
         <v>300</v>
@@ -9463,10 +9489,16 @@
         <v>162</v>
       </c>
       <c r="T78" t="s">
+        <v>389</v>
+      </c>
+      <c r="U78" t="s">
         <v>390</v>
       </c>
-      <c r="U78" t="s">
-        <v>391</v>
+      <c r="V78" t="s">
+        <v>162</v>
+      </c>
+      <c r="W78" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="X78">
         <v>0</v>
@@ -9488,20 +9520,32 @@
       </c>
       <c r="AD78" t="b">
         <v>0</v>
+      </c>
+      <c r="AE78" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF78" t="s">
+        <v>162</v>
+      </c>
+      <c r="AG78" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH78" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="79" spans="1:34">
       <c r="B79">
-        <v>8003</v>
+        <v>8001</v>
       </c>
       <c r="C79" t="s">
+        <v>391</v>
+      </c>
+      <c r="D79" t="s">
         <v>392</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>393</v>
-      </c>
-      <c r="E79" t="s">
-        <v>385</v>
       </c>
       <c r="F79" t="s">
         <v>162</v>
@@ -9575,7 +9619,7 @@
     </row>
     <row r="80" spans="1:34">
       <c r="B80">
-        <v>8004</v>
+        <v>8002</v>
       </c>
       <c r="C80" t="s">
         <v>396</v>
@@ -9584,7 +9628,7 @@
         <v>397</v>
       </c>
       <c r="E80" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="F80" t="s">
         <v>162</v>
@@ -9592,8 +9636,8 @@
       <c r="G80" t="s">
         <v>162</v>
       </c>
-      <c r="H80" t="s">
-        <v>105</v>
+      <c r="H80" s="9" t="s">
+        <v>121</v>
       </c>
       <c r="I80">
         <v>300</v>
@@ -9629,10 +9673,10 @@
         <v>162</v>
       </c>
       <c r="T80" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="U80" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="X80">
         <v>0</v>
@@ -9658,16 +9702,16 @@
     </row>
     <row r="81" spans="1:34">
       <c r="B81">
-        <v>8005</v>
+        <v>8003</v>
       </c>
       <c r="C81" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D81" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E81" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F81" t="s">
         <v>162</v>
@@ -9676,7 +9720,7 @@
         <v>162</v>
       </c>
       <c r="H81" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I81">
         <v>300</v>
@@ -9712,10 +9756,10 @@
         <v>162</v>
       </c>
       <c r="T81" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="U81" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="X81">
         <v>0</v>
@@ -9741,16 +9785,16 @@
     </row>
     <row r="82" spans="1:34">
       <c r="B82">
-        <v>8006</v>
+        <v>8004</v>
       </c>
       <c r="C82" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D82" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E82" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F82" t="s">
         <v>162</v>
@@ -9759,7 +9803,7 @@
         <v>162</v>
       </c>
       <c r="H82" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="I82">
         <v>300</v>
@@ -9795,10 +9839,10 @@
         <v>162</v>
       </c>
       <c r="T82" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="U82" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="X82">
         <v>0</v>
@@ -9824,16 +9868,16 @@
     </row>
     <row r="83" spans="1:34">
       <c r="B83">
-        <v>8007</v>
+        <v>8005</v>
       </c>
       <c r="C83" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D83" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E83" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F83" t="s">
         <v>162</v>
@@ -9842,7 +9886,7 @@
         <v>162</v>
       </c>
       <c r="H83" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="I83">
         <v>300</v>
@@ -9878,10 +9922,10 @@
         <v>162</v>
       </c>
       <c r="T83" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="U83" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="X83">
         <v>0</v>
@@ -9907,16 +9951,16 @@
     </row>
     <row r="84" spans="1:34">
       <c r="B84">
-        <v>8008</v>
+        <v>8006</v>
       </c>
       <c r="C84" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D84" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E84" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="F84" t="s">
         <v>162</v>
@@ -9924,8 +9968,8 @@
       <c r="G84" t="s">
         <v>162</v>
       </c>
-      <c r="H84" t="s">
-        <v>110</v>
+      <c r="H84" s="9" t="s">
+        <v>141</v>
       </c>
       <c r="I84">
         <v>300</v>
@@ -9961,10 +10005,10 @@
         <v>162</v>
       </c>
       <c r="T84" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U84" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="X84">
         <v>0</v>
@@ -9990,19 +10034,25 @@
     </row>
     <row r="85" spans="1:34">
       <c r="B85">
-        <v>8009</v>
+        <v>8007</v>
       </c>
       <c r="C85" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D85" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E85" t="s">
-        <v>385</v>
+        <v>393</v>
+      </c>
+      <c r="F85" t="s">
+        <v>162</v>
+      </c>
+      <c r="G85" t="s">
+        <v>162</v>
       </c>
       <c r="H85" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I85">
         <v>300</v>
@@ -10028,11 +10078,20 @@
       <c r="P85">
         <v>300</v>
       </c>
+      <c r="Q85" t="s">
+        <v>162</v>
+      </c>
+      <c r="R85" t="s">
+        <v>162</v>
+      </c>
+      <c r="S85" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="T85" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="U85" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="X85">
         <v>0</v>
@@ -10058,19 +10117,25 @@
     </row>
     <row r="86" spans="1:34">
       <c r="B86">
-        <v>8010</v>
+        <v>8008</v>
       </c>
       <c r="C86" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D86" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E86" t="s">
-        <v>385</v>
+        <v>393</v>
+      </c>
+      <c r="F86" t="s">
+        <v>162</v>
+      </c>
+      <c r="G86" t="s">
+        <v>162</v>
       </c>
       <c r="H86" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="I86">
         <v>300</v>
@@ -10096,11 +10161,20 @@
       <c r="P86">
         <v>300</v>
       </c>
+      <c r="Q86" t="s">
+        <v>162</v>
+      </c>
+      <c r="R86" t="s">
+        <v>162</v>
+      </c>
+      <c r="S86" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="T86" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="U86" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="X86">
         <v>0</v>
@@ -10126,19 +10200,19 @@
     </row>
     <row r="87" spans="1:34">
       <c r="B87">
-        <v>8011</v>
+        <v>8009</v>
       </c>
       <c r="C87" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D87" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E87" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="H87" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="I87">
         <v>300</v>
@@ -10165,10 +10239,10 @@
         <v>300</v>
       </c>
       <c r="T87" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="U87" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="X87">
         <v>0</v>
@@ -10193,29 +10267,20 @@
       </c>
     </row>
     <row r="88" spans="1:34">
-      <c r="A88" t="s">
-        <v>162</v>
-      </c>
       <c r="B88">
-        <v>8012</v>
+        <v>8010</v>
       </c>
       <c r="C88" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D88" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E88" t="s">
-        <v>385</v>
-      </c>
-      <c r="F88" t="s">
-        <v>162</v>
-      </c>
-      <c r="G88" t="s">
-        <v>162</v>
+        <v>393</v>
       </c>
       <c r="H88" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I88">
         <v>300</v>
@@ -10241,26 +10306,11 @@
       <c r="P88">
         <v>300</v>
       </c>
-      <c r="Q88" t="s">
-        <v>162</v>
-      </c>
-      <c r="R88" t="s">
-        <v>162</v>
-      </c>
-      <c r="S88" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="T88" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="U88" t="s">
-        <v>431</v>
-      </c>
-      <c r="V88" t="s">
-        <v>162</v>
-      </c>
-      <c r="W88" s="2" t="s">
-        <v>162</v>
+        <v>432</v>
       </c>
       <c r="X88">
         <v>0</v>
@@ -10283,43 +10333,22 @@
       <c r="AD88" t="b">
         <v>0</v>
       </c>
-      <c r="AE88" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF88" t="s">
-        <v>162</v>
-      </c>
-      <c r="AG88" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH88" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="89" spans="1:34">
-      <c r="A89" t="s">
-        <v>162</v>
-      </c>
       <c r="B89">
-        <v>8013</v>
+        <v>8011</v>
       </c>
       <c r="C89" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D89" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E89" t="s">
-        <v>385</v>
-      </c>
-      <c r="F89" t="s">
-        <v>162</v>
-      </c>
-      <c r="G89" t="s">
-        <v>162</v>
+        <v>393</v>
       </c>
       <c r="H89" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I89">
         <v>300</v>
@@ -10345,26 +10374,11 @@
       <c r="P89">
         <v>300</v>
       </c>
-      <c r="Q89" t="s">
-        <v>162</v>
-      </c>
-      <c r="R89" t="s">
-        <v>162</v>
-      </c>
-      <c r="S89" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="T89" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="U89" t="s">
-        <v>435</v>
-      </c>
-      <c r="V89" t="s">
-        <v>162</v>
-      </c>
-      <c r="W89" s="2" t="s">
-        <v>162</v>
+        <v>436</v>
       </c>
       <c r="X89">
         <v>0</v>
@@ -10387,37 +10401,34 @@
       <c r="AD89" t="b">
         <v>0</v>
       </c>
-      <c r="AE89" t="s">
-        <v>162</v>
-      </c>
-      <c r="AF89" t="s">
-        <v>162</v>
-      </c>
-      <c r="AG89" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH89" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="90" spans="1:34">
+      <c r="A90" t="s">
+        <v>162</v>
+      </c>
       <c r="B90">
-        <v>9001</v>
+        <v>8012</v>
       </c>
       <c r="C90" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D90" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E90" t="s">
-        <v>438</v>
+        <v>393</v>
+      </c>
+      <c r="F90" t="s">
+        <v>162</v>
+      </c>
+      <c r="G90" t="s">
+        <v>162</v>
       </c>
       <c r="H90" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I90">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J90">
         <v>300</v>
@@ -10426,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="s">
-        <v>439</v>
+        <v>100</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -10435,66 +10446,93 @@
         <v>1001</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>300</v>
+        <v>300</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>162</v>
+      </c>
+      <c r="R90" t="s">
+        <v>162</v>
+      </c>
+      <c r="S90" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="T90" t="s">
+        <v>439</v>
+      </c>
+      <c r="U90" t="s">
         <v>440</v>
       </c>
-      <c r="U90" t="s">
+      <c r="V90" t="s">
+        <v>162</v>
+      </c>
+      <c r="W90" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="X90">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z90" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF90" t="s">
+        <v>162</v>
+      </c>
+      <c r="AG90" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH90" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="91" spans="1:34">
+      <c r="A91" t="s">
+        <v>162</v>
+      </c>
+      <c r="B91">
+        <v>8013</v>
+      </c>
+      <c r="C91" t="s">
         <v>441</v>
       </c>
-      <c r="X90">
-        <v>0</v>
-      </c>
-      <c r="Y90" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:34">
-      <c r="B91">
-        <v>9002</v>
-      </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>442</v>
       </c>
-      <c r="D91" t="s">
-        <v>443</v>
-      </c>
       <c r="E91" t="s">
-        <v>438</v>
+        <v>393</v>
       </c>
       <c r="F91" t="s">
-        <v>444</v>
-      </c>
-      <c r="G91">
-        <v>9009</v>
+        <v>162</v>
+      </c>
+      <c r="G91" t="s">
+        <v>162</v>
       </c>
       <c r="H91" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="I91">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J91">
         <v>300</v>
@@ -10503,7 +10541,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="s">
-        <v>439</v>
+        <v>100</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
@@ -10512,22 +10550,31 @@
         <v>1001</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P91">
-        <v>0</v>
-      </c>
-      <c r="Q91">
-        <v>300</v>
+        <v>300</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>162</v>
+      </c>
+      <c r="R91" t="s">
+        <v>162</v>
+      </c>
+      <c r="S91" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="T91" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="U91" t="s">
-        <v>446</v>
+        <v>444</v>
+      </c>
+      <c r="V91" t="s">
+        <v>162</v>
       </c>
       <c r="W91" s="2" t="s">
-        <v>447</v>
+        <v>162</v>
       </c>
       <c r="X91">
         <v>0</v>
@@ -10545,33 +10592,39 @@
         <v>0</v>
       </c>
       <c r="AC91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="b">
         <v>0</v>
+      </c>
+      <c r="AE91" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF91" t="s">
+        <v>162</v>
+      </c>
+      <c r="AG91" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH91" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="92" spans="1:34">
       <c r="B92">
-        <v>9003</v>
+        <v>9001</v>
       </c>
       <c r="C92" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D92" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E92" t="s">
-        <v>438</v>
-      </c>
-      <c r="F92" t="s">
-        <v>444</v>
-      </c>
-      <c r="G92">
-        <v>9009</v>
+        <v>447</v>
       </c>
       <c r="H92" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="I92">
         <v>200</v>
@@ -10583,7 +10636,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
@@ -10601,13 +10654,10 @@
         <v>300</v>
       </c>
       <c r="T92" t="s">
+        <v>449</v>
+      </c>
+      <c r="U92" t="s">
         <v>450</v>
-      </c>
-      <c r="U92" t="s">
-        <v>451</v>
-      </c>
-      <c r="W92" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="X92">
         <v>0</v>
@@ -10633,19 +10683,19 @@
     </row>
     <row r="93" spans="1:34">
       <c r="B93">
-        <v>9004</v>
+        <v>9002</v>
       </c>
       <c r="C93" t="s">
+        <v>451</v>
+      </c>
+      <c r="D93" t="s">
         <v>452</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
+        <v>447</v>
+      </c>
+      <c r="F93" t="s">
         <v>453</v>
-      </c>
-      <c r="E93" t="s">
-        <v>438</v>
-      </c>
-      <c r="F93" t="s">
-        <v>444</v>
       </c>
       <c r="G93">
         <v>9009</v>
@@ -10663,7 +10713,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
@@ -10687,7 +10737,7 @@
         <v>455</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="X93">
         <v>0</v>
@@ -10713,19 +10763,19 @@
     </row>
     <row r="94" spans="1:34">
       <c r="B94">
-        <v>9005</v>
+        <v>9003</v>
       </c>
       <c r="C94" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D94" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E94" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F94" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="G94">
         <v>9009</v>
@@ -10743,7 +10793,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="M94" t="b">
         <v>0</v>
@@ -10761,13 +10811,13 @@
         <v>300</v>
       </c>
       <c r="T94" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="U94" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="X94">
         <v>0</v>
@@ -10793,25 +10843,25 @@
     </row>
     <row r="95" spans="1:34">
       <c r="B95">
-        <v>9006</v>
+        <v>9004</v>
       </c>
       <c r="C95" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D95" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E95" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F95" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="G95">
         <v>9009</v>
       </c>
       <c r="H95" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I95">
         <v>200</v>
@@ -10823,7 +10873,7 @@
         <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="M95" t="b">
         <v>0</v>
@@ -10841,13 +10891,13 @@
         <v>300</v>
       </c>
       <c r="T95" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="U95" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="X95">
         <v>0</v>
@@ -10873,25 +10923,25 @@
     </row>
     <row r="96" spans="1:34">
       <c r="B96">
-        <v>9007</v>
+        <v>9005</v>
       </c>
       <c r="C96" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D96" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E96" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F96" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="G96">
         <v>9009</v>
       </c>
       <c r="H96" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="I96">
         <v>200</v>
@@ -10903,7 +10953,7 @@
         <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="M96" t="b">
         <v>0</v>
@@ -10921,13 +10971,13 @@
         <v>300</v>
       </c>
       <c r="T96" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="U96" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="X96">
         <v>0</v>
@@ -10953,25 +11003,25 @@
     </row>
     <row r="97" spans="2:30">
       <c r="B97">
-        <v>9008</v>
+        <v>9006</v>
       </c>
       <c r="C97" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D97" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E97" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F97" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="G97">
         <v>9009</v>
       </c>
       <c r="H97" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="I97">
         <v>200</v>
@@ -10983,7 +11033,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
@@ -11001,13 +11051,13 @@
         <v>300</v>
       </c>
       <c r="T97" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="U97" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="X97">
         <v>0</v>
@@ -11033,19 +11083,25 @@
     </row>
     <row r="98" spans="2:30">
       <c r="B98">
+        <v>9007</v>
+      </c>
+      <c r="C98" t="s">
+        <v>473</v>
+      </c>
+      <c r="D98" t="s">
+        <v>474</v>
+      </c>
+      <c r="E98" t="s">
+        <v>447</v>
+      </c>
+      <c r="F98" t="s">
+        <v>453</v>
+      </c>
+      <c r="G98">
         <v>9009</v>
       </c>
-      <c r="C98" t="s">
-        <v>472</v>
-      </c>
-      <c r="D98" t="s">
-        <v>473</v>
-      </c>
-      <c r="E98" t="s">
-        <v>438</v>
-      </c>
       <c r="H98" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="I98">
         <v>200</v>
@@ -11057,13 +11113,13 @@
         <v>0</v>
       </c>
       <c r="L98" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="M98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="O98">
         <v>0</v>
@@ -11075,13 +11131,13 @@
         <v>300</v>
       </c>
       <c r="T98" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="U98" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="X98">
         <v>0</v>
@@ -11107,19 +11163,19 @@
     </row>
     <row r="99" spans="2:30">
       <c r="B99">
-        <v>9010</v>
+        <v>9008</v>
       </c>
       <c r="C99" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D99" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E99" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F99" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="G99">
         <v>9009</v>
@@ -11137,7 +11193,7 @@
         <v>0</v>
       </c>
       <c r="L99" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="M99" t="b">
         <v>0</v>
@@ -11155,10 +11211,13 @@
         <v>300</v>
       </c>
       <c r="T99" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="U99" t="s">
-        <v>479</v>
+        <v>480</v>
+      </c>
+      <c r="W99" s="2" t="s">
+        <v>456</v>
       </c>
       <c r="X99">
         <v>0</v>
@@ -11184,25 +11243,19 @@
     </row>
     <row r="100" spans="2:30">
       <c r="B100">
-        <v>9011</v>
+        <v>9009</v>
       </c>
       <c r="C100" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D100" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E100" t="s">
-        <v>438</v>
-      </c>
-      <c r="F100" t="s">
-        <v>444</v>
-      </c>
-      <c r="G100">
-        <v>9009</v>
+        <v>447</v>
       </c>
       <c r="H100" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="I100">
         <v>200</v>
@@ -11214,13 +11267,13 @@
         <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="M100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N100">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -11232,13 +11285,13 @@
         <v>300</v>
       </c>
       <c r="T100" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="U100" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="X100">
         <v>0</v>
@@ -11264,43 +11317,52 @@
     </row>
     <row r="101" spans="2:30">
       <c r="B101">
-        <v>10001</v>
+        <v>9010</v>
       </c>
       <c r="C101" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D101" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E101" t="s">
-        <v>486</v>
+        <v>447</v>
+      </c>
+      <c r="F101" t="s">
+        <v>453</v>
+      </c>
+      <c r="G101">
+        <v>9009</v>
       </c>
       <c r="H101" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="I101">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J101">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" t="s">
-        <v>93</v>
+        <v>448</v>
       </c>
       <c r="M101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="O101">
         <v>0</v>
       </c>
       <c r="P101">
         <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>300</v>
       </c>
       <c r="T101" t="s">
         <v>487</v>
@@ -11324,7 +11386,7 @@
         <v>0</v>
       </c>
       <c r="AC101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD101" t="b">
         <v>0</v>
@@ -11332,7 +11394,7 @@
     </row>
     <row r="102" spans="2:30">
       <c r="B102">
-        <v>11001</v>
+        <v>9011</v>
       </c>
       <c r="C102" t="s">
         <v>489</v>
@@ -11341,43 +11403,52 @@
         <v>490</v>
       </c>
       <c r="E102" t="s">
+        <v>447</v>
+      </c>
+      <c r="F102" t="s">
+        <v>453</v>
+      </c>
+      <c r="G102">
+        <v>9009</v>
+      </c>
+      <c r="H102" t="s">
+        <v>110</v>
+      </c>
+      <c r="I102">
+        <v>200</v>
+      </c>
+      <c r="J102">
+        <v>300</v>
+      </c>
+      <c r="K102" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102" t="s">
+        <v>448</v>
+      </c>
+      <c r="M102" t="b">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>1001</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>300</v>
+      </c>
+      <c r="T102" t="s">
         <v>491</v>
       </c>
-      <c r="H102" t="s">
-        <v>92</v>
-      </c>
-      <c r="I102">
-        <v>300</v>
-      </c>
-      <c r="J102">
-        <v>0</v>
-      </c>
-      <c r="K102" t="b">
-        <v>1</v>
-      </c>
-      <c r="L102" t="s">
-        <v>93</v>
-      </c>
-      <c r="M102" t="b">
-        <v>1</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <v>0</v>
-      </c>
-      <c r="T102" t="s">
+      <c r="U102" t="s">
         <v>492</v>
       </c>
-      <c r="U102" t="s">
-        <v>493</v>
-      </c>
       <c r="W102" s="2" t="s">
-        <v>494</v>
+        <v>456</v>
       </c>
       <c r="X102">
         <v>0</v>
@@ -11395,7 +11466,7 @@
         <v>0</v>
       </c>
       <c r="AC102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD102" t="b">
         <v>0</v>
@@ -11403,19 +11474,16 @@
     </row>
     <row r="103" spans="2:30">
       <c r="B103">
-        <v>11002</v>
+        <v>10001</v>
       </c>
       <c r="C103" t="s">
+        <v>493</v>
+      </c>
+      <c r="D103" t="s">
+        <v>494</v>
+      </c>
+      <c r="E103" t="s">
         <v>495</v>
-      </c>
-      <c r="D103" t="s">
-        <v>496</v>
-      </c>
-      <c r="E103" t="s">
-        <v>491</v>
-      </c>
-      <c r="G103">
-        <v>11001</v>
       </c>
       <c r="H103" t="s">
         <v>92</v>
@@ -11445,7 +11513,7 @@
         <v>0</v>
       </c>
       <c r="T103" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="U103" t="s">
         <v>497</v>
@@ -11472,144 +11540,286 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" customFormat="1" spans="2:30">
+    <row r="104" spans="2:30">
       <c r="B104">
+        <v>11001</v>
+      </c>
+      <c r="C104" t="s">
+        <v>498</v>
+      </c>
+      <c r="D104" t="s">
+        <v>499</v>
+      </c>
+      <c r="E104" t="s">
+        <v>500</v>
+      </c>
+      <c r="H104" t="s">
+        <v>92</v>
+      </c>
+      <c r="I104">
+        <v>300</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104" t="b">
+        <v>1</v>
+      </c>
+      <c r="L104" t="s">
+        <v>93</v>
+      </c>
+      <c r="M104" t="b">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="T104" t="s">
+        <v>501</v>
+      </c>
+      <c r="U104" t="s">
+        <v>502</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="X104">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z104" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:30">
+      <c r="B105">
+        <v>11002</v>
+      </c>
+      <c r="C105" t="s">
+        <v>504</v>
+      </c>
+      <c r="D105" t="s">
+        <v>505</v>
+      </c>
+      <c r="E105" t="s">
+        <v>500</v>
+      </c>
+      <c r="G105">
+        <v>11001</v>
+      </c>
+      <c r="H105" t="s">
+        <v>92</v>
+      </c>
+      <c r="I105">
+        <v>300</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105" t="b">
+        <v>1</v>
+      </c>
+      <c r="L105" t="s">
+        <v>93</v>
+      </c>
+      <c r="M105" t="b">
+        <v>1</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="T105" t="s">
+        <v>501</v>
+      </c>
+      <c r="U105" t="s">
+        <v>506</v>
+      </c>
+      <c r="X105">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z105" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customFormat="1" spans="2:30">
+      <c r="B106">
         <v>92005</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C106" t="s">
         <v>156</v>
       </c>
-      <c r="D104" t="s">
-        <v>498</v>
-      </c>
-      <c r="E104" t="s">
+      <c r="D106" t="s">
+        <v>507</v>
+      </c>
+      <c r="E106" t="s">
         <v>140</v>
       </c>
-      <c r="H104" t="s">
-        <v>499</v>
-      </c>
-      <c r="I104">
+      <c r="H106" t="s">
+        <v>508</v>
+      </c>
+      <c r="I106">
         <v>100</v>
       </c>
-      <c r="J104">
-        <v>300</v>
-      </c>
-      <c r="K104" t="b">
-        <v>0</v>
-      </c>
-      <c r="L104" t="s">
-        <v>500</v>
-      </c>
-      <c r="M104" t="b">
-        <v>0</v>
-      </c>
-      <c r="N104">
+      <c r="J106">
+        <v>300</v>
+      </c>
+      <c r="K106" t="b">
+        <v>0</v>
+      </c>
+      <c r="L106" t="s">
+        <v>509</v>
+      </c>
+      <c r="M106" t="b">
+        <v>0</v>
+      </c>
+      <c r="N106">
         <v>1001</v>
       </c>
-      <c r="R104">
+      <c r="R106">
         <v>100</v>
       </c>
-      <c r="S104" s="2"/>
-      <c r="T104" t="s">
+      <c r="S106" s="2"/>
+      <c r="T106" t="s">
         <v>158</v>
       </c>
-      <c r="U104" t="s">
+      <c r="U106" t="s">
         <v>159</v>
       </c>
-      <c r="W104" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="X104">
-        <v>0</v>
-      </c>
-      <c r="Y104" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z104" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD104" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" customFormat="1" spans="2:30">
-      <c r="B105">
+      <c r="W106" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="X106">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z106" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" customFormat="1" spans="2:30">
+      <c r="B107">
         <v>91012</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C107" t="s">
         <v>135</v>
       </c>
-      <c r="D105" t="s">
-        <v>502</v>
-      </c>
-      <c r="E105" t="s">
+      <c r="D107" t="s">
+        <v>511</v>
+      </c>
+      <c r="E107" t="s">
         <v>91</v>
       </c>
-      <c r="H105" t="s">
-        <v>499</v>
-      </c>
-      <c r="I105">
+      <c r="H107" t="s">
+        <v>508</v>
+      </c>
+      <c r="I107">
         <v>100</v>
       </c>
-      <c r="J105">
+      <c r="J107">
         <v>100</v>
       </c>
-      <c r="K105" t="b">
-        <v>0</v>
-      </c>
-      <c r="L105" t="s">
-        <v>500</v>
-      </c>
-      <c r="M105" t="b">
-        <v>0</v>
-      </c>
-      <c r="N105">
+      <c r="K107" t="b">
+        <v>0</v>
+      </c>
+      <c r="L107" t="s">
+        <v>509</v>
+      </c>
+      <c r="M107" t="b">
+        <v>0</v>
+      </c>
+      <c r="N107">
         <v>1001</v>
       </c>
-      <c r="R105">
+      <c r="R107">
         <v>100</v>
       </c>
-      <c r="S105" s="2"/>
-      <c r="T105" t="s">
+      <c r="S107" s="2"/>
+      <c r="T107" t="s">
         <v>111</v>
       </c>
-      <c r="U105" t="s">
+      <c r="U107" t="s">
         <v>137</v>
       </c>
-      <c r="V105">
+      <c r="V107">
         <v>1012</v>
       </c>
-      <c r="W105" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="X105">
-        <v>0</v>
-      </c>
-      <c r="Y105" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z105" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD105" t="b">
+      <c r="W107" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="X107">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z107" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11635,10 +11845,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H27 H30:H75 H77:H86 H90:H105">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H27 H30:H77 H79:H88 H92:H107">
       <formula1>枚举示例!$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L16 L18:L27 L30:L75 L77:L87 L90:L105">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L16 L18:L27 L30:L77 L79:L89 L92:L107">
       <formula1>枚举示例!$C$18:$C$23</formula1>
     </dataValidation>
   </dataValidations>
@@ -12180,7 +12390,7 @@
         <v>132</v>
       </c>
       <c r="D15" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -12212,7 +12422,7 @@
         <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -12406,7 +12616,7 @@
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="D23" t="s">
         <v>161</v>
@@ -12726,10 +12936,10 @@
         <v>4001</v>
       </c>
       <c r="C33" t="s">
-        <v>210</v>
+        <v>754</v>
       </c>
       <c r="D33" t="s">
-        <v>211</v>
+        <v>755</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -12758,10 +12968,10 @@
         <v>4002</v>
       </c>
       <c r="C34" t="s">
-        <v>216</v>
+        <v>756</v>
       </c>
       <c r="D34" t="s">
-        <v>217</v>
+        <v>757</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -12790,10 +13000,10 @@
         <v>4003</v>
       </c>
       <c r="C35" t="s">
-        <v>220</v>
+        <v>758</v>
       </c>
       <c r="D35" t="s">
-        <v>221</v>
+        <v>759</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -12822,10 +13032,10 @@
         <v>4004</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>760</v>
       </c>
       <c r="D36" t="s">
-        <v>225</v>
+        <v>761</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -12854,10 +13064,10 @@
         <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D37" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -12886,10 +13096,10 @@
         <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D38" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -12918,10 +13128,10 @@
         <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D39" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -12950,10 +13160,10 @@
         <v>5004</v>
       </c>
       <c r="C40" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D40" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -12982,10 +13192,10 @@
         <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D41" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -13014,10 +13224,10 @@
         <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D42" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -13046,10 +13256,10 @@
         <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -13078,10 +13288,10 @@
         <v>5008</v>
       </c>
       <c r="C44" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D44" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -13110,10 +13320,10 @@
         <v>6001</v>
       </c>
       <c r="C45" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D45" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -13142,10 +13352,10 @@
         <v>6002</v>
       </c>
       <c r="C46" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="D46" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -13174,10 +13384,10 @@
         <v>6003</v>
       </c>
       <c r="C47" t="s">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="D47" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -13206,10 +13416,10 @@
         <v>6004</v>
       </c>
       <c r="C48" t="s">
-        <v>746</v>
+        <v>766</v>
       </c>
       <c r="D48" t="s">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -13238,10 +13448,10 @@
         <v>6005</v>
       </c>
       <c r="C49" t="s">
-        <v>748</v>
+        <v>768</v>
       </c>
       <c r="D49" t="s">
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -13270,10 +13480,10 @@
         <v>6006</v>
       </c>
       <c r="C50" t="s">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="D50" t="s">
-        <v>751</v>
+        <v>771</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -13302,10 +13512,10 @@
         <v>6007</v>
       </c>
       <c r="C51" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="D51" t="s">
-        <v>753</v>
+        <v>773</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -13334,10 +13544,10 @@
         <v>6008</v>
       </c>
       <c r="C52" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="D52" t="s">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -13366,10 +13576,10 @@
         <v>6009</v>
       </c>
       <c r="C53" t="s">
-        <v>756</v>
+        <v>776</v>
       </c>
       <c r="D53" t="s">
-        <v>757</v>
+        <v>777</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -13398,10 +13608,10 @@
         <v>6010</v>
       </c>
       <c r="C54" t="s">
-        <v>758</v>
+        <v>778</v>
       </c>
       <c r="D54" t="s">
-        <v>759</v>
+        <v>779</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -13430,10 +13640,10 @@
         <v>6011</v>
       </c>
       <c r="C55" t="s">
-        <v>760</v>
+        <v>780</v>
       </c>
       <c r="D55" t="s">
-        <v>761</v>
+        <v>781</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -13462,10 +13672,10 @@
         <v>7001</v>
       </c>
       <c r="C56" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D56" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -13494,10 +13704,10 @@
         <v>7002</v>
       </c>
       <c r="C57" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D57" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -13526,10 +13736,10 @@
         <v>7003</v>
       </c>
       <c r="C58" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -13558,10 +13768,10 @@
         <v>7004</v>
       </c>
       <c r="C59" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -13590,10 +13800,10 @@
         <v>7005</v>
       </c>
       <c r="C60" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -13622,10 +13832,10 @@
         <v>7006</v>
       </c>
       <c r="C61" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="D61" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -13654,10 +13864,10 @@
         <v>7007</v>
       </c>
       <c r="C62" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D62" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -13686,10 +13896,10 @@
         <v>7008</v>
       </c>
       <c r="C63" t="s">
-        <v>762</v>
+        <v>782</v>
       </c>
       <c r="D63" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -13718,10 +13928,10 @@
         <v>7009</v>
       </c>
       <c r="C64" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D64" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -13750,10 +13960,10 @@
         <v>7010</v>
       </c>
       <c r="C65" t="s">
-        <v>764</v>
+        <v>784</v>
       </c>
       <c r="D65" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -13782,10 +13992,10 @@
         <v>7011</v>
       </c>
       <c r="C66" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D66" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -13814,10 +14024,10 @@
         <v>7012</v>
       </c>
       <c r="C67" t="s">
-        <v>766</v>
+        <v>786</v>
       </c>
       <c r="D67" t="s">
-        <v>767</v>
+        <v>787</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -13846,10 +14056,10 @@
         <v>7013</v>
       </c>
       <c r="C68" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="D68" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -13878,10 +14088,10 @@
         <v>7014</v>
       </c>
       <c r="C69" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D69" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -13910,10 +14120,10 @@
         <v>7015</v>
       </c>
       <c r="C70" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="D70" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -13942,10 +14152,10 @@
         <v>7016</v>
       </c>
       <c r="C71" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D71" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -13974,10 +14184,10 @@
         <v>7017</v>
       </c>
       <c r="C72" t="s">
-        <v>768</v>
+        <v>788</v>
       </c>
       <c r="D72" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -14006,10 +14216,10 @@
         <v>7018</v>
       </c>
       <c r="C73" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="D73" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -14038,10 +14248,10 @@
         <v>8001</v>
       </c>
       <c r="C74" t="s">
-        <v>770</v>
+        <v>790</v>
       </c>
       <c r="D74" t="s">
-        <v>770</v>
+        <v>790</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -14070,10 +14280,10 @@
         <v>8002</v>
       </c>
       <c r="C75" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D75" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -14102,10 +14312,10 @@
         <v>8003</v>
       </c>
       <c r="C76" t="s">
-        <v>771</v>
+        <v>791</v>
       </c>
       <c r="D76" t="s">
-        <v>771</v>
+        <v>791</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -14134,10 +14344,10 @@
         <v>8004</v>
       </c>
       <c r="C77" t="s">
-        <v>772</v>
+        <v>792</v>
       </c>
       <c r="D77" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -14166,10 +14376,10 @@
         <v>8005</v>
       </c>
       <c r="C78" t="s">
-        <v>773</v>
+        <v>793</v>
       </c>
       <c r="D78" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -14198,10 +14408,10 @@
         <v>8006</v>
       </c>
       <c r="C79" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="D79" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -14230,10 +14440,10 @@
         <v>8007</v>
       </c>
       <c r="C80" t="s">
-        <v>774</v>
+        <v>794</v>
       </c>
       <c r="D80" t="s">
-        <v>775</v>
+        <v>795</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -14262,10 +14472,10 @@
         <v>8008</v>
       </c>
       <c r="C81" t="s">
-        <v>776</v>
+        <v>796</v>
       </c>
       <c r="D81" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -14294,10 +14504,10 @@
         <v>8009</v>
       </c>
       <c r="C82" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="D82" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -14326,10 +14536,10 @@
         <v>8010</v>
       </c>
       <c r="C83" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D83" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -14358,10 +14568,10 @@
         <v>8011</v>
       </c>
       <c r="C84" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D84" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -14390,10 +14600,10 @@
         <v>9001</v>
       </c>
       <c r="C85" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D85" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -14422,10 +14632,10 @@
         <v>9002</v>
       </c>
       <c r="C86" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="D86" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -14454,10 +14664,10 @@
         <v>9003</v>
       </c>
       <c r="C87" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="D87" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -14486,10 +14696,10 @@
         <v>9004</v>
       </c>
       <c r="C88" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="D88" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -14518,10 +14728,10 @@
         <v>9005</v>
       </c>
       <c r="C89" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="D89" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -14550,10 +14760,10 @@
         <v>9006</v>
       </c>
       <c r="C90" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="D90" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -14582,10 +14792,10 @@
         <v>9007</v>
       </c>
       <c r="C91" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="D91" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -14614,10 +14824,10 @@
         <v>9008</v>
       </c>
       <c r="C92" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="D92" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -14646,10 +14856,10 @@
         <v>9009</v>
       </c>
       <c r="C93" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="D93" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -14678,10 +14888,10 @@
         <v>9010</v>
       </c>
       <c r="C94" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="D94" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -14710,10 +14920,10 @@
         <v>9011</v>
       </c>
       <c r="C95" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="D95" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -14742,10 +14952,10 @@
         <v>10001</v>
       </c>
       <c r="C96" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="D96" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -14774,10 +14984,10 @@
         <v>11001</v>
       </c>
       <c r="C97" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="D97" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -14806,10 +15016,10 @@
         <v>11002</v>
       </c>
       <c r="C98" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="D98" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -14841,7 +15051,7 @@
         <v>156</v>
       </c>
       <c r="D99" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -14873,7 +15083,7 @@
         <v>135</v>
       </c>
       <c r="D100" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -14919,17 +15129,17 @@
         <v>91</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="E2" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="F2" t="s">
         <v>99</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>213</v>
@@ -14938,13 +15148,13 @@
         <v>1</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" spans="2:16">
@@ -14952,32 +15162,32 @@
         <v>140</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="J3" s="6">
         <v>2</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4" spans="2:16">
@@ -14985,32 +15195,32 @@
         <v>191</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>105</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="J4" s="6">
         <v>4</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="2:16">
@@ -15018,241 +15228,247 @@
         <v>212</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>121</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="J5" s="6">
         <v>8</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
     </row>
     <row r="6" spans="2:16">
       <c r="B6" s="6" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="E6" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="F6" t="s">
         <v>141</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="J6" s="6">
         <v>16</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7" spans="2:16">
       <c r="B7" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>92</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="J7" s="6">
         <v>32</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="2:16">
       <c r="B8" s="6" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="J8" s="6">
         <v>64</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" spans="2:16">
       <c r="B9" s="6" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="J9" s="6">
         <v>128</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
     </row>
     <row r="10" spans="2:16">
       <c r="B10" s="6" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="J10" s="6">
         <v>256</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" spans="2:16">
       <c r="B11" s="6" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="J11" s="6">
         <v>512</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" s="6" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="J12" s="6">
         <v>1024</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
     </row>
     <row r="13" spans="2:16">
+      <c r="B13" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>580</v>
+      </c>
       <c r="H13" s="6" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="J13" s="6">
         <v>2048</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="6" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>93</v>
@@ -15260,7 +15476,7 @@
     </row>
     <row r="19" spans="2:3">
       <c r="B19" s="6" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>100</v>
@@ -15268,34 +15484,34 @@
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="6" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" s="6" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="6" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="B23" s="6" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
     </row>
   </sheetData>
@@ -15336,34 +15552,34 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="E1" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="F1" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="G1" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="H1" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="I1" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="J1" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="K1" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="L1" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="M1" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -15377,10 +15593,10 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="E2" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="F2" t="s">
         <v>32</v>
@@ -15389,7 +15605,7 @@
         <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="I2" t="s">
         <v>37</v>
@@ -15412,81 +15628,81 @@
         <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="4" s="9" customFormat="1" spans="1:13">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="4" s="10" customFormat="1" spans="1:13">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>606</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>609</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>614</v>
-      </c>
-      <c r="L4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>616</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>625</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15494,16 +15710,16 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="F5">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -15532,16 +15748,16 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>621</v>
+        <v>631</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="F6">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -15570,16 +15786,16 @@
         <v>2001</v>
       </c>
       <c r="C7" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="F7">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -15608,13 +15824,13 @@
         <v>3001</v>
       </c>
       <c r="C8" t="s">
-        <v>623</v>
+        <v>633</v>
       </c>
       <c r="D8" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -15687,31 +15903,31 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="E1" t="s">
-        <v>627</v>
+        <v>637</v>
       </c>
       <c r="F1" t="s">
-        <v>628</v>
+        <v>638</v>
       </c>
       <c r="G1" t="s">
-        <v>629</v>
+        <v>639</v>
       </c>
       <c r="H1" t="s">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="I1" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="J1" t="s">
-        <v>632</v>
+        <v>642</v>
       </c>
       <c r="K1" t="s">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="L1" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -15758,31 +15974,31 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>636</v>
+        <v>646</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>638</v>
+        <v>648</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>641</v>
+        <v>651</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15793,37 +16009,37 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="D4" t="s">
-        <v>642</v>
+        <v>652</v>
       </c>
       <c r="E4" t="s">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="F4" t="s">
-        <v>644</v>
+        <v>654</v>
       </c>
       <c r="G4" t="s">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="H4" t="s">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="I4" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="J4" t="s">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="K4" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="L4" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="M4" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -15861,7 +16077,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15899,7 +16115,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15937,7 +16153,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>653</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -15975,7 +16191,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>654</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -16013,7 +16229,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -16051,7 +16267,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -16089,7 +16305,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -16127,7 +16343,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -16165,7 +16381,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>659</v>
+        <v>669</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -16203,7 +16419,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -16241,7 +16457,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -16279,7 +16495,7 @@
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -16317,7 +16533,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -16355,7 +16571,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -16389,13 +16605,13 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="E1" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="G1" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -16424,17 +16640,17 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="1" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -16445,19 +16661,19 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="D4" t="s">
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="G4" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="H4" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -16533,12 +16749,12 @@
       <c r="D8" t="s">
         <v>105</v>
       </c>
-      <c r="E8">
-        <v>90000</v>
+      <c r="E8" s="9">
+        <v>900</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -16554,7 +16770,7 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="9">
         <v>180</v>
       </c>
       <c r="F9" s="7">
@@ -16592,7 +16808,7 @@
       </c>
       <c r="F11" s="7">
         <f>SUM(F5:F10)</f>
-        <v>9.91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -16637,7 +16853,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -16750,7 +16966,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -16770,7 +16986,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -16790,7 +17006,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -16810,7 +17026,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -16830,7 +17046,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -16850,7 +17066,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -16866,7 +17082,7 @@
         <v>3001</v>
       </c>
       <c r="D26" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -16875,7 +17091,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -16910,28 +17126,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="D1" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="E1" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="F1" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="G1" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="H1" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="I1" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="J1" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -16974,28 +17190,28 @@
         <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -17006,31 +17222,31 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="D4" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="E4" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="F4" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="G4" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="H4" t="s">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="I4" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="J4" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="K4" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -17446,7 +17662,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -17481,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -17580,7 +17796,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -17615,7 +17831,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -17778,7 +17994,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -17813,7 +18029,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -17848,7 +18064,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -17891,22 +18107,22 @@
         <v>200101</v>
       </c>
       <c r="C31" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="D31">
         <v>100</v>
       </c>
       <c r="E31" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="F31" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G31" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="H31" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -17923,22 +18139,22 @@
         <v>200201</v>
       </c>
       <c r="C32" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="D32">
         <v>100</v>
       </c>
       <c r="E32" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="F32" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="G32" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="H32" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -18055,25 +18271,25 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="F1" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="G1" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="H1" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="I1" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="K1" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="L1" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -18117,23 +18333,23 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -18150,28 +18366,28 @@
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="F4" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="G4" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="H4" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="I4" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="J4" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="K4" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="L4" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -18179,22 +18395,22 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="D5" t="s">
         <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="F5" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="H5" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="K5" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -18202,22 +18418,22 @@
         <v>1002</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="F6" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="H6" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="K6" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -18225,22 +18441,22 @@
         <v>1003</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="F7" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="H7" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="K7" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -18248,22 +18464,22 @@
         <v>1004</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="F8" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="H8" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="K8" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -18271,22 +18487,22 @@
         <v>1005</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>141</v>
       </c>
       <c r="E9" t="s">
+        <v>733</v>
+      </c>
+      <c r="F9" t="s">
+        <v>721</v>
+      </c>
+      <c r="H9" t="s">
+        <v>734</v>
+      </c>
+      <c r="K9" t="s">
         <v>723</v>
-      </c>
-      <c r="F9" t="s">
-        <v>711</v>
-      </c>
-      <c r="H9" t="s">
-        <v>724</v>
-      </c>
-      <c r="K9" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -18294,22 +18510,22 @@
         <v>1006</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="F10" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="H10" t="s">
+        <v>736</v>
+      </c>
+      <c r="K10" t="s">
         <v>726</v>
-      </c>
-      <c r="K10" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -18317,22 +18533,22 @@
         <v>2001</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E11" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="F11" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="H11" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="J11" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -18340,22 +18556,22 @@
         <v>2002</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="E12" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="F12" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="H12" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="J12" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -18367,7 +18583,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="13.5" customWidth="1"/>
@@ -18383,10 +18599,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>728</v>
+        <v>738</v>
       </c>
       <c r="D1" t="s">
-        <v>729</v>
+        <v>739</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -18403,7 +18619,7 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>730</v>
+        <v>740</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -18420,10 +18636,10 @@
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="E3" t="s">
-        <v>732</v>
+        <v>742</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -18445,7 +18661,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
       <c r="D5" t="s">
         <v>140</v>
@@ -18459,7 +18675,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>734</v>
+        <v>744</v>
       </c>
       <c r="D6" t="s">
         <v>191</v>
@@ -18473,10 +18689,10 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="D7" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -18484,66 +18700,67 @@
     </row>
     <row r="8" spans="1:5">
       <c r="D8" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="B9">
+      <c r="D9" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10">
         <v>1005</v>
       </c>
-      <c r="C9" t="s">
-        <v>736</v>
-      </c>
-      <c r="D9" t="s">
-        <v>263</v>
-      </c>
-      <c r="E9">
+      <c r="C10" t="s">
+        <v>746</v>
+      </c>
+      <c r="D10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E10">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="D10" t="s">
-        <v>308</v>
-      </c>
-    </row>
     <row r="11" spans="1:5">
-      <c r="B11">
+      <c r="D11" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12">
         <v>1006</v>
       </c>
-      <c r="C11" t="s">
-        <v>438</v>
-      </c>
-      <c r="D11" t="s">
-        <v>438</v>
-      </c>
-      <c r="E11">
+      <c r="C12" t="s">
+        <v>447</v>
+      </c>
+      <c r="D12" t="s">
+        <v>447</v>
+      </c>
+      <c r="E12">
         <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="D12" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="D13" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="D14" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="D15" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="21" spans="3:4">
-      <c r="C21" s="6"/>
     </row>
     <row r="22" spans="3:4">
       <c r="C22" s="6"/>
     </row>
     <row r="23" spans="3:4">
       <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
     </row>
     <row r="24" spans="3:4">
       <c r="C24" s="6"/>
@@ -18572,6 +18789,10 @@
     <row r="30" spans="3:4">
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
+    </row>
+    <row r="31" spans="3:4">
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18582,15 +18803,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="2"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
-    <col min="2" max="2" width="11.0833333333333" customWidth="1"/>
-    <col min="3" max="3" width="11.1666666666667" customWidth="1"/>
+    <col min="2" max="2" width="14.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="4" max="4" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -18598,10 +18820,13 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>747</v>
+      </c>
+      <c r="D1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
@@ -18611,8 +18836,11 @@
       <c r="C2" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
@@ -18620,18 +18848,24 @@
         <v>60</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>749</v>
+      </c>
+      <c r="D3" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="B5" t="s">
         <v>91</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="B6" t="s">
         <v>140</v>
       </c>
@@ -18639,7 +18873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="B7" t="s">
         <v>191</v>
       </c>
@@ -18647,68 +18881,91 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="B8" t="s">
         <v>212</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="B9" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="B10" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="B11" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11">
+        <v>6001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="B12" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12">
+        <v>7004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="B13" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="B14" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="B15" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
+      </c>
+      <c r="D15">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" t="s">
+        <v>398</v>
+      </c>
+      <c r="C16" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/Items.xlsx
+++ b/luban-excels/bak/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="632"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="703" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
     <sheet name="BlindBoxVisual" sheetId="16" r:id="rId7"/>
     <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
     <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId9"/>
-    <sheet name="Item_SteamDef" sheetId="12" r:id="rId10"/>
+    <sheet name="LinkTree" sheetId="17" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="819">
   <si>
     <t>##var</t>
   </si>
@@ -2301,145 +2301,208 @@
     <t>默认穿戴物品id</t>
   </si>
   <si>
-    <t>瘦芝麻柴</t>
-  </si>
-  <si>
-    <t>胡渣芝麻柴</t>
-  </si>
-  <si>
-    <t>Lucky</t>
-  </si>
-  <si>
-    <t>Male A</t>
-  </si>
-  <si>
-    <t>男性手臂A</t>
-  </si>
-  <si>
-    <t>Male B</t>
-  </si>
-  <si>
-    <t>男性手臂B</t>
-  </si>
-  <si>
-    <t>Male C</t>
-  </si>
-  <si>
-    <t>男性手臂C</t>
-  </si>
-  <si>
-    <t>Male D</t>
-  </si>
-  <si>
-    <t>男性手臂D</t>
-  </si>
-  <si>
-    <t>Full Tilt Like</t>
-  </si>
-  <si>
-    <t>Full Tilt风格</t>
-  </si>
-  <si>
-    <t>Hustler Like</t>
-  </si>
-  <si>
-    <t>Hustler风格</t>
-  </si>
-  <si>
-    <t>Les Ambassadeurs Like</t>
-  </si>
-  <si>
-    <t>Les Ambassadeurs风格</t>
-  </si>
-  <si>
-    <t>Maestral Like</t>
-  </si>
-  <si>
-    <t>Maestral风格</t>
-  </si>
-  <si>
-    <t>Mezcal Like</t>
-  </si>
-  <si>
-    <t>Mezcal风格</t>
-  </si>
-  <si>
-    <t>Poker Go Like</t>
-  </si>
-  <si>
-    <t>Poker Go风格</t>
-  </si>
-  <si>
-    <t>Pure Indigo</t>
-  </si>
-  <si>
-    <t>纯靛蓝</t>
-  </si>
-  <si>
-    <t>Pure Purple</t>
-  </si>
-  <si>
-    <t>纯紫色</t>
-  </si>
-  <si>
-    <t>Pure Teal</t>
-  </si>
-  <si>
-    <t>纯青色</t>
-  </si>
-  <si>
-    <t>The King of Hill Like</t>
-  </si>
-  <si>
-    <t>King of Hill风格</t>
-  </si>
-  <si>
-    <t>Highstakes Poker Like</t>
-  </si>
-  <si>
-    <t>Highstakes Poker风格</t>
-  </si>
-  <si>
-    <t>Part Poker Like</t>
-  </si>
-  <si>
-    <t>Part Poker风格</t>
-  </si>
-  <si>
-    <t>Poker King Like</t>
-  </si>
-  <si>
-    <t>Poker King风格</t>
-  </si>
-  <si>
-    <t>World Poker Tour Like</t>
-  </si>
-  <si>
-    <t>World Poker Tour风格</t>
-  </si>
-  <si>
-    <t>A158UUA</t>
-  </si>
-  <si>
-    <t>F91UU</t>
-  </si>
-  <si>
-    <t>Feng Shui Bracelet</t>
-  </si>
-  <si>
-    <t>Good Luck Bracelet</t>
-  </si>
-  <si>
-    <t>Relax Driver Black</t>
-  </si>
-  <si>
-    <t>黑色Relax Driver</t>
-  </si>
-  <si>
-    <t>Relax Driver Green</t>
-  </si>
-  <si>
-    <t>绿色Relax Driver</t>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>TooltipKey</t>
+  </si>
+  <si>
+    <t>BannerTexturePath</t>
+  </si>
+  <si>
+    <t>BadgeTexturePath</t>
+  </si>
+  <si>
+    <t>PreClaimUrl</t>
+  </si>
+  <si>
+    <t>PostClaimUrl</t>
+  </si>
+  <si>
+    <t>OpenCheckType</t>
+  </si>
+  <si>
+    <t>RewardType</t>
+  </si>
+  <si>
+    <t>RewardItemId</t>
+  </si>
+  <si>
+    <t>RewardChips</t>
+  </si>
+  <si>
+    <t>SequentialPackId</t>
+  </si>
+  <si>
+    <t>SteamPromoItemDefId</t>
+  </si>
+  <si>
+    <t>ClaimLimit</t>
+  </si>
+  <si>
+    <t>ELinkTreeOpenCheckType</t>
+  </si>
+  <si>
+    <t>ELinkTreeRewardType</t>
+  </si>
+  <si>
+    <t>稳定机器名，代码和存档/Steam 记录用，不要随意改名</t>
+  </si>
+  <si>
+    <t>显示顺序，数字越小越靠前</t>
+  </si>
+  <si>
+    <t>是否显示这个入口</t>
+  </si>
+  <si>
+    <t>Tooltip 本地化 key；当前也可直接作为显示名来源</t>
+  </si>
+  <si>
+    <t>Banner 图片路径；可填 res:// 或项目相对路径</t>
+  </si>
+  <si>
+    <t>角标图片路径；空则使用默认礼物角标</t>
+  </si>
+  <si>
+    <t>领奖前点击打开的外部链接，可带 UTM</t>
+  </si>
+  <si>
+    <t>领奖后点击打开的外部链接，可带 UTM</t>
+  </si>
+  <si>
+    <t>打开校验方式；当前合法值见 ELinkTreeOpenCheckType</t>
+  </si>
+  <si>
+    <t>奖励类型；当前合法值见 ELinkTreeRewardType</t>
+  </si>
+  <si>
+    <t>RewardType=FixedItem 时发放的 Item.Id；不用填 0</t>
+  </si>
+  <si>
+    <t>RewardType=FixedChips 时发放的固定筹码数；不用填 0</t>
+  </si>
+  <si>
+    <t>RewardType=SequentialPack 时关联的顺序礼包 ID；当前不用填 0</t>
+  </si>
+  <si>
+    <t>未来 Steam 库存发奖/领取标记的 itemdef id；当前填 0</t>
+  </si>
+  <si>
+    <t>每个玩家最多领取次数；常规填 1</t>
+  </si>
+  <si>
+    <t>入口ID</t>
+  </si>
+  <si>
+    <t>机器名</t>
+  </si>
+  <si>
+    <t>排序</t>
+  </si>
+  <si>
+    <t>启用</t>
+  </si>
+  <si>
+    <t>提示文本Key</t>
+  </si>
+  <si>
+    <t>Banner图片</t>
+  </si>
+  <si>
+    <t>角标图片</t>
+  </si>
+  <si>
+    <t>领奖前链接</t>
+  </si>
+  <si>
+    <t>领奖后链接</t>
+  </si>
+  <si>
+    <t>打开校验</t>
+  </si>
+  <si>
+    <t>奖励类型</t>
+  </si>
+  <si>
+    <t>奖励道具ID</t>
+  </si>
+  <si>
+    <t>奖励筹码</t>
+  </si>
+  <si>
+    <t>顺序礼包ID</t>
+  </si>
+  <si>
+    <t>Steam奖励定义ID</t>
+  </si>
+  <si>
+    <t>领取次数上限</t>
+  </si>
+  <si>
+    <t>TwitterFollow</t>
+  </si>
+  <si>
+    <t>Twitter</t>
+  </si>
+  <si>
+    <t>UI/LinkTree/Banner_Twitter.png</t>
+  </si>
+  <si>
+    <t>UI/LinkTree/Icon_Gift.svg</t>
+  </si>
+  <si>
+    <t>https://x.com/intent/follow?screen_name=LuckyDogRise</t>
+  </si>
+  <si>
+    <t>https://x.com/LuckyDogRise</t>
+  </si>
+  <si>
+    <t>ShellOpenOk</t>
+  </si>
+  <si>
+    <t>FixedItem</t>
+  </si>
+  <si>
+    <t>SteamCommunity</t>
+  </si>
+  <si>
+    <t>Steam Community</t>
+  </si>
+  <si>
+    <t>UI/LinkTree/Banner_SteamCommunity.png</t>
+  </si>
+  <si>
+    <t>https://steamcommunity.com/app/2583700</t>
+  </si>
+  <si>
+    <t>FixedChips</t>
+  </si>
+  <si>
+    <t>SteamStore</t>
+  </si>
+  <si>
+    <t>Steam Store</t>
+  </si>
+  <si>
+    <t>UI/LinkTree/Banner_SteamStore.png</t>
+  </si>
+  <si>
+    <t>https://store.steampowered.com/app/2583700?utm_source=linktree&amp;utm_medium=in_game_client&amp;utm_campaign=linktree_pre_claim</t>
+  </si>
+  <si>
+    <t>https://store.steampowered.com/app/2583700?utm_source=linktree&amp;utm_medium=in_game_client&amp;utm_campaign=linktree_post_claim</t>
+  </si>
+  <si>
+    <t>XiaohongshuProfile</t>
+  </si>
+  <si>
+    <t>Xiaohongshu</t>
+  </si>
+  <si>
+    <t>UI/LinkTree/Banner_Xiaohongshu.png</t>
+  </si>
+  <si>
+    <t>https://www.xiaohongshu.com/user/profile/647bc1b5000000001001f13a</t>
   </si>
 </sst>
 </file>
@@ -3078,16 +3141,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3105,7 +3162,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3689,11 +3752,11 @@
     <col min="16" max="16" width="16.5833333333333" customWidth="1"/>
     <col min="17" max="17" width="20.9166666666667" customWidth="1"/>
     <col min="18" max="18" width="14.75" customWidth="1"/>
-    <col min="19" max="19" width="5.08333333333333" style="2" customWidth="1"/>
+    <col min="19" max="19" width="5.08333333333333" style="9" customWidth="1"/>
     <col min="20" max="20" width="44" customWidth="1"/>
     <col min="21" max="21" width="48.5833333333333" customWidth="1"/>
     <col min="22" max="22" width="15.4166666666667" customWidth="1"/>
-    <col min="23" max="23" width="7" style="2" customWidth="1"/>
+    <col min="23" max="23" width="7" style="9" customWidth="1"/>
     <col min="24" max="24" width="15.1666666666667" customWidth="1"/>
     <col min="25" max="25" width="10.5833333333333" customWidth="1"/>
     <col min="26" max="26" width="11.6666666666667" customWidth="1"/>
@@ -3708,16 +3771,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
+      <c r="D1" s="2"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -3804,16 +3867,16 @@
       </c>
     </row>
     <row r="2" spans="1:34">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="2"/>
       <c r="E2" t="s">
         <v>34</v>
       </c>
@@ -3900,12 +3963,12 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="121.8" spans="1:34">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -3920,7 +3983,7 @@
       <c r="J3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="10"/>
       <c r="M3" s="1" t="s">
         <v>47</v>
       </c>
@@ -3933,14 +3996,14 @@
       <c r="R3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="S3" s="5"/>
+      <c r="S3" s="11"/>
       <c r="T3" s="1" t="s">
         <v>51</v>
       </c>
       <c r="U3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="5"/>
+      <c r="W3" s="11"/>
       <c r="X3" s="1" t="s">
         <v>53</v>
       </c>
@@ -3976,16 +4039,16 @@
       </c>
     </row>
     <row r="4" spans="1:34">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E4" t="s">
@@ -4604,10 +4667,10 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="7">
         <v>100</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="7">
         <v>200</v>
       </c>
       <c r="T12" t="s">
@@ -5322,7 +5385,7 @@
       <c r="R23" t="s">
         <v>162</v>
       </c>
-      <c r="S23" s="2" t="s">
+      <c r="S23" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T23" t="s">
@@ -5680,7 +5743,7 @@
       <c r="R28" t="s">
         <v>162</v>
       </c>
-      <c r="S28" s="2" t="s">
+      <c r="S28" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T28" t="s">
@@ -5692,7 +5755,7 @@
       <c r="V28" t="s">
         <v>162</v>
       </c>
-      <c r="W28" s="2" t="s">
+      <c r="W28" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X28">
@@ -5784,7 +5847,7 @@
       <c r="R29" t="s">
         <v>162</v>
       </c>
-      <c r="S29" s="2" t="s">
+      <c r="S29" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T29" t="s">
@@ -5796,7 +5859,7 @@
       <c r="V29" t="s">
         <v>162</v>
       </c>
-      <c r="W29" s="2" t="s">
+      <c r="W29" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X29">
@@ -7195,7 +7258,7 @@
       <c r="R49" t="s">
         <v>162</v>
       </c>
-      <c r="S49" s="2" t="s">
+      <c r="S49" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T49" t="s">
@@ -7278,7 +7341,7 @@
       <c r="R50" t="s">
         <v>162</v>
       </c>
-      <c r="S50" s="2" t="s">
+      <c r="S50" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T50" t="s">
@@ -7361,7 +7424,7 @@
       <c r="R51" t="s">
         <v>162</v>
       </c>
-      <c r="S51" s="2" t="s">
+      <c r="S51" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T51" t="s">
@@ -7444,7 +7507,7 @@
       <c r="R52" t="s">
         <v>162</v>
       </c>
-      <c r="S52" s="2" t="s">
+      <c r="S52" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T52" t="s">
@@ -7527,7 +7590,7 @@
       <c r="R53" t="s">
         <v>162</v>
       </c>
-      <c r="S53" s="2" t="s">
+      <c r="S53" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T53" t="s">
@@ -7610,7 +7673,7 @@
       <c r="R54" t="s">
         <v>162</v>
       </c>
-      <c r="S54" s="2" t="s">
+      <c r="S54" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T54" t="s">
@@ -7693,7 +7756,7 @@
       <c r="R55" t="s">
         <v>162</v>
       </c>
-      <c r="S55" s="2" t="s">
+      <c r="S55" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T55" t="s">
@@ -7776,7 +7839,7 @@
       <c r="R56" t="s">
         <v>162</v>
       </c>
-      <c r="S56" s="2" t="s">
+      <c r="S56" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T56" t="s">
@@ -7859,7 +7922,7 @@
       <c r="R57" t="s">
         <v>162</v>
       </c>
-      <c r="S57" s="2" t="s">
+      <c r="S57" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T57" t="s">
@@ -7942,7 +8005,7 @@
       <c r="R58" t="s">
         <v>162</v>
       </c>
-      <c r="S58" s="2" t="s">
+      <c r="S58" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T58" t="s">
@@ -8025,7 +8088,7 @@
       <c r="R59" t="s">
         <v>162</v>
       </c>
-      <c r="S59" s="2" t="s">
+      <c r="S59" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T59" t="s">
@@ -8273,7 +8336,7 @@
       <c r="E63" t="s">
         <v>316</v>
       </c>
-      <c r="H63" s="9" t="s">
+      <c r="H63" s="7" t="s">
         <v>92</v>
       </c>
       <c r="I63">
@@ -8341,7 +8404,7 @@
       <c r="E64" t="s">
         <v>316</v>
       </c>
-      <c r="H64" s="9" t="s">
+      <c r="H64" s="7" t="s">
         <v>121</v>
       </c>
       <c r="I64">
@@ -8409,7 +8472,7 @@
       <c r="E65" t="s">
         <v>316</v>
       </c>
-      <c r="H65" s="9" t="s">
+      <c r="H65" s="7" t="s">
         <v>121</v>
       </c>
       <c r="I65">
@@ -8584,7 +8647,7 @@
       <c r="R67" t="s">
         <v>162</v>
       </c>
-      <c r="S67" s="2" t="s">
+      <c r="S67" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T67" t="s">
@@ -8667,7 +8730,7 @@
       <c r="R68" t="s">
         <v>162</v>
       </c>
-      <c r="S68" s="2" t="s">
+      <c r="S68" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T68" t="s">
@@ -8750,7 +8813,7 @@
       <c r="R69" t="s">
         <v>162</v>
       </c>
-      <c r="S69" s="2" t="s">
+      <c r="S69" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T69" t="s">
@@ -8833,7 +8896,7 @@
       <c r="R70" t="s">
         <v>162</v>
       </c>
-      <c r="S70" s="2" t="s">
+      <c r="S70" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T70" t="s">
@@ -8916,7 +8979,7 @@
       <c r="R71" t="s">
         <v>162</v>
       </c>
-      <c r="S71" s="2" t="s">
+      <c r="S71" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T71" t="s">
@@ -8999,7 +9062,7 @@
       <c r="R72" t="s">
         <v>162</v>
       </c>
-      <c r="S72" s="2" t="s">
+      <c r="S72" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T72" t="s">
@@ -9082,7 +9145,7 @@
       <c r="R73" t="s">
         <v>162</v>
       </c>
-      <c r="S73" s="2" t="s">
+      <c r="S73" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T73" t="s">
@@ -9165,7 +9228,7 @@
       <c r="R74" t="s">
         <v>162</v>
       </c>
-      <c r="S74" s="2" t="s">
+      <c r="S74" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T74" t="s">
@@ -9248,7 +9311,7 @@
       <c r="R75" t="s">
         <v>162</v>
       </c>
-      <c r="S75" s="2" t="s">
+      <c r="S75" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T75" t="s">
@@ -9331,7 +9394,7 @@
       <c r="R76" t="s">
         <v>162</v>
       </c>
-      <c r="S76" s="2" t="s">
+      <c r="S76" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T76" t="s">
@@ -9485,7 +9548,7 @@
       <c r="R78" t="s">
         <v>162</v>
       </c>
-      <c r="S78" s="2" t="s">
+      <c r="S78" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T78" t="s">
@@ -9497,7 +9560,7 @@
       <c r="V78" t="s">
         <v>162</v>
       </c>
-      <c r="W78" s="2" t="s">
+      <c r="W78" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X78">
@@ -9586,7 +9649,7 @@
       <c r="R79" t="s">
         <v>162</v>
       </c>
-      <c r="S79" s="2" t="s">
+      <c r="S79" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T79" t="s">
@@ -9636,7 +9699,7 @@
       <c r="G80" t="s">
         <v>162</v>
       </c>
-      <c r="H80" s="9" t="s">
+      <c r="H80" s="7" t="s">
         <v>121</v>
       </c>
       <c r="I80">
@@ -9669,7 +9732,7 @@
       <c r="R80" t="s">
         <v>162</v>
       </c>
-      <c r="S80" s="2" t="s">
+      <c r="S80" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T80" t="s">
@@ -9752,7 +9815,7 @@
       <c r="R81" t="s">
         <v>162</v>
       </c>
-      <c r="S81" s="2" t="s">
+      <c r="S81" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T81" t="s">
@@ -9835,7 +9898,7 @@
       <c r="R82" t="s">
         <v>162</v>
       </c>
-      <c r="S82" s="2" t="s">
+      <c r="S82" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T82" t="s">
@@ -9918,7 +9981,7 @@
       <c r="R83" t="s">
         <v>162</v>
       </c>
-      <c r="S83" s="2" t="s">
+      <c r="S83" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T83" t="s">
@@ -9968,7 +10031,7 @@
       <c r="G84" t="s">
         <v>162</v>
       </c>
-      <c r="H84" s="9" t="s">
+      <c r="H84" s="7" t="s">
         <v>141</v>
       </c>
       <c r="I84">
@@ -10001,7 +10064,7 @@
       <c r="R84" t="s">
         <v>162</v>
       </c>
-      <c r="S84" s="2" t="s">
+      <c r="S84" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T84" t="s">
@@ -10084,7 +10147,7 @@
       <c r="R85" t="s">
         <v>162</v>
       </c>
-      <c r="S85" s="2" t="s">
+      <c r="S85" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T85" t="s">
@@ -10167,7 +10230,7 @@
       <c r="R86" t="s">
         <v>162</v>
       </c>
-      <c r="S86" s="2" t="s">
+      <c r="S86" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T86" t="s">
@@ -10457,7 +10520,7 @@
       <c r="R90" t="s">
         <v>162</v>
       </c>
-      <c r="S90" s="2" t="s">
+      <c r="S90" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T90" t="s">
@@ -10469,7 +10532,7 @@
       <c r="V90" t="s">
         <v>162</v>
       </c>
-      <c r="W90" s="2" t="s">
+      <c r="W90" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X90">
@@ -10561,7 +10624,7 @@
       <c r="R91" t="s">
         <v>162</v>
       </c>
-      <c r="S91" s="2" t="s">
+      <c r="S91" s="9" t="s">
         <v>162</v>
       </c>
       <c r="T91" t="s">
@@ -10573,7 +10636,7 @@
       <c r="V91" t="s">
         <v>162</v>
       </c>
-      <c r="W91" s="2" t="s">
+      <c r="W91" s="9" t="s">
         <v>162</v>
       </c>
       <c r="X91">
@@ -10736,7 +10799,7 @@
       <c r="U93" t="s">
         <v>455</v>
       </c>
-      <c r="W93" s="2" t="s">
+      <c r="W93" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X93">
@@ -10816,7 +10879,7 @@
       <c r="U94" t="s">
         <v>460</v>
       </c>
-      <c r="W94" s="2" t="s">
+      <c r="W94" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X94">
@@ -10896,7 +10959,7 @@
       <c r="U95" t="s">
         <v>464</v>
       </c>
-      <c r="W95" s="2" t="s">
+      <c r="W95" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X95">
@@ -10976,7 +11039,7 @@
       <c r="U96" t="s">
         <v>468</v>
       </c>
-      <c r="W96" s="2" t="s">
+      <c r="W96" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X96">
@@ -11056,7 +11119,7 @@
       <c r="U97" t="s">
         <v>472</v>
       </c>
-      <c r="W97" s="2" t="s">
+      <c r="W97" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X97">
@@ -11136,7 +11199,7 @@
       <c r="U98" t="s">
         <v>476</v>
       </c>
-      <c r="W98" s="2" t="s">
+      <c r="W98" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X98">
@@ -11216,7 +11279,7 @@
       <c r="U99" t="s">
         <v>480</v>
       </c>
-      <c r="W99" s="2" t="s">
+      <c r="W99" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X99">
@@ -11290,7 +11353,7 @@
       <c r="U100" t="s">
         <v>484</v>
       </c>
-      <c r="W100" s="2" t="s">
+      <c r="W100" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X100">
@@ -11447,7 +11510,7 @@
       <c r="U102" t="s">
         <v>492</v>
       </c>
-      <c r="W102" s="2" t="s">
+      <c r="W102" s="9" t="s">
         <v>456</v>
       </c>
       <c r="X102">
@@ -11586,7 +11649,7 @@
       <c r="U104" t="s">
         <v>502</v>
       </c>
-      <c r="W104" s="2" t="s">
+      <c r="W104" s="9" t="s">
         <v>503</v>
       </c>
       <c r="X104">
@@ -11719,14 +11782,14 @@
       <c r="R106">
         <v>100</v>
       </c>
-      <c r="S106" s="2"/>
+      <c r="S106" s="9"/>
       <c r="T106" t="s">
         <v>158</v>
       </c>
       <c r="U106" t="s">
         <v>159</v>
       </c>
-      <c r="W106" s="2" t="s">
+      <c r="W106" s="9" t="s">
         <v>510</v>
       </c>
       <c r="X106">
@@ -11788,7 +11851,7 @@
       <c r="R107">
         <v>100</v>
       </c>
-      <c r="S107" s="2"/>
+      <c r="S107" s="9"/>
       <c r="T107" t="s">
         <v>111</v>
       </c>
@@ -11798,7 +11861,7 @@
       <c r="V107">
         <v>1012</v>
       </c>
-      <c r="W107" s="2" t="s">
+      <c r="W107" s="9" t="s">
         <v>510</v>
       </c>
       <c r="X107">
@@ -11860,3251 +11923,437 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P100"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
-    <col min="2" max="2" width="6.25" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="20.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.1666666666667" customWidth="1"/>
-    <col min="6" max="6" width="10.5833333333333" customWidth="1"/>
-    <col min="7" max="7" width="11.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="7.83333333333333" customWidth="1"/>
-    <col min="9" max="9" width="10.4166666666667" customWidth="1"/>
-    <col min="10" max="10" width="7.41666666666667" customWidth="1"/>
-    <col min="11" max="11" width="11.3333333333333" customWidth="1"/>
-    <col min="12" max="12" width="7.41666666666667" customWidth="1"/>
-    <col min="13" max="13" width="5.41666666666667" customWidth="1"/>
-    <col min="14" max="14" width="5.66666666666667" customWidth="1"/>
-    <col min="15" max="15" width="5.91666666666667" customWidth="1"/>
-    <col min="16" max="16" width="3.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.83333333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.4166666666667" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="10.75" customWidth="1"/>
+    <col min="6" max="6" width="16.8333333333333" customWidth="1"/>
+    <col min="7" max="7" width="36.75" customWidth="1"/>
+    <col min="8" max="8" width="22.75" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="13.0833333333333" customWidth="1"/>
+    <col min="11" max="11" width="21.3333333333333" customWidth="1"/>
+    <col min="12" max="12" width="21.6666666666667" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="15.6666666666667" customWidth="1"/>
+    <col min="15" max="15" width="20.0833333333333" customWidth="1"/>
+    <col min="16" max="17" width="22.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3"/>
+    <row r="1" spans="1:17">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>751</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>598</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>752</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
+        <v>753</v>
       </c>
       <c r="H1" t="s">
-        <v>23</v>
+        <v>754</v>
       </c>
       <c r="I1" t="s">
-        <v>24</v>
+        <v>755</v>
       </c>
       <c r="J1" t="s">
-        <v>25</v>
+        <v>756</v>
       </c>
       <c r="K1" t="s">
-        <v>26</v>
+        <v>757</v>
       </c>
       <c r="L1" t="s">
-        <v>27</v>
+        <v>758</v>
       </c>
       <c r="M1" t="s">
-        <v>28</v>
+        <v>759</v>
       </c>
       <c r="N1" t="s">
-        <v>29</v>
+        <v>760</v>
       </c>
       <c r="O1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="P1" t="s">
+        <v>762</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
       <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
+        <v>764</v>
+      </c>
+      <c r="L2" t="s">
+        <v>765</v>
+      </c>
+      <c r="M2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" t="s">
-        <v>33</v>
-      </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="72" customHeight="1" spans="1:16">
-      <c r="A3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="77" customHeight="1" spans="1:17">
+      <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>42</v>
+      <c r="B3" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>767</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>768</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>54</v>
+        <v>769</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>55</v>
+        <v>770</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>56</v>
+        <v>771</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>56</v>
+        <v>772</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>57</v>
+        <v>773</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>58</v>
+        <v>774</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>59</v>
+        <v>775</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>59</v>
+        <v>776</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>59</v>
+        <v>777</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P3" s="5"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>62</v>
+      <c r="B4" t="s">
+        <v>781</v>
+      </c>
+      <c r="C4" t="s">
+        <v>782</v>
+      </c>
+      <c r="D4" t="s">
+        <v>783</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>784</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>785</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
+        <v>786</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>787</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>788</v>
       </c>
       <c r="J4" t="s">
-        <v>83</v>
+        <v>789</v>
       </c>
       <c r="K4" t="s">
-        <v>84</v>
+        <v>790</v>
       </c>
       <c r="L4" t="s">
-        <v>85</v>
+        <v>791</v>
       </c>
       <c r="M4" t="s">
-        <v>86</v>
+        <v>792</v>
       </c>
       <c r="N4" t="s">
-        <v>87</v>
+        <v>793</v>
       </c>
       <c r="O4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>794</v>
+      </c>
+      <c r="P4" t="s">
+        <v>795</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
+        <v>797</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>798</v>
+      </c>
+      <c r="G5" t="s">
+        <v>799</v>
+      </c>
+      <c r="H5" t="s">
+        <v>800</v>
+      </c>
+      <c r="I5" t="s">
+        <v>801</v>
+      </c>
+      <c r="J5" t="s">
+        <v>802</v>
+      </c>
+      <c r="K5" t="s">
+        <v>803</v>
+      </c>
+      <c r="L5" t="s">
+        <v>804</v>
+      </c>
+      <c r="M5">
+        <v>92005</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
+        <v>805</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>806</v>
+      </c>
+      <c r="G6" t="s">
+        <v>807</v>
+      </c>
+      <c r="H6" t="s">
+        <v>800</v>
+      </c>
+      <c r="I6" t="s">
+        <v>808</v>
+      </c>
+      <c r="J6" t="s">
+        <v>808</v>
+      </c>
+      <c r="K6" t="s">
+        <v>803</v>
+      </c>
+      <c r="L6" t="s">
+        <v>809</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>2500</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
+        <v>810</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>811</v>
+      </c>
+      <c r="G7" t="s">
+        <v>812</v>
+      </c>
+      <c r="H7" t="s">
+        <v>800</v>
+      </c>
+      <c r="I7" t="s">
+        <v>813</v>
+      </c>
+      <c r="J7" t="s">
+        <v>814</v>
+      </c>
+      <c r="K7" t="s">
+        <v>803</v>
+      </c>
+      <c r="L7" t="s">
+        <v>809</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>2500</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
+        <v>815</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="B9">
-        <v>1005</v>
-      </c>
-      <c r="C9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="B10">
-        <v>1006</v>
-      </c>
-      <c r="C10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="s">
-        <v>96</v>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="B11">
-        <v>1007</v>
-      </c>
-      <c r="C11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="B12">
-        <v>1008</v>
-      </c>
-      <c r="C12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="B13">
-        <v>1009</v>
-      </c>
-      <c r="C13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13" t="s">
-        <v>96</v>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="B14">
-        <v>1010</v>
-      </c>
-      <c r="C14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="B15">
-        <v>1011</v>
-      </c>
-      <c r="C15" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" t="s">
-        <v>751</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15" t="s">
-        <v>96</v>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="B16">
-        <v>1012</v>
-      </c>
-      <c r="C16" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" t="s">
-        <v>752</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" t="s">
-        <v>96</v>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="B18">
-        <v>2001</v>
-      </c>
-      <c r="C18" t="s">
-        <v>138</v>
-      </c>
-      <c r="D18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="B19">
-        <v>2002</v>
-      </c>
-      <c r="C19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D19" t="s">
-        <v>145</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" t="s">
-        <v>96</v>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="B20">
-        <v>2003</v>
-      </c>
-      <c r="C20" t="s">
-        <v>148</v>
-      </c>
-      <c r="D20" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" t="s">
-        <v>96</v>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="B21">
-        <v>2004</v>
-      </c>
-      <c r="C21" t="s">
-        <v>152</v>
-      </c>
-      <c r="D21" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="B22">
-        <v>2005</v>
-      </c>
-      <c r="C22" t="s">
-        <v>156</v>
-      </c>
-      <c r="D22" t="s">
-        <v>157</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="B23">
-        <v>2006</v>
-      </c>
-      <c r="C23" t="s">
-        <v>753</v>
-      </c>
-      <c r="D23" t="s">
-        <v>161</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="B24">
-        <v>2007</v>
-      </c>
-      <c r="C24" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" t="s">
-        <v>166</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" t="s">
-        <v>96</v>
-      </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="B25">
-        <v>2008</v>
-      </c>
-      <c r="C25" t="s">
-        <v>169</v>
-      </c>
-      <c r="D25" t="s">
-        <v>170</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25" t="s">
-        <v>96</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="B26">
-        <v>2009</v>
-      </c>
-      <c r="C26" t="s">
-        <v>173</v>
-      </c>
-      <c r="D26" t="s">
-        <v>174</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26" t="s">
-        <v>96</v>
-      </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="B27">
-        <v>2010</v>
-      </c>
-      <c r="C27" t="s">
-        <v>177</v>
-      </c>
-      <c r="D27" t="s">
-        <v>178</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27" t="s">
-        <v>96</v>
-      </c>
-      <c r="G27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="B28">
-        <v>3001</v>
-      </c>
-      <c r="C28" t="s">
-        <v>189</v>
-      </c>
-      <c r="D28" t="s">
-        <v>190</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28" t="s">
-        <v>96</v>
-      </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="B29">
-        <v>3002</v>
-      </c>
-      <c r="C29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D29" t="s">
-        <v>195</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" t="s">
-        <v>96</v>
-      </c>
-      <c r="G29" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="B30">
-        <v>3003</v>
-      </c>
-      <c r="C30" t="s">
-        <v>198</v>
-      </c>
-      <c r="D30" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30" t="s">
-        <v>96</v>
-      </c>
-      <c r="G30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="B31">
-        <v>3004</v>
-      </c>
-      <c r="C31" t="s">
-        <v>202</v>
-      </c>
-      <c r="D31" t="s">
-        <v>203</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31" t="s">
-        <v>96</v>
-      </c>
-      <c r="G31" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="B32">
-        <v>3005</v>
-      </c>
-      <c r="C32" t="s">
-        <v>206</v>
-      </c>
-      <c r="D32" t="s">
-        <v>207</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32" t="s">
-        <v>96</v>
-      </c>
-      <c r="G32" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11">
-      <c r="B33">
-        <v>4001</v>
-      </c>
-      <c r="C33" t="s">
-        <v>754</v>
-      </c>
-      <c r="D33" t="s">
-        <v>755</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33" t="s">
-        <v>96</v>
-      </c>
-      <c r="G33" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
-      <c r="B34">
-        <v>4002</v>
-      </c>
-      <c r="C34" t="s">
-        <v>756</v>
-      </c>
-      <c r="D34" t="s">
-        <v>757</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34" t="s">
-        <v>96</v>
-      </c>
-      <c r="G34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="B35">
-        <v>4003</v>
-      </c>
-      <c r="C35" t="s">
-        <v>758</v>
-      </c>
-      <c r="D35" t="s">
-        <v>759</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35" t="s">
-        <v>96</v>
-      </c>
-      <c r="G35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11">
-      <c r="B36">
-        <v>4004</v>
-      </c>
-      <c r="C36" t="s">
-        <v>760</v>
-      </c>
-      <c r="D36" t="s">
-        <v>761</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36" t="s">
-        <v>96</v>
-      </c>
-      <c r="G36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11">
-      <c r="B37">
-        <v>5001</v>
-      </c>
-      <c r="C37" t="s">
-        <v>236</v>
-      </c>
-      <c r="D37" t="s">
-        <v>237</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37" t="s">
-        <v>96</v>
-      </c>
-      <c r="G37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11">
-      <c r="B38">
-        <v>5002</v>
-      </c>
-      <c r="C38" t="s">
-        <v>241</v>
-      </c>
-      <c r="D38" t="s">
-        <v>242</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38" t="s">
-        <v>96</v>
-      </c>
-      <c r="G38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11">
-      <c r="B39">
-        <v>5003</v>
-      </c>
-      <c r="C39" t="s">
-        <v>245</v>
-      </c>
-      <c r="D39" t="s">
-        <v>246</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39" t="s">
-        <v>96</v>
-      </c>
-      <c r="G39" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11">
-      <c r="B40">
-        <v>5004</v>
-      </c>
-      <c r="C40" t="s">
-        <v>249</v>
-      </c>
-      <c r="D40" t="s">
-        <v>250</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40" t="s">
-        <v>96</v>
-      </c>
-      <c r="G40" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" t="b">
-        <v>0</v>
-      </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11">
-      <c r="B41">
-        <v>5005</v>
-      </c>
-      <c r="C41" t="s">
-        <v>253</v>
-      </c>
-      <c r="D41" t="s">
-        <v>254</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41" t="s">
-        <v>96</v>
-      </c>
-      <c r="G41" t="b">
-        <v>1</v>
-      </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" t="b">
-        <v>0</v>
-      </c>
-      <c r="K41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
-      <c r="B42">
-        <v>5006</v>
-      </c>
-      <c r="C42" t="s">
-        <v>257</v>
-      </c>
-      <c r="D42" t="s">
-        <v>258</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42" t="s">
-        <v>96</v>
-      </c>
-      <c r="G42" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" t="b">
-        <v>0</v>
-      </c>
-      <c r="I42" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" t="b">
-        <v>0</v>
-      </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11">
-      <c r="B43">
-        <v>5007</v>
-      </c>
-      <c r="C43" t="s">
-        <v>261</v>
-      </c>
-      <c r="D43" t="s">
-        <v>262</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43" t="s">
-        <v>96</v>
-      </c>
-      <c r="G43" t="b">
-        <v>1</v>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
-      </c>
-      <c r="I43" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11">
-      <c r="B44">
-        <v>5008</v>
-      </c>
-      <c r="C44" t="s">
-        <v>265</v>
-      </c>
-      <c r="D44" t="s">
-        <v>266</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44" t="s">
-        <v>96</v>
-      </c>
-      <c r="G44" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" t="b">
-        <v>0</v>
-      </c>
-      <c r="I44" t="b">
-        <v>0</v>
-      </c>
-      <c r="J44" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11">
-      <c r="B45">
-        <v>6001</v>
-      </c>
-      <c r="C45" t="s">
-        <v>269</v>
-      </c>
-      <c r="D45" t="s">
-        <v>270</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45" t="s">
-        <v>96</v>
-      </c>
-      <c r="G45" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" t="b">
-        <v>0</v>
-      </c>
-      <c r="K45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11">
-      <c r="B46">
-        <v>6002</v>
-      </c>
-      <c r="C46" t="s">
-        <v>762</v>
-      </c>
-      <c r="D46" t="s">
-        <v>763</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46" t="s">
-        <v>96</v>
-      </c>
-      <c r="G46" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46" t="b">
-        <v>0</v>
-      </c>
-      <c r="I46" t="b">
-        <v>0</v>
-      </c>
-      <c r="J46" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11">
-      <c r="B47">
-        <v>6003</v>
-      </c>
-      <c r="C47" t="s">
-        <v>764</v>
-      </c>
-      <c r="D47" t="s">
-        <v>765</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47" t="s">
-        <v>96</v>
-      </c>
-      <c r="G47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11">
-      <c r="B48">
-        <v>6004</v>
-      </c>
-      <c r="C48" t="s">
-        <v>766</v>
-      </c>
-      <c r="D48" t="s">
-        <v>767</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48" t="s">
-        <v>96</v>
-      </c>
-      <c r="G48" t="b">
-        <v>1</v>
-      </c>
-      <c r="H48" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11">
-      <c r="B49">
-        <v>6005</v>
-      </c>
-      <c r="C49" t="s">
-        <v>768</v>
-      </c>
-      <c r="D49" t="s">
-        <v>769</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49" t="s">
-        <v>96</v>
-      </c>
-      <c r="G49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H49" t="b">
-        <v>0</v>
-      </c>
-      <c r="I49" t="b">
-        <v>0</v>
-      </c>
-      <c r="J49" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11">
-      <c r="B50">
-        <v>6006</v>
-      </c>
-      <c r="C50" t="s">
-        <v>770</v>
-      </c>
-      <c r="D50" t="s">
-        <v>771</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50" t="s">
-        <v>96</v>
-      </c>
-      <c r="G50" t="b">
-        <v>1</v>
-      </c>
-      <c r="H50" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11">
-      <c r="B51">
-        <v>6007</v>
-      </c>
-      <c r="C51" t="s">
-        <v>772</v>
-      </c>
-      <c r="D51" t="s">
-        <v>773</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51" t="s">
-        <v>96</v>
-      </c>
-      <c r="G51" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" t="b">
-        <v>0</v>
-      </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11">
-      <c r="B52">
-        <v>6008</v>
-      </c>
-      <c r="C52" t="s">
-        <v>774</v>
-      </c>
-      <c r="D52" t="s">
-        <v>775</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52" t="s">
-        <v>96</v>
-      </c>
-      <c r="G52" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" t="b">
-        <v>0</v>
-      </c>
-      <c r="I52" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11">
-      <c r="B53">
-        <v>6009</v>
-      </c>
-      <c r="C53" t="s">
-        <v>776</v>
-      </c>
-      <c r="D53" t="s">
-        <v>777</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53" t="s">
-        <v>96</v>
-      </c>
-      <c r="G53" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" t="b">
-        <v>0</v>
-      </c>
-      <c r="I53" t="b">
-        <v>0</v>
-      </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11">
-      <c r="B54">
-        <v>6010</v>
-      </c>
-      <c r="C54" t="s">
-        <v>778</v>
-      </c>
-      <c r="D54" t="s">
-        <v>779</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54" t="s">
-        <v>96</v>
-      </c>
-      <c r="G54" t="b">
-        <v>1</v>
-      </c>
-      <c r="H54" t="b">
-        <v>0</v>
-      </c>
-      <c r="I54" t="b">
-        <v>0</v>
-      </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
-      <c r="B55">
-        <v>6011</v>
-      </c>
-      <c r="C55" t="s">
-        <v>780</v>
-      </c>
-      <c r="D55" t="s">
-        <v>781</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55" t="s">
-        <v>96</v>
-      </c>
-      <c r="G55" t="b">
-        <v>1</v>
-      </c>
-      <c r="H55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I55" t="b">
-        <v>0</v>
-      </c>
-      <c r="J55" t="b">
-        <v>0</v>
-      </c>
-      <c r="K55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
-      <c r="B56">
-        <v>7001</v>
-      </c>
-      <c r="C56" t="s">
-        <v>314</v>
-      </c>
-      <c r="D56" t="s">
-        <v>315</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56" t="s">
-        <v>96</v>
-      </c>
-      <c r="G56" t="b">
-        <v>1</v>
-      </c>
-      <c r="H56" t="b">
-        <v>0</v>
-      </c>
-      <c r="I56" t="b">
-        <v>0</v>
-      </c>
-      <c r="J56" t="b">
-        <v>0</v>
-      </c>
-      <c r="K56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="B57">
-        <v>7002</v>
-      </c>
-      <c r="C57" t="s">
-        <v>319</v>
-      </c>
-      <c r="D57" t="s">
-        <v>320</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57" t="s">
-        <v>96</v>
-      </c>
-      <c r="G57" t="b">
-        <v>1</v>
-      </c>
-      <c r="H57" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57" t="b">
-        <v>0</v>
-      </c>
-      <c r="J57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11">
-      <c r="B58">
-        <v>7003</v>
-      </c>
-      <c r="C58" t="s">
-        <v>323</v>
-      </c>
-      <c r="D58" t="s">
-        <v>324</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58" t="s">
-        <v>96</v>
-      </c>
-      <c r="G58" t="b">
-        <v>1</v>
-      </c>
-      <c r="H58" t="b">
-        <v>0</v>
-      </c>
-      <c r="I58" t="b">
-        <v>0</v>
-      </c>
-      <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11">
-      <c r="B59">
-        <v>7004</v>
-      </c>
-      <c r="C59" t="s">
-        <v>327</v>
-      </c>
-      <c r="D59" t="s">
-        <v>328</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59" t="s">
-        <v>96</v>
-      </c>
-      <c r="G59" t="b">
-        <v>1</v>
-      </c>
-      <c r="H59" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11">
-      <c r="B60">
-        <v>7005</v>
-      </c>
-      <c r="C60" t="s">
-        <v>331</v>
-      </c>
-      <c r="D60" t="s">
-        <v>332</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60" t="s">
-        <v>96</v>
-      </c>
-      <c r="G60" t="b">
-        <v>1</v>
-      </c>
-      <c r="H60" t="b">
-        <v>0</v>
-      </c>
-      <c r="I60" t="b">
-        <v>0</v>
-      </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="B61">
-        <v>7006</v>
-      </c>
-      <c r="C61" t="s">
-        <v>335</v>
-      </c>
-      <c r="D61" t="s">
-        <v>336</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="F61" t="s">
-        <v>96</v>
-      </c>
-      <c r="G61" t="b">
-        <v>1</v>
-      </c>
-      <c r="H61" t="b">
-        <v>0</v>
-      </c>
-      <c r="I61" t="b">
-        <v>0</v>
-      </c>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="B62">
-        <v>7007</v>
-      </c>
-      <c r="C62" t="s">
-        <v>339</v>
-      </c>
-      <c r="D62" t="s">
-        <v>340</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62" t="s">
-        <v>96</v>
-      </c>
-      <c r="G62" t="b">
-        <v>1</v>
-      </c>
-      <c r="H62" t="b">
-        <v>0</v>
-      </c>
-      <c r="I62" t="b">
-        <v>0</v>
-      </c>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="B63">
-        <v>7008</v>
-      </c>
-      <c r="C63" t="s">
-        <v>782</v>
-      </c>
-      <c r="D63" t="s">
-        <v>783</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63" t="s">
-        <v>96</v>
-      </c>
-      <c r="G63" t="b">
-        <v>1</v>
-      </c>
-      <c r="H63" t="b">
-        <v>0</v>
-      </c>
-      <c r="I63" t="b">
-        <v>0</v>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64">
-        <v>7009</v>
-      </c>
-      <c r="C64" t="s">
-        <v>347</v>
-      </c>
-      <c r="D64" t="s">
-        <v>348</v>
-      </c>
-      <c r="E64">
-        <v>0</v>
-      </c>
-      <c r="F64" t="s">
-        <v>96</v>
-      </c>
-      <c r="G64" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64" t="b">
-        <v>0</v>
-      </c>
-      <c r="I64" t="b">
-        <v>0</v>
-      </c>
-      <c r="J64" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11">
-      <c r="B65">
-        <v>7010</v>
-      </c>
-      <c r="C65" t="s">
-        <v>784</v>
-      </c>
-      <c r="D65" t="s">
-        <v>785</v>
-      </c>
-      <c r="E65">
-        <v>0</v>
-      </c>
-      <c r="F65" t="s">
-        <v>96</v>
-      </c>
-      <c r="G65" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65" t="b">
-        <v>0</v>
-      </c>
-      <c r="I65" t="b">
-        <v>0</v>
-      </c>
-      <c r="J65" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="B66">
-        <v>7011</v>
-      </c>
-      <c r="C66" t="s">
-        <v>355</v>
-      </c>
-      <c r="D66" t="s">
-        <v>356</v>
-      </c>
-      <c r="E66">
-        <v>0</v>
-      </c>
-      <c r="F66" t="s">
-        <v>96</v>
-      </c>
-      <c r="G66" t="b">
-        <v>1</v>
-      </c>
-      <c r="H66" t="b">
-        <v>0</v>
-      </c>
-      <c r="I66" t="b">
-        <v>0</v>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67">
-        <v>7012</v>
-      </c>
-      <c r="C67" t="s">
-        <v>786</v>
-      </c>
-      <c r="D67" t="s">
-        <v>787</v>
-      </c>
-      <c r="E67">
-        <v>0</v>
-      </c>
-      <c r="F67" t="s">
-        <v>96</v>
-      </c>
-      <c r="G67" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67" t="b">
-        <v>0</v>
-      </c>
-      <c r="I67" t="b">
-        <v>0</v>
-      </c>
-      <c r="J67" t="b">
-        <v>0</v>
-      </c>
-      <c r="K67" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="B68">
-        <v>7013</v>
-      </c>
-      <c r="C68" t="s">
-        <v>363</v>
-      </c>
-      <c r="D68" t="s">
-        <v>364</v>
-      </c>
-      <c r="E68">
-        <v>0</v>
-      </c>
-      <c r="F68" t="s">
-        <v>96</v>
-      </c>
-      <c r="G68" t="b">
-        <v>1</v>
-      </c>
-      <c r="H68" t="b">
-        <v>0</v>
-      </c>
-      <c r="I68" t="b">
-        <v>0</v>
-      </c>
-      <c r="J68" t="b">
-        <v>0</v>
-      </c>
-      <c r="K68" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11">
-      <c r="B69">
-        <v>7014</v>
-      </c>
-      <c r="C69" t="s">
-        <v>367</v>
-      </c>
-      <c r="D69" t="s">
-        <v>368</v>
-      </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-      <c r="F69" t="s">
-        <v>96</v>
-      </c>
-      <c r="G69" t="b">
-        <v>1</v>
-      </c>
-      <c r="H69" t="b">
-        <v>0</v>
-      </c>
-      <c r="I69" t="b">
-        <v>0</v>
-      </c>
-      <c r="J69" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11">
-      <c r="B70">
-        <v>7015</v>
-      </c>
-      <c r="C70" t="s">
-        <v>371</v>
-      </c>
-      <c r="D70" t="s">
-        <v>372</v>
-      </c>
-      <c r="E70">
-        <v>0</v>
-      </c>
-      <c r="F70" t="s">
-        <v>96</v>
-      </c>
-      <c r="G70" t="b">
-        <v>1</v>
-      </c>
-      <c r="H70" t="b">
-        <v>0</v>
-      </c>
-      <c r="I70" t="b">
-        <v>0</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11">
-      <c r="B71">
-        <v>7016</v>
-      </c>
-      <c r="C71" t="s">
-        <v>375</v>
-      </c>
-      <c r="D71" t="s">
-        <v>376</v>
-      </c>
-      <c r="E71">
-        <v>0</v>
-      </c>
-      <c r="F71" t="s">
-        <v>96</v>
-      </c>
-      <c r="G71" t="b">
-        <v>1</v>
-      </c>
-      <c r="H71" t="b">
-        <v>0</v>
-      </c>
-      <c r="I71" t="b">
-        <v>0</v>
-      </c>
-      <c r="J71" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72">
-        <v>7017</v>
-      </c>
-      <c r="C72" t="s">
-        <v>788</v>
-      </c>
-      <c r="D72" t="s">
-        <v>789</v>
-      </c>
-      <c r="E72">
-        <v>0</v>
-      </c>
-      <c r="F72" t="s">
-        <v>96</v>
-      </c>
-      <c r="G72" t="b">
-        <v>1</v>
-      </c>
-      <c r="H72" t="b">
-        <v>0</v>
-      </c>
-      <c r="I72" t="b">
-        <v>0</v>
-      </c>
-      <c r="J72" t="b">
-        <v>0</v>
-      </c>
-      <c r="K72" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11">
-      <c r="B73">
-        <v>7018</v>
-      </c>
-      <c r="C73" t="s">
-        <v>383</v>
-      </c>
-      <c r="D73" t="s">
-        <v>384</v>
-      </c>
-      <c r="E73">
-        <v>0</v>
-      </c>
-      <c r="F73" t="s">
-        <v>96</v>
-      </c>
-      <c r="G73" t="b">
-        <v>1</v>
-      </c>
-      <c r="H73" t="b">
-        <v>0</v>
-      </c>
-      <c r="I73" t="b">
-        <v>0</v>
-      </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11">
-      <c r="B74">
-        <v>8001</v>
-      </c>
-      <c r="C74" t="s">
-        <v>790</v>
-      </c>
-      <c r="D74" t="s">
-        <v>790</v>
-      </c>
-      <c r="E74">
-        <v>0</v>
-      </c>
-      <c r="F74" t="s">
-        <v>96</v>
-      </c>
-      <c r="G74" t="b">
-        <v>1</v>
-      </c>
-      <c r="H74" t="b">
-        <v>0</v>
-      </c>
-      <c r="I74" t="b">
-        <v>0</v>
-      </c>
-      <c r="J74" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11">
-      <c r="B75">
-        <v>8002</v>
-      </c>
-      <c r="C75" t="s">
-        <v>396</v>
-      </c>
-      <c r="D75" t="s">
-        <v>397</v>
-      </c>
-      <c r="E75">
-        <v>0</v>
-      </c>
-      <c r="F75" t="s">
-        <v>96</v>
-      </c>
-      <c r="G75" t="b">
-        <v>1</v>
-      </c>
-      <c r="H75" t="b">
-        <v>0</v>
-      </c>
-      <c r="I75" t="b">
-        <v>0</v>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76">
-        <v>8003</v>
-      </c>
-      <c r="C76" t="s">
-        <v>791</v>
-      </c>
-      <c r="D76" t="s">
-        <v>791</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76" t="s">
-        <v>96</v>
-      </c>
-      <c r="G76" t="b">
-        <v>1</v>
-      </c>
-      <c r="H76" t="b">
-        <v>0</v>
-      </c>
-      <c r="I76" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11">
-      <c r="B77">
-        <v>8004</v>
-      </c>
-      <c r="C77" t="s">
-        <v>792</v>
-      </c>
-      <c r="D77" t="s">
-        <v>406</v>
-      </c>
-      <c r="E77">
-        <v>0</v>
-      </c>
-      <c r="F77" t="s">
-        <v>96</v>
-      </c>
-      <c r="G77" t="b">
-        <v>1</v>
-      </c>
-      <c r="H77" t="b">
-        <v>0</v>
-      </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="B78">
-        <v>8005</v>
-      </c>
-      <c r="C78" t="s">
-        <v>793</v>
-      </c>
-      <c r="D78" t="s">
-        <v>410</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-      <c r="F78" t="s">
-        <v>96</v>
-      </c>
-      <c r="G78" t="b">
-        <v>1</v>
-      </c>
-      <c r="H78" t="b">
-        <v>0</v>
-      </c>
-      <c r="I78" t="b">
-        <v>0</v>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
-      <c r="B79">
-        <v>8006</v>
-      </c>
-      <c r="C79" t="s">
-        <v>413</v>
-      </c>
-      <c r="D79" t="s">
-        <v>414</v>
-      </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
-      <c r="F79" t="s">
-        <v>96</v>
-      </c>
-      <c r="G79" t="b">
-        <v>1</v>
-      </c>
-      <c r="H79" t="b">
-        <v>0</v>
-      </c>
-      <c r="I79" t="b">
-        <v>0</v>
-      </c>
-      <c r="J79" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11">
-      <c r="B80">
-        <v>8007</v>
-      </c>
-      <c r="C80" t="s">
-        <v>794</v>
-      </c>
-      <c r="D80" t="s">
-        <v>795</v>
-      </c>
-      <c r="E80">
-        <v>0</v>
-      </c>
-      <c r="F80" t="s">
-        <v>96</v>
-      </c>
-      <c r="G80" t="b">
-        <v>1</v>
-      </c>
-      <c r="H80" t="b">
-        <v>0</v>
-      </c>
-      <c r="I80" t="b">
-        <v>0</v>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11">
-      <c r="B81">
-        <v>8008</v>
-      </c>
-      <c r="C81" t="s">
-        <v>796</v>
-      </c>
-      <c r="D81" t="s">
-        <v>797</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="F81" t="s">
-        <v>96</v>
-      </c>
-      <c r="G81" t="b">
-        <v>1</v>
-      </c>
-      <c r="H81" t="b">
-        <v>0</v>
-      </c>
-      <c r="I81" t="b">
-        <v>0</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
-      <c r="B82">
-        <v>8009</v>
-      </c>
-      <c r="C82" t="s">
-        <v>425</v>
-      </c>
-      <c r="D82" t="s">
-        <v>426</v>
-      </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-      <c r="F82" t="s">
-        <v>96</v>
-      </c>
-      <c r="G82" t="b">
-        <v>1</v>
-      </c>
-      <c r="H82" t="b">
-        <v>0</v>
-      </c>
-      <c r="I82" t="b">
-        <v>0</v>
-      </c>
-      <c r="J82" t="b">
-        <v>0</v>
-      </c>
-      <c r="K82" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11">
-      <c r="B83">
-        <v>8010</v>
-      </c>
-      <c r="C83" t="s">
-        <v>429</v>
-      </c>
-      <c r="D83" t="s">
-        <v>430</v>
-      </c>
-      <c r="E83">
-        <v>0</v>
-      </c>
-      <c r="F83" t="s">
-        <v>96</v>
-      </c>
-      <c r="G83" t="b">
-        <v>1</v>
-      </c>
-      <c r="H83" t="b">
-        <v>0</v>
-      </c>
-      <c r="I83" t="b">
-        <v>0</v>
-      </c>
-      <c r="J83" t="b">
-        <v>0</v>
-      </c>
-      <c r="K83" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11">
-      <c r="B84">
-        <v>8011</v>
-      </c>
-      <c r="C84" t="s">
-        <v>433</v>
-      </c>
-      <c r="D84" t="s">
-        <v>434</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-      <c r="F84" t="s">
-        <v>96</v>
-      </c>
-      <c r="G84" t="b">
-        <v>1</v>
-      </c>
-      <c r="H84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I84" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11">
-      <c r="B85">
-        <v>9001</v>
-      </c>
-      <c r="C85" t="s">
-        <v>445</v>
-      </c>
-      <c r="D85" t="s">
-        <v>446</v>
-      </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-      <c r="F85" t="s">
-        <v>96</v>
-      </c>
-      <c r="G85" t="b">
-        <v>1</v>
-      </c>
-      <c r="H85" t="b">
-        <v>0</v>
-      </c>
-      <c r="I85" t="b">
-        <v>0</v>
-      </c>
-      <c r="J85" t="b">
-        <v>1</v>
-      </c>
-      <c r="K85" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11">
-      <c r="B86">
-        <v>9002</v>
-      </c>
-      <c r="C86" t="s">
-        <v>451</v>
-      </c>
-      <c r="D86" t="s">
-        <v>452</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86" t="s">
-        <v>96</v>
-      </c>
-      <c r="G86" t="b">
-        <v>1</v>
-      </c>
-      <c r="H86" t="b">
-        <v>0</v>
-      </c>
-      <c r="I86" t="b">
-        <v>0</v>
-      </c>
-      <c r="J86" t="b">
-        <v>1</v>
-      </c>
-      <c r="K86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11">
-      <c r="B87">
-        <v>9003</v>
-      </c>
-      <c r="C87" t="s">
-        <v>457</v>
-      </c>
-      <c r="D87" t="s">
-        <v>458</v>
-      </c>
-      <c r="E87">
-        <v>0</v>
-      </c>
-      <c r="F87" t="s">
-        <v>96</v>
-      </c>
-      <c r="G87" t="b">
-        <v>1</v>
-      </c>
-      <c r="H87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I87" t="b">
-        <v>0</v>
-      </c>
-      <c r="J87" t="b">
-        <v>1</v>
-      </c>
-      <c r="K87" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11">
-      <c r="B88">
-        <v>9004</v>
-      </c>
-      <c r="C88" t="s">
-        <v>461</v>
-      </c>
-      <c r="D88" t="s">
-        <v>462</v>
-      </c>
-      <c r="E88">
-        <v>0</v>
-      </c>
-      <c r="F88" t="s">
-        <v>96</v>
-      </c>
-      <c r="G88" t="b">
-        <v>1</v>
-      </c>
-      <c r="H88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I88" t="b">
-        <v>0</v>
-      </c>
-      <c r="J88" t="b">
-        <v>1</v>
-      </c>
-      <c r="K88" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11">
-      <c r="B89">
-        <v>9005</v>
-      </c>
-      <c r="C89" t="s">
-        <v>465</v>
-      </c>
-      <c r="D89" t="s">
-        <v>466</v>
-      </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-      <c r="F89" t="s">
-        <v>96</v>
-      </c>
-      <c r="G89" t="b">
-        <v>1</v>
-      </c>
-      <c r="H89" t="b">
-        <v>0</v>
-      </c>
-      <c r="I89" t="b">
-        <v>0</v>
-      </c>
-      <c r="J89" t="b">
-        <v>1</v>
-      </c>
-      <c r="K89" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11">
-      <c r="B90">
-        <v>9006</v>
-      </c>
-      <c r="C90" t="s">
-        <v>469</v>
-      </c>
-      <c r="D90" t="s">
-        <v>470</v>
-      </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
-      <c r="F90" t="s">
-        <v>96</v>
-      </c>
-      <c r="G90" t="b">
-        <v>1</v>
-      </c>
-      <c r="H90" t="b">
-        <v>0</v>
-      </c>
-      <c r="I90" t="b">
-        <v>0</v>
-      </c>
-      <c r="J90" t="b">
-        <v>1</v>
-      </c>
-      <c r="K90" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11">
-      <c r="B91">
-        <v>9007</v>
-      </c>
-      <c r="C91" t="s">
-        <v>473</v>
-      </c>
-      <c r="D91" t="s">
-        <v>474</v>
-      </c>
-      <c r="E91">
-        <v>0</v>
-      </c>
-      <c r="F91" t="s">
-        <v>96</v>
-      </c>
-      <c r="G91" t="b">
-        <v>1</v>
-      </c>
-      <c r="H91" t="b">
-        <v>0</v>
-      </c>
-      <c r="I91" t="b">
-        <v>0</v>
-      </c>
-      <c r="J91" t="b">
-        <v>1</v>
-      </c>
-      <c r="K91" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11">
-      <c r="B92">
-        <v>9008</v>
-      </c>
-      <c r="C92" t="s">
-        <v>477</v>
-      </c>
-      <c r="D92" t="s">
-        <v>478</v>
-      </c>
-      <c r="E92">
-        <v>0</v>
-      </c>
-      <c r="F92" t="s">
-        <v>96</v>
-      </c>
-      <c r="G92" t="b">
-        <v>1</v>
-      </c>
-      <c r="H92" t="b">
-        <v>0</v>
-      </c>
-      <c r="I92" t="b">
-        <v>0</v>
-      </c>
-      <c r="J92" t="b">
-        <v>1</v>
-      </c>
-      <c r="K92" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11">
-      <c r="B93">
-        <v>9009</v>
-      </c>
-      <c r="C93" t="s">
-        <v>481</v>
-      </c>
-      <c r="D93" t="s">
-        <v>482</v>
-      </c>
-      <c r="E93">
-        <v>0</v>
-      </c>
-      <c r="F93" t="s">
-        <v>96</v>
-      </c>
-      <c r="G93" t="b">
-        <v>1</v>
-      </c>
-      <c r="H93" t="b">
-        <v>0</v>
-      </c>
-      <c r="I93" t="b">
-        <v>0</v>
-      </c>
-      <c r="J93" t="b">
-        <v>1</v>
-      </c>
-      <c r="K93" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11">
-      <c r="B94">
-        <v>9010</v>
-      </c>
-      <c r="C94" t="s">
-        <v>485</v>
-      </c>
-      <c r="D94" t="s">
-        <v>486</v>
-      </c>
-      <c r="E94">
-        <v>0</v>
-      </c>
-      <c r="F94" t="s">
-        <v>96</v>
-      </c>
-      <c r="G94" t="b">
-        <v>1</v>
-      </c>
-      <c r="H94" t="b">
-        <v>0</v>
-      </c>
-      <c r="I94" t="b">
-        <v>0</v>
-      </c>
-      <c r="J94" t="b">
-        <v>1</v>
-      </c>
-      <c r="K94" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11">
-      <c r="B95">
-        <v>9011</v>
-      </c>
-      <c r="C95" t="s">
-        <v>489</v>
-      </c>
-      <c r="D95" t="s">
-        <v>490</v>
-      </c>
-      <c r="E95">
-        <v>0</v>
-      </c>
-      <c r="F95" t="s">
-        <v>96</v>
-      </c>
-      <c r="G95" t="b">
-        <v>1</v>
-      </c>
-      <c r="H95" t="b">
-        <v>0</v>
-      </c>
-      <c r="I95" t="b">
-        <v>0</v>
-      </c>
-      <c r="J95" t="b">
-        <v>1</v>
-      </c>
-      <c r="K95" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11">
-      <c r="B96">
-        <v>10001</v>
-      </c>
-      <c r="C96" t="s">
-        <v>493</v>
-      </c>
-      <c r="D96" t="s">
-        <v>494</v>
-      </c>
-      <c r="E96">
-        <v>0</v>
-      </c>
-      <c r="F96" t="s">
-        <v>96</v>
-      </c>
-      <c r="G96" t="b">
-        <v>1</v>
-      </c>
-      <c r="H96" t="b">
-        <v>0</v>
-      </c>
-      <c r="I96" t="b">
-        <v>0</v>
-      </c>
-      <c r="J96" t="b">
-        <v>0</v>
-      </c>
-      <c r="K96" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11">
-      <c r="B97">
-        <v>11001</v>
-      </c>
-      <c r="C97" t="s">
-        <v>498</v>
-      </c>
-      <c r="D97" t="s">
-        <v>499</v>
-      </c>
-      <c r="E97">
-        <v>0</v>
-      </c>
-      <c r="F97" t="s">
-        <v>96</v>
-      </c>
-      <c r="G97" t="b">
-        <v>1</v>
-      </c>
-      <c r="H97" t="b">
-        <v>0</v>
-      </c>
-      <c r="I97" t="b">
-        <v>0</v>
-      </c>
-      <c r="J97" t="b">
-        <v>0</v>
-      </c>
-      <c r="K97" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="2:11">
-      <c r="B98">
-        <v>11002</v>
-      </c>
-      <c r="C98" t="s">
-        <v>504</v>
-      </c>
-      <c r="D98" t="s">
-        <v>505</v>
-      </c>
-      <c r="E98">
-        <v>0</v>
-      </c>
-      <c r="F98" t="s">
-        <v>96</v>
-      </c>
-      <c r="G98" t="b">
-        <v>1</v>
-      </c>
-      <c r="H98" t="b">
-        <v>0</v>
-      </c>
-      <c r="I98" t="b">
-        <v>0</v>
-      </c>
-      <c r="J98" t="b">
-        <v>0</v>
-      </c>
-      <c r="K98" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11">
-      <c r="B99">
-        <v>92005</v>
-      </c>
-      <c r="C99" t="s">
-        <v>156</v>
-      </c>
-      <c r="D99" t="s">
-        <v>507</v>
-      </c>
-      <c r="E99">
-        <v>0</v>
-      </c>
-      <c r="F99" t="s">
-        <v>96</v>
-      </c>
-      <c r="G99" t="b">
-        <v>1</v>
-      </c>
-      <c r="H99" t="b">
-        <v>0</v>
-      </c>
-      <c r="I99" t="b">
-        <v>0</v>
-      </c>
-      <c r="J99" t="b">
-        <v>0</v>
-      </c>
-      <c r="K99" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11">
-      <c r="B100">
+        <v>816</v>
+      </c>
+      <c r="G8" t="s">
+        <v>817</v>
+      </c>
+      <c r="H8" t="s">
+        <v>800</v>
+      </c>
+      <c r="I8" t="s">
+        <v>818</v>
+      </c>
+      <c r="J8" t="s">
+        <v>818</v>
+      </c>
+      <c r="K8" t="s">
+        <v>803</v>
+      </c>
+      <c r="L8" t="s">
+        <v>804</v>
+      </c>
+      <c r="M8">
         <v>91012</v>
       </c>
-      <c r="C100" t="s">
-        <v>135</v>
-      </c>
-      <c r="D100" t="s">
-        <v>511</v>
-      </c>
-      <c r="E100">
-        <v>0</v>
-      </c>
-      <c r="F100" t="s">
-        <v>96</v>
-      </c>
-      <c r="G100" t="b">
-        <v>1</v>
-      </c>
-      <c r="H100" t="b">
-        <v>0</v>
-      </c>
-      <c r="I100" t="b">
-        <v>0</v>
-      </c>
-      <c r="J100" t="b">
-        <v>0</v>
-      </c>
-      <c r="K100" t="b">
-        <v>0</v>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -15125,10 +12374,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>512</v>
       </c>
       <c r="E2" t="s">
@@ -15137,130 +12386,130 @@
       <c r="F2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="J2" s="6">
-        <v>1</v>
-      </c>
-      <c r="K2" s="6" t="s">
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="4" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="4" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="4">
         <v>4</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="4" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="4">
         <v>8</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="4" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>539</v>
       </c>
       <c r="E6" t="s">
@@ -15269,248 +12518,248 @@
       <c r="F6" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="4">
         <v>16</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="O6" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="P6" s="6" t="s">
+      <c r="P6" s="4" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="4">
         <v>32</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="P7" s="4" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="4">
         <v>64</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="O8" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="P8" s="4" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="4">
         <v>128</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="O9" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="P9" s="4" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="4">
         <v>256</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="4" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="4">
         <v>512</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="4" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="4">
         <v>1024</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="4" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="4">
         <v>2048</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="4" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>591</v>
       </c>
     </row>
@@ -15542,7 +12791,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -15583,7 +12832,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
@@ -15664,44 +12913,44 @@
         <v>614</v>
       </c>
     </row>
-    <row r="4" s="10" customFormat="1" spans="1:13">
-      <c r="A4" s="3" t="s">
+    <row r="4" s="8" customFormat="1" spans="1:13">
+      <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="8" t="s">
         <v>620</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="8" t="s">
         <v>626</v>
       </c>
     </row>
@@ -15712,10 +12961,10 @@
       <c r="C5" t="s">
         <v>627</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>629</v>
       </c>
       <c r="F5">
@@ -15750,10 +12999,10 @@
       <c r="C6" t="s">
         <v>630</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>629</v>
       </c>
       <c r="F6">
@@ -15788,10 +13037,10 @@
       <c r="C7" t="s">
         <v>632</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>629</v>
       </c>
       <c r="F7">
@@ -15829,7 +13078,7 @@
       <c r="D8" t="s">
         <v>634</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>635</v>
       </c>
       <c r="F8">
@@ -15858,13 +13107,13 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="E15" s="6"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="E16" s="6"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="6"/>
+      <c r="E17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15893,7 +13142,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -15931,7 +13180,7 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B2" t="s">
@@ -15969,7 +13218,7 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:13">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B3" s="1"/>
@@ -16002,7 +13251,7 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B4" t="s">
@@ -16590,7 +13839,7 @@
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="7.25" customWidth="1"/>
     <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="11.0833333333333" style="7" customWidth="1"/>
+    <col min="6" max="6" width="11.0833333333333" style="5" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16648,7 +13897,7 @@
       <c r="E3" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="F3" s="8"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="1" t="s">
         <v>623</v>
       </c>
@@ -16689,7 +13938,7 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <f>E5/10000</f>
         <v>0</v>
       </c>
@@ -16710,7 +13959,7 @@
       <c r="E6">
         <v>6700</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <f>E6/10000</f>
         <v>0.67</v>
       </c>
@@ -16731,7 +13980,7 @@
       <c r="E7">
         <v>2200</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <f t="shared" ref="F7:F17" si="0">E7/10000</f>
         <v>0.22</v>
       </c>
@@ -16749,10 +13998,10 @@
       <c r="D8" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="7">
         <v>900</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
@@ -16770,10 +14019,10 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="7">
         <v>180</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="5">
         <f t="shared" si="0"/>
         <v>0.018</v>
       </c>
@@ -16794,7 +14043,7 @@
       <c r="E10">
         <v>20</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -16806,7 +14055,7 @@
       <c r="A11" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="5">
         <f>SUM(F5:F10)</f>
         <v>1</v>
       </c>
@@ -16824,7 +14073,7 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -16845,7 +14094,7 @@
       <c r="E13">
         <v>3700</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
@@ -16869,7 +14118,7 @@
       <c r="E14">
         <v>4200</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="5">
         <f t="shared" si="0"/>
         <v>0.42</v>
       </c>
@@ -16890,7 +14139,7 @@
       <c r="E15">
         <v>1700</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="5">
         <f t="shared" si="0"/>
         <v>0.17</v>
       </c>
@@ -16911,7 +14160,7 @@
       <c r="E16">
         <v>380</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="5">
         <f t="shared" si="0"/>
         <v>0.038</v>
       </c>
@@ -16932,7 +14181,7 @@
       <c r="E17">
         <v>20</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="5">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -16944,7 +14193,7 @@
       <c r="A18" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="5">
         <f>SUM(F12:F17)</f>
         <v>1</v>
       </c>
@@ -18258,13 +15507,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -18293,13 +15542,13 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
@@ -18328,11 +15577,11 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="121.8" spans="1:12">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>708</v>
       </c>
       <c r="D3" s="1"/>
@@ -18417,10 +15666,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
@@ -18440,10 +15689,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
@@ -18463,10 +15712,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
@@ -18486,10 +15735,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>141</v>
       </c>
       <c r="E9" t="s">
@@ -18509,10 +15758,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
@@ -18532,10 +15781,10 @@
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>508</v>
       </c>
       <c r="E11" t="s">
@@ -18555,10 +15804,10 @@
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>562</v>
       </c>
       <c r="E12" t="s">
@@ -18592,10 +15841,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -18609,10 +15858,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
@@ -18626,10 +15875,10 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C3" t="s">
@@ -18757,42 +16006,42 @@
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="6"/>
+      <c r="C22" s="4"/>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="6"/>
+      <c r="C23" s="4"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18813,7 +16062,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -18827,13 +16076,13 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D2" t="s">
@@ -18841,13 +16090,13 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>749</v>
       </c>
       <c r="D3" t="s">

--- a/luban-excels/bak/xlsx/Items.xlsx
+++ b/luban-excels/bak/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="703" activeTab="9"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="766" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
     <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId9"/>
     <sheet name="LinkTree" sheetId="17" r:id="rId10"/>
+    <sheet name="SteamItemDef" sheetId="18" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="875">
   <si>
     <t>##var</t>
   </si>
@@ -1828,12 +1829,18 @@
     <t>CostChips</t>
   </si>
   <si>
+    <t>HintValueMode</t>
+  </si>
+  <si>
     <t>MaxRevealClickCount</t>
   </si>
   <si>
     <t>AutoCollectSeconds</t>
   </si>
   <si>
+    <t>HintIconPath</t>
+  </si>
+  <si>
     <t>IsSteamRequired</t>
   </si>
   <si>
@@ -1853,6 +1860,9 @@
   </si>
   <si>
     <t>EBlindBoxDisplayMode</t>
+  </si>
+  <si>
+    <t>EBlindBoxValueMode</t>
   </si>
   <si>
     <t>float</t>
@@ -1904,6 +1914,9 @@
     <t>消耗筹码</t>
   </si>
   <si>
+    <t>提示文字模式</t>
+  </si>
+  <si>
     <t>最大揭晓点击次数</t>
   </si>
   <si>
@@ -1934,6 +1947,12 @@
     <t>三次升级表演</t>
   </si>
   <si>
+    <t>Chips</t>
+  </si>
+  <si>
+    <t>UI\BlindBox\HintIcon_Common.png</t>
+  </si>
+  <si>
     <t>新手盲盒</t>
   </si>
   <si>
@@ -1950,6 +1969,15 @@
   </si>
   <si>
     <t>直接展示奖励</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>盲盒券</t>
+  </si>
+  <si>
+    <t>UI\BlindBox\HintIcon_Common_Ticket.png</t>
   </si>
   <si>
     <t>IsLoopTrack</t>
@@ -2304,6 +2332,9 @@
     <t>Key</t>
   </si>
   <si>
+    <t>IsPinned</t>
+  </si>
+  <si>
     <t>TooltipKey</t>
   </si>
   <si>
@@ -2337,9 +2368,6 @@
     <t>SteamPromoItemDefId</t>
   </si>
   <si>
-    <t>ClaimLimit</t>
-  </si>
-  <si>
     <t>ELinkTreeOpenCheckType</t>
   </si>
   <si>
@@ -2352,6 +2380,9 @@
     <t>显示顺序，数字越小越靠前</t>
   </si>
   <si>
+    <t>该值为TRUE 的条目始终参与 LinkTree 展示，不因奖励已领取而被替换，并优先占用展示位置</t>
+  </si>
+  <si>
     <t>是否显示这个入口</t>
   </si>
   <si>
@@ -2388,9 +2419,6 @@
     <t>未来 Steam 库存发奖/领取标记的 itemdef id；当前填 0</t>
   </si>
   <si>
-    <t>每个玩家最多领取次数；常规填 1</t>
-  </si>
-  <si>
     <t>入口ID</t>
   </si>
   <si>
@@ -2400,6 +2428,9 @@
     <t>排序</t>
   </si>
   <si>
+    <t>固定</t>
+  </si>
+  <si>
     <t>启用</t>
   </si>
   <si>
@@ -2436,9 +2467,6 @@
     <t>Steam奖励定义ID</t>
   </si>
   <si>
-    <t>领取次数上限</t>
-  </si>
-  <si>
     <t>TwitterFollow</t>
   </si>
   <si>
@@ -2503,6 +2531,147 @@
   </si>
   <si>
     <t>https://www.xiaohongshu.com/user/profile/647bc1b5000000001001f13a</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>PromoRule</t>
+  </si>
+  <si>
+    <t>GrantedManually</t>
+  </si>
+  <si>
+    <t>Tradable</t>
+  </si>
+  <si>
+    <t>Marketable</t>
+  </si>
+  <si>
+    <t>GameOnly</t>
+  </si>
+  <si>
+    <t>StoreHidden</t>
+  </si>
+  <si>
+    <t>AutoStack</t>
+  </si>
+  <si>
+    <t>Bundle</t>
+  </si>
+  <si>
+    <t>Steam Inventory 内唯一的 ItemDef ID；发布后不得改作他用</t>
+  </si>
+  <si>
+    <t>稳定机器名；发布后不要改名</t>
+  </si>
+  <si>
+    <t>Steam 定义类型；当前合法值见 ESteamItemDefType</t>
+  </si>
+  <si>
+    <t>Steam 后台英文名称；game_only 回执不向玩家展示</t>
+  </si>
+  <si>
+    <t>Steam 后台英文说明；game_only 回执不向玩家展示</t>
+  </si>
+  <si>
+    <t>Steam promo 属性；LinkTree 固定填 manual；补偿可填 owns:AppID</t>
+  </si>
+  <si>
+    <t>TRUE 时只能由 AddPromoItem/AddPromoItems 指定领取</t>
+  </si>
+  <si>
+    <t>是否允许 Steam 交易</t>
+  </si>
+  <si>
+    <t>是否允许 Steam 社区市场出售</t>
+  </si>
+  <si>
+    <t>TRUE 时不显示在 Steam 背包；回执和内部令牌填 TRUE</t>
+  </si>
+  <si>
+    <t>TRUE 时不在 Steam 物品商店展示</t>
+  </si>
+  <si>
+    <t>是否将同定义物品自动堆叠；一次性回执填 FALSE</t>
+  </si>
+  <si>
+    <t>Bundle/Generator 的内容配方；普通 Item 留空</t>
+  </si>
+  <si>
+    <t>是否参与导出到 Steam ItemDef 配置</t>
+  </si>
+  <si>
+    <t>Steam物品定义ID</t>
+  </si>
+  <si>
+    <t>Steam定义类型</t>
+  </si>
+  <si>
+    <t>英文名称</t>
+  </si>
+  <si>
+    <t>英文说明</t>
+  </si>
+  <si>
+    <t>促销规则</t>
+  </si>
+  <si>
+    <t>仅显式领取</t>
+  </si>
+  <si>
+    <t>可上市场</t>
+  </si>
+  <si>
+    <t>仅游戏内</t>
+  </si>
+  <si>
+    <t>商店隐藏</t>
+  </si>
+  <si>
+    <t>内容配方</t>
+  </si>
+  <si>
+    <t>LinkTreeTwitterFollowClaim</t>
+  </si>
+  <si>
+    <t>LinkTree Claim - Twitter Follow</t>
+  </si>
+  <si>
+    <t>Permanent receipt for the Twitter follow reward.</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>LinkTreeSteamCommunityClaim</t>
+  </si>
+  <si>
+    <t>LinkTree Claim - Steam Community</t>
+  </si>
+  <si>
+    <t>Permanent receipt for the Steam Community reward.</t>
+  </si>
+  <si>
+    <t>LinkTreeSteamStoreClaim</t>
+  </si>
+  <si>
+    <t>LinkTree Claim - Steam Store</t>
+  </si>
+  <si>
+    <t>Permanent receipt for the Steam Store reward.</t>
+  </si>
+  <si>
+    <t>LinkTreeXiaohongshuProfileClaim</t>
+  </si>
+  <si>
+    <t>LinkTree Claim - Xiaohongshu Profile</t>
+  </si>
+  <si>
+    <t>Permanent receipt for the Xiaohongshu profile reward.</t>
   </si>
 </sst>
 </file>
@@ -11908,10 +12077,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H27 H30:H77 H79:H88 H92:H107">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H108 H5:H16 H18:H27 H30:H77 H79:H88 H92:H107">
       <formula1>枚举示例!$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L16 L18:L27 L30:L77 L79:L89 L92:L107">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L108 L5:L16 L18:L27 L30:L77 L79:L89 L92:L107">
       <formula1>枚举示例!$C$18:$C$23</formula1>
     </dataValidation>
   </dataValidations>
@@ -11930,18 +12099,19 @@
     <col min="2" max="2" width="6.83333333333333" customWidth="1"/>
     <col min="3" max="3" width="17.4166666666667" customWidth="1"/>
     <col min="4" max="4" width="9.5" customWidth="1"/>
-    <col min="5" max="5" width="10.75" customWidth="1"/>
-    <col min="6" max="6" width="16.8333333333333" customWidth="1"/>
-    <col min="7" max="7" width="36.75" customWidth="1"/>
-    <col min="8" max="8" width="22.75" customWidth="1"/>
-    <col min="9" max="9" width="28" customWidth="1"/>
-    <col min="10" max="10" width="13.0833333333333" customWidth="1"/>
-    <col min="11" max="11" width="21.3333333333333" customWidth="1"/>
-    <col min="12" max="12" width="21.6666666666667" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="15.6666666666667" customWidth="1"/>
-    <col min="15" max="15" width="20.0833333333333" customWidth="1"/>
-    <col min="16" max="17" width="22.1666666666667" customWidth="1"/>
+    <col min="5" max="5" width="10.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.75" customWidth="1"/>
+    <col min="7" max="7" width="16.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="36.75" customWidth="1"/>
+    <col min="9" max="9" width="22.75" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="13.0833333333333" customWidth="1"/>
+    <col min="12" max="12" width="21.3333333333333" customWidth="1"/>
+    <col min="13" max="13" width="21.6666666666667" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="15.6666666666667" customWidth="1"/>
+    <col min="16" max="16" width="20.0833333333333" customWidth="1"/>
+    <col min="17" max="17" width="22.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -11952,49 +12122,49 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>598</v>
+        <v>761</v>
       </c>
       <c r="F1" t="s">
-        <v>752</v>
+        <v>600</v>
       </c>
       <c r="G1" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="H1" t="s">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="I1" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="J1" t="s">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="K1" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="L1" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="M1" t="s">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="N1" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="O1" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="P1" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="Q1" t="s">
-        <v>763</v>
+        <v>772</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -12014,7 +12184,7 @@
         <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
         <v>33</v>
@@ -12029,13 +12199,13 @@
         <v>33</v>
       </c>
       <c r="K2" t="s">
-        <v>764</v>
+        <v>33</v>
       </c>
       <c r="L2" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>774</v>
       </c>
       <c r="N2" t="s">
         <v>32</v>
@@ -12055,52 +12225,52 @@
         <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>772</v>
+        <v>781</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>780</v>
+        <v>789</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -12108,52 +12278,52 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="C4" t="s">
-        <v>782</v>
+        <v>791</v>
       </c>
       <c r="D4" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="E4" t="s">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="F4" t="s">
-        <v>785</v>
+        <v>794</v>
       </c>
       <c r="G4" t="s">
-        <v>786</v>
+        <v>795</v>
       </c>
       <c r="H4" t="s">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="I4" t="s">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="J4" t="s">
-        <v>789</v>
+        <v>798</v>
       </c>
       <c r="K4" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="L4" t="s">
-        <v>791</v>
+        <v>800</v>
       </c>
       <c r="M4" t="s">
-        <v>792</v>
+        <v>801</v>
       </c>
       <c r="N4" t="s">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="O4" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="P4" t="s">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="Q4" t="s">
-        <v>796</v>
+        <v>805</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -12161,41 +12331,41 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>798</v>
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="H5" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="I5" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="J5" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="K5" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="L5" t="s">
-        <v>804</v>
-      </c>
-      <c r="M5">
+        <v>812</v>
+      </c>
+      <c r="M5" t="s">
+        <v>813</v>
+      </c>
+      <c r="N5">
         <v>92005</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
       <c r="O5">
         <v>0</v>
       </c>
@@ -12203,7 +12373,7 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>401001</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -12211,49 +12381,49 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
-        <v>806</v>
+      <c r="F6" t="b">
+        <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="H6" t="s">
-        <v>800</v>
+        <v>816</v>
       </c>
       <c r="I6" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="J6" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
       <c r="K6" t="s">
-        <v>803</v>
+        <v>817</v>
       </c>
       <c r="L6" t="s">
-        <v>809</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
+        <v>812</v>
+      </c>
+      <c r="M6" t="s">
+        <v>818</v>
       </c>
       <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
         <v>2500</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>401002</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -12261,49 +12431,49 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>811</v>
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
       </c>
       <c r="G7" t="s">
+        <v>820</v>
+      </c>
+      <c r="H7" t="s">
+        <v>821</v>
+      </c>
+      <c r="I7" t="s">
+        <v>809</v>
+      </c>
+      <c r="J7" t="s">
+        <v>822</v>
+      </c>
+      <c r="K7" t="s">
+        <v>823</v>
+      </c>
+      <c r="L7" t="s">
         <v>812</v>
       </c>
-      <c r="H7" t="s">
-        <v>800</v>
-      </c>
-      <c r="I7" t="s">
-        <v>813</v>
-      </c>
-      <c r="J7" t="s">
-        <v>814</v>
-      </c>
-      <c r="K7" t="s">
-        <v>803</v>
-      </c>
-      <c r="L7" t="s">
-        <v>809</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
+      <c r="M7" t="s">
+        <v>818</v>
       </c>
       <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
         <v>2500</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>401003</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -12311,48 +12481,454 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="D8">
         <v>40</v>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>825</v>
+      </c>
+      <c r="H8" t="s">
+        <v>826</v>
+      </c>
+      <c r="I8" t="s">
+        <v>809</v>
+      </c>
+      <c r="J8" t="s">
+        <v>827</v>
+      </c>
+      <c r="K8" t="s">
+        <v>827</v>
+      </c>
+      <c r="L8" t="s">
+        <v>812</v>
+      </c>
+      <c r="M8" t="s">
+        <v>813</v>
+      </c>
+      <c r="N8">
+        <v>91012</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>401004</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr defaultColWidth="27" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="15.8333333333333" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="14.5" customWidth="1"/>
+    <col min="5" max="5" width="32.5" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="19.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="15.3333333333333" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="12.0833333333333" customWidth="1"/>
+    <col min="11" max="11" width="15.3333333333333" customWidth="1"/>
+    <col min="12" max="12" width="13.5833333333333" customWidth="1"/>
+    <col min="13" max="13" width="10.8333333333333" customWidth="1"/>
+    <col min="14" max="14" width="14.3333333333333" customWidth="1"/>
+    <col min="15" max="15" width="14.5" customWidth="1"/>
+    <col min="16" max="16384" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>760</v>
+      </c>
+      <c r="D1" t="s">
+        <v>828</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>829</v>
+      </c>
+      <c r="G1" t="s">
+        <v>830</v>
+      </c>
+      <c r="H1" t="s">
+        <v>831</v>
+      </c>
+      <c r="I1" t="s">
+        <v>832</v>
+      </c>
+      <c r="J1" t="s">
+        <v>833</v>
+      </c>
+      <c r="K1" t="s">
+        <v>834</v>
+      </c>
+      <c r="L1" t="s">
+        <v>835</v>
+      </c>
+      <c r="M1" t="s">
+        <v>836</v>
+      </c>
+      <c r="N1" t="s">
+        <v>837</v>
+      </c>
+      <c r="O1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="72" customHeight="1" spans="1:15">
+      <c r="A3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>852</v>
+      </c>
+      <c r="C4" t="s">
+        <v>791</v>
+      </c>
+      <c r="D4" t="s">
+        <v>853</v>
+      </c>
+      <c r="E4" t="s">
+        <v>854</v>
+      </c>
+      <c r="F4" t="s">
+        <v>855</v>
+      </c>
+      <c r="G4" t="s">
+        <v>856</v>
+      </c>
+      <c r="H4" t="s">
+        <v>857</v>
+      </c>
+      <c r="I4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J4" t="s">
+        <v>858</v>
+      </c>
+      <c r="K4" t="s">
+        <v>859</v>
+      </c>
+      <c r="L4" t="s">
+        <v>860</v>
+      </c>
+      <c r="M4" t="s">
+        <v>83</v>
+      </c>
+      <c r="N4" t="s">
+        <v>861</v>
+      </c>
+      <c r="O4" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5">
+        <v>401001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>862</v>
+      </c>
+      <c r="D5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" t="s">
+        <v>863</v>
+      </c>
+      <c r="F5" t="s">
+        <v>864</v>
+      </c>
+      <c r="G5" t="s">
+        <v>865</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>162</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6">
+        <v>401002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>866</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" t="s">
+        <v>867</v>
+      </c>
+      <c r="F6" t="s">
+        <v>868</v>
+      </c>
+      <c r="G6" t="s">
+        <v>865</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>162</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7">
+        <v>401003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>869</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>870</v>
+      </c>
+      <c r="F7" t="s">
+        <v>871</v>
+      </c>
+      <c r="G7" t="s">
+        <v>865</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>162</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8">
+        <v>401004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>872</v>
+      </c>
+      <c r="D8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" t="s">
+        <v>873</v>
       </c>
       <c r="F8" t="s">
-        <v>816</v>
+        <v>874</v>
       </c>
       <c r="G8" t="s">
-        <v>817</v>
-      </c>
-      <c r="H8" t="s">
-        <v>800</v>
-      </c>
-      <c r="I8" t="s">
-        <v>818</v>
-      </c>
-      <c r="J8" t="s">
-        <v>818</v>
-      </c>
-      <c r="K8" t="s">
-        <v>803</v>
-      </c>
-      <c r="L8" t="s">
-        <v>804</v>
-      </c>
-      <c r="M8">
-        <v>91012</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
+        <v>865</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>162</v>
+      </c>
+      <c r="O8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -12772,7 +13348,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -12780,17 +13356,19 @@
     <col min="3" max="3" width="13.3333333333333" customWidth="1"/>
     <col min="4" max="4" width="14.5833333333333" customWidth="1"/>
     <col min="5" max="5" width="22.8333333333333" customWidth="1"/>
-    <col min="6" max="6" width="7.41666666666667" customWidth="1"/>
-    <col min="7" max="7" width="12.25" customWidth="1"/>
-    <col min="8" max="8" width="20.5833333333333" customWidth="1"/>
-    <col min="9" max="9" width="25.4166666666667" customWidth="1"/>
-    <col min="10" max="10" width="8.83333333333333" customWidth="1"/>
-    <col min="11" max="11" width="17.25" customWidth="1"/>
-    <col min="12" max="12" width="19.9166666666667" customWidth="1"/>
-    <col min="13" max="13" width="21.25" customWidth="1"/>
+    <col min="6" max="6" width="8.75" customWidth="1"/>
+    <col min="7" max="7" width="19.1666666666667" customWidth="1"/>
+    <col min="8" max="8" width="12.25" customWidth="1"/>
+    <col min="9" max="9" width="20.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="36.75" customWidth="1"/>
+    <col min="11" max="11" width="14.8333333333333" customWidth="1"/>
+    <col min="12" max="12" width="8.83333333333333" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="14" width="23.4166666666667" customWidth="1"/>
+    <col min="15" max="15" width="28.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12830,8 +13408,14 @@
       <c r="M1" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>602</v>
+      </c>
+      <c r="O1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
         <v>31</v>
       </c>
@@ -12842,274 +13426,357 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="F2" t="s">
         <v>32</v>
       </c>
       <c r="G2" t="s">
+        <v>606</v>
+      </c>
+      <c r="H2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" t="s">
-        <v>604</v>
-      </c>
       <c r="I2" t="s">
+        <v>607</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
         <v>37</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>37</v>
-      </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" t="s">
-        <v>32</v>
       </c>
       <c r="M2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:13">
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>613</v>
+        <v>76</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="4" s="8" customFormat="1" spans="1:13">
+        <v>617</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="4" s="8" customFormat="1" spans="1:15">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>623</v>
+        <v>76</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>628</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="F5">
         <v>1000</v>
       </c>
-      <c r="G5">
-        <v>3</v>
+      <c r="G5" t="s">
+        <v>634</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5" t="s">
+        <v>635</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="F6">
         <v>1000</v>
       </c>
-      <c r="G6">
-        <v>3</v>
+      <c r="G6" t="s">
+        <v>634</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6" t="s">
+        <v>635</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="B7">
         <v>2001</v>
       </c>
       <c r="C7" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="F7">
         <v>1000</v>
       </c>
-      <c r="G7">
-        <v>3</v>
+      <c r="G7" t="s">
+        <v>634</v>
       </c>
       <c r="H7">
         <v>3</v>
       </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7" t="s">
+        <v>635</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="B8">
         <v>3001</v>
       </c>
       <c r="C8" t="s">
+        <v>639</v>
+      </c>
+      <c r="D8" t="s">
+        <v>640</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>642</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8" t="s">
+        <v>635</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="B9">
+        <v>4001</v>
+      </c>
+      <c r="C9" t="s">
+        <v>643</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="D8" t="s">
-        <v>634</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>642</v>
+      </c>
+      <c r="H9">
         <v>3</v>
       </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="I9">
+        <v>3</v>
+      </c>
+      <c r="J9" t="s">
+        <v>644</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:15">
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="5:5">
@@ -13152,31 +13819,31 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="E1" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="F1" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="G1" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="H1" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="I1" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="J1" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="K1" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="L1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -13223,31 +13890,31 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -13258,37 +13925,37 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D4" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="E4" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="F4" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="G4" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="H4" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="I4" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="J4" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="K4" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="L4" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="M4" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -13296,7 +13963,7 @@
         <v>1001</v>
       </c>
       <c r="C5">
-        <v>1001</v>
+        <v>4001</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -13326,7 +13993,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13364,7 +14031,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13402,7 +14069,7 @@
         <v>1</v>
       </c>
       <c r="M7" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -13440,7 +14107,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -13478,7 +14145,7 @@
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -13516,7 +14183,7 @@
         <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -13554,7 +14221,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -13592,7 +14259,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -13630,7 +14297,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -13668,7 +14335,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -13706,7 +14373,7 @@
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -13744,7 +14411,7 @@
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
     </row>
     <row r="17" spans="2:13">
@@ -13782,7 +14449,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
     </row>
     <row r="18" spans="2:13">
@@ -13820,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -13832,7 +14499,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7.08333333333333" customWidth="1"/>
@@ -13854,13 +14521,13 @@
         <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="E1" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="G1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -13889,17 +14556,17 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -13910,19 +14577,19 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D4" t="s">
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="G4" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="H4" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -14102,7 +14769,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -14340,7 +15007,147 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>681</v>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="B28">
+        <v>400101</v>
+      </c>
+      <c r="C28">
+        <v>4001</v>
+      </c>
+      <c r="D28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5">
+        <f t="shared" ref="F28:F33" si="1">E28/10000</f>
+        <v>0</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="B29">
+        <v>400102</v>
+      </c>
+      <c r="C29">
+        <v>4001</v>
+      </c>
+      <c r="D29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29">
+        <v>6700</v>
+      </c>
+      <c r="F29" s="5">
+        <f t="shared" si="1"/>
+        <v>0.67</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="B30">
+        <v>400103</v>
+      </c>
+      <c r="C30">
+        <v>4001</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30">
+        <v>2200</v>
+      </c>
+      <c r="F30" s="5">
+        <f t="shared" si="1"/>
+        <v>0.22</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="B31">
+        <v>400104</v>
+      </c>
+      <c r="C31">
+        <v>4001</v>
+      </c>
+      <c r="D31" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="7">
+        <v>900</v>
+      </c>
+      <c r="F31" s="5">
+        <f t="shared" si="1"/>
+        <v>0.09</v>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="B32">
+        <v>400105</v>
+      </c>
+      <c r="C32">
+        <v>4001</v>
+      </c>
+      <c r="D32" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="7">
+        <v>180</v>
+      </c>
+      <c r="F32" s="5">
+        <f t="shared" si="1"/>
+        <v>0.018</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33">
+        <v>400106</v>
+      </c>
+      <c r="C33">
+        <v>4001</v>
+      </c>
+      <c r="D33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E33">
+        <v>20</v>
+      </c>
+      <c r="F33" s="5">
+        <f t="shared" si="1"/>
+        <v>0.002</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="F34" s="5">
+        <f>SUM(F28:F33)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -14375,28 +15182,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="D1" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="E1" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="F1" t="s">
-        <v>684</v>
+        <v>693</v>
       </c>
       <c r="G1" t="s">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="H1" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="I1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J1" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -14439,28 +15246,28 @@
         <v>162</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>693</v>
+        <v>702</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -14471,31 +15278,31 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="D4" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="E4" t="s">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="F4" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="G4" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="H4" t="s">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="I4" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="J4" t="s">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="K4" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -14911,7 +15718,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -14946,7 +15753,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -15045,7 +15852,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -15080,7 +15887,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -15243,7 +16050,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -15278,7 +16085,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -15313,7 +16120,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -15520,25 +16327,25 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="F1" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="G1" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="H1" t="s">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="I1" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="K1" t="s">
-        <v>706</v>
+        <v>715</v>
       </c>
       <c r="L1" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -15582,23 +16389,23 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>712</v>
+        <v>721</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -15615,28 +16422,28 @@
         <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="F4" t="s">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="G4" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="H4" t="s">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="I4" t="s">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="J4" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="K4" t="s">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="L4" t="s">
-        <v>719</v>
+        <v>728</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -15650,16 +16457,16 @@
         <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="F5" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="H5" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="K5" t="s">
-        <v>723</v>
+        <v>732</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -15673,16 +16480,16 @@
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="F6" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="H6" t="s">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="K6" t="s">
-        <v>726</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -15696,16 +16503,16 @@
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="F7" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="H7" t="s">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="K7" t="s">
-        <v>729</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -15719,16 +16526,16 @@
         <v>121</v>
       </c>
       <c r="E8" t="s">
+        <v>739</v>
+      </c>
+      <c r="F8" t="s">
         <v>730</v>
       </c>
-      <c r="F8" t="s">
-        <v>721</v>
-      </c>
       <c r="H8" t="s">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="K8" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -15742,16 +16549,16 @@
         <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="F9" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="H9" t="s">
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="K9" t="s">
-        <v>723</v>
+        <v>732</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -15765,16 +16572,16 @@
         <v>92</v>
       </c>
       <c r="E10" t="s">
+        <v>744</v>
+      </c>
+      <c r="F10" t="s">
+        <v>730</v>
+      </c>
+      <c r="H10" t="s">
+        <v>745</v>
+      </c>
+      <c r="K10" t="s">
         <v>735</v>
-      </c>
-      <c r="F10" t="s">
-        <v>721</v>
-      </c>
-      <c r="H10" t="s">
-        <v>736</v>
-      </c>
-      <c r="K10" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -15788,16 +16595,16 @@
         <v>508</v>
       </c>
       <c r="E11" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="F11" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="H11" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="J11" t="s">
-        <v>737</v>
+        <v>746</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -15811,16 +16618,16 @@
         <v>562</v>
       </c>
       <c r="E12" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="F12" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="H12" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="J12" t="s">
-        <v>737</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -15848,10 +16655,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="D1" t="s">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -15868,7 +16675,7 @@
         <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -15885,10 +16692,10 @@
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>741</v>
+        <v>750</v>
       </c>
       <c r="E3" t="s">
-        <v>742</v>
+        <v>751</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -15910,7 +16717,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>743</v>
+        <v>752</v>
       </c>
       <c r="D5" t="s">
         <v>140</v>
@@ -15924,7 +16731,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="D6" t="s">
         <v>191</v>
@@ -15938,7 +16745,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="D7" t="s">
         <v>393</v>
@@ -15962,7 +16769,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="D10" t="s">
         <v>271</v>
@@ -16069,10 +16876,10 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="D1" t="s">
-        <v>748</v>
+        <v>757</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -16097,10 +16904,10 @@
         <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="D3" t="s">
-        <v>750</v>
+        <v>759</v>
       </c>
     </row>
     <row r="5" spans="1:4">

--- a/luban-excels/bak/xlsx/Items.xlsx
+++ b/luban-excels/bak/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="712" activeTab="10"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="712" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2259" uniqueCount="973">
   <si>
     <t>##var</t>
   </si>
@@ -1997,46 +1997,43 @@
     <t>MaxGrantCount</t>
   </si>
   <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>CanAccumulate</t>
-  </si>
-  <si>
-    <t>MaxPendingCount</t>
-  </si>
-  <si>
     <t>SteamPlaytimeGeneratorItemDefId</t>
   </si>
   <si>
+    <t>SteamDropWindowSeconds</t>
+  </si>
+  <si>
+    <t>SteamDropMaxPerWindow</t>
+  </si>
+  <si>
     <t>对应 BlindBox.Id</t>
   </si>
   <si>
-    <t>按玩家总游玩秒数计算的生效时间
-该数值主要用于Steam库存中判定玩家是否可以领取该奖励的时间下限</t>
-  </si>
-  <si>
-    <t>间隔时间
-玩家领取一个盲盒之后，等待下一个盲盒到达需要多长间隔时间</t>
-  </si>
-  <si>
-    <t>结束时间；无限循环填 -1
-策划注意导SteamJSON是需要确认改字段的用途</t>
+    <t>TRUE 表示正常阶段循环装扮券生产行</t>
+  </si>
+  <si>
+    <t>按玩家调度时钟计算的最早生效时间</t>
+  </si>
+  <si>
+    <t>非循环行为相对上次领取间隔；循环行为 Steam 装扮券掉落间隔</t>
+  </si>
+  <si>
+    <t>结束时间；无限循环填 -1</t>
   </si>
   <si>
     <t>最多发放次数；不限填 -1</t>
   </si>
   <si>
-    <t>开启优先级，数值越大越优先</t>
-  </si>
-  <si>
-    <t>是否允许累积多个待领取资格</t>
-  </si>
-  <si>
-    <t>最多保留几个待领取资格</t>
-  </si>
-  <si>
-    <t>该调度到达资格时间时，通过 TriggerItemDrop 请求的 Steam playtimegenerator ItemDef ID。不接入 Steam 掉落时填 0。同一个 ItemDef ID 不建议被多条调度共用。</t>
+    <t>通过 TriggerItemDrop 请求的 Steam PlaytimeGenerator ItemDef ID；本地消耗品填 0</t>
+  </si>
+  <si>
+    <t>Steam 掉落窗口基础秒数；乘等待倍率后转为分钟；0 表示不启用</t>
+  </si>
+  <si>
+    <t>Steam 掉落窗口内最多发放次数；未启用窗口时填 0</t>
+  </si>
+  <si>
+    <t>前 12 条控制新手顺序；正常阶段只保留一条循环装扮券生产行</t>
   </si>
   <si>
     <t>是循环生效的</t>
@@ -2054,18 +2051,15 @@
     <t>最多发放次数</t>
   </si>
   <si>
-    <t>优先级</t>
-  </si>
-  <si>
-    <t>是否可累积</t>
-  </si>
-  <si>
-    <t>最大待领取数</t>
-  </si>
-  <si>
     <t>Steam游玩时间生成器DefID</t>
   </si>
   <si>
+    <t>Steam掉落窗口秒数</t>
+  </si>
+  <si>
+    <t>Steam窗口最大发放数</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -2075,7 +2069,7 @@
     <t>新手期固定：15 分钟新手礼盒</t>
   </si>
   <si>
-    <t>新手期固定：25 分钟 消耗品盲盒</t>
+    <t>新手期固定：25 分钟消耗品盲盒</t>
   </si>
   <si>
     <t>新手期固定：35 分钟装扮盲盒</t>
@@ -2084,7 +2078,7 @@
     <t>新手期固定：45 分钟新手礼盒</t>
   </si>
   <si>
-    <t>新手期固定：55 分钟 消耗品 盲盒</t>
+    <t>新手期固定：55 分钟消耗品盲盒</t>
   </si>
   <si>
     <t>新手期固定：65 分钟装扮盲盒</t>
@@ -2093,7 +2087,7 @@
     <t>新手期固定：75 分钟新手礼盒</t>
   </si>
   <si>
-    <t>新手期固定：85 分钟 消耗品 盲盒</t>
+    <t>新手期固定：85 分钟消耗品盲盒</t>
   </si>
   <si>
     <t>新手期固定：95 分钟装扮盲盒</t>
@@ -2102,13 +2096,10 @@
     <t>新手期固定：105 分钟新手礼盒</t>
   </si>
   <si>
-    <t>新手期固定：115 分钟 消耗品 盲盒</t>
-  </si>
-  <si>
-    <t>正常期循环：125 分钟起每 30 分钟装扮盲盒</t>
-  </si>
-  <si>
-    <t>正常期循环：140 分钟起每 30 分钟 消耗品 盲盒</t>
+    <t>新手期固定：115 分钟消耗品盲盒</t>
+  </si>
+  <si>
+    <t>正常阶段：第 12 个奖励入账后启动；正式倍率下每 30 分钟生产装扮券，60 分钟窗口最多 2 张</t>
   </si>
   <si>
     <t>Rarity</t>
@@ -2376,7 +2367,13 @@
     <t>SequentialPackId</t>
   </si>
   <si>
-    <t>SteamPromoItemDefId</t>
+    <t>RewardBlindBoxId</t>
+  </si>
+  <si>
+    <t>SteamReceiptItemDefId</t>
+  </si>
+  <si>
+    <t>SteamClaimBundleItemDefId</t>
   </si>
   <si>
     <t>ELinkTreeOpenCheckType</t>
@@ -2427,7 +2424,16 @@
     <t>RewardType=SequentialPack 时关联的顺序礼包 ID；当前不用填 0</t>
   </si>
   <si>
-    <t>未来 Steam 库存发奖/领取标记的 itemdef id；当前填 0</t>
+    <t>RewardType=BlindBox 时填写 BlindBox.Id</t>
+  </si>
+  <si>
+    <t>领过奖励的玩家会在Steam服务器上留下凭证，防止再次领奖
+Bundle 中永久保留的回执。
+Banner 是否已领取只检查这个 ID。</t>
+  </si>
+  <si>
+    <t>客户端调用 AddPromoItem 的目标。
+必须指向 Type=Bundle、PromoRule=manual 的定义。</t>
   </si>
   <si>
     <t>入口ID</t>
@@ -2475,7 +2481,13 @@
     <t>顺序礼包ID</t>
   </si>
   <si>
-    <t>Steam奖励定义ID</t>
+    <t>奖励盲盒ID</t>
+  </si>
+  <si>
+    <t>Steam永久领取回执DefID</t>
+  </si>
+  <si>
+    <t>Steam领奖礼包DefID</t>
   </si>
   <si>
     <t>TwitterFollow</t>
@@ -2572,6 +2584,12 @@
   </si>
   <si>
     <t>Bundle</t>
+  </si>
+  <si>
+    <t>SteamUseDropLimit</t>
+  </si>
+  <si>
+    <t>SteamDropLimit</t>
   </si>
   <si>
     <t>Steam Inventory 内唯一的 ItemDef ID；发布后不得改作他用</t>
@@ -2608,12 +2626,21 @@
     <t>是否将同定义物品自动堆叠；一次性回执填 FALSE</t>
   </si>
   <si>
-    <t>Bundle/Generator 的内容配方；普通 Item 留空</t>
+    <t>Bundle/Generator 的内容配方。
+留空表示不输出 bundle；
+填写 @AUTO 表示由转换器根据业务表生成；
+也可直接填写 Steam 配方，例如 101002x1;101003x1。</t>
   </si>
   <si>
     <t>是否参与导出到 Steam ItemDef 配置</t>
   </si>
   <si>
+    <t>仅用于未被启用 Schedule 引用的 PlaytimeGenerator；TRUE 时显式输出 Steam use_drop_limit</t>
+  </si>
+  <si>
+    <t>Steam 永久投放上限；退役 PlaytimeGenerator 填 0</t>
+  </si>
+  <si>
     <t>Steam物品定义ID</t>
   </si>
   <si>
@@ -2644,6 +2671,12 @@
     <t>内容配方</t>
   </si>
   <si>
+    <t>Steam启用投放上限</t>
+  </si>
+  <si>
+    <t>Steam投放上限</t>
+  </si>
+  <si>
     <t>LinkTreeTwitterFollowClaim</t>
   </si>
   <si>
@@ -2695,6 +2728,21 @@
     <t>Permanent receipt for the Xiaohongshu profile reward.</t>
   </si>
   <si>
+    <t>推特领奖回执凭证</t>
+  </si>
+  <si>
+    <t>社区领奖回执凭证</t>
+  </si>
+  <si>
+    <t>商店页面领奖回执凭证</t>
+  </si>
+  <si>
+    <t>小红书领奖回执凭证</t>
+  </si>
+  <si>
+    <t>402表示开盒成本</t>
+  </si>
+  <si>
     <t>DecorationBlindBoxVoucher</t>
   </si>
   <si>
@@ -2704,6 +2752,33 @@
     <t>Opens one decoration blind box.</t>
   </si>
   <si>
+    <t>StandardBlindBoxContainer</t>
+  </si>
+  <si>
+    <t>标准盲盒券</t>
+  </si>
+  <si>
+    <t>Standard Blind Box</t>
+  </si>
+  <si>
+    <t>A consumable Steam inventory item used to open one standard blind box.</t>
+  </si>
+  <si>
+    <t>NewbieBlindBoxContainer</t>
+  </si>
+  <si>
+    <t>新手盲盒券</t>
+  </si>
+  <si>
+    <t>Newbie Blind Box</t>
+  </si>
+  <si>
+    <t>A consumable Steam inventory item used to open one newbie blind box.</t>
+  </si>
+  <si>
+    <t>403盲盒物品生成器</t>
+  </si>
+  <si>
     <t>DecorationBlindBoxV1Generator</t>
   </si>
   <si>
@@ -2720,6 +2795,183 @@
   </si>
   <si>
     <t>101002x1;101003x1</t>
+  </si>
+  <si>
+    <t>StandardBlindBoxV1Generator</t>
+  </si>
+  <si>
+    <t>标准盲盒物品生成器V1</t>
+  </si>
+  <si>
+    <t>Standard Blind Box V1 Generator</t>
+  </si>
+  <si>
+    <t>Generates one standard blind box reward.</t>
+  </si>
+  <si>
+    <t>@AUTO</t>
+  </si>
+  <si>
+    <t>NewbieBlindBoxV1Generator</t>
+  </si>
+  <si>
+    <t>新手盲盒物品生成器V1</t>
+  </si>
+  <si>
+    <t>Newbie Blind Box V1 Generator</t>
+  </si>
+  <si>
+    <t>Generates one newbie blind box reward.</t>
+  </si>
+  <si>
+    <t>401005x1;192005x1</t>
+  </si>
+  <si>
+    <t>401006x1</t>
+  </si>
+  <si>
+    <t>401007x1</t>
+  </si>
+  <si>
+    <t>401008x1;192012x1</t>
+  </si>
+  <si>
+    <t>404 表示游玩时间用的生成器</t>
+  </si>
+  <si>
+    <t>Schedule1001PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1001游玩时间掉落</t>
+  </si>
+  <si>
+    <t>PlaytimeGenerator</t>
+  </si>
+  <si>
+    <t>Schedule 1001 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1001.</t>
+  </si>
+  <si>
+    <t>402001x1</t>
+  </si>
+  <si>
+    <t>Schedule1002PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1002游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1002 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1002.</t>
+  </si>
+  <si>
+    <t>402003x1</t>
+  </si>
+  <si>
+    <t>Schedule1004PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1004游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1004 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1004.</t>
+  </si>
+  <si>
+    <t>402002x1</t>
+  </si>
+  <si>
+    <t>Schedule1005PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1005游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1005 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1005.</t>
+  </si>
+  <si>
+    <t>Schedule1007PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1007游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1007 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1007.</t>
+  </si>
+  <si>
+    <t>Schedule1008PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1008游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1008 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1008.</t>
+  </si>
+  <si>
+    <t>Schedule1010PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1010游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1010 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1010.</t>
+  </si>
+  <si>
+    <t>Schedule1011PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1011游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1011 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by schedule 1011.</t>
+  </si>
+  <si>
+    <t>Schedule1013PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>调度1013循环游玩时间掉落</t>
+  </si>
+  <si>
+    <t>Schedule 1013 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the recurring standard blind box item configured by schedule 1013.</t>
+  </si>
+  <si>
+    <t>405 表示掉落窗口用的生成器</t>
+  </si>
+  <si>
+    <t>RecurringDecorationBlindBoxDropV2</t>
+  </si>
+  <si>
+    <t>新版循环装扮盲盒券投放</t>
+  </si>
+  <si>
+    <t>Recurring Decoration Blind Box Drop V2</t>
+  </si>
+  <si>
+    <t>Grants recurring standard blind box vouchers under the Steam playtime drop window.</t>
   </si>
 </sst>
 </file>
@@ -2889,12 +3141,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2904,7 +3162,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.6"/>
+        <fgColor rgb="FFEFE4B7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3233,7 +3491,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3257,16 +3515,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -3275,89 +3533,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3365,6 +3623,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3388,14 +3649,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3713,6 +3977,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="14"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="00EFE4B7"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3985,11 +4254,11 @@
     <col min="16" max="16" width="16.5833333333333" customWidth="1"/>
     <col min="17" max="17" width="20.9166666666667" customWidth="1"/>
     <col min="18" max="18" width="14.75" customWidth="1"/>
-    <col min="19" max="19" width="5.08333333333333" style="10" customWidth="1"/>
+    <col min="19" max="19" width="5.08333333333333" style="12" customWidth="1"/>
     <col min="20" max="20" width="44" customWidth="1"/>
     <col min="21" max="21" width="48.5833333333333" customWidth="1"/>
     <col min="22" max="22" width="15.4166666666667" customWidth="1"/>
-    <col min="23" max="23" width="7" style="10" customWidth="1"/>
+    <col min="23" max="23" width="7" style="12" customWidth="1"/>
     <col min="24" max="24" width="15.1666666666667" customWidth="1"/>
     <col min="25" max="25" width="18.0833333333333" customWidth="1"/>
     <col min="26" max="26" width="21.4166666666667" customWidth="1"/>
@@ -4006,16 +4275,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
+      <c r="D1" s="4"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -4031,15 +4300,12 @@
       <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1"/>
       <c r="K1" t="s">
         <v>8</v>
       </c>
       <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="M1"/>
-      <c r="N1"/>
       <c r="O1" t="s">
         <v>10</v>
       </c>
@@ -4099,16 +4365,16 @@
       </c>
     </row>
     <row r="2" spans="1:35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="4"/>
       <c r="E2" t="s">
         <v>32</v>
       </c>
@@ -4133,8 +4399,6 @@
       <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="M2"/>
-      <c r="N2"/>
       <c r="O2" t="s">
         <v>30</v>
       </c>
@@ -4194,12 +4458,12 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="121.8" spans="1:35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -4214,7 +4478,7 @@
       <c r="J3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="13"/>
       <c r="M3" s="1" t="s">
         <v>45</v>
       </c>
@@ -4225,14 +4489,14 @@
       <c r="R3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="12"/>
+      <c r="S3" s="2"/>
       <c r="T3" s="1" t="s">
         <v>48</v>
       </c>
       <c r="U3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="12"/>
+      <c r="W3" s="2"/>
       <c r="X3" s="1" t="s">
         <v>50</v>
       </c>
@@ -4271,16 +4535,16 @@
       </c>
     </row>
     <row r="4" spans="1:35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E4" t="s">
@@ -4371,71 +4635,72 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
-      <c r="B5">
+    <row r="5" s="11" customFormat="1" spans="1:35">
+      <c r="B5" s="11">
         <v>1001</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="11">
         <v>200</v>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="J5" s="11">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="T5" t="s">
+      <c r="M5" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="11">
+        <v>0</v>
+      </c>
+      <c r="O5" s="11">
+        <v>0</v>
+      </c>
+      <c r="P5" s="11">
+        <v>0</v>
+      </c>
+      <c r="T5" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="U5" t="s">
+      <c r="U5" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="11">
         <v>1001</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="W5" s="11"/>
+      <c r="Y5" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
+      <c r="AA5" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4494,9 +4759,6 @@
       <c r="Y6" t="s">
         <v>96</v>
       </c>
-      <c r="Z6" t="s">
-        <v>97</v>
-      </c>
       <c r="AA6" t="b">
         <v>1</v>
       </c>
@@ -4568,9 +4830,6 @@
       <c r="Y7" t="s">
         <v>96</v>
       </c>
-      <c r="Z7" t="s">
-        <v>103</v>
-      </c>
       <c r="AA7" t="b">
         <v>1</v>
       </c>
@@ -4637,7 +4896,7 @@
         <v>1004</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>101004</v>
       </c>
       <c r="Y8" t="s">
         <v>96</v>
@@ -4708,7 +4967,7 @@
         <v>1005</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>101005</v>
       </c>
       <c r="Y9" t="s">
         <v>96</v>
@@ -4779,7 +5038,7 @@
         <v>1006</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>101006</v>
       </c>
       <c r="Y10" t="s">
         <v>96</v>
@@ -4850,7 +5109,7 @@
         <v>1007</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>101007</v>
       </c>
       <c r="Y11" t="s">
         <v>96</v>
@@ -4905,10 +5164,10 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="9">
         <v>100</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="9">
         <v>200</v>
       </c>
       <c r="T12" t="s">
@@ -4921,7 +5180,7 @@
         <v>1008</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>101008</v>
       </c>
       <c r="Y12" t="s">
         <v>96</v>
@@ -4992,7 +5251,7 @@
         <v>1009</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>101009</v>
       </c>
       <c r="Y13" t="s">
         <v>96</v>
@@ -5063,7 +5322,7 @@
         <v>1010</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>101010</v>
       </c>
       <c r="Y14" t="s">
         <v>96</v>
@@ -5134,7 +5393,7 @@
         <v>1011</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>101011</v>
       </c>
       <c r="Y15" t="s">
         <v>96</v>
@@ -5205,7 +5464,7 @@
         <v>1012</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>101012</v>
       </c>
       <c r="Y16" t="s">
         <v>96</v>
@@ -5278,7 +5537,7 @@
         <v>142</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>102001</v>
       </c>
       <c r="Y18" t="s">
         <v>96</v>
@@ -5346,7 +5605,7 @@
         <v>146</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>102002</v>
       </c>
       <c r="Y19" t="s">
         <v>96</v>
@@ -5414,7 +5673,7 @@
         <v>150</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>102003</v>
       </c>
       <c r="Y20" t="s">
         <v>96</v>
@@ -5482,7 +5741,7 @@
         <v>154</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>102004</v>
       </c>
       <c r="Y21" t="s">
         <v>96</v>
@@ -5550,7 +5809,7 @@
         <v>158</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>102005</v>
       </c>
       <c r="Y22" t="s">
         <v>96</v>
@@ -5623,7 +5882,7 @@
       <c r="R23" t="s">
         <v>161</v>
       </c>
-      <c r="S23" s="10" t="s">
+      <c r="S23" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T23" t="s">
@@ -5633,7 +5892,7 @@
         <v>163</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>102006</v>
       </c>
       <c r="Y23" t="s">
         <v>96</v>
@@ -5701,7 +5960,7 @@
         <v>167</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>102007</v>
       </c>
       <c r="Y24" t="s">
         <v>96</v>
@@ -5769,7 +6028,7 @@
         <v>171</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>102008</v>
       </c>
       <c r="Y25" t="s">
         <v>96</v>
@@ -5837,7 +6096,7 @@
         <v>175</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>102009</v>
       </c>
       <c r="Y26" t="s">
         <v>96</v>
@@ -5905,7 +6164,7 @@
         <v>179</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>102010</v>
       </c>
       <c r="Y27" t="s">
         <v>96</v>
@@ -5981,7 +6240,7 @@
       <c r="R28" t="s">
         <v>161</v>
       </c>
-      <c r="S28" s="10" t="s">
+      <c r="S28" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T28" t="s">
@@ -5993,11 +6252,11 @@
       <c r="V28" t="s">
         <v>161</v>
       </c>
-      <c r="W28" s="10" t="s">
+      <c r="W28" s="12" t="s">
         <v>161</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>102011</v>
       </c>
       <c r="Y28" t="s">
         <v>96</v>
@@ -6085,7 +6344,7 @@
       <c r="R29" t="s">
         <v>161</v>
       </c>
-      <c r="S29" s="10" t="s">
+      <c r="S29" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T29" t="s">
@@ -6097,11 +6356,11 @@
       <c r="V29" t="s">
         <v>161</v>
       </c>
-      <c r="W29" s="10" t="s">
+      <c r="W29" s="12" t="s">
         <v>161</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>102012</v>
       </c>
       <c r="Y29" t="s">
         <v>96</v>
@@ -6181,7 +6440,7 @@
         <v>192</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>103001</v>
       </c>
       <c r="Y30" t="s">
         <v>96</v>
@@ -6249,7 +6508,7 @@
         <v>196</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>103002</v>
       </c>
       <c r="Y31" t="s">
         <v>96</v>
@@ -6317,7 +6576,7 @@
         <v>200</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>103003</v>
       </c>
       <c r="Y32" t="s">
         <v>96</v>
@@ -6385,7 +6644,7 @@
         <v>204</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>103004</v>
       </c>
       <c r="Y33" t="s">
         <v>96</v>
@@ -6453,7 +6712,7 @@
         <v>208</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>103005</v>
       </c>
       <c r="Y34" t="s">
         <v>96</v>
@@ -6474,429 +6733,435 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:31">
-      <c r="B35">
+    <row r="35" s="11" customFormat="1" spans="2:31">
+      <c r="B35" s="11">
         <v>4001</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" t="s">
+      <c r="I35" s="11">
+        <v>0</v>
+      </c>
+      <c r="J35" s="11">
+        <v>0</v>
+      </c>
+      <c r="K35" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M35" t="b">
-        <v>1</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="T35" t="s">
+      <c r="M35" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" s="11">
+        <v>0</v>
+      </c>
+      <c r="O35" s="11">
+        <v>0</v>
+      </c>
+      <c r="P35" s="11">
+        <v>0</v>
+      </c>
+      <c r="T35" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="U35" t="s">
+      <c r="U35" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="s">
+      <c r="X35" s="11">
+        <v>104001</v>
+      </c>
+      <c r="Y35" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:31">
-      <c r="B36">
+      <c r="Z35" s="11"/>
+      <c r="AA35" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" s="11" customFormat="1" spans="2:31">
+      <c r="B36" s="11">
         <v>4002</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" t="s">
+      <c r="I36" s="11">
+        <v>0</v>
+      </c>
+      <c r="J36" s="11">
+        <v>0</v>
+      </c>
+      <c r="K36" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M36" t="b">
-        <v>1</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="T36" t="s">
+      <c r="M36" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" s="11">
+        <v>0</v>
+      </c>
+      <c r="O36" s="11">
+        <v>0</v>
+      </c>
+      <c r="P36" s="11">
+        <v>0</v>
+      </c>
+      <c r="T36" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="U36" t="s">
+      <c r="U36" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="s">
+      <c r="X36" s="11">
+        <v>104002</v>
+      </c>
+      <c r="Y36" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31">
-      <c r="B37">
+      <c r="Z36" s="11"/>
+      <c r="AA36" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" s="11" customFormat="1" spans="2:31">
+      <c r="B37" s="11">
         <v>4003</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37" t="b">
-        <v>1</v>
-      </c>
-      <c r="L37" t="s">
+      <c r="I37" s="11">
+        <v>0</v>
+      </c>
+      <c r="J37" s="11">
+        <v>0</v>
+      </c>
+      <c r="K37" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M37" t="b">
-        <v>1</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="T37" t="s">
+      <c r="M37" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" s="11">
+        <v>0</v>
+      </c>
+      <c r="O37" s="11">
+        <v>0</v>
+      </c>
+      <c r="P37" s="11">
+        <v>0</v>
+      </c>
+      <c r="T37" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="U37" t="s">
+      <c r="U37" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="X37">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="s">
+      <c r="X37" s="11">
+        <v>104003</v>
+      </c>
+      <c r="Y37" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:31">
-      <c r="B38">
+      <c r="Z37" s="11"/>
+      <c r="AA37" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="11" customFormat="1" spans="2:31">
+      <c r="B38" s="11">
         <v>4004</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38" t="b">
-        <v>1</v>
-      </c>
-      <c r="L38" t="s">
+      <c r="I38" s="11">
+        <v>0</v>
+      </c>
+      <c r="J38" s="11">
+        <v>0</v>
+      </c>
+      <c r="K38" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M38" t="b">
-        <v>1</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="T38" t="s">
+      <c r="M38" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" s="11">
+        <v>0</v>
+      </c>
+      <c r="O38" s="11">
+        <v>0</v>
+      </c>
+      <c r="P38" s="11">
+        <v>0</v>
+      </c>
+      <c r="T38" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="U38" t="s">
+      <c r="U38" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="X38">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="s">
+      <c r="X38" s="11">
+        <v>104004</v>
+      </c>
+      <c r="Y38" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31">
-      <c r="B39">
+      <c r="Z38" s="11"/>
+      <c r="AA38" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" s="11" customFormat="1" spans="2:31">
+      <c r="B39" s="11">
         <v>4005</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" t="s">
+      <c r="I39" s="11">
+        <v>0</v>
+      </c>
+      <c r="J39" s="11">
+        <v>0</v>
+      </c>
+      <c r="K39" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M39" t="b">
-        <v>1</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="T39" t="s">
+      <c r="M39" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" s="11">
+        <v>0</v>
+      </c>
+      <c r="O39" s="11">
+        <v>0</v>
+      </c>
+      <c r="P39" s="11">
+        <v>0</v>
+      </c>
+      <c r="T39" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="U39" t="s">
+      <c r="U39" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="X39">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="s">
+      <c r="X39" s="11">
+        <v>104005</v>
+      </c>
+      <c r="Y39" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:31">
-      <c r="B40">
+      <c r="Z39" s="11"/>
+      <c r="AA39" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" s="11" customFormat="1" spans="2:31">
+      <c r="B40" s="11">
         <v>4006</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40" t="b">
-        <v>1</v>
-      </c>
-      <c r="L40" t="s">
+      <c r="I40" s="11">
+        <v>0</v>
+      </c>
+      <c r="J40" s="11">
+        <v>0</v>
+      </c>
+      <c r="K40" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M40" t="b">
-        <v>1</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="T40" t="s">
+      <c r="M40" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" s="11">
+        <v>0</v>
+      </c>
+      <c r="O40" s="11">
+        <v>0</v>
+      </c>
+      <c r="P40" s="11">
+        <v>0</v>
+      </c>
+      <c r="T40" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="U40" t="s">
+      <c r="U40" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="s">
+      <c r="X40" s="11">
+        <v>104006</v>
+      </c>
+      <c r="Y40" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
+      <c r="Z40" s="11"/>
+      <c r="AA40" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6947,7 +7212,7 @@
         <v>239</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>105001</v>
       </c>
       <c r="Y41" t="s">
         <v>96</v>
@@ -7015,7 +7280,7 @@
         <v>243</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>105002</v>
       </c>
       <c r="Y42" t="s">
         <v>96</v>
@@ -7083,7 +7348,7 @@
         <v>247</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>105003</v>
       </c>
       <c r="Y43" t="s">
         <v>96</v>
@@ -7151,7 +7416,7 @@
         <v>251</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>105004</v>
       </c>
       <c r="Y44" t="s">
         <v>96</v>
@@ -7219,7 +7484,7 @@
         <v>255</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>105005</v>
       </c>
       <c r="Y45" t="s">
         <v>96</v>
@@ -7287,7 +7552,7 @@
         <v>259</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>105006</v>
       </c>
       <c r="Y46" t="s">
         <v>96</v>
@@ -7355,7 +7620,7 @@
         <v>263</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>105007</v>
       </c>
       <c r="Y47" t="s">
         <v>96</v>
@@ -7423,7 +7688,7 @@
         <v>267</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>105008</v>
       </c>
       <c r="Y48" t="s">
         <v>96</v>
@@ -7444,86 +7709,87 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:31">
-      <c r="B49">
+    <row r="49" s="11" customFormat="1" spans="2:31">
+      <c r="B49" s="11">
         <v>6001</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="F49" t="s">
-        <v>161</v>
-      </c>
-      <c r="G49" t="s">
-        <v>161</v>
-      </c>
-      <c r="H49" t="s">
+      <c r="F49" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I49">
-        <v>300</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" t="s">
+      <c r="I49" s="11">
+        <v>300</v>
+      </c>
+      <c r="J49" s="11">
+        <v>0</v>
+      </c>
+      <c r="K49" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M49" t="b">
-        <v>1</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>161</v>
-      </c>
-      <c r="R49" t="s">
-        <v>161</v>
-      </c>
-      <c r="S49" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="T49" t="s">
+      <c r="M49" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" s="11">
+        <v>0</v>
+      </c>
+      <c r="O49" s="11">
+        <v>0</v>
+      </c>
+      <c r="P49" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="R49" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="S49" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="T49" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="U49" t="s">
+      <c r="U49" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="s">
+      <c r="X49" s="11">
+        <v>106001</v>
+      </c>
+      <c r="Y49" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
+      <c r="Z49" s="11"/>
+      <c r="AA49" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7579,7 +7845,7 @@
       <c r="R50" t="s">
         <v>161</v>
       </c>
-      <c r="S50" s="10" t="s">
+      <c r="S50" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T50" t="s">
@@ -7589,7 +7855,7 @@
         <v>276</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>106002</v>
       </c>
       <c r="Y50" t="s">
         <v>96</v>
@@ -7662,7 +7928,7 @@
       <c r="R51" t="s">
         <v>161</v>
       </c>
-      <c r="S51" s="10" t="s">
+      <c r="S51" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T51" t="s">
@@ -7672,7 +7938,7 @@
         <v>280</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>106003</v>
       </c>
       <c r="Y51" t="s">
         <v>96</v>
@@ -7745,7 +8011,7 @@
       <c r="R52" t="s">
         <v>161</v>
       </c>
-      <c r="S52" s="10" t="s">
+      <c r="S52" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T52" t="s">
@@ -7755,7 +8021,7 @@
         <v>284</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>106004</v>
       </c>
       <c r="Y52" t="s">
         <v>96</v>
@@ -7828,7 +8094,7 @@
       <c r="R53" t="s">
         <v>161</v>
       </c>
-      <c r="S53" s="10" t="s">
+      <c r="S53" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T53" t="s">
@@ -7838,7 +8104,7 @@
         <v>288</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>106005</v>
       </c>
       <c r="Y53" t="s">
         <v>96</v>
@@ -7911,7 +8177,7 @@
       <c r="R54" t="s">
         <v>161</v>
       </c>
-      <c r="S54" s="10" t="s">
+      <c r="S54" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T54" t="s">
@@ -7921,7 +8187,7 @@
         <v>292</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>106006</v>
       </c>
       <c r="Y54" t="s">
         <v>96</v>
@@ -7994,7 +8260,7 @@
       <c r="R55" t="s">
         <v>161</v>
       </c>
-      <c r="S55" s="10" t="s">
+      <c r="S55" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T55" t="s">
@@ -8004,7 +8270,7 @@
         <v>296</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>106007</v>
       </c>
       <c r="Y55" t="s">
         <v>96</v>
@@ -8077,7 +8343,7 @@
       <c r="R56" t="s">
         <v>161</v>
       </c>
-      <c r="S56" s="10" t="s">
+      <c r="S56" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T56" t="s">
@@ -8087,7 +8353,7 @@
         <v>300</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>106008</v>
       </c>
       <c r="Y56" t="s">
         <v>96</v>
@@ -8160,7 +8426,7 @@
       <c r="R57" t="s">
         <v>161</v>
       </c>
-      <c r="S57" s="10" t="s">
+      <c r="S57" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T57" t="s">
@@ -8170,7 +8436,7 @@
         <v>304</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>106009</v>
       </c>
       <c r="Y57" t="s">
         <v>96</v>
@@ -8243,7 +8509,7 @@
       <c r="R58" t="s">
         <v>161</v>
       </c>
-      <c r="S58" s="10" t="s">
+      <c r="S58" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T58" t="s">
@@ -8253,7 +8519,7 @@
         <v>308</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>106010</v>
       </c>
       <c r="Y58" t="s">
         <v>96</v>
@@ -8326,7 +8592,7 @@
       <c r="R59" t="s">
         <v>161</v>
       </c>
-      <c r="S59" s="10" t="s">
+      <c r="S59" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T59" t="s">
@@ -8336,7 +8602,7 @@
         <v>312</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>106011</v>
       </c>
       <c r="Y59" t="s">
         <v>96</v>
@@ -8404,7 +8670,7 @@
         <v>317</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>107001</v>
       </c>
       <c r="Y60" t="s">
         <v>96</v>
@@ -8472,7 +8738,7 @@
         <v>321</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>107002</v>
       </c>
       <c r="Y61" t="s">
         <v>96</v>
@@ -8540,7 +8806,7 @@
         <v>325</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>107003</v>
       </c>
       <c r="Y62" t="s">
         <v>96</v>
@@ -8561,71 +8827,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:31">
-      <c r="B63">
+    <row r="63" s="11" customFormat="1" spans="2:31">
+      <c r="B63" s="11">
         <v>7004</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="H63" s="8" t="s">
+      <c r="H63" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I63">
-        <v>300</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63" t="s">
+      <c r="I63" s="11">
+        <v>300</v>
+      </c>
+      <c r="J63" s="11">
+        <v>0</v>
+      </c>
+      <c r="K63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M63" t="b">
-        <v>1</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="T63" t="s">
+      <c r="M63" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" s="11">
+        <v>0</v>
+      </c>
+      <c r="O63" s="11">
+        <v>0</v>
+      </c>
+      <c r="P63" s="11">
+        <v>0</v>
+      </c>
+      <c r="T63" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="U63" t="s">
+      <c r="U63" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="s">
+      <c r="X63" s="11">
+        <v>107004</v>
+      </c>
+      <c r="Y63" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
+      <c r="Z63" s="11"/>
+      <c r="AA63" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8642,7 +8909,7 @@
       <c r="E64" t="s">
         <v>315</v>
       </c>
-      <c r="H64" s="8" t="s">
+      <c r="H64" s="9" t="s">
         <v>121</v>
       </c>
       <c r="I64">
@@ -8676,7 +8943,7 @@
         <v>333</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>107005</v>
       </c>
       <c r="Y64" t="s">
         <v>96</v>
@@ -8710,7 +8977,7 @@
       <c r="E65" t="s">
         <v>315</v>
       </c>
-      <c r="H65" s="8" t="s">
+      <c r="H65" s="9" t="s">
         <v>121</v>
       </c>
       <c r="I65">
@@ -8744,7 +9011,7 @@
         <v>337</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>107006</v>
       </c>
       <c r="Y65" t="s">
         <v>96</v>
@@ -8812,7 +9079,7 @@
         <v>341</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>107007</v>
       </c>
       <c r="Y66" t="s">
         <v>96</v>
@@ -8885,7 +9152,7 @@
       <c r="R67" t="s">
         <v>161</v>
       </c>
-      <c r="S67" s="10" t="s">
+      <c r="S67" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T67" t="s">
@@ -8895,7 +9162,7 @@
         <v>345</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>107008</v>
       </c>
       <c r="Y67" t="s">
         <v>96</v>
@@ -8968,7 +9235,7 @@
       <c r="R68" t="s">
         <v>161</v>
       </c>
-      <c r="S68" s="10" t="s">
+      <c r="S68" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T68" t="s">
@@ -8978,7 +9245,7 @@
         <v>349</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>107009</v>
       </c>
       <c r="Y68" t="s">
         <v>96</v>
@@ -9051,7 +9318,7 @@
       <c r="R69" t="s">
         <v>161</v>
       </c>
-      <c r="S69" s="10" t="s">
+      <c r="S69" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T69" t="s">
@@ -9061,7 +9328,7 @@
         <v>353</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>107010</v>
       </c>
       <c r="Y69" t="s">
         <v>96</v>
@@ -9134,7 +9401,7 @@
       <c r="R70" t="s">
         <v>161</v>
       </c>
-      <c r="S70" s="10" t="s">
+      <c r="S70" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T70" t="s">
@@ -9144,7 +9411,7 @@
         <v>357</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>107011</v>
       </c>
       <c r="Y70" t="s">
         <v>96</v>
@@ -9217,7 +9484,7 @@
       <c r="R71" t="s">
         <v>161</v>
       </c>
-      <c r="S71" s="10" t="s">
+      <c r="S71" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T71" t="s">
@@ -9227,7 +9494,7 @@
         <v>361</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>107012</v>
       </c>
       <c r="Y71" t="s">
         <v>96</v>
@@ -9300,7 +9567,7 @@
       <c r="R72" t="s">
         <v>161</v>
       </c>
-      <c r="S72" s="10" t="s">
+      <c r="S72" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T72" t="s">
@@ -9310,7 +9577,7 @@
         <v>365</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>107013</v>
       </c>
       <c r="Y72" t="s">
         <v>96</v>
@@ -9383,7 +9650,7 @@
       <c r="R73" t="s">
         <v>161</v>
       </c>
-      <c r="S73" s="10" t="s">
+      <c r="S73" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T73" t="s">
@@ -9393,7 +9660,7 @@
         <v>369</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>107014</v>
       </c>
       <c r="Y73" t="s">
         <v>96</v>
@@ -9466,7 +9733,7 @@
       <c r="R74" t="s">
         <v>161</v>
       </c>
-      <c r="S74" s="10" t="s">
+      <c r="S74" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T74" t="s">
@@ -9476,7 +9743,7 @@
         <v>373</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>107015</v>
       </c>
       <c r="Y74" t="s">
         <v>96</v>
@@ -9549,7 +9816,7 @@
       <c r="R75" t="s">
         <v>161</v>
       </c>
-      <c r="S75" s="10" t="s">
+      <c r="S75" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T75" t="s">
@@ -9559,7 +9826,7 @@
         <v>377</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>107016</v>
       </c>
       <c r="Y75" t="s">
         <v>96</v>
@@ -9632,7 +9899,7 @@
       <c r="R76" t="s">
         <v>161</v>
       </c>
-      <c r="S76" s="10" t="s">
+      <c r="S76" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T76" t="s">
@@ -9642,7 +9909,7 @@
         <v>381</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>107017</v>
       </c>
       <c r="Y76" t="s">
         <v>96</v>
@@ -9710,7 +9977,7 @@
         <v>385</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>107018</v>
       </c>
       <c r="Y77" t="s">
         <v>96</v>
@@ -9786,7 +10053,7 @@
       <c r="R78" t="s">
         <v>161</v>
       </c>
-      <c r="S78" s="10" t="s">
+      <c r="S78" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T78" t="s">
@@ -9798,11 +10065,11 @@
       <c r="V78" t="s">
         <v>161</v>
       </c>
-      <c r="W78" s="10" t="s">
+      <c r="W78" s="12" t="s">
         <v>161</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>107019</v>
       </c>
       <c r="Y78" t="s">
         <v>96</v>
@@ -9887,7 +10154,7 @@
       <c r="R79" t="s">
         <v>161</v>
       </c>
-      <c r="S79" s="10" t="s">
+      <c r="S79" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T79" t="s">
@@ -9897,7 +10164,7 @@
         <v>394</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>108001</v>
       </c>
       <c r="Y79" t="s">
         <v>96</v>
@@ -9970,7 +10237,7 @@
       <c r="R80" t="s">
         <v>161</v>
       </c>
-      <c r="S80" s="10" t="s">
+      <c r="S80" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T80" t="s">
@@ -9980,7 +10247,7 @@
         <v>398</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>108003</v>
       </c>
       <c r="Y80" t="s">
         <v>96</v>
@@ -10053,7 +10320,7 @@
       <c r="R81" t="s">
         <v>161</v>
       </c>
-      <c r="S81" s="10" t="s">
+      <c r="S81" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T81" t="s">
@@ -10063,7 +10330,7 @@
         <v>402</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>108004</v>
       </c>
       <c r="Y81" t="s">
         <v>96</v>
@@ -10136,7 +10403,7 @@
       <c r="R82" t="s">
         <v>161</v>
       </c>
-      <c r="S82" s="10" t="s">
+      <c r="S82" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T82" t="s">
@@ -10146,7 +10413,7 @@
         <v>406</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>108005</v>
       </c>
       <c r="Y82" t="s">
         <v>96</v>
@@ -10219,7 +10486,7 @@
       <c r="R83" t="s">
         <v>161</v>
       </c>
-      <c r="S83" s="10" t="s">
+      <c r="S83" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T83" t="s">
@@ -10229,7 +10496,7 @@
         <v>410</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>108007</v>
       </c>
       <c r="Y83" t="s">
         <v>96</v>
@@ -10302,7 +10569,7 @@
       <c r="R84" t="s">
         <v>161</v>
       </c>
-      <c r="S84" s="10" t="s">
+      <c r="S84" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T84" t="s">
@@ -10312,7 +10579,7 @@
         <v>414</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>108008</v>
       </c>
       <c r="Y84" t="s">
         <v>96</v>
@@ -10380,7 +10647,7 @@
         <v>418</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>108009</v>
       </c>
       <c r="Y85" t="s">
         <v>96</v>
@@ -10448,7 +10715,7 @@
         <v>422</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>108010</v>
       </c>
       <c r="Y86" t="s">
         <v>96</v>
@@ -10516,7 +10783,7 @@
         <v>426</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>108011</v>
       </c>
       <c r="Y87" t="s">
         <v>96</v>
@@ -10592,7 +10859,7 @@
       <c r="R88" t="s">
         <v>161</v>
       </c>
-      <c r="S88" s="10" t="s">
+      <c r="S88" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T88" t="s">
@@ -10604,11 +10871,11 @@
       <c r="V88" t="s">
         <v>161</v>
       </c>
-      <c r="W88" s="10" t="s">
+      <c r="W88" s="12" t="s">
         <v>161</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>108012</v>
       </c>
       <c r="Y88" t="s">
         <v>96</v>
@@ -10696,7 +10963,7 @@
       <c r="R89" t="s">
         <v>161</v>
       </c>
-      <c r="S89" s="10" t="s">
+      <c r="S89" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T89" t="s">
@@ -10708,11 +10975,11 @@
       <c r="V89" t="s">
         <v>161</v>
       </c>
-      <c r="W89" s="10" t="s">
+      <c r="W89" s="12" t="s">
         <v>161</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>108013</v>
       </c>
       <c r="Y89" t="s">
         <v>96</v>
@@ -10795,7 +11062,7 @@
         <v>440</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>109001</v>
       </c>
       <c r="Y90" t="s">
         <v>96</v>
@@ -10871,11 +11138,11 @@
       <c r="U91" t="s">
         <v>445</v>
       </c>
-      <c r="W91" s="10" t="s">
+      <c r="W91" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>109002</v>
       </c>
       <c r="Y91" t="s">
         <v>96</v>
@@ -10951,11 +11218,11 @@
       <c r="U92" t="s">
         <v>450</v>
       </c>
-      <c r="W92" s="10" t="s">
+      <c r="W92" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>109003</v>
       </c>
       <c r="Y92" t="s">
         <v>96</v>
@@ -11031,11 +11298,11 @@
       <c r="U93" t="s">
         <v>454</v>
       </c>
-      <c r="W93" s="10" t="s">
+      <c r="W93" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>109004</v>
       </c>
       <c r="Y93" t="s">
         <v>96</v>
@@ -11111,11 +11378,11 @@
       <c r="U94" t="s">
         <v>458</v>
       </c>
-      <c r="W94" s="10" t="s">
+      <c r="W94" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>109005</v>
       </c>
       <c r="Y94" t="s">
         <v>96</v>
@@ -11191,11 +11458,11 @@
       <c r="U95" t="s">
         <v>462</v>
       </c>
-      <c r="W95" s="10" t="s">
+      <c r="W95" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>109006</v>
       </c>
       <c r="Y95" t="s">
         <v>96</v>
@@ -11271,11 +11538,11 @@
       <c r="U96" t="s">
         <v>466</v>
       </c>
-      <c r="W96" s="10" t="s">
+      <c r="W96" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>109007</v>
       </c>
       <c r="Y96" t="s">
         <v>96</v>
@@ -11351,11 +11618,11 @@
       <c r="U97" t="s">
         <v>470</v>
       </c>
-      <c r="W97" s="10" t="s">
+      <c r="W97" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>109008</v>
       </c>
       <c r="Y97" t="s">
         <v>96</v>
@@ -11425,11 +11692,11 @@
       <c r="U98" t="s">
         <v>474</v>
       </c>
-      <c r="W98" s="10" t="s">
+      <c r="W98" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>109009</v>
       </c>
       <c r="Y98" t="s">
         <v>96</v>
@@ -11506,7 +11773,7 @@
         <v>478</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>109010</v>
       </c>
       <c r="Y99" t="s">
         <v>96</v>
@@ -11582,11 +11849,11 @@
       <c r="U100" t="s">
         <v>482</v>
       </c>
-      <c r="W100" s="10" t="s">
+      <c r="W100" s="12" t="s">
         <v>446</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>109011</v>
       </c>
       <c r="Y100" t="s">
         <v>96</v>
@@ -11607,213 +11874,216 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:31">
-      <c r="B101">
+    <row r="101" s="11" customFormat="1" spans="2:31">
+      <c r="B101" s="11">
         <v>10001</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I101">
-        <v>300</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101" t="b">
-        <v>1</v>
-      </c>
-      <c r="L101" t="s">
+      <c r="I101" s="11">
+        <v>300</v>
+      </c>
+      <c r="J101" s="11">
+        <v>0</v>
+      </c>
+      <c r="K101" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L101" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M101" t="b">
-        <v>1</v>
-      </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>0</v>
-      </c>
-      <c r="T101" t="s">
+      <c r="M101" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N101" s="11">
+        <v>0</v>
+      </c>
+      <c r="O101" s="11">
+        <v>0</v>
+      </c>
+      <c r="P101" s="11">
+        <v>0</v>
+      </c>
+      <c r="T101" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="U101" t="s">
+      <c r="U101" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="X101">
-        <v>0</v>
-      </c>
-      <c r="Y101" t="s">
+      <c r="X101" s="11">
+        <v>110001</v>
+      </c>
+      <c r="Y101" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA101" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="2:31">
-      <c r="B102">
+      <c r="Z101" s="11"/>
+      <c r="AA101" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" s="11" customFormat="1" spans="2:31">
+      <c r="B102" s="11">
         <v>11001</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="H102" t="s">
+      <c r="H102" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I102">
-        <v>300</v>
-      </c>
-      <c r="J102">
-        <v>0</v>
-      </c>
-      <c r="K102" t="b">
-        <v>1</v>
-      </c>
-      <c r="L102" t="s">
+      <c r="I102" s="11">
+        <v>300</v>
+      </c>
+      <c r="J102" s="11">
+        <v>0</v>
+      </c>
+      <c r="K102" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L102" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M102" t="b">
-        <v>1</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <v>0</v>
-      </c>
-      <c r="T102" t="s">
+      <c r="M102" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N102" s="11">
+        <v>0</v>
+      </c>
+      <c r="O102" s="11">
+        <v>0</v>
+      </c>
+      <c r="P102" s="11">
+        <v>0</v>
+      </c>
+      <c r="T102" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="U102" t="s">
+      <c r="U102" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="W102" s="10" t="s">
+      <c r="W102" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="X102">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="s">
+      <c r="X102" s="11">
+        <v>111001</v>
+      </c>
+      <c r="Y102" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="2:31">
-      <c r="B103">
+      <c r="Z102" s="11"/>
+      <c r="AA102" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" s="11" customFormat="1" spans="2:31">
+      <c r="B103" s="11">
         <v>11002</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="G103">
+      <c r="G103" s="11">
         <v>11001</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H103" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I103">
-        <v>300</v>
-      </c>
-      <c r="J103">
-        <v>0</v>
-      </c>
-      <c r="K103" t="b">
-        <v>1</v>
-      </c>
-      <c r="L103" t="s">
+      <c r="I103" s="11">
+        <v>300</v>
+      </c>
+      <c r="J103" s="11">
+        <v>0</v>
+      </c>
+      <c r="K103" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L103" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M103" t="b">
-        <v>1</v>
-      </c>
-      <c r="N103">
-        <v>0</v>
-      </c>
-      <c r="O103">
-        <v>0</v>
-      </c>
-      <c r="P103">
-        <v>0</v>
-      </c>
-      <c r="T103" t="s">
+      <c r="M103" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N103" s="11">
+        <v>0</v>
+      </c>
+      <c r="O103" s="11">
+        <v>0</v>
+      </c>
+      <c r="P103" s="11">
+        <v>0</v>
+      </c>
+      <c r="T103" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="U103" t="s">
+      <c r="U103" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="X103">
-        <v>0</v>
-      </c>
-      <c r="Y103" t="s">
+      <c r="X103" s="11">
+        <v>111002</v>
+      </c>
+      <c r="Y103" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="AA103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE103" t="b">
+      <c r="Z103" s="11"/>
+      <c r="AA103" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB103" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -11836,7 +12106,7 @@
       <c r="G104" t="s">
         <v>161</v>
       </c>
-      <c r="H104" s="8" t="s">
+      <c r="H104" s="9" t="s">
         <v>121</v>
       </c>
       <c r="I104">
@@ -11869,7 +12139,7 @@
       <c r="R104" t="s">
         <v>161</v>
       </c>
-      <c r="S104" s="10" t="s">
+      <c r="S104" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T104" t="s">
@@ -11879,7 +12149,7 @@
         <v>501</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>112001</v>
       </c>
       <c r="Y104" t="s">
         <v>96</v>
@@ -11919,7 +12189,7 @@
       <c r="G105" t="s">
         <v>161</v>
       </c>
-      <c r="H105" s="8" t="s">
+      <c r="H105" s="9" t="s">
         <v>140</v>
       </c>
       <c r="I105">
@@ -11952,7 +12222,7 @@
       <c r="R105" t="s">
         <v>161</v>
       </c>
-      <c r="S105" s="10" t="s">
+      <c r="S105" s="12" t="s">
         <v>161</v>
       </c>
       <c r="T105" t="s">
@@ -11962,7 +12232,7 @@
         <v>505</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>112002</v>
       </c>
       <c r="Y105" t="s">
         <v>96</v>
@@ -12020,22 +12290,23 @@
       <c r="R106">
         <v>100</v>
       </c>
-      <c r="S106" s="10"/>
+      <c r="S106" s="12"/>
       <c r="T106" t="s">
         <v>157</v>
       </c>
       <c r="U106" t="s">
         <v>158</v>
       </c>
-      <c r="W106" s="10" t="s">
+      <c r="W106" s="12" t="s">
         <v>509</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>192005</v>
       </c>
       <c r="Y106" t="s">
         <v>96</v>
       </c>
+      <c r="Z106"/>
       <c r="AA106" t="b">
         <v>1</v>
       </c>
@@ -12089,7 +12360,7 @@
       <c r="R107">
         <v>100</v>
       </c>
-      <c r="S107" s="10"/>
+      <c r="S107" s="12"/>
       <c r="T107" t="s">
         <v>111</v>
       </c>
@@ -12099,15 +12370,16 @@
       <c r="V107">
         <v>1012</v>
       </c>
-      <c r="W107" s="10" t="s">
+      <c r="W107" s="12" t="s">
         <v>509</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>191012</v>
       </c>
       <c r="Y107" t="s">
         <v>96</v>
       </c>
+      <c r="Z107"/>
       <c r="AA107" t="b">
         <v>1</v>
       </c>
@@ -12151,10 +12423,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H79 H104 H105 H5:H16 H18:H27 H30:H77 H80:H82 H83:H86 H90:H103 H106:H108">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H16 H18:H27 H30:H77 H79:H86 H90:H108">
       <formula1>枚举示例!$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L79 L104 L105 L5:L16 L18:L27 L30:L77 L80:L82 L83:L87 L90:L103 L106:L108">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L16 L18:L27 L30:L77 L79:L87 L90:L108">
       <formula1>枚举示例!$C$18:$C$23</formula1>
     </dataValidation>
   </dataValidations>
@@ -12166,8 +12438,8 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <dimension ref="A1:S12"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="6.83333333333333" customWidth="1"/>
@@ -12185,10 +12457,12 @@
     <col min="14" max="14" width="13" customWidth="1"/>
     <col min="15" max="15" width="15.6666666666667" customWidth="1"/>
     <col min="16" max="16" width="20.0833333333333" customWidth="1"/>
-    <col min="17" max="17" width="22.1666666666667" customWidth="1"/>
+    <col min="17" max="17" width="21.9166666666667" customWidth="1"/>
+    <col min="18" max="18" width="22.1666666666667" customWidth="1"/>
+    <col min="19" max="19" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12196,52 +12470,58 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="F1" t="s">
         <v>600</v>
       </c>
       <c r="G1" t="s">
+        <v>763</v>
+      </c>
+      <c r="H1" t="s">
+        <v>764</v>
+      </c>
+      <c r="I1" t="s">
         <v>765</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>766</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>767</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>768</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>769</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>770</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>771</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>772</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>773</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>774</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -12293,8 +12573,14 @@
       <c r="Q2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="77" customHeight="1" spans="1:17">
+      <c r="R2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="77" customHeight="1" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
@@ -12346,66 +12632,78 @@
       <c r="Q3" s="1" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C4" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D4" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E4" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F4" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="G4" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="H4" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="I4" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="J4" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="K4" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="L4" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="M4" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="N4" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="O4" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="P4" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="Q4" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
+        <v>810</v>
+      </c>
+      <c r="R4" t="s">
+        <v>811</v>
+      </c>
+      <c r="S4" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -12414,28 +12712,28 @@
         <v>0</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="H5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="I5" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="J5" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="K5" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="L5" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="M5" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="N5">
         <v>92005</v>
@@ -12446,16 +12744,16 @@
       <c r="P5">
         <v>0</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>401001</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:19">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -12464,28 +12762,28 @@
         <v>1</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="H6" t="s">
+        <v>823</v>
+      </c>
+      <c r="I6" t="s">
+        <v>816</v>
+      </c>
+      <c r="J6" t="s">
+        <v>824</v>
+      </c>
+      <c r="K6" t="s">
+        <v>824</v>
+      </c>
+      <c r="L6" t="s">
         <v>819</v>
       </c>
-      <c r="I6" t="s">
-        <v>812</v>
-      </c>
-      <c r="J6" t="s">
-        <v>820</v>
-      </c>
-      <c r="K6" t="s">
-        <v>820</v>
-      </c>
-      <c r="L6" t="s">
-        <v>815</v>
-      </c>
       <c r="M6" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -12496,16 +12794,16 @@
       <c r="P6">
         <v>0</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>401002</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:19">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -12514,28 +12812,28 @@
         <v>0</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="H7" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="I7" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="J7" t="s">
+        <v>829</v>
+      </c>
+      <c r="K7" t="s">
+        <v>830</v>
+      </c>
+      <c r="L7" t="s">
+        <v>819</v>
+      </c>
+      <c r="M7" t="s">
         <v>825</v>
-      </c>
-      <c r="K7" t="s">
-        <v>826</v>
-      </c>
-      <c r="L7" t="s">
-        <v>815</v>
-      </c>
-      <c r="M7" t="s">
-        <v>821</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -12546,16 +12844,16 @@
       <c r="P7">
         <v>0</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>401003</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:19">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -12564,28 +12862,28 @@
         <v>0</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="H8" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="I8" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="J8" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="K8" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="L8" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="M8" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="N8">
         <v>91012</v>
@@ -12596,8 +12894,220 @@
       <c r="P8">
         <v>0</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>401004</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:19">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>813</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>814</v>
+      </c>
+      <c r="H9" t="s">
+        <v>815</v>
+      </c>
+      <c r="I9" t="s">
+        <v>816</v>
+      </c>
+      <c r="J9" t="s">
+        <v>817</v>
+      </c>
+      <c r="K9" t="s">
+        <v>818</v>
+      </c>
+      <c r="L9" t="s">
+        <v>819</v>
+      </c>
+      <c r="M9" t="s">
+        <v>820</v>
+      </c>
+      <c r="N9">
+        <v>92005</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>401005</v>
+      </c>
+      <c r="S9">
+        <v>403105</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:19">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>821</v>
+      </c>
+      <c r="D10">
+        <v>80</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>822</v>
+      </c>
+      <c r="H10" t="s">
+        <v>823</v>
+      </c>
+      <c r="I10" t="s">
+        <v>816</v>
+      </c>
+      <c r="J10" t="s">
+        <v>824</v>
+      </c>
+      <c r="K10" t="s">
+        <v>824</v>
+      </c>
+      <c r="L10" t="s">
+        <v>819</v>
+      </c>
+      <c r="M10" t="s">
+        <v>825</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>2500</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>401006</v>
+      </c>
+      <c r="S10">
+        <v>403106</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:19">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>826</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>827</v>
+      </c>
+      <c r="H11" t="s">
+        <v>828</v>
+      </c>
+      <c r="I11" t="s">
+        <v>816</v>
+      </c>
+      <c r="J11" t="s">
+        <v>829</v>
+      </c>
+      <c r="K11" t="s">
+        <v>830</v>
+      </c>
+      <c r="L11" t="s">
+        <v>819</v>
+      </c>
+      <c r="M11" t="s">
+        <v>825</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>2500</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>401007</v>
+      </c>
+      <c r="S11">
+        <v>403107</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:19">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>831</v>
+      </c>
+      <c r="D12">
+        <v>120</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>832</v>
+      </c>
+      <c r="H12" t="s">
+        <v>833</v>
+      </c>
+      <c r="I12" t="s">
+        <v>816</v>
+      </c>
+      <c r="J12" t="s">
+        <v>834</v>
+      </c>
+      <c r="K12" t="s">
+        <v>834</v>
+      </c>
+      <c r="L12" t="s">
+        <v>819</v>
+      </c>
+      <c r="M12" t="s">
+        <v>820</v>
+      </c>
+      <c r="N12">
+        <v>91012</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>401008</v>
+      </c>
+      <c r="S12">
+        <v>403108</v>
       </c>
     </row>
   </sheetData>
@@ -12609,13 +13119,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultColWidth="27" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="15.8333333333333" customWidth="1"/>
-    <col min="3" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="18.0833333333333" customWidth="1"/>
     <col min="6" max="6" width="32.5" customWidth="1"/>
     <col min="7" max="7" width="48.0833333333333" customWidth="1"/>
     <col min="8" max="8" width="19.8333333333333" customWidth="1"/>
@@ -12630,7 +13141,7 @@
     <col min="17" max="16384" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12638,46 +13149,52 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E1" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="H1" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="I1" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="J1" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="K1" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="L1" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="M1" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="N1" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="O1" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="P1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" t="s">
+        <v>845</v>
+      </c>
+      <c r="R1" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -12723,105 +13240,123 @@
       <c r="P2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="72" customHeight="1" spans="1:16">
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="72" customHeight="1" spans="1:18">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>844</v>
+        <v>849</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>850</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>845</v>
+      <c r="H3" s="3" t="s">
+        <v>851</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <v>859</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="C4" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D4" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="E4" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="F4" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="G4" t="s">
         <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="I4" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="J4" t="s">
         <v>81</v>
       </c>
       <c r="K4" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="L4" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="M4" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="N4" t="s">
         <v>83</v>
       </c>
       <c r="O4" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="P4" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>799</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>872</v>
+      </c>
+      <c r="R4" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>161</v>
       </c>
@@ -12829,22 +13364,22 @@
         <v>401001</v>
       </c>
       <c r="C5" t="s">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="D5" t="s">
-        <v>865</v>
+        <v>875</v>
       </c>
       <c r="E5" t="s">
         <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>866</v>
+        <v>876</v>
       </c>
       <c r="G5" t="s">
-        <v>867</v>
+        <v>877</v>
       </c>
       <c r="H5" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -12870,8 +13405,14 @@
       <c r="P5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
         <v>161</v>
       </c>
@@ -12879,22 +13420,22 @@
         <v>401002</v>
       </c>
       <c r="C6" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="D6" t="s">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="E6" t="s">
         <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>871</v>
+        <v>881</v>
       </c>
       <c r="G6" t="s">
-        <v>872</v>
+        <v>882</v>
       </c>
       <c r="H6" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -12920,8 +13461,14 @@
       <c r="P6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
         <v>161</v>
       </c>
@@ -12929,22 +13476,22 @@
         <v>401003</v>
       </c>
       <c r="C7" t="s">
-        <v>873</v>
+        <v>883</v>
       </c>
       <c r="D7" t="s">
-        <v>874</v>
+        <v>884</v>
       </c>
       <c r="E7" t="s">
         <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>875</v>
+        <v>885</v>
       </c>
       <c r="G7" t="s">
-        <v>876</v>
+        <v>886</v>
       </c>
       <c r="H7" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -12970,8 +13517,14 @@
       <c r="P7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
         <v>161</v>
       </c>
@@ -12979,151 +13532,1272 @@
         <v>401004</v>
       </c>
       <c r="C8" t="s">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="D8" t="s">
-        <v>878</v>
+        <v>888</v>
       </c>
       <c r="E8" t="s">
         <v>96</v>
       </c>
       <c r="F8" t="s">
+        <v>889</v>
+      </c>
+      <c r="G8" t="s">
+        <v>890</v>
+      </c>
+      <c r="H8" t="s">
+        <v>878</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>161</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:18">
+      <c r="A9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9">
+        <v>401005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>874</v>
+      </c>
+      <c r="D9" t="s">
+        <v>891</v>
+      </c>
+      <c r="E9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" t="s">
+        <v>876</v>
+      </c>
+      <c r="G9" t="s">
+        <v>877</v>
+      </c>
+      <c r="H9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>161</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:18">
+      <c r="A10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10">
+        <v>401006</v>
+      </c>
+      <c r="C10" t="s">
         <v>879</v>
       </c>
-      <c r="G8" t="s">
-        <v>880</v>
-      </c>
-      <c r="H8" t="s">
-        <v>868</v>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>161</v>
-      </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10">
-        <v>402001</v>
-      </c>
-      <c r="C10" t="s">
-        <v>881</v>
-      </c>
       <c r="D10" t="s">
-        <v>642</v>
+        <v>892</v>
       </c>
       <c r="E10" t="s">
         <v>96</v>
       </c>
       <c r="F10" t="s">
+        <v>881</v>
+      </c>
+      <c r="G10" t="s">
         <v>882</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
+        <v>878</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>161</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:18">
+      <c r="A11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11">
+        <v>401007</v>
+      </c>
+      <c r="C11" t="s">
         <v>883</v>
       </c>
-      <c r="H10" t="s">
-        <v>868</v>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" t="b">
-        <v>1</v>
-      </c>
-      <c r="N10" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" t="s">
-        <v>161</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B11">
+      <c r="D11" t="s">
+        <v>893</v>
+      </c>
+      <c r="E11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" t="s">
+        <v>885</v>
+      </c>
+      <c r="G11" t="s">
+        <v>886</v>
+      </c>
+      <c r="H11" t="s">
+        <v>878</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:18">
+      <c r="A12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12">
+        <v>401008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>887</v>
+      </c>
+      <c r="D12" t="s">
+        <v>894</v>
+      </c>
+      <c r="E12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" t="s">
+        <v>889</v>
+      </c>
+      <c r="G12" t="s">
+        <v>890</v>
+      </c>
+      <c r="H12" t="s">
+        <v>878</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>161</v>
+      </c>
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>895</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14">
+        <v>402001</v>
+      </c>
+      <c r="C14" t="s">
+        <v>896</v>
+      </c>
+      <c r="D14" t="s">
+        <v>642</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" t="s">
+        <v>897</v>
+      </c>
+      <c r="G14" t="s">
+        <v>898</v>
+      </c>
+      <c r="H14" t="s">
+        <v>878</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="s">
+        <v>161</v>
+      </c>
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="B15">
+        <v>402002</v>
+      </c>
+      <c r="C15" t="s">
+        <v>899</v>
+      </c>
+      <c r="D15" t="s">
+        <v>900</v>
+      </c>
+      <c r="E15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" t="s">
+        <v>901</v>
+      </c>
+      <c r="G15" t="s">
+        <v>902</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="B16">
+        <v>402003</v>
+      </c>
+      <c r="C16" t="s">
+        <v>903</v>
+      </c>
+      <c r="D16" t="s">
+        <v>904</v>
+      </c>
+      <c r="E16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" t="s">
+        <v>905</v>
+      </c>
+      <c r="G16" t="s">
+        <v>906</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18">
         <v>403001</v>
       </c>
-      <c r="C11" t="s">
-        <v>884</v>
-      </c>
-      <c r="D11" t="s">
-        <v>885</v>
-      </c>
-      <c r="E11" t="s">
-        <v>886</v>
-      </c>
-      <c r="F11" t="s">
-        <v>887</v>
-      </c>
-      <c r="G11" t="s">
-        <v>888</v>
-      </c>
-      <c r="H11" t="s">
-        <v>161</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" t="b">
-        <v>1</v>
-      </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>889</v>
-      </c>
-      <c r="P11" t="b">
-        <v>1</v>
+      <c r="C18" t="s">
+        <v>908</v>
+      </c>
+      <c r="D18" t="s">
+        <v>909</v>
+      </c>
+      <c r="E18" t="s">
+        <v>910</v>
+      </c>
+      <c r="F18" t="s">
+        <v>911</v>
+      </c>
+      <c r="G18" t="s">
+        <v>912</v>
+      </c>
+      <c r="H18" t="s">
+        <v>161</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>913</v>
+      </c>
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="B19">
+        <v>403002</v>
+      </c>
+      <c r="C19" t="s">
+        <v>914</v>
+      </c>
+      <c r="D19" t="s">
+        <v>915</v>
+      </c>
+      <c r="E19" t="s">
+        <v>910</v>
+      </c>
+      <c r="F19" t="s">
+        <v>916</v>
+      </c>
+      <c r="G19" t="s">
+        <v>917</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>918</v>
+      </c>
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="B20">
+        <v>403003</v>
+      </c>
+      <c r="C20" t="s">
+        <v>919</v>
+      </c>
+      <c r="D20" t="s">
+        <v>920</v>
+      </c>
+      <c r="E20" t="s">
+        <v>910</v>
+      </c>
+      <c r="F20" t="s">
+        <v>921</v>
+      </c>
+      <c r="G20" t="s">
+        <v>922</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>918</v>
+      </c>
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="B21">
+        <v>403105</v>
+      </c>
+      <c r="E21" t="s">
+        <v>910</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>923</v>
+      </c>
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="B22">
+        <v>403106</v>
+      </c>
+      <c r="E22" t="s">
+        <v>910</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>924</v>
+      </c>
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="B23">
+        <v>403107</v>
+      </c>
+      <c r="E23" t="s">
+        <v>910</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>925</v>
+      </c>
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="B24">
+        <v>403108</v>
+      </c>
+      <c r="E24" t="s">
+        <v>910</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" t="s">
+        <v>926</v>
+      </c>
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="B26">
+        <v>404001</v>
+      </c>
+      <c r="C26" t="s">
+        <v>928</v>
+      </c>
+      <c r="D26" t="s">
+        <v>929</v>
+      </c>
+      <c r="E26" t="s">
+        <v>930</v>
+      </c>
+      <c r="F26" t="s">
+        <v>931</v>
+      </c>
+      <c r="G26" t="s">
+        <v>932</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>933</v>
+      </c>
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="B27">
+        <v>404002</v>
+      </c>
+      <c r="C27" t="s">
+        <v>934</v>
+      </c>
+      <c r="D27" t="s">
+        <v>935</v>
+      </c>
+      <c r="E27" t="s">
+        <v>930</v>
+      </c>
+      <c r="F27" t="s">
+        <v>936</v>
+      </c>
+      <c r="G27" t="s">
+        <v>937</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>938</v>
+      </c>
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="B28">
+        <v>404004</v>
+      </c>
+      <c r="C28" t="s">
+        <v>939</v>
+      </c>
+      <c r="D28" t="s">
+        <v>940</v>
+      </c>
+      <c r="E28" t="s">
+        <v>930</v>
+      </c>
+      <c r="F28" t="s">
+        <v>941</v>
+      </c>
+      <c r="G28" t="s">
+        <v>942</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>943</v>
+      </c>
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="B29">
+        <v>404005</v>
+      </c>
+      <c r="C29" t="s">
+        <v>944</v>
+      </c>
+      <c r="D29" t="s">
+        <v>945</v>
+      </c>
+      <c r="E29" t="s">
+        <v>930</v>
+      </c>
+      <c r="F29" t="s">
+        <v>946</v>
+      </c>
+      <c r="G29" t="s">
+        <v>947</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>938</v>
+      </c>
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="B30">
+        <v>404007</v>
+      </c>
+      <c r="C30" t="s">
+        <v>948</v>
+      </c>
+      <c r="D30" t="s">
+        <v>949</v>
+      </c>
+      <c r="E30" t="s">
+        <v>930</v>
+      </c>
+      <c r="F30" t="s">
+        <v>950</v>
+      </c>
+      <c r="G30" t="s">
+        <v>951</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" t="s">
+        <v>943</v>
+      </c>
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="B31">
+        <v>404008</v>
+      </c>
+      <c r="C31" t="s">
+        <v>952</v>
+      </c>
+      <c r="D31" t="s">
+        <v>953</v>
+      </c>
+      <c r="E31" t="s">
+        <v>930</v>
+      </c>
+      <c r="F31" t="s">
+        <v>954</v>
+      </c>
+      <c r="G31" t="s">
+        <v>955</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="b">
+        <v>1</v>
+      </c>
+      <c r="N31" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>938</v>
+      </c>
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="B32">
+        <v>404010</v>
+      </c>
+      <c r="C32" t="s">
+        <v>956</v>
+      </c>
+      <c r="D32" t="s">
+        <v>957</v>
+      </c>
+      <c r="E32" t="s">
+        <v>930</v>
+      </c>
+      <c r="F32" t="s">
+        <v>958</v>
+      </c>
+      <c r="G32" t="s">
+        <v>959</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="b">
+        <v>1</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>943</v>
+      </c>
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="B33">
+        <v>404011</v>
+      </c>
+      <c r="C33" t="s">
+        <v>960</v>
+      </c>
+      <c r="D33" t="s">
+        <v>961</v>
+      </c>
+      <c r="E33" t="s">
+        <v>930</v>
+      </c>
+      <c r="F33" t="s">
+        <v>962</v>
+      </c>
+      <c r="G33" t="s">
+        <v>963</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="b">
+        <v>1</v>
+      </c>
+      <c r="N33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>938</v>
+      </c>
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="B34">
+        <v>404013</v>
+      </c>
+      <c r="C34" t="s">
+        <v>964</v>
+      </c>
+      <c r="D34" t="s">
+        <v>965</v>
+      </c>
+      <c r="E34" t="s">
+        <v>930</v>
+      </c>
+      <c r="F34" t="s">
+        <v>966</v>
+      </c>
+      <c r="G34" t="s">
+        <v>967</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="b">
+        <v>1</v>
+      </c>
+      <c r="N34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>943</v>
+      </c>
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="B36">
+        <v>405001</v>
+      </c>
+      <c r="C36" t="s">
+        <v>969</v>
+      </c>
+      <c r="D36" t="s">
+        <v>970</v>
+      </c>
+      <c r="E36" t="s">
+        <v>930</v>
+      </c>
+      <c r="F36" t="s">
+        <v>971</v>
+      </c>
+      <c r="G36" t="s">
+        <v>972</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" t="b">
+        <v>0</v>
+      </c>
+      <c r="O36" t="s">
+        <v>943</v>
+      </c>
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -13144,10 +14818,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>512</v>
       </c>
       <c r="E2" t="s">
@@ -13156,130 +14830,130 @@
       <c r="F2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="J2" s="5">
-        <v>1</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="J2" s="6">
+        <v>1</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="6" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="6">
         <v>2</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="6" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="6"/>
+      <c r="H4" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="6">
         <v>4</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="6" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="6">
         <v>8</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="6" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>539</v>
       </c>
       <c r="E6" t="s">
@@ -13288,248 +14962,248 @@
       <c r="F6" t="s">
         <v>140</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="6"/>
+      <c r="H6" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="6">
         <v>16</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="P6" s="6" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="6">
         <v>32</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="6" t="s">
         <v>550</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="P7" s="6" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="6">
         <v>64</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="P8" s="6" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>562</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>564</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="6">
         <v>128</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="P9" s="6" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>568</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="6" t="s">
         <v>570</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="6">
         <v>256</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="6" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="6" t="s">
         <v>574</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="6">
         <v>512</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="6" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="6">
         <v>1024</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="6" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>580</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>581</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="6">
         <v>2048</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="6" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>585</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>586</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>591</v>
       </c>
     </row>
@@ -13562,7 +15236,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -13606,7 +15280,7 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B2" t="s">
@@ -13690,47 +15364,47 @@
         <v>617</v>
       </c>
     </row>
-    <row r="4" s="9" customFormat="1" spans="1:14">
-      <c r="A4" s="3" t="s">
+    <row r="4" s="10" customFormat="1" spans="1:14">
+      <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>623</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>625</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>626</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="10" t="s">
         <v>629</v>
       </c>
     </row>
@@ -13741,10 +15415,10 @@
       <c r="C5" t="s">
         <v>630</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>632</v>
       </c>
       <c r="F5">
@@ -13769,10 +15443,10 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>402002</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>403002</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -13782,10 +15456,10 @@
       <c r="C6" t="s">
         <v>635</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>632</v>
       </c>
       <c r="F6">
@@ -13810,10 +15484,10 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>402003</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>403003</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -13823,10 +15497,10 @@
       <c r="C7" t="s">
         <v>637</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>637</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>632</v>
       </c>
       <c r="F7">
@@ -13867,7 +15541,7 @@
       <c r="D8" t="s">
         <v>639</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>640</v>
       </c>
       <c r="F8">
@@ -13905,10 +15579,10 @@
       <c r="C9" t="s">
         <v>642</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>632</v>
       </c>
       <c r="F9">
@@ -13940,13 +15614,13 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="E15" s="5"/>
+      <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="E16" s="5"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="5"/>
+      <c r="E17" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13957,7 +15631,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -13969,14 +15643,14 @@
     <col min="8" max="8" width="14.25" customWidth="1"/>
     <col min="9" max="9" width="13.1666666666667" customWidth="1"/>
     <col min="10" max="10" width="10.25" customWidth="1"/>
-    <col min="11" max="11" width="16.5833333333333" customWidth="1"/>
-    <col min="12" max="12" width="8.83333333333333" customWidth="1"/>
+    <col min="11" max="11" width="18.6666666666667" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
     <col min="13" max="13" width="30.8333333333333" customWidth="1"/>
     <col min="14" max="14" width="45.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -14001,23 +15675,20 @@
         <v>649</v>
       </c>
       <c r="I1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J1" t="s">
         <v>650</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>651</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>652</v>
       </c>
-      <c r="L1" t="s">
-        <v>600</v>
-      </c>
-      <c r="M1" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B2" t="s">
@@ -14042,27 +15713,27 @@
         <v>30</v>
       </c>
       <c r="I2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" t="s">
         <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>35</v>
       </c>
       <c r="K2" t="s">
         <v>30</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:14">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="128" customHeight="1" spans="1:13">
+      <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>654</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -14078,23 +15749,23 @@
         <v>658</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>661</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>627</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:13">
+      <c r="A4" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B4" t="s">
@@ -14119,25 +15790,22 @@
         <v>667</v>
       </c>
       <c r="I4" t="s">
+        <v>627</v>
+      </c>
+      <c r="J4" t="s">
         <v>668</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>669</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>670</v>
-      </c>
-      <c r="L4" t="s">
-        <v>627</v>
       </c>
       <c r="M4" t="s">
         <v>671</v>
       </c>
-      <c r="N4" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+    </row>
+    <row r="5" spans="1:13">
       <c r="B5">
         <v>1001</v>
       </c>
@@ -14159,23 +15827,23 @@
       <c r="H5">
         <v>1</v>
       </c>
-      <c r="I5">
-        <v>50</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>404001</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -14197,26 +15865,23 @@
       <c r="H6">
         <v>1</v>
       </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>404002</v>
       </c>
       <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -14238,23 +15903,23 @@
       <c r="H7">
         <v>1</v>
       </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7" t="b">
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-      <c r="N7" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -14276,23 +15941,23 @@
       <c r="H8">
         <v>1</v>
       </c>
-      <c r="I8">
-        <v>50</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>404004</v>
       </c>
       <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -14314,23 +15979,23 @@
       <c r="H9">
         <v>1</v>
       </c>
-      <c r="I9">
-        <v>100</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>404005</v>
       </c>
       <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9" t="b">
-        <v>1</v>
-      </c>
-      <c r="N9" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -14352,26 +16017,23 @@
       <c r="H10">
         <v>1</v>
       </c>
-      <c r="I10">
-        <v>10</v>
-      </c>
-      <c r="J10" t="b">
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="B11">
         <v>1007</v>
       </c>
@@ -14393,23 +16055,23 @@
       <c r="H11">
         <v>1</v>
       </c>
-      <c r="I11">
-        <v>50</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>404007</v>
       </c>
       <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
-      <c r="N11" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="B12">
         <v>1008</v>
       </c>
@@ -14431,23 +16093,23 @@
       <c r="H12">
         <v>1</v>
       </c>
-      <c r="I12">
-        <v>100</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>404008</v>
       </c>
       <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12" t="b">
-        <v>1</v>
-      </c>
-      <c r="N12" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="B13">
         <v>1009</v>
       </c>
@@ -14469,26 +16131,23 @@
       <c r="H13">
         <v>1</v>
       </c>
-      <c r="I13">
-        <v>10</v>
-      </c>
-      <c r="J13" t="b">
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="B14">
         <v>1010</v>
       </c>
@@ -14510,23 +16169,23 @@
       <c r="H14">
         <v>1</v>
       </c>
-      <c r="I14">
-        <v>50</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>404010</v>
       </c>
       <c r="K14">
-        <v>1</v>
-      </c>
-      <c r="L14" t="b">
-        <v>1</v>
-      </c>
-      <c r="N14" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="B15">
         <v>1011</v>
       </c>
@@ -14548,23 +16207,23 @@
       <c r="H15">
         <v>1</v>
       </c>
-      <c r="I15">
-        <v>100</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>404011</v>
       </c>
       <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15" t="b">
-        <v>1</v>
-      </c>
-      <c r="N15" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="B16">
         <v>1012</v>
       </c>
@@ -14586,75 +16245,39 @@
       <c r="H16">
         <v>1</v>
       </c>
-      <c r="I16">
-        <v>10</v>
-      </c>
-      <c r="J16" t="b">
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14">
-      <c r="B17">
-        <v>1013</v>
-      </c>
-      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="B18">
+        <v>2001</v>
+      </c>
+      <c r="C18">
         <v>1001</v>
       </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>750</v>
-      </c>
-      <c r="F17">
-        <v>180</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-      <c r="H17">
-        <v>-1</v>
-      </c>
-      <c r="I17">
-        <v>50</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
-      <c r="B18">
-        <v>1014</v>
-      </c>
-      <c r="C18">
-        <v>2001</v>
-      </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>840</v>
+        <v>780</v>
       </c>
       <c r="F18">
         <v>180</v>
@@ -14665,23 +16288,20 @@
       <c r="H18">
         <v>-1</v>
       </c>
-      <c r="I18">
-        <v>10</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>405001</v>
       </c>
       <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>686</v>
+        <v>360</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18" t="s">
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -14700,7 +16320,7 @@
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="7.25" customWidth="1"/>
     <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="11.0833333333333" style="6" customWidth="1"/>
+    <col min="6" max="6" width="11.0833333333333" style="7" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14715,10 +16335,10 @@
         <v>644</v>
       </c>
       <c r="D1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G1" t="s">
         <v>600</v>
@@ -14750,15 +16370,15 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="F3" s="7"/>
+        <v>688</v>
+      </c>
+      <c r="F3" s="8"/>
       <c r="G3" s="1" t="s">
         <v>627</v>
       </c>
@@ -14777,13 +16397,13 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G4" t="s">
         <v>627</v>
       </c>
       <c r="H4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -14799,7 +16419,7 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <f>E5/10000</f>
         <v>0</v>
       </c>
@@ -14820,7 +16440,7 @@
       <c r="E6">
         <v>6700</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <f>E6/10000</f>
         <v>0.67</v>
       </c>
@@ -14841,7 +16461,7 @@
       <c r="E7">
         <v>2200</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <f t="shared" ref="F7:F17" si="0">E7/10000</f>
         <v>0.22</v>
       </c>
@@ -14859,10 +16479,10 @@
       <c r="D8" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="9">
         <v>900</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
@@ -14880,10 +16500,10 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="9">
         <v>180</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <f t="shared" si="0"/>
         <v>0.018</v>
       </c>
@@ -14904,7 +16524,7 @@
       <c r="E10">
         <v>20</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -14916,7 +16536,7 @@
       <c r="A11" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <f>SUM(F5:F10)</f>
         <v>1</v>
       </c>
@@ -14934,7 +16554,7 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -14955,7 +16575,7 @@
       <c r="E13">
         <v>3700</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
@@ -14963,7 +16583,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -14979,7 +16599,7 @@
       <c r="E14">
         <v>4200</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="7">
         <f t="shared" si="0"/>
         <v>0.42</v>
       </c>
@@ -15000,7 +16620,7 @@
       <c r="E15">
         <v>1700</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="7">
         <f t="shared" si="0"/>
         <v>0.17</v>
       </c>
@@ -15021,7 +16641,7 @@
       <c r="E16">
         <v>380</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="7">
         <f t="shared" si="0"/>
         <v>0.038</v>
       </c>
@@ -15042,7 +16662,7 @@
       <c r="E17">
         <v>20</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="7">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -15054,7 +16674,7 @@
       <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="7">
         <f>SUM(F12:F17)</f>
         <v>1</v>
       </c>
@@ -15201,7 +16821,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -15222,7 +16842,7 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="7">
         <f t="shared" ref="F28:F33" si="1">E28/10000</f>
         <v>0</v>
       </c>
@@ -15246,7 +16866,7 @@
       <c r="E29">
         <v>6700</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="7">
         <f t="shared" si="1"/>
         <v>0.67</v>
       </c>
@@ -15267,7 +16887,7 @@
       <c r="E30">
         <v>2200</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="7">
         <f t="shared" si="1"/>
         <v>0.22</v>
       </c>
@@ -15285,10 +16905,10 @@
       <c r="D31" t="s">
         <v>105</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="9">
         <v>900</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="7">
         <f t="shared" si="1"/>
         <v>0.09</v>
       </c>
@@ -15306,10 +16926,10 @@
       <c r="D32" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="9">
         <v>180</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="7">
         <f t="shared" si="1"/>
         <v>0.018</v>
       </c>
@@ -15330,7 +16950,7 @@
       <c r="E33">
         <v>20</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="7">
         <f t="shared" si="1"/>
         <v>0.002</v>
       </c>
@@ -15339,7 +16959,7 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="F34" s="6">
+      <c r="F34" s="7">
         <f>SUM(F28:F33)</f>
         <v>1</v>
       </c>
@@ -15376,28 +16996,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>692</v>
+      </c>
+      <c r="D1" t="s">
+        <v>686</v>
+      </c>
+      <c r="E1" t="s">
+        <v>693</v>
+      </c>
+      <c r="F1" t="s">
         <v>694</v>
       </c>
-      <c r="D1" t="s">
-        <v>688</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>695</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>696</v>
-      </c>
-      <c r="G1" t="s">
-        <v>697</v>
-      </c>
-      <c r="H1" t="s">
-        <v>698</v>
       </c>
       <c r="I1" t="s">
         <v>600</v>
       </c>
       <c r="J1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -15440,28 +17060,28 @@
         <v>161</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>702</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>704</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>627</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -15472,31 +17092,31 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
+        <v>704</v>
+      </c>
+      <c r="D4" t="s">
+        <v>705</v>
+      </c>
+      <c r="E4" t="s">
         <v>706</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>707</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>707</v>
+      </c>
+      <c r="H4" t="s">
         <v>708</v>
-      </c>
-      <c r="F4" t="s">
-        <v>709</v>
-      </c>
-      <c r="G4" t="s">
-        <v>709</v>
-      </c>
-      <c r="H4" t="s">
-        <v>710</v>
       </c>
       <c r="I4" t="s">
         <v>627</v>
       </c>
       <c r="J4" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="K4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -15912,7 +17532,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -15947,7 +17567,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -16046,7 +17666,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -16081,7 +17701,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -16244,7 +17864,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -16279,7 +17899,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -16314,7 +17934,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -16508,48 +18128,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>6</v>
       </c>
       <c r="E1" t="s">
+        <v>711</v>
+      </c>
+      <c r="F1" t="s">
+        <v>712</v>
+      </c>
+      <c r="G1" t="s">
         <v>713</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>714</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>715</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>716</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>717</v>
       </c>
-      <c r="K1" t="s">
-        <v>718</v>
-      </c>
-      <c r="L1" t="s">
-        <v>719</v>
-      </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D2" t="s">
@@ -16578,28 +18198,28 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="121.8" spans="1:12">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
-        <v>720</v>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>718</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -16616,28 +18236,28 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
+        <v>723</v>
+      </c>
+      <c r="F4" t="s">
+        <v>724</v>
+      </c>
+      <c r="G4" t="s">
         <v>725</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>726</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>727</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
+        <v>671</v>
+      </c>
+      <c r="K4" t="s">
         <v>728</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>729</v>
-      </c>
-      <c r="J4" t="s">
-        <v>672</v>
-      </c>
-      <c r="K4" t="s">
-        <v>730</v>
-      </c>
-      <c r="L4" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -16651,177 +18271,177 @@
         <v>99</v>
       </c>
       <c r="E5" t="s">
+        <v>730</v>
+      </c>
+      <c r="F5" t="s">
+        <v>731</v>
+      </c>
+      <c r="H5" t="s">
         <v>732</v>
       </c>
-      <c r="F5" t="s">
+      <c r="K5" t="s">
         <v>733</v>
-      </c>
-      <c r="H5" t="s">
-        <v>734</v>
-      </c>
-      <c r="K5" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
+        <v>734</v>
+      </c>
+      <c r="F6" t="s">
+        <v>731</v>
+      </c>
+      <c r="H6" t="s">
+        <v>735</v>
+      </c>
+      <c r="K6" t="s">
         <v>736</v>
-      </c>
-      <c r="F6" t="s">
-        <v>733</v>
-      </c>
-      <c r="H6" t="s">
-        <v>737</v>
-      </c>
-      <c r="K6" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
+        <v>737</v>
+      </c>
+      <c r="F7" t="s">
+        <v>731</v>
+      </c>
+      <c r="H7" t="s">
+        <v>738</v>
+      </c>
+      <c r="K7" t="s">
         <v>739</v>
-      </c>
-      <c r="F7" t="s">
-        <v>733</v>
-      </c>
-      <c r="H7" t="s">
-        <v>740</v>
-      </c>
-      <c r="K7" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
+        <v>740</v>
+      </c>
+      <c r="F8" t="s">
+        <v>731</v>
+      </c>
+      <c r="H8" t="s">
+        <v>741</v>
+      </c>
+      <c r="K8" t="s">
         <v>742</v>
-      </c>
-      <c r="F8" t="s">
-        <v>733</v>
-      </c>
-      <c r="H8" t="s">
-        <v>743</v>
-      </c>
-      <c r="K8" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="F9" t="s">
+        <v>731</v>
+      </c>
+      <c r="H9" t="s">
+        <v>744</v>
+      </c>
+      <c r="K9" t="s">
         <v>733</v>
-      </c>
-      <c r="H9" t="s">
-        <v>746</v>
-      </c>
-      <c r="K9" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F10" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="H10" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="K10" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>507</v>
       </c>
       <c r="E11" t="s">
+        <v>745</v>
+      </c>
+      <c r="F11" t="s">
+        <v>731</v>
+      </c>
+      <c r="H11" t="s">
+        <v>746</v>
+      </c>
+      <c r="J11" t="s">
         <v>747</v>
-      </c>
-      <c r="F11" t="s">
-        <v>733</v>
-      </c>
-      <c r="H11" t="s">
-        <v>748</v>
-      </c>
-      <c r="J11" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>562</v>
       </c>
       <c r="E12" t="s">
+        <v>745</v>
+      </c>
+      <c r="F12" t="s">
+        <v>731</v>
+      </c>
+      <c r="H12" t="s">
+        <v>746</v>
+      </c>
+      <c r="J12" t="s">
         <v>747</v>
-      </c>
-      <c r="F12" t="s">
-        <v>733</v>
-      </c>
-      <c r="H12" t="s">
-        <v>748</v>
-      </c>
-      <c r="J12" t="s">
-        <v>749</v>
       </c>
     </row>
   </sheetData>
@@ -16842,54 +18462,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C3" t="s">
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -16911,7 +18531,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D5" t="s">
         <v>139</v>
@@ -16925,7 +18545,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D6" t="s">
         <v>190</v>
@@ -16939,7 +18559,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D7" t="s">
         <v>392</v>
@@ -16963,7 +18583,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D10" t="s">
         <v>270</v>
@@ -17007,42 +18627,42 @@
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="5"/>
+      <c r="C22" s="6"/>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="5"/>
+      <c r="C23" s="6"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17063,27 +18683,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D2" t="s">
@@ -17091,17 +18711,17 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>761</v>
+      <c r="C3" s="5" t="s">
+        <v>759</v>
       </c>
       <c r="D3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="5" spans="1:4">

--- a/luban-excels/bak/xlsx/Items.xlsx
+++ b/luban-excels/bak/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="735"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -14,11 +14,12 @@
     <sheet name="BlindBoxRarityRate" sheetId="14" r:id="rId5"/>
     <sheet name="BlindBoxRevealPath" sheetId="15" r:id="rId6"/>
     <sheet name="BlindBoxVisual" sheetId="16" r:id="rId7"/>
-    <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
-    <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId9"/>
-    <sheet name="LinkTree" sheetId="17" r:id="rId10"/>
-    <sheet name="SteamItemDef" sheetId="18" r:id="rId11"/>
-    <sheet name="SteamItemDefIdRange" sheetId="19" r:id="rId12"/>
+    <sheet name="RefreshmentConfig" sheetId="20" r:id="rId8"/>
+    <sheet name="TabGroup" sheetId="8" r:id="rId9"/>
+    <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId10"/>
+    <sheet name="LinkTree" sheetId="17" r:id="rId11"/>
+    <sheet name="SteamItemDef" sheetId="18" r:id="rId12"/>
+    <sheet name="SteamItemDefIdRange" sheetId="19" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2780" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="1246">
   <si>
     <t>##var</t>
   </si>
@@ -2607,6 +2608,87 @@
     <t>实际上特殊品质的盲盒没有显示图片的机会</t>
   </si>
   <si>
+    <t>ItemId</t>
+  </si>
+  <si>
+    <t>DurationHands</t>
+  </si>
+  <si>
+    <t>LuckyDealMode</t>
+  </si>
+  <si>
+    <t>LuckyDealTriggerChance</t>
+  </si>
+  <si>
+    <t>InteractionHintSfxCue</t>
+  </si>
+  <si>
+    <t>UseSfxCue</t>
+  </si>
+  <si>
+    <t>BalloonOffsetY</t>
+  </si>
+  <si>
+    <t>int#ref=TbItem</t>
+  </si>
+  <si>
+    <t>ELuckyDealMode</t>
+  </si>
+  <si>
+    <t>关联 `Item.Id` 的唯一配置。仅允许填写 `ItemType = Refreshment` 的物品；</t>
+  </si>
+  <si>
+    <t>使用成功后获得的 BUFF 持续牌局数。每次成功下注并开始新局时消耗 1 局；建议填写 1-99。</t>
+  </si>
+  <si>
+    <t>决定幸运发牌的具体规则。第一版只支持 `GuidedDraw`；其他枚举为后续预留，暂勿配置。</t>
+  </si>
+  <si>
+    <t>BUFF 生效期间，每局开始时触发幸运发牌的概率。填写 0-1 小数，例如 `0.75` 表示 75%；未触发也会消耗该局。</t>
+  </si>
+  <si>
+    <t>点击桌面 Refreshment 时，播放交互提示动画所用的 AudioManager 逻辑 Cue。填空则静音；不要填写文件扩展名或资源路径。</t>
+  </si>
+  <si>
+    <t>玩家确认使用 Refreshment 并激活 BUFF 时播放的 AudioManager 逻辑 Cue。可按饮品/食物/器具分别配置；填空则静音。</t>
+  </si>
+  <si>
+    <t>在 PSD 导出定位的基础上，对 UseBalloon 和 StatusBalloon 同时追加的 Y 轴像素偏移。正数向下、负数向上；例如热气使气球偏高时填写正数。</t>
+  </si>
+  <si>
+    <t>关联物品 ID</t>
+  </si>
+  <si>
+    <t>持续局数</t>
+  </si>
+  <si>
+    <t>幸运发牌模式</t>
+  </si>
+  <si>
+    <t>Look校验品质</t>
+  </si>
+  <si>
+    <t>幸运触发概率</t>
+  </si>
+  <si>
+    <t>交互提示音效</t>
+  </si>
+  <si>
+    <t>使用音效</t>
+  </si>
+  <si>
+    <t>气球高度微调</t>
+  </si>
+  <si>
+    <t>GuidedDraw</t>
+  </si>
+  <si>
+    <t>Refreshment_Hint</t>
+  </si>
+  <si>
+    <t>Refreshment_BuffStart</t>
+  </si>
+  <si>
     <t>TabName</t>
   </si>
   <si>
@@ -3583,7 +3665,7 @@
     <t>通常保存在玩家 Steam 库存中、等待被消耗的可堆叠物品</t>
   </si>
   <si>
-    <t>盲盒券、熔炼材料</t>
+    <t>熔炼材料</t>
   </si>
   <si>
     <t>盲盒开箱成本与 BlindBox 一一对应：SteamOpenCostItemDefId = 200000 + BlindBox.Id。采用该映射的 BlindBox.Id 必须为 1-29999，并由转换器校验。</t>
@@ -3595,13 +3677,22 @@
     <t>BlindBox 1001 的开箱成本 ItemDef 为 201001</t>
   </si>
   <si>
+    <t>历史盲盒券与开箱成本冻结段。</t>
+  </si>
+  <si>
+    <t>兼容旧ID</t>
+  </si>
+  <si>
+    <t>201001、201002、204001 只保留兼容，不再分配新定义或改变身份。</t>
+  </si>
+  <si>
     <t>可消耗库存物品的后续功能预留段。</t>
   </si>
   <si>
-    <t>盲盒券以外的可堆叠材料</t>
-  </si>
-  <si>
-    <t>230xxx 可用于熔炼助燃剂等材料</t>
+    <t>可堆叠材料</t>
+  </si>
+  <si>
+    <t>210xxx 可用于熔炼助燃剂等材料</t>
   </si>
   <si>
     <t>Generator 与交换产物定义总段；同一个权重随机池可以被多种途径使用，不要求与 BlindBox 一一对应。</t>
@@ -3613,6 +3704,12 @@
     <t>301xxx 盲盒 Generator、302xxx 熔炼 Generator</t>
   </si>
   <si>
+    <t>随机奖励 Generator 总段；同一个权重随机池可以被多种途径使用，不要求与 BlindBox 一一对应。</t>
+  </si>
+  <si>
+    <t>为多种发奖流程提供随机奖励池</t>
+  </si>
+  <si>
     <t>盲盒随机奖池 Generator 子段。</t>
   </si>
   <si>
@@ -3622,6 +3719,12 @@
     <t>标准盲盒、新手盲盒等 Generator</t>
   </si>
   <si>
+    <t>盲盒奖励池 Generator。可以被 PlaytimeGenerator 直接引用，也兼容历史 Exchange。</t>
+  </si>
+  <si>
+    <t>盲盒装扮奖励池</t>
+  </si>
+  <si>
     <t>熔炼随机奖池 Generator 子段。</t>
   </si>
   <si>
@@ -3727,7 +3830,7 @@
     <t>发放补偿回执及补偿内容</t>
   </si>
   <si>
-    <t>补偿回执加盲盒券或固定物品</t>
+    <t>补偿回执加固定物品或材料</t>
   </si>
   <si>
     <t>新手礼包 Bundle 子段。</t>
@@ -3736,7 +3839,7 @@
     <t>发放新玩家的一次性固定礼包</t>
   </si>
   <si>
-    <t>新玩家盲盒招待券礼包</t>
+    <t>新玩家一次性固定物品礼包</t>
   </si>
   <si>
     <t>Promo/Claim Bundle 后续功能预留段。</t>
@@ -3775,6 +3878,33 @@
     <t>新手盲盒队列中的 Steam 投放</t>
   </si>
   <si>
+    <t>新手一次性 PlaytimeGenerator 总段，同时包含历史券版与新版直接奖励。</t>
+  </si>
+  <si>
+    <t>管理前 12 个新手 Schedule 的一次性 Steam 投放定义</t>
+  </si>
+  <si>
+    <t>7000xx 历史券版、7001xx 新版直接奖励</t>
+  </si>
+  <si>
+    <t>历史新手券 PlaytimeGenerator 子段，永久冻结。</t>
+  </si>
+  <si>
+    <t>保存旧版新手券投放定义</t>
+  </si>
+  <si>
+    <t>700001、700002、700004 等历史定义</t>
+  </si>
+  <si>
+    <t>新版新手直接奖励 PlaytimeGenerator 子段</t>
+  </si>
+  <si>
+    <t>新手阶段的 PlaytimeGenerator</t>
+  </si>
+  <si>
+    <t>前12个奖励当中的装扮奖励</t>
+  </si>
+  <si>
     <t>长期循环投放子段。</t>
   </si>
   <si>
@@ -3782,6 +3912,30 @@
   </si>
   <si>
     <t>长期循环装扮盲盒券，受掉落窗口控制</t>
+  </si>
+  <si>
+    <t>长期循环 PlaytimeGenerator 总段</t>
+  </si>
+  <si>
+    <t>管理游戏正常阶段持续运行的循环投放定义</t>
+  </si>
+  <si>
+    <t>7010xx 历史券版、7011xx 新版直接奖励</t>
+  </si>
+  <si>
+    <t>历史循环券 PlaytimeGenerator 子段，永久冻结。</t>
+  </si>
+  <si>
+    <t>保存旧版循环券投放定义</t>
+  </si>
+  <si>
+    <t>701001 历史循环券投放</t>
+  </si>
+  <si>
+    <t>新版循环直接奖励 PlaytimeGenerator 子段</t>
+  </si>
+  <si>
+    <t>长期循环直接生成装扮，受掉落窗口控制</t>
   </si>
   <si>
     <t>固定系统投放预留段。</t>
@@ -3827,8 +3981,15 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -3990,12 +4151,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -4340,16 +4507,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4358,37 +4522,37 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4403,74 +4567,77 @@
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4492,16 +4659,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4513,31 +4695,34 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5154,11 +5339,11 @@
     <col min="16" max="16" width="16.5833333333333" customWidth="1"/>
     <col min="17" max="17" width="20.9166666666667" customWidth="1"/>
     <col min="18" max="18" width="14.75" customWidth="1"/>
-    <col min="19" max="19" width="5.08333333333333" style="20" customWidth="1"/>
+    <col min="19" max="19" width="5.08333333333333" style="26" customWidth="1"/>
     <col min="20" max="20" width="44" customWidth="1"/>
     <col min="21" max="21" width="48.5833333333333" customWidth="1"/>
     <col min="22" max="22" width="15.4166666666667" customWidth="1"/>
-    <col min="23" max="23" width="7" style="20" customWidth="1"/>
+    <col min="23" max="23" width="7" style="26" customWidth="1"/>
     <col min="24" max="24" width="15.1666666666667" customWidth="1"/>
     <col min="25" max="25" width="18.0833333333333" customWidth="1"/>
     <col min="26" max="26" width="21.4166666666667" customWidth="1"/>
@@ -5378,7 +5563,7 @@
       <c r="J3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="21"/>
+      <c r="L3" s="27"/>
       <c r="M3" s="2" t="s">
         <v>45</v>
       </c>
@@ -5389,14 +5574,14 @@
       <c r="R3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="9"/>
+      <c r="S3" s="14"/>
       <c r="T3" s="2" t="s">
         <v>48</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="9"/>
+      <c r="W3" s="14"/>
       <c r="X3" s="2" t="s">
         <v>50</v>
       </c>
@@ -5535,72 +5720,72 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" s="19" customFormat="1" spans="1:35">
-      <c r="B5" s="19">
+    <row r="5" s="25" customFormat="1" spans="1:35">
+      <c r="B5" s="25">
         <v>1001</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="25">
         <v>200</v>
       </c>
-      <c r="J5" s="19">
-        <v>0</v>
-      </c>
-      <c r="K5" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="25">
+        <v>0</v>
+      </c>
+      <c r="K5" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="M5" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="19">
-        <v>0</v>
-      </c>
-      <c r="O5" s="19">
-        <v>0</v>
-      </c>
-      <c r="P5" s="19">
-        <v>0</v>
-      </c>
-      <c r="T5" s="19" t="s">
+      <c r="M5" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="25">
+        <v>0</v>
+      </c>
+      <c r="O5" s="25">
+        <v>0</v>
+      </c>
+      <c r="P5" s="25">
+        <v>0</v>
+      </c>
+      <c r="T5" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="U5" s="19" t="s">
+      <c r="U5" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="V5" s="19">
+      <c r="V5" s="25">
         <v>1001</v>
       </c>
-      <c r="W5" s="19"/>
-      <c r="Y5" s="19" t="s">
+      <c r="W5" s="25"/>
+      <c r="Y5" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="AA5" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="19" t="b">
+      <c r="AA5" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6064,10 +6249,10 @@
       <c r="N12">
         <v>1001</v>
       </c>
-      <c r="O12" s="14">
+      <c r="O12" s="19">
         <v>100</v>
       </c>
-      <c r="P12" s="14">
+      <c r="P12" s="19">
         <v>200</v>
       </c>
       <c r="T12" t="s">
@@ -6782,7 +6967,7 @@
       <c r="R23" t="s">
         <v>161</v>
       </c>
-      <c r="S23" s="20" t="s">
+      <c r="S23" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T23" t="s">
@@ -7140,7 +7325,7 @@
       <c r="R28" t="s">
         <v>161</v>
       </c>
-      <c r="S28" s="20" t="s">
+      <c r="S28" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T28" t="s">
@@ -7152,7 +7337,7 @@
       <c r="V28" t="s">
         <v>161</v>
       </c>
-      <c r="W28" s="20" t="s">
+      <c r="W28" s="26" t="s">
         <v>161</v>
       </c>
       <c r="X28">
@@ -7244,7 +7429,7 @@
       <c r="R29" t="s">
         <v>161</v>
       </c>
-      <c r="S29" s="20" t="s">
+      <c r="S29" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T29" t="s">
@@ -7256,7 +7441,7 @@
       <c r="V29" t="s">
         <v>161</v>
       </c>
-      <c r="W29" s="20" t="s">
+      <c r="W29" s="26" t="s">
         <v>161</v>
       </c>
       <c r="X29">
@@ -7633,435 +7818,435 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" s="19" customFormat="1" spans="2:31">
-      <c r="B35" s="19">
+    <row r="35" s="25" customFormat="1" spans="2:31">
+      <c r="B35" s="25">
         <v>4001</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="F35" s="19" t="s">
+      <c r="F35" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="H35" s="19" t="s">
+      <c r="H35" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I35" s="19">
-        <v>0</v>
-      </c>
-      <c r="J35" s="19">
-        <v>0</v>
-      </c>
-      <c r="K35" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" s="19" t="s">
+      <c r="I35" s="25">
+        <v>0</v>
+      </c>
+      <c r="J35" s="25">
+        <v>0</v>
+      </c>
+      <c r="K35" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="M35" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N35" s="19">
-        <v>0</v>
-      </c>
-      <c r="O35" s="19">
-        <v>0</v>
-      </c>
-      <c r="P35" s="19">
-        <v>0</v>
-      </c>
-      <c r="T35" s="19" t="s">
+      <c r="M35" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" s="25">
+        <v>0</v>
+      </c>
+      <c r="O35" s="25">
+        <v>0</v>
+      </c>
+      <c r="P35" s="25">
+        <v>0</v>
+      </c>
+      <c r="T35" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="U35" s="19" t="s">
+      <c r="U35" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="X35" s="19">
+      <c r="X35" s="25">
         <v>104001</v>
       </c>
-      <c r="Y35" s="19" t="s">
+      <c r="Y35" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="Z35" s="19"/>
-      <c r="AA35" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" s="19" customFormat="1" spans="2:31">
-      <c r="B36" s="19">
+      <c r="Z35" s="25"/>
+      <c r="AA35" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" s="25" customFormat="1" spans="2:31">
+      <c r="B36" s="25">
         <v>4002</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="F36" s="19" t="s">
+      <c r="F36" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="H36" s="19" t="s">
+      <c r="H36" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I36" s="19">
-        <v>0</v>
-      </c>
-      <c r="J36" s="19">
-        <v>0</v>
-      </c>
-      <c r="K36" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" s="19" t="s">
+      <c r="I36" s="25">
+        <v>0</v>
+      </c>
+      <c r="J36" s="25">
+        <v>0</v>
+      </c>
+      <c r="K36" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="M36" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N36" s="19">
-        <v>0</v>
-      </c>
-      <c r="O36" s="19">
-        <v>0</v>
-      </c>
-      <c r="P36" s="19">
-        <v>0</v>
-      </c>
-      <c r="T36" s="19" t="s">
+      <c r="M36" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" s="25">
+        <v>0</v>
+      </c>
+      <c r="O36" s="25">
+        <v>0</v>
+      </c>
+      <c r="P36" s="25">
+        <v>0</v>
+      </c>
+      <c r="T36" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="U36" s="19" t="s">
+      <c r="U36" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="X36" s="19">
+      <c r="X36" s="25">
         <v>104002</v>
       </c>
-      <c r="Y36" s="19" t="s">
+      <c r="Y36" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="Z36" s="19"/>
-      <c r="AA36" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" s="19" customFormat="1" spans="2:31">
-      <c r="B37" s="19">
+      <c r="Z36" s="25"/>
+      <c r="AA36" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" s="25" customFormat="1" spans="2:31">
+      <c r="B37" s="25">
         <v>4003</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="F37" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="H37" s="19" t="s">
+      <c r="H37" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I37" s="19">
-        <v>0</v>
-      </c>
-      <c r="J37" s="19">
-        <v>0</v>
-      </c>
-      <c r="K37" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L37" s="19" t="s">
+      <c r="I37" s="25">
+        <v>0</v>
+      </c>
+      <c r="J37" s="25">
+        <v>0</v>
+      </c>
+      <c r="K37" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="M37" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N37" s="19">
-        <v>0</v>
-      </c>
-      <c r="O37" s="19">
-        <v>0</v>
-      </c>
-      <c r="P37" s="19">
-        <v>0</v>
-      </c>
-      <c r="T37" s="19" t="s">
+      <c r="M37" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" s="25">
+        <v>0</v>
+      </c>
+      <c r="O37" s="25">
+        <v>0</v>
+      </c>
+      <c r="P37" s="25">
+        <v>0</v>
+      </c>
+      <c r="T37" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="U37" s="19" t="s">
+      <c r="U37" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="X37" s="19">
+      <c r="X37" s="25">
         <v>104003</v>
       </c>
-      <c r="Y37" s="19" t="s">
+      <c r="Y37" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="Z37" s="19"/>
-      <c r="AA37" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" s="19" customFormat="1" spans="2:31">
-      <c r="B38" s="19">
+      <c r="Z37" s="25"/>
+      <c r="AA37" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="25" customFormat="1" spans="2:31">
+      <c r="B38" s="25">
         <v>4004</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="F38" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="H38" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I38" s="19">
-        <v>0</v>
-      </c>
-      <c r="J38" s="19">
-        <v>0</v>
-      </c>
-      <c r="K38" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L38" s="19" t="s">
+      <c r="I38" s="25">
+        <v>0</v>
+      </c>
+      <c r="J38" s="25">
+        <v>0</v>
+      </c>
+      <c r="K38" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="M38" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N38" s="19">
-        <v>0</v>
-      </c>
-      <c r="O38" s="19">
-        <v>0</v>
-      </c>
-      <c r="P38" s="19">
-        <v>0</v>
-      </c>
-      <c r="T38" s="19" t="s">
+      <c r="M38" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" s="25">
+        <v>0</v>
+      </c>
+      <c r="O38" s="25">
+        <v>0</v>
+      </c>
+      <c r="P38" s="25">
+        <v>0</v>
+      </c>
+      <c r="T38" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="U38" s="19" t="s">
+      <c r="U38" s="25" t="s">
         <v>226</v>
       </c>
-      <c r="X38" s="19">
+      <c r="X38" s="25">
         <v>104004</v>
       </c>
-      <c r="Y38" s="19" t="s">
+      <c r="Y38" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="Z38" s="19"/>
-      <c r="AA38" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB38" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" s="19" customFormat="1" spans="2:31">
-      <c r="B39" s="19">
+      <c r="Z38" s="25"/>
+      <c r="AA38" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" s="25" customFormat="1" spans="2:31">
+      <c r="B39" s="25">
         <v>4005</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="F39" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="H39" s="19" t="s">
+      <c r="H39" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I39" s="19">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19">
-        <v>0</v>
-      </c>
-      <c r="K39" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" s="19" t="s">
+      <c r="I39" s="25">
+        <v>0</v>
+      </c>
+      <c r="J39" s="25">
+        <v>0</v>
+      </c>
+      <c r="K39" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="M39" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N39" s="19">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19">
-        <v>0</v>
-      </c>
-      <c r="P39" s="19">
-        <v>0</v>
-      </c>
-      <c r="T39" s="19" t="s">
+      <c r="M39" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" s="25">
+        <v>0</v>
+      </c>
+      <c r="O39" s="25">
+        <v>0</v>
+      </c>
+      <c r="P39" s="25">
+        <v>0</v>
+      </c>
+      <c r="T39" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="U39" s="19" t="s">
+      <c r="U39" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="X39" s="19">
+      <c r="X39" s="25">
         <v>104005</v>
       </c>
-      <c r="Y39" s="19" t="s">
+      <c r="Y39" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="Z39" s="19"/>
-      <c r="AA39" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB39" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" s="19" customFormat="1" spans="2:31">
-      <c r="B40" s="19">
+      <c r="Z39" s="25"/>
+      <c r="AA39" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" s="25" customFormat="1" spans="2:31">
+      <c r="B40" s="25">
         <v>4006</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="F40" s="19" t="s">
+      <c r="F40" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="H40" s="19" t="s">
+      <c r="H40" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I40" s="19">
-        <v>0</v>
-      </c>
-      <c r="J40" s="19">
-        <v>0</v>
-      </c>
-      <c r="K40" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L40" s="19" t="s">
+      <c r="I40" s="25">
+        <v>0</v>
+      </c>
+      <c r="J40" s="25">
+        <v>0</v>
+      </c>
+      <c r="K40" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="M40" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N40" s="19">
-        <v>0</v>
-      </c>
-      <c r="O40" s="19">
-        <v>0</v>
-      </c>
-      <c r="P40" s="19">
-        <v>0</v>
-      </c>
-      <c r="T40" s="19" t="s">
+      <c r="M40" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" s="25">
+        <v>0</v>
+      </c>
+      <c r="O40" s="25">
+        <v>0</v>
+      </c>
+      <c r="P40" s="25">
+        <v>0</v>
+      </c>
+      <c r="T40" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="U40" s="19" t="s">
+      <c r="U40" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="X40" s="19">
+      <c r="X40" s="25">
         <v>104006</v>
       </c>
-      <c r="Y40" s="19" t="s">
+      <c r="Y40" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="Z40" s="19"/>
-      <c r="AA40" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="19" t="b">
+      <c r="Z40" s="25"/>
+      <c r="AA40" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8609,87 +8794,87 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" s="19" customFormat="1" spans="2:31">
-      <c r="B49" s="19">
+    <row r="49" s="25" customFormat="1" spans="2:31">
+      <c r="B49" s="25">
         <v>6001</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C49" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D49" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="E49" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="F49" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H49" s="19" t="s">
+      <c r="F49" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="G49" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="H49" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I49" s="19">
-        <v>300</v>
-      </c>
-      <c r="J49" s="19">
-        <v>0</v>
-      </c>
-      <c r="K49" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" s="19" t="s">
+      <c r="I49" s="25">
+        <v>300</v>
+      </c>
+      <c r="J49" s="25">
+        <v>0</v>
+      </c>
+      <c r="K49" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="M49" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N49" s="19">
-        <v>0</v>
-      </c>
-      <c r="O49" s="19">
-        <v>0</v>
-      </c>
-      <c r="P49" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="R49" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="S49" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="T49" s="19" t="s">
+      <c r="M49" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" s="25">
+        <v>0</v>
+      </c>
+      <c r="O49" s="25">
+        <v>0</v>
+      </c>
+      <c r="P49" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="R49" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="S49" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="T49" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="U49" s="19" t="s">
+      <c r="U49" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="X49" s="19">
+      <c r="X49" s="25">
         <v>106001</v>
       </c>
-      <c r="Y49" s="19" t="s">
+      <c r="Y49" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="Z49" s="19"/>
-      <c r="AA49" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB49" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="19" t="b">
+      <c r="Z49" s="25"/>
+      <c r="AA49" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8745,7 +8930,7 @@
       <c r="R50" t="s">
         <v>161</v>
       </c>
-      <c r="S50" s="20" t="s">
+      <c r="S50" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T50" t="s">
@@ -8828,7 +9013,7 @@
       <c r="R51" t="s">
         <v>161</v>
       </c>
-      <c r="S51" s="20" t="s">
+      <c r="S51" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T51" t="s">
@@ -8911,7 +9096,7 @@
       <c r="R52" t="s">
         <v>161</v>
       </c>
-      <c r="S52" s="20" t="s">
+      <c r="S52" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T52" t="s">
@@ -8994,7 +9179,7 @@
       <c r="R53" t="s">
         <v>161</v>
       </c>
-      <c r="S53" s="20" t="s">
+      <c r="S53" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T53" t="s">
@@ -9077,7 +9262,7 @@
       <c r="R54" t="s">
         <v>161</v>
       </c>
-      <c r="S54" s="20" t="s">
+      <c r="S54" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T54" t="s">
@@ -9160,7 +9345,7 @@
       <c r="R55" t="s">
         <v>161</v>
       </c>
-      <c r="S55" s="20" t="s">
+      <c r="S55" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T55" t="s">
@@ -9243,7 +9428,7 @@
       <c r="R56" t="s">
         <v>161</v>
       </c>
-      <c r="S56" s="20" t="s">
+      <c r="S56" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T56" t="s">
@@ -9326,7 +9511,7 @@
       <c r="R57" t="s">
         <v>161</v>
       </c>
-      <c r="S57" s="20" t="s">
+      <c r="S57" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T57" t="s">
@@ -9409,7 +9594,7 @@
       <c r="R58" t="s">
         <v>161</v>
       </c>
-      <c r="S58" s="20" t="s">
+      <c r="S58" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T58" t="s">
@@ -9492,7 +9677,7 @@
       <c r="R59" t="s">
         <v>161</v>
       </c>
-      <c r="S59" s="20" t="s">
+      <c r="S59" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T59" t="s">
@@ -9727,72 +9912,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" s="19" customFormat="1" spans="2:31">
-      <c r="B63" s="19">
+    <row r="63" s="25" customFormat="1" spans="2:31">
+      <c r="B63" s="25">
         <v>7004</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="25" t="s">
         <v>326</v>
       </c>
-      <c r="D63" s="19" t="s">
+      <c r="D63" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="E63" s="19" t="s">
+      <c r="E63" s="25" t="s">
         <v>315</v>
       </c>
-      <c r="H63" s="22" t="s">
+      <c r="H63" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="I63" s="19">
-        <v>300</v>
-      </c>
-      <c r="J63" s="19">
-        <v>0</v>
-      </c>
-      <c r="K63" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63" s="19" t="s">
+      <c r="I63" s="25">
+        <v>300</v>
+      </c>
+      <c r="J63" s="25">
+        <v>0</v>
+      </c>
+      <c r="K63" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="M63" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N63" s="19">
-        <v>0</v>
-      </c>
-      <c r="O63" s="19">
-        <v>0</v>
-      </c>
-      <c r="P63" s="19">
-        <v>0</v>
-      </c>
-      <c r="T63" s="19" t="s">
+      <c r="M63" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" s="25">
+        <v>0</v>
+      </c>
+      <c r="O63" s="25">
+        <v>0</v>
+      </c>
+      <c r="P63" s="25">
+        <v>0</v>
+      </c>
+      <c r="T63" s="25" t="s">
         <v>328</v>
       </c>
-      <c r="U63" s="19" t="s">
+      <c r="U63" s="25" t="s">
         <v>329</v>
       </c>
-      <c r="X63" s="19">
+      <c r="X63" s="25">
         <v>107004</v>
       </c>
-      <c r="Y63" s="19" t="s">
+      <c r="Y63" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="Z63" s="19"/>
-      <c r="AA63" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB63" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC63" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD63" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" s="19" t="b">
+      <c r="Z63" s="25"/>
+      <c r="AA63" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9809,7 +9994,7 @@
       <c r="E64" t="s">
         <v>315</v>
       </c>
-      <c r="H64" s="14" t="s">
+      <c r="H64" s="19" t="s">
         <v>121</v>
       </c>
       <c r="I64">
@@ -9877,7 +10062,7 @@
       <c r="E65" t="s">
         <v>315</v>
       </c>
-      <c r="H65" s="14" t="s">
+      <c r="H65" s="19" t="s">
         <v>121</v>
       </c>
       <c r="I65">
@@ -10052,7 +10237,7 @@
       <c r="R67" t="s">
         <v>161</v>
       </c>
-      <c r="S67" s="20" t="s">
+      <c r="S67" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T67" t="s">
@@ -10135,7 +10320,7 @@
       <c r="R68" t="s">
         <v>161</v>
       </c>
-      <c r="S68" s="20" t="s">
+      <c r="S68" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T68" t="s">
@@ -10218,7 +10403,7 @@
       <c r="R69" t="s">
         <v>161</v>
       </c>
-      <c r="S69" s="20" t="s">
+      <c r="S69" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T69" t="s">
@@ -10301,7 +10486,7 @@
       <c r="R70" t="s">
         <v>161</v>
       </c>
-      <c r="S70" s="20" t="s">
+      <c r="S70" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T70" t="s">
@@ -10384,7 +10569,7 @@
       <c r="R71" t="s">
         <v>161</v>
       </c>
-      <c r="S71" s="20" t="s">
+      <c r="S71" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T71" t="s">
@@ -10467,7 +10652,7 @@
       <c r="R72" t="s">
         <v>161</v>
       </c>
-      <c r="S72" s="20" t="s">
+      <c r="S72" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T72" t="s">
@@ -10550,7 +10735,7 @@
       <c r="R73" t="s">
         <v>161</v>
       </c>
-      <c r="S73" s="20" t="s">
+      <c r="S73" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T73" t="s">
@@ -10633,7 +10818,7 @@
       <c r="R74" t="s">
         <v>161</v>
       </c>
-      <c r="S74" s="20" t="s">
+      <c r="S74" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T74" t="s">
@@ -10716,7 +10901,7 @@
       <c r="R75" t="s">
         <v>161</v>
       </c>
-      <c r="S75" s="20" t="s">
+      <c r="S75" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T75" t="s">
@@ -10799,7 +10984,7 @@
       <c r="R76" t="s">
         <v>161</v>
       </c>
-      <c r="S76" s="20" t="s">
+      <c r="S76" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T76" t="s">
@@ -10953,7 +11138,7 @@
       <c r="R78" t="s">
         <v>161</v>
       </c>
-      <c r="S78" s="20" t="s">
+      <c r="S78" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T78" t="s">
@@ -10965,7 +11150,7 @@
       <c r="V78" t="s">
         <v>161</v>
       </c>
-      <c r="W78" s="20" t="s">
+      <c r="W78" s="26" t="s">
         <v>161</v>
       </c>
       <c r="X78">
@@ -11054,7 +11239,7 @@
       <c r="R79" t="s">
         <v>161</v>
       </c>
-      <c r="S79" s="20" t="s">
+      <c r="S79" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T79" t="s">
@@ -11137,7 +11322,7 @@
       <c r="R80" t="s">
         <v>161</v>
       </c>
-      <c r="S80" s="20" t="s">
+      <c r="S80" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T80" t="s">
@@ -11220,7 +11405,7 @@
       <c r="R81" t="s">
         <v>161</v>
       </c>
-      <c r="S81" s="20" t="s">
+      <c r="S81" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T81" t="s">
@@ -11303,7 +11488,7 @@
       <c r="R82" t="s">
         <v>161</v>
       </c>
-      <c r="S82" s="20" t="s">
+      <c r="S82" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T82" t="s">
@@ -11386,7 +11571,7 @@
       <c r="R83" t="s">
         <v>161</v>
       </c>
-      <c r="S83" s="20" t="s">
+      <c r="S83" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T83" t="s">
@@ -11469,7 +11654,7 @@
       <c r="R84" t="s">
         <v>161</v>
       </c>
-      <c r="S84" s="20" t="s">
+      <c r="S84" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T84" t="s">
@@ -11759,7 +11944,7 @@
       <c r="R88" t="s">
         <v>161</v>
       </c>
-      <c r="S88" s="20" t="s">
+      <c r="S88" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T88" t="s">
@@ -11771,7 +11956,7 @@
       <c r="V88" t="s">
         <v>161</v>
       </c>
-      <c r="W88" s="20" t="s">
+      <c r="W88" s="26" t="s">
         <v>161</v>
       </c>
       <c r="X88">
@@ -11863,7 +12048,7 @@
       <c r="R89" t="s">
         <v>161</v>
       </c>
-      <c r="S89" s="20" t="s">
+      <c r="S89" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T89" t="s">
@@ -11875,7 +12060,7 @@
       <c r="V89" t="s">
         <v>161</v>
       </c>
-      <c r="W89" s="20" t="s">
+      <c r="W89" s="26" t="s">
         <v>161</v>
       </c>
       <c r="X89">
@@ -12038,7 +12223,7 @@
       <c r="U91" t="s">
         <v>445</v>
       </c>
-      <c r="W91" s="20" t="s">
+      <c r="W91" s="26" t="s">
         <v>446</v>
       </c>
       <c r="X91">
@@ -12118,7 +12303,7 @@
       <c r="U92" t="s">
         <v>450</v>
       </c>
-      <c r="W92" s="20" t="s">
+      <c r="W92" s="26" t="s">
         <v>446</v>
       </c>
       <c r="X92">
@@ -12198,7 +12383,7 @@
       <c r="U93" t="s">
         <v>454</v>
       </c>
-      <c r="W93" s="20" t="s">
+      <c r="W93" s="26" t="s">
         <v>446</v>
       </c>
       <c r="X93">
@@ -12278,7 +12463,7 @@
       <c r="U94" t="s">
         <v>458</v>
       </c>
-      <c r="W94" s="20" t="s">
+      <c r="W94" s="26" t="s">
         <v>446</v>
       </c>
       <c r="X94">
@@ -12358,7 +12543,7 @@
       <c r="U95" t="s">
         <v>462</v>
       </c>
-      <c r="W95" s="20" t="s">
+      <c r="W95" s="26" t="s">
         <v>446</v>
       </c>
       <c r="X95">
@@ -12438,7 +12623,7 @@
       <c r="U96" t="s">
         <v>466</v>
       </c>
-      <c r="W96" s="20" t="s">
+      <c r="W96" s="26" t="s">
         <v>446</v>
       </c>
       <c r="X96">
@@ -12518,7 +12703,7 @@
       <c r="U97" t="s">
         <v>470</v>
       </c>
-      <c r="W97" s="20" t="s">
+      <c r="W97" s="26" t="s">
         <v>446</v>
       </c>
       <c r="X97">
@@ -12592,7 +12777,7 @@
       <c r="U98" t="s">
         <v>474</v>
       </c>
-      <c r="W98" s="20" t="s">
+      <c r="W98" s="26" t="s">
         <v>446</v>
       </c>
       <c r="X98">
@@ -12749,7 +12934,7 @@
       <c r="U100" t="s">
         <v>482</v>
       </c>
-      <c r="W100" s="20" t="s">
+      <c r="W100" s="26" t="s">
         <v>446</v>
       </c>
       <c r="X100">
@@ -12774,216 +12959,216 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" s="19" customFormat="1" spans="2:31">
-      <c r="B101" s="19">
+    <row r="101" s="25" customFormat="1" spans="2:31">
+      <c r="B101" s="25">
         <v>10001</v>
       </c>
-      <c r="C101" s="19" t="s">
+      <c r="C101" s="25" t="s">
         <v>483</v>
       </c>
-      <c r="D101" s="19" t="s">
+      <c r="D101" s="25" t="s">
         <v>484</v>
       </c>
-      <c r="E101" s="19" t="s">
+      <c r="E101" s="25" t="s">
         <v>485</v>
       </c>
-      <c r="H101" s="19" t="s">
+      <c r="H101" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I101" s="19">
-        <v>300</v>
-      </c>
-      <c r="J101" s="19">
-        <v>0</v>
-      </c>
-      <c r="K101" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L101" s="19" t="s">
+      <c r="I101" s="25">
+        <v>300</v>
+      </c>
+      <c r="J101" s="25">
+        <v>0</v>
+      </c>
+      <c r="K101" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L101" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="M101" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N101" s="19">
-        <v>0</v>
-      </c>
-      <c r="O101" s="19">
-        <v>0</v>
-      </c>
-      <c r="P101" s="19">
-        <v>0</v>
-      </c>
-      <c r="T101" s="19" t="s">
+      <c r="M101" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N101" s="25">
+        <v>0</v>
+      </c>
+      <c r="O101" s="25">
+        <v>0</v>
+      </c>
+      <c r="P101" s="25">
+        <v>0</v>
+      </c>
+      <c r="T101" s="25" t="s">
         <v>486</v>
       </c>
-      <c r="U101" s="19" t="s">
+      <c r="U101" s="25" t="s">
         <v>487</v>
       </c>
-      <c r="X101" s="19">
+      <c r="X101" s="25">
         <v>110001</v>
       </c>
-      <c r="Y101" s="19" t="s">
+      <c r="Y101" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="Z101" s="19"/>
-      <c r="AA101" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB101" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" s="19" customFormat="1" spans="2:31">
-      <c r="B102" s="19">
+      <c r="Z101" s="25"/>
+      <c r="AA101" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB101" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" s="25" customFormat="1" spans="2:31">
+      <c r="B102" s="25">
         <v>11001</v>
       </c>
-      <c r="C102" s="19" t="s">
+      <c r="C102" s="25" t="s">
         <v>488</v>
       </c>
-      <c r="D102" s="19" t="s">
+      <c r="D102" s="25" t="s">
         <v>489</v>
       </c>
-      <c r="E102" s="19" t="s">
+      <c r="E102" s="25" t="s">
         <v>490</v>
       </c>
-      <c r="H102" s="19" t="s">
+      <c r="H102" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I102" s="19">
-        <v>300</v>
-      </c>
-      <c r="J102" s="19">
-        <v>0</v>
-      </c>
-      <c r="K102" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L102" s="19" t="s">
+      <c r="I102" s="25">
+        <v>300</v>
+      </c>
+      <c r="J102" s="25">
+        <v>0</v>
+      </c>
+      <c r="K102" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L102" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="M102" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N102" s="19">
-        <v>0</v>
-      </c>
-      <c r="O102" s="19">
-        <v>0</v>
-      </c>
-      <c r="P102" s="19">
-        <v>0</v>
-      </c>
-      <c r="T102" s="19" t="s">
+      <c r="M102" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N102" s="25">
+        <v>0</v>
+      </c>
+      <c r="O102" s="25">
+        <v>0</v>
+      </c>
+      <c r="P102" s="25">
+        <v>0</v>
+      </c>
+      <c r="T102" s="25" t="s">
         <v>491</v>
       </c>
-      <c r="U102" s="19" t="s">
+      <c r="U102" s="25" t="s">
         <v>492</v>
       </c>
-      <c r="W102" s="19" t="s">
+      <c r="W102" s="25" t="s">
         <v>493</v>
       </c>
-      <c r="X102" s="19">
+      <c r="X102" s="25">
         <v>111001</v>
       </c>
-      <c r="Y102" s="19" t="s">
+      <c r="Y102" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="Z102" s="19"/>
-      <c r="AA102" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB102" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" s="19" customFormat="1" spans="2:31">
-      <c r="B103" s="19">
+      <c r="Z102" s="25"/>
+      <c r="AA102" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB102" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" s="25" customFormat="1" spans="2:31">
+      <c r="B103" s="25">
         <v>11002</v>
       </c>
-      <c r="C103" s="19" t="s">
+      <c r="C103" s="25" t="s">
         <v>494</v>
       </c>
-      <c r="D103" s="19" t="s">
+      <c r="D103" s="25" t="s">
         <v>495</v>
       </c>
-      <c r="E103" s="19" t="s">
+      <c r="E103" s="25" t="s">
         <v>490</v>
       </c>
-      <c r="G103" s="19">
+      <c r="G103" s="25">
         <v>11001</v>
       </c>
-      <c r="H103" s="19" t="s">
+      <c r="H103" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="I103" s="19">
-        <v>300</v>
-      </c>
-      <c r="J103" s="19">
-        <v>0</v>
-      </c>
-      <c r="K103" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L103" s="19" t="s">
+      <c r="I103" s="25">
+        <v>300</v>
+      </c>
+      <c r="J103" s="25">
+        <v>0</v>
+      </c>
+      <c r="K103" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L103" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="M103" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="N103" s="19">
-        <v>0</v>
-      </c>
-      <c r="O103" s="19">
-        <v>0</v>
-      </c>
-      <c r="P103" s="19">
-        <v>0</v>
-      </c>
-      <c r="T103" s="19" t="s">
+      <c r="M103" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="N103" s="25">
+        <v>0</v>
+      </c>
+      <c r="O103" s="25">
+        <v>0</v>
+      </c>
+      <c r="P103" s="25">
+        <v>0</v>
+      </c>
+      <c r="T103" s="25" t="s">
         <v>491</v>
       </c>
-      <c r="U103" s="19" t="s">
+      <c r="U103" s="25" t="s">
         <v>496</v>
       </c>
-      <c r="X103" s="19">
+      <c r="X103" s="25">
         <v>111002</v>
       </c>
-      <c r="Y103" s="19" t="s">
+      <c r="Y103" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="Z103" s="19"/>
-      <c r="AA103" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB103" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC103" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD103" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE103" s="19" t="b">
+      <c r="Z103" s="25"/>
+      <c r="AA103" s="25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB103" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -13006,7 +13191,7 @@
       <c r="G104" t="s">
         <v>161</v>
       </c>
-      <c r="H104" s="14" t="s">
+      <c r="H104" s="19" t="s">
         <v>121</v>
       </c>
       <c r="I104">
@@ -13039,7 +13224,7 @@
       <c r="R104" t="s">
         <v>161</v>
       </c>
-      <c r="S104" s="20" t="s">
+      <c r="S104" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T104" t="s">
@@ -13089,7 +13274,7 @@
       <c r="G105" t="s">
         <v>161</v>
       </c>
-      <c r="H105" s="14" t="s">
+      <c r="H105" s="19" t="s">
         <v>140</v>
       </c>
       <c r="I105">
@@ -13122,7 +13307,7 @@
       <c r="R105" t="s">
         <v>161</v>
       </c>
-      <c r="S105" s="20" t="s">
+      <c r="S105" s="26" t="s">
         <v>161</v>
       </c>
       <c r="T105" t="s">
@@ -13190,14 +13375,14 @@
       <c r="R106">
         <v>100</v>
       </c>
-      <c r="S106" s="20"/>
+      <c r="S106" s="26"/>
       <c r="T106" t="s">
         <v>157</v>
       </c>
       <c r="U106" t="s">
         <v>158</v>
       </c>
-      <c r="W106" s="20" t="s">
+      <c r="W106" s="26" t="s">
         <v>509</v>
       </c>
       <c r="X106">
@@ -13260,7 +13445,7 @@
       <c r="R107">
         <v>100</v>
       </c>
-      <c r="S107" s="20"/>
+      <c r="S107" s="26"/>
       <c r="T107" t="s">
         <v>111</v>
       </c>
@@ -13270,7 +13455,7 @@
       <c r="V107">
         <v>1012</v>
       </c>
-      <c r="W107" s="20" t="s">
+      <c r="W107" s="26" t="s">
         <v>509</v>
       </c>
       <c r="X107">
@@ -13338,6 +13523,180 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="14.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="4" max="4" width="14.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>830</v>
+      </c>
+      <c r="D1" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="D3" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" t="s">
+        <v>392</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>6001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>7004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" t="s">
+        <v>437</v>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" t="s">
+        <v>485</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" t="s">
+        <v>490</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>11002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" t="s">
+        <v>499</v>
+      </c>
+      <c r="C16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:S12"/>
   <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
   <cols>
@@ -13370,55 +13729,55 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>807</v>
+        <v>834</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>808</v>
+        <v>835</v>
       </c>
       <c r="F1" t="s">
         <v>640</v>
       </c>
       <c r="G1" t="s">
-        <v>809</v>
+        <v>836</v>
       </c>
       <c r="H1" t="s">
-        <v>810</v>
+        <v>837</v>
       </c>
       <c r="I1" t="s">
-        <v>811</v>
+        <v>838</v>
       </c>
       <c r="J1" t="s">
-        <v>812</v>
+        <v>839</v>
       </c>
       <c r="K1" t="s">
-        <v>813</v>
+        <v>840</v>
       </c>
       <c r="L1" t="s">
-        <v>814</v>
+        <v>841</v>
       </c>
       <c r="M1" t="s">
-        <v>815</v>
+        <v>842</v>
       </c>
       <c r="N1" t="s">
-        <v>816</v>
+        <v>843</v>
       </c>
       <c r="O1" t="s">
-        <v>817</v>
+        <v>844</v>
       </c>
       <c r="P1" t="s">
-        <v>818</v>
+        <v>845</v>
       </c>
       <c r="Q1" t="s">
-        <v>819</v>
+        <v>846</v>
       </c>
       <c r="R1" t="s">
-        <v>820</v>
+        <v>847</v>
       </c>
       <c r="S1" t="s">
-        <v>821</v>
+        <v>848</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -13456,10 +13815,10 @@
         <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>822</v>
+        <v>849</v>
       </c>
       <c r="M2" t="s">
-        <v>823</v>
+        <v>850</v>
       </c>
       <c r="N2" t="s">
         <v>30</v>
@@ -13485,58 +13844,58 @@
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>824</v>
+        <v>851</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>825</v>
+        <v>852</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>826</v>
+        <v>853</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>827</v>
+        <v>854</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>828</v>
+        <v>855</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>829</v>
+        <v>856</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>830</v>
+        <v>857</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>831</v>
+        <v>858</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>832</v>
+        <v>859</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>833</v>
+        <v>860</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>834</v>
+        <v>861</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>835</v>
+        <v>862</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>836</v>
+        <v>863</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>837</v>
+        <v>864</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>838</v>
+        <v>865</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>839</v>
+        <v>866</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>840</v>
+        <v>867</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>841</v>
+        <v>868</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -13544,58 +13903,58 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="C4" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="D4" t="s">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="E4" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
       <c r="F4" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="G4" t="s">
-        <v>847</v>
+        <v>874</v>
       </c>
       <c r="H4" t="s">
-        <v>848</v>
+        <v>875</v>
       </c>
       <c r="I4" t="s">
-        <v>849</v>
+        <v>876</v>
       </c>
       <c r="J4" t="s">
-        <v>850</v>
+        <v>877</v>
       </c>
       <c r="K4" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="L4" t="s">
-        <v>852</v>
+        <v>879</v>
       </c>
       <c r="M4" t="s">
-        <v>853</v>
+        <v>880</v>
       </c>
       <c r="N4" t="s">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="O4" t="s">
-        <v>855</v>
+        <v>882</v>
       </c>
       <c r="P4" t="s">
-        <v>856</v>
+        <v>883</v>
       </c>
       <c r="Q4" t="s">
-        <v>857</v>
+        <v>884</v>
       </c>
       <c r="R4" t="s">
-        <v>858</v>
+        <v>885</v>
       </c>
       <c r="S4" t="s">
-        <v>859</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -13603,7 +13962,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>860</v>
+        <v>887</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -13615,25 +13974,25 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>861</v>
+        <v>888</v>
       </c>
       <c r="H5" t="s">
-        <v>862</v>
+        <v>889</v>
       </c>
       <c r="I5" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J5" t="s">
-        <v>864</v>
+        <v>891</v>
       </c>
       <c r="K5" t="s">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="L5" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M5" t="s">
-        <v>867</v>
+        <v>894</v>
       </c>
       <c r="N5">
         <v>92005</v>
@@ -13653,7 +14012,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>868</v>
+        <v>895</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -13665,25 +14024,25 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>869</v>
+        <v>896</v>
       </c>
       <c r="H6" t="s">
-        <v>870</v>
+        <v>897</v>
       </c>
       <c r="I6" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J6" t="s">
-        <v>871</v>
+        <v>898</v>
       </c>
       <c r="K6" t="s">
-        <v>871</v>
+        <v>898</v>
       </c>
       <c r="L6" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M6" t="s">
-        <v>872</v>
+        <v>899</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -13703,7 +14062,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>873</v>
+        <v>900</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -13715,25 +14074,25 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>874</v>
+        <v>901</v>
       </c>
       <c r="H7" t="s">
-        <v>875</v>
+        <v>902</v>
       </c>
       <c r="I7" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J7" t="s">
-        <v>876</v>
+        <v>903</v>
       </c>
       <c r="K7" t="s">
-        <v>877</v>
+        <v>904</v>
       </c>
       <c r="L7" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M7" t="s">
-        <v>872</v>
+        <v>899</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -13753,7 +14112,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>878</v>
+        <v>905</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -13765,25 +14124,25 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>879</v>
+        <v>906</v>
       </c>
       <c r="H8" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="I8" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J8" t="s">
-        <v>881</v>
+        <v>908</v>
       </c>
       <c r="K8" t="s">
-        <v>881</v>
+        <v>908</v>
       </c>
       <c r="L8" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M8" t="s">
-        <v>867</v>
+        <v>894</v>
       </c>
       <c r="N8">
         <v>91012</v>
@@ -13803,7 +14162,7 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>860</v>
+        <v>887</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -13815,25 +14174,25 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>861</v>
+        <v>888</v>
       </c>
       <c r="H9" t="s">
-        <v>862</v>
+        <v>889</v>
       </c>
       <c r="I9" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J9" t="s">
-        <v>864</v>
+        <v>891</v>
       </c>
       <c r="K9" t="s">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="L9" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M9" t="s">
-        <v>867</v>
+        <v>894</v>
       </c>
       <c r="N9">
         <v>92005</v>
@@ -13856,7 +14215,7 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>868</v>
+        <v>895</v>
       </c>
       <c r="D10">
         <v>80</v>
@@ -13868,25 +14227,25 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>869</v>
+        <v>896</v>
       </c>
       <c r="H10" t="s">
-        <v>870</v>
+        <v>897</v>
       </c>
       <c r="I10" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J10" t="s">
-        <v>871</v>
+        <v>898</v>
       </c>
       <c r="K10" t="s">
-        <v>871</v>
+        <v>898</v>
       </c>
       <c r="L10" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M10" t="s">
-        <v>872</v>
+        <v>899</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -13909,7 +14268,7 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>873</v>
+        <v>900</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -13921,25 +14280,25 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>874</v>
+        <v>901</v>
       </c>
       <c r="H11" t="s">
-        <v>875</v>
+        <v>902</v>
       </c>
       <c r="I11" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J11" t="s">
-        <v>876</v>
+        <v>903</v>
       </c>
       <c r="K11" t="s">
-        <v>877</v>
+        <v>904</v>
       </c>
       <c r="L11" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M11" t="s">
-        <v>872</v>
+        <v>899</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -13962,7 +14321,7 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>878</v>
+        <v>905</v>
       </c>
       <c r="D12">
         <v>120</v>
@@ -13974,25 +14333,25 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>879</v>
+        <v>906</v>
       </c>
       <c r="H12" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="I12" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="J12" t="s">
-        <v>881</v>
+        <v>908</v>
       </c>
       <c r="K12" t="s">
-        <v>881</v>
+        <v>908</v>
       </c>
       <c r="L12" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="M12" t="s">
-        <v>867</v>
+        <v>894</v>
       </c>
       <c r="N12">
         <v>91012</v>
@@ -14016,7 +14375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R66"/>
@@ -14049,49 +14408,49 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>807</v>
+        <v>834</v>
       </c>
       <c r="E1" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>883</v>
+        <v>910</v>
       </c>
       <c r="H1" t="s">
-        <v>884</v>
+        <v>911</v>
       </c>
       <c r="I1" t="s">
-        <v>885</v>
+        <v>912</v>
       </c>
       <c r="J1" t="s">
-        <v>886</v>
+        <v>913</v>
       </c>
       <c r="K1" t="s">
-        <v>887</v>
+        <v>914</v>
       </c>
       <c r="L1" t="s">
-        <v>888</v>
+        <v>915</v>
       </c>
       <c r="M1" t="s">
-        <v>889</v>
+        <v>916</v>
       </c>
       <c r="N1" t="s">
-        <v>890</v>
+        <v>917</v>
       </c>
       <c r="O1" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="P1" t="s">
         <v>640</v>
       </c>
       <c r="Q1" t="s">
-        <v>892</v>
+        <v>919</v>
       </c>
       <c r="R1" t="s">
-        <v>893</v>
+        <v>920</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -14152,52 +14511,52 @@
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>894</v>
+        <v>921</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>895</v>
+        <v>922</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>897</v>
+        <v>923</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>924</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>898</v>
+      <c r="H3" s="15" t="s">
+        <v>925</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>899</v>
+        <v>926</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>900</v>
+        <v>927</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>901</v>
+        <v>928</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>902</v>
+        <v>929</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>903</v>
+        <v>930</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>904</v>
+        <v>931</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>905</v>
+        <v>932</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>906</v>
+        <v>933</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>907</v>
+        <v>934</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>908</v>
+        <v>935</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -14205,55 +14564,55 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>909</v>
+        <v>936</v>
       </c>
       <c r="C4" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="D4" t="s">
-        <v>910</v>
+        <v>937</v>
       </c>
       <c r="E4" t="s">
-        <v>911</v>
+        <v>938</v>
       </c>
       <c r="F4" t="s">
-        <v>912</v>
+        <v>939</v>
       </c>
       <c r="G4" t="s">
         <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>913</v>
+        <v>940</v>
       </c>
       <c r="I4" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="J4" t="s">
         <v>81</v>
       </c>
       <c r="K4" t="s">
-        <v>915</v>
+        <v>942</v>
       </c>
       <c r="L4" t="s">
-        <v>916</v>
+        <v>943</v>
       </c>
       <c r="M4" t="s">
-        <v>917</v>
+        <v>944</v>
       </c>
       <c r="N4" t="s">
         <v>83</v>
       </c>
       <c r="O4" t="s">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="P4" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="Q4" t="s">
-        <v>919</v>
+        <v>946</v>
       </c>
       <c r="R4" t="s">
-        <v>920</v>
+        <v>947</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -14264,22 +14623,22 @@
         <v>401001</v>
       </c>
       <c r="C5" t="s">
-        <v>921</v>
+        <v>948</v>
       </c>
       <c r="D5" t="s">
-        <v>922</v>
+        <v>949</v>
       </c>
       <c r="E5" t="s">
         <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="G5" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H5" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -14320,22 +14679,22 @@
         <v>401002</v>
       </c>
       <c r="C6" t="s">
-        <v>926</v>
+        <v>953</v>
       </c>
       <c r="D6" t="s">
-        <v>927</v>
+        <v>954</v>
       </c>
       <c r="E6" t="s">
         <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>928</v>
+        <v>955</v>
       </c>
       <c r="G6" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H6" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -14376,22 +14735,22 @@
         <v>401003</v>
       </c>
       <c r="C7" t="s">
-        <v>930</v>
+        <v>957</v>
       </c>
       <c r="D7" t="s">
-        <v>931</v>
+        <v>958</v>
       </c>
       <c r="E7" t="s">
         <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>932</v>
+        <v>959</v>
       </c>
       <c r="G7" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="H7" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -14432,22 +14791,22 @@
         <v>401004</v>
       </c>
       <c r="C8" t="s">
-        <v>934</v>
+        <v>961</v>
       </c>
       <c r="D8" t="s">
-        <v>935</v>
+        <v>962</v>
       </c>
       <c r="E8" t="s">
         <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="G8" t="s">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="H8" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -14488,22 +14847,22 @@
         <v>401005</v>
       </c>
       <c r="C9" t="s">
-        <v>938</v>
+        <v>965</v>
       </c>
       <c r="D9" t="s">
-        <v>939</v>
+        <v>966</v>
       </c>
       <c r="E9" t="s">
         <v>96</v>
       </c>
       <c r="F9" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="G9" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H9" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -14544,22 +14903,22 @@
         <v>401006</v>
       </c>
       <c r="C10" t="s">
-        <v>940</v>
+        <v>967</v>
       </c>
       <c r="D10" t="s">
-        <v>941</v>
+        <v>968</v>
       </c>
       <c r="E10" t="s">
         <v>96</v>
       </c>
       <c r="F10" t="s">
-        <v>928</v>
+        <v>955</v>
       </c>
       <c r="G10" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H10" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -14600,22 +14959,22 @@
         <v>401007</v>
       </c>
       <c r="C11" t="s">
-        <v>942</v>
+        <v>969</v>
       </c>
       <c r="D11" t="s">
-        <v>943</v>
+        <v>970</v>
       </c>
       <c r="E11" t="s">
         <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>932</v>
+        <v>959</v>
       </c>
       <c r="G11" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="H11" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -14656,22 +15015,22 @@
         <v>401008</v>
       </c>
       <c r="C12" t="s">
-        <v>944</v>
+        <v>971</v>
       </c>
       <c r="D12" t="s">
-        <v>945</v>
+        <v>972</v>
       </c>
       <c r="E12" t="s">
         <v>96</v>
       </c>
       <c r="F12" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="G12" t="s">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="H12" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -14709,7 +15068,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>946</v>
+        <v>973</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -14720,19 +15079,19 @@
         <v>402001</v>
       </c>
       <c r="C14" t="s">
-        <v>947</v>
+        <v>974</v>
       </c>
       <c r="D14" t="s">
-        <v>948</v>
+        <v>975</v>
       </c>
       <c r="E14" t="s">
         <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="G14" t="s">
-        <v>950</v>
+        <v>977</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -14770,19 +15129,19 @@
         <v>402002</v>
       </c>
       <c r="C15" t="s">
-        <v>951</v>
+        <v>978</v>
       </c>
       <c r="D15" t="s">
-        <v>952</v>
+        <v>979</v>
       </c>
       <c r="E15" t="s">
         <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>953</v>
+        <v>980</v>
       </c>
       <c r="G15" t="s">
-        <v>954</v>
+        <v>981</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -14817,19 +15176,19 @@
         <v>402003</v>
       </c>
       <c r="C16" t="s">
-        <v>955</v>
+        <v>982</v>
       </c>
       <c r="D16" t="s">
-        <v>956</v>
+        <v>983</v>
       </c>
       <c r="E16" t="s">
         <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>957</v>
+        <v>984</v>
       </c>
       <c r="G16" t="s">
-        <v>958</v>
+        <v>985</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -14864,7 +15223,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>959</v>
+        <v>986</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -14875,19 +15234,19 @@
         <v>403001</v>
       </c>
       <c r="C18" t="s">
-        <v>960</v>
+        <v>987</v>
       </c>
       <c r="D18" t="s">
-        <v>961</v>
+        <v>988</v>
       </c>
       <c r="E18" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="F18" t="s">
-        <v>963</v>
+        <v>990</v>
       </c>
       <c r="G18" t="s">
-        <v>964</v>
+        <v>991</v>
       </c>
       <c r="H18" t="s">
         <v>161</v>
@@ -14911,7 +15270,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>965</v>
+        <v>992</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
@@ -14928,19 +15287,19 @@
         <v>403002</v>
       </c>
       <c r="C19" t="s">
-        <v>966</v>
+        <v>993</v>
       </c>
       <c r="D19" t="s">
-        <v>967</v>
+        <v>994</v>
       </c>
       <c r="E19" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="F19" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="G19" t="s">
-        <v>969</v>
+        <v>996</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -14961,7 +15320,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
@@ -14978,19 +15337,19 @@
         <v>403003</v>
       </c>
       <c r="C20" t="s">
-        <v>971</v>
+        <v>998</v>
       </c>
       <c r="D20" t="s">
-        <v>972</v>
+        <v>999</v>
       </c>
       <c r="E20" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="F20" t="s">
-        <v>973</v>
+        <v>1000</v>
       </c>
       <c r="G20" t="s">
-        <v>974</v>
+        <v>1001</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -15011,7 +15370,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
@@ -15028,7 +15387,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>975</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -15036,19 +15395,19 @@
         <v>404001</v>
       </c>
       <c r="C22" t="s">
-        <v>976</v>
+        <v>1003</v>
       </c>
       <c r="D22" t="s">
-        <v>977</v>
+        <v>1004</v>
       </c>
       <c r="E22" t="s">
         <v>621</v>
       </c>
       <c r="F22" t="s">
-        <v>978</v>
+        <v>1005</v>
       </c>
       <c r="G22" t="s">
-        <v>979</v>
+        <v>1006</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -15069,7 +15428,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>980</v>
+        <v>1007</v>
       </c>
       <c r="P22" t="b">
         <v>1</v>
@@ -15086,19 +15445,19 @@
         <v>404002</v>
       </c>
       <c r="C23" t="s">
-        <v>981</v>
+        <v>1008</v>
       </c>
       <c r="D23" t="s">
-        <v>982</v>
+        <v>1009</v>
       </c>
       <c r="E23" t="s">
         <v>621</v>
       </c>
       <c r="F23" t="s">
-        <v>983</v>
+        <v>1010</v>
       </c>
       <c r="G23" t="s">
-        <v>984</v>
+        <v>1011</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -15119,7 +15478,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>985</v>
+        <v>1012</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
@@ -15136,19 +15495,19 @@
         <v>404004</v>
       </c>
       <c r="C24" t="s">
-        <v>986</v>
+        <v>1013</v>
       </c>
       <c r="D24" t="s">
-        <v>987</v>
+        <v>1014</v>
       </c>
       <c r="E24" t="s">
         <v>621</v>
       </c>
       <c r="F24" t="s">
-        <v>988</v>
+        <v>1015</v>
       </c>
       <c r="G24" t="s">
-        <v>989</v>
+        <v>1016</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -15169,7 +15528,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
@@ -15186,19 +15545,19 @@
         <v>404005</v>
       </c>
       <c r="C25" t="s">
-        <v>991</v>
+        <v>1018</v>
       </c>
       <c r="D25" t="s">
-        <v>992</v>
+        <v>1019</v>
       </c>
       <c r="E25" t="s">
         <v>621</v>
       </c>
       <c r="F25" t="s">
-        <v>993</v>
+        <v>1020</v>
       </c>
       <c r="G25" t="s">
-        <v>994</v>
+        <v>1021</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -15219,7 +15578,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>985</v>
+        <v>1012</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
@@ -15236,19 +15595,19 @@
         <v>404007</v>
       </c>
       <c r="C26" t="s">
-        <v>995</v>
+        <v>1022</v>
       </c>
       <c r="D26" t="s">
-        <v>996</v>
+        <v>1023</v>
       </c>
       <c r="E26" t="s">
         <v>621</v>
       </c>
       <c r="F26" t="s">
-        <v>997</v>
+        <v>1024</v>
       </c>
       <c r="G26" t="s">
-        <v>998</v>
+        <v>1025</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -15269,7 +15628,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
@@ -15286,19 +15645,19 @@
         <v>404008</v>
       </c>
       <c r="C27" t="s">
-        <v>999</v>
+        <v>1026</v>
       </c>
       <c r="D27" t="s">
-        <v>1000</v>
+        <v>1027</v>
       </c>
       <c r="E27" t="s">
         <v>621</v>
       </c>
       <c r="F27" t="s">
-        <v>1001</v>
+        <v>1028</v>
       </c>
       <c r="G27" t="s">
-        <v>1002</v>
+        <v>1029</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -15319,7 +15678,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>985</v>
+        <v>1012</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -15336,19 +15695,19 @@
         <v>404010</v>
       </c>
       <c r="C28" t="s">
-        <v>1003</v>
+        <v>1030</v>
       </c>
       <c r="D28" t="s">
-        <v>1004</v>
+        <v>1031</v>
       </c>
       <c r="E28" t="s">
         <v>621</v>
       </c>
       <c r="F28" t="s">
-        <v>1005</v>
+        <v>1032</v>
       </c>
       <c r="G28" t="s">
-        <v>1006</v>
+        <v>1033</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -15369,7 +15728,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
@@ -15386,19 +15745,19 @@
         <v>404011</v>
       </c>
       <c r="C29" t="s">
-        <v>1007</v>
+        <v>1034</v>
       </c>
       <c r="D29" t="s">
-        <v>1008</v>
+        <v>1035</v>
       </c>
       <c r="E29" t="s">
         <v>621</v>
       </c>
       <c r="F29" t="s">
-        <v>1009</v>
+        <v>1036</v>
       </c>
       <c r="G29" t="s">
-        <v>1010</v>
+        <v>1037</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -15419,7 +15778,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>985</v>
+        <v>1012</v>
       </c>
       <c r="P29" t="b">
         <v>1</v>
@@ -15436,19 +15795,19 @@
         <v>404013</v>
       </c>
       <c r="C30" t="s">
-        <v>1011</v>
+        <v>1038</v>
       </c>
       <c r="D30" t="s">
-        <v>1012</v>
+        <v>1039</v>
       </c>
       <c r="E30" t="s">
         <v>621</v>
       </c>
       <c r="F30" t="s">
-        <v>1013</v>
+        <v>1040</v>
       </c>
       <c r="G30" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -15469,7 +15828,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -15486,7 +15845,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>1015</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -15494,19 +15853,19 @@
         <v>405001</v>
       </c>
       <c r="C32" t="s">
-        <v>1016</v>
+        <v>1043</v>
       </c>
       <c r="D32" t="s">
-        <v>1017</v>
+        <v>1044</v>
       </c>
       <c r="E32" t="s">
         <v>621</v>
       </c>
       <c r="F32" t="s">
-        <v>1018</v>
+        <v>1045</v>
       </c>
       <c r="G32" t="s">
-        <v>1019</v>
+        <v>1046</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -15527,7 +15886,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -15544,7 +15903,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>1020</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -15552,22 +15911,22 @@
         <v>406005</v>
       </c>
       <c r="C34" t="s">
-        <v>1021</v>
+        <v>1048</v>
       </c>
       <c r="D34" t="s">
-        <v>1022</v>
+        <v>1049</v>
       </c>
       <c r="E34" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F34" t="s">
-        <v>1023</v>
+        <v>1050</v>
       </c>
       <c r="G34" t="s">
-        <v>1024</v>
+        <v>1051</v>
       </c>
       <c r="H34" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I34" t="b">
         <v>1</v>
@@ -15588,7 +15947,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>1025</v>
+        <v>1052</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -15605,22 +15964,22 @@
         <v>406006</v>
       </c>
       <c r="C35" t="s">
-        <v>1026</v>
+        <v>1053</v>
       </c>
       <c r="D35" t="s">
-        <v>1027</v>
+        <v>1054</v>
       </c>
       <c r="E35" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F35" t="s">
-        <v>1028</v>
+        <v>1055</v>
       </c>
       <c r="G35" t="s">
-        <v>1029</v>
+        <v>1056</v>
       </c>
       <c r="H35" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I35" t="b">
         <v>1</v>
@@ -15641,7 +16000,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>1030</v>
+        <v>1057</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -15658,22 +16017,22 @@
         <v>406007</v>
       </c>
       <c r="C36" t="s">
-        <v>1031</v>
+        <v>1058</v>
       </c>
       <c r="D36" t="s">
-        <v>1032</v>
+        <v>1059</v>
       </c>
       <c r="E36" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F36" t="s">
-        <v>1033</v>
+        <v>1060</v>
       </c>
       <c r="G36" t="s">
-        <v>1034</v>
+        <v>1061</v>
       </c>
       <c r="H36" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -15694,7 +16053,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>1035</v>
+        <v>1062</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -15711,22 +16070,22 @@
         <v>406008</v>
       </c>
       <c r="C37" t="s">
-        <v>1036</v>
+        <v>1063</v>
       </c>
       <c r="D37" t="s">
-        <v>1037</v>
+        <v>1064</v>
       </c>
       <c r="E37" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F37" t="s">
-        <v>1038</v>
+        <v>1065</v>
       </c>
       <c r="G37" t="s">
-        <v>1039</v>
+        <v>1066</v>
       </c>
       <c r="H37" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
@@ -15747,7 +16106,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>1040</v>
+        <v>1067</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -15769,7 +16128,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>1041</v>
+        <v>1068</v>
       </c>
       <c r="C39" t="s">
         <v>161</v>
@@ -15828,19 +16187,19 @@
         <v>201001</v>
       </c>
       <c r="C40" t="s">
-        <v>1042</v>
+        <v>1069</v>
       </c>
       <c r="D40" t="s">
-        <v>952</v>
+        <v>979</v>
       </c>
       <c r="E40" t="s">
         <v>96</v>
       </c>
       <c r="F40" t="s">
-        <v>953</v>
+        <v>980</v>
       </c>
       <c r="G40" t="s">
-        <v>954</v>
+        <v>981</v>
       </c>
       <c r="H40" t="s">
         <v>161</v>
@@ -15884,19 +16243,19 @@
         <v>201002</v>
       </c>
       <c r="C41" t="s">
-        <v>1043</v>
+        <v>1070</v>
       </c>
       <c r="D41" t="s">
-        <v>956</v>
+        <v>983</v>
       </c>
       <c r="E41" t="s">
         <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>957</v>
+        <v>984</v>
       </c>
       <c r="G41" t="s">
-        <v>958</v>
+        <v>985</v>
       </c>
       <c r="H41" t="s">
         <v>161</v>
@@ -15940,19 +16299,19 @@
         <v>204001</v>
       </c>
       <c r="C42" t="s">
-        <v>1044</v>
+        <v>1071</v>
       </c>
       <c r="D42" t="s">
-        <v>948</v>
+        <v>975</v>
       </c>
       <c r="E42" t="s">
         <v>96</v>
       </c>
       <c r="F42" t="s">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="G42" t="s">
-        <v>950</v>
+        <v>977</v>
       </c>
       <c r="H42" t="s">
         <v>161</v>
@@ -15993,7 +16352,7 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>1045</v>
+        <v>1072</v>
       </c>
       <c r="C43" t="s">
         <v>161</v>
@@ -16052,19 +16411,19 @@
         <v>301001</v>
       </c>
       <c r="C44" t="s">
-        <v>1046</v>
+        <v>1073</v>
       </c>
       <c r="D44" t="s">
-        <v>967</v>
+        <v>994</v>
       </c>
       <c r="E44" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="F44" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="G44" t="s">
-        <v>969</v>
+        <v>996</v>
       </c>
       <c r="H44" t="s">
         <v>161</v>
@@ -16088,7 +16447,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -16108,19 +16467,19 @@
         <v>301002</v>
       </c>
       <c r="C45" t="s">
-        <v>1047</v>
+        <v>1074</v>
       </c>
       <c r="D45" t="s">
-        <v>972</v>
+        <v>999</v>
       </c>
       <c r="E45" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="F45" t="s">
-        <v>973</v>
+        <v>1000</v>
       </c>
       <c r="G45" t="s">
-        <v>974</v>
+        <v>1001</v>
       </c>
       <c r="H45" t="s">
         <v>161</v>
@@ -16144,7 +16503,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -16161,7 +16520,7 @@
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>1048</v>
+        <v>1075</v>
       </c>
       <c r="C46" t="s">
         <v>161</v>
@@ -16220,22 +16579,22 @@
         <v>501001</v>
       </c>
       <c r="C47" t="s">
-        <v>1049</v>
+        <v>1076</v>
       </c>
       <c r="D47" t="s">
-        <v>1050</v>
+        <v>1077</v>
       </c>
       <c r="E47" t="s">
         <v>96</v>
       </c>
       <c r="F47" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="G47" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
       <c r="H47" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I47" t="b">
         <v>1</v>
@@ -16276,22 +16635,22 @@
         <v>501002</v>
       </c>
       <c r="C48" t="s">
-        <v>1051</v>
+        <v>1078</v>
       </c>
       <c r="D48" t="s">
-        <v>1052</v>
+        <v>1079</v>
       </c>
       <c r="E48" t="s">
         <v>96</v>
       </c>
       <c r="F48" t="s">
-        <v>928</v>
+        <v>955</v>
       </c>
       <c r="G48" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="H48" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I48" t="b">
         <v>1</v>
@@ -16332,22 +16691,22 @@
         <v>501003</v>
       </c>
       <c r="C49" t="s">
-        <v>1053</v>
+        <v>1080</v>
       </c>
       <c r="D49" t="s">
-        <v>1054</v>
+        <v>1081</v>
       </c>
       <c r="E49" t="s">
         <v>96</v>
       </c>
       <c r="F49" t="s">
-        <v>932</v>
+        <v>959</v>
       </c>
       <c r="G49" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="H49" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I49" t="b">
         <v>1</v>
@@ -16388,22 +16747,22 @@
         <v>501004</v>
       </c>
       <c r="C50" t="s">
-        <v>1055</v>
+        <v>1082</v>
       </c>
       <c r="D50" t="s">
-        <v>1056</v>
+        <v>1083</v>
       </c>
       <c r="E50" t="s">
         <v>96</v>
       </c>
       <c r="F50" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
       <c r="G50" t="s">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="H50" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I50" t="b">
         <v>1</v>
@@ -16441,7 +16800,7 @@
         <v>39</v>
       </c>
       <c r="B51" t="s">
-        <v>1057</v>
+        <v>1084</v>
       </c>
       <c r="C51" t="s">
         <v>161</v>
@@ -16500,22 +16859,22 @@
         <v>601001</v>
       </c>
       <c r="C52" t="s">
-        <v>1058</v>
+        <v>1085</v>
       </c>
       <c r="D52" t="s">
-        <v>1022</v>
+        <v>1049</v>
       </c>
       <c r="E52" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F52" t="s">
-        <v>1023</v>
+        <v>1050</v>
       </c>
       <c r="G52" t="s">
-        <v>1024</v>
+        <v>1051</v>
       </c>
       <c r="H52" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
@@ -16536,7 +16895,7 @@
         <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>1059</v>
+        <v>1086</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -16556,22 +16915,22 @@
         <v>601002</v>
       </c>
       <c r="C53" t="s">
-        <v>1060</v>
+        <v>1087</v>
       </c>
       <c r="D53" t="s">
-        <v>1027</v>
+        <v>1054</v>
       </c>
       <c r="E53" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F53" t="s">
-        <v>1028</v>
+        <v>1055</v>
       </c>
       <c r="G53" t="s">
-        <v>1029</v>
+        <v>1056</v>
       </c>
       <c r="H53" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I53" t="b">
         <v>1</v>
@@ -16592,7 +16951,7 @@
         <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>1061</v>
+        <v>1088</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -16612,22 +16971,22 @@
         <v>601003</v>
       </c>
       <c r="C54" t="s">
-        <v>1062</v>
+        <v>1089</v>
       </c>
       <c r="D54" t="s">
-        <v>1032</v>
+        <v>1059</v>
       </c>
       <c r="E54" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F54" t="s">
-        <v>1033</v>
+        <v>1060</v>
       </c>
       <c r="G54" t="s">
-        <v>1034</v>
+        <v>1061</v>
       </c>
       <c r="H54" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
@@ -16648,7 +17007,7 @@
         <v>0</v>
       </c>
       <c r="O54" t="s">
-        <v>1063</v>
+        <v>1090</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -16668,22 +17027,22 @@
         <v>601004</v>
       </c>
       <c r="C55" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D55" t="s">
         <v>1064</v>
       </c>
-      <c r="D55" t="s">
-        <v>1037</v>
-      </c>
       <c r="E55" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="F55" t="s">
-        <v>1038</v>
+        <v>1065</v>
       </c>
       <c r="G55" t="s">
-        <v>1039</v>
+        <v>1066</v>
       </c>
       <c r="H55" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
@@ -16704,7 +17063,7 @@
         <v>0</v>
       </c>
       <c r="O55" t="s">
-        <v>1065</v>
+        <v>1092</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
@@ -16721,7 +17080,7 @@
         <v>39</v>
       </c>
       <c r="B56" t="s">
-        <v>1066</v>
+        <v>1093</v>
       </c>
       <c r="C56" t="s">
         <v>161</v>
@@ -16780,19 +17139,19 @@
         <v>700001</v>
       </c>
       <c r="C57" t="s">
-        <v>1067</v>
+        <v>1094</v>
       </c>
       <c r="D57" t="s">
-        <v>1068</v>
+        <v>1095</v>
       </c>
       <c r="E57" t="s">
         <v>621</v>
       </c>
       <c r="F57" t="s">
-        <v>1069</v>
+        <v>1096</v>
       </c>
       <c r="G57" t="s">
-        <v>1070</v>
+        <v>1097</v>
       </c>
       <c r="H57" t="s">
         <v>161</v>
@@ -16816,7 +17175,7 @@
         <v>0</v>
       </c>
       <c r="O57" t="s">
-        <v>1071</v>
+        <v>1098</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
@@ -16836,19 +17195,19 @@
         <v>700002</v>
       </c>
       <c r="C58" t="s">
-        <v>1072</v>
+        <v>1099</v>
       </c>
       <c r="D58" t="s">
-        <v>1073</v>
+        <v>1100</v>
       </c>
       <c r="E58" t="s">
         <v>621</v>
       </c>
       <c r="F58" t="s">
-        <v>1074</v>
+        <v>1101</v>
       </c>
       <c r="G58" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="H58" t="s">
         <v>161</v>
@@ -16872,7 +17231,7 @@
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>1076</v>
+        <v>1103</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -16892,19 +17251,19 @@
         <v>700004</v>
       </c>
       <c r="C59" t="s">
-        <v>1077</v>
+        <v>1104</v>
       </c>
       <c r="D59" t="s">
-        <v>1078</v>
+        <v>1105</v>
       </c>
       <c r="E59" t="s">
         <v>621</v>
       </c>
       <c r="F59" t="s">
-        <v>1079</v>
+        <v>1106</v>
       </c>
       <c r="G59" t="s">
-        <v>1080</v>
+        <v>1107</v>
       </c>
       <c r="H59" t="s">
         <v>161</v>
@@ -16928,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="O59" t="s">
-        <v>1081</v>
+        <v>1108</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
@@ -16948,19 +17307,19 @@
         <v>700005</v>
       </c>
       <c r="C60" t="s">
-        <v>1082</v>
+        <v>1109</v>
       </c>
       <c r="D60" t="s">
-        <v>1083</v>
+        <v>1110</v>
       </c>
       <c r="E60" t="s">
         <v>621</v>
       </c>
       <c r="F60" t="s">
-        <v>1084</v>
+        <v>1111</v>
       </c>
       <c r="G60" t="s">
-        <v>1085</v>
+        <v>1112</v>
       </c>
       <c r="H60" t="s">
         <v>161</v>
@@ -16984,7 +17343,7 @@
         <v>0</v>
       </c>
       <c r="O60" t="s">
-        <v>1076</v>
+        <v>1103</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
@@ -17004,19 +17363,19 @@
         <v>700007</v>
       </c>
       <c r="C61" t="s">
-        <v>1086</v>
+        <v>1113</v>
       </c>
       <c r="D61" t="s">
-        <v>1087</v>
+        <v>1114</v>
       </c>
       <c r="E61" t="s">
         <v>621</v>
       </c>
       <c r="F61" t="s">
-        <v>1088</v>
+        <v>1115</v>
       </c>
       <c r="G61" t="s">
-        <v>1089</v>
+        <v>1116</v>
       </c>
       <c r="H61" t="s">
         <v>161</v>
@@ -17040,7 +17399,7 @@
         <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>1081</v>
+        <v>1108</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
@@ -17060,19 +17419,19 @@
         <v>700008</v>
       </c>
       <c r="C62" t="s">
-        <v>1090</v>
+        <v>1117</v>
       </c>
       <c r="D62" t="s">
-        <v>1091</v>
+        <v>1118</v>
       </c>
       <c r="E62" t="s">
         <v>621</v>
       </c>
       <c r="F62" t="s">
-        <v>1092</v>
+        <v>1119</v>
       </c>
       <c r="G62" t="s">
-        <v>1093</v>
+        <v>1120</v>
       </c>
       <c r="H62" t="s">
         <v>161</v>
@@ -17096,7 +17455,7 @@
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>1076</v>
+        <v>1103</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
@@ -17116,19 +17475,19 @@
         <v>700010</v>
       </c>
       <c r="C63" t="s">
-        <v>1094</v>
+        <v>1121</v>
       </c>
       <c r="D63" t="s">
-        <v>1095</v>
+        <v>1122</v>
       </c>
       <c r="E63" t="s">
         <v>621</v>
       </c>
       <c r="F63" t="s">
-        <v>1096</v>
+        <v>1123</v>
       </c>
       <c r="G63" t="s">
-        <v>1097</v>
+        <v>1124</v>
       </c>
       <c r="H63" t="s">
         <v>161</v>
@@ -17152,7 +17511,7 @@
         <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>1081</v>
+        <v>1108</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
@@ -17172,19 +17531,19 @@
         <v>700011</v>
       </c>
       <c r="C64" t="s">
-        <v>1098</v>
+        <v>1125</v>
       </c>
       <c r="D64" t="s">
-        <v>1099</v>
+        <v>1126</v>
       </c>
       <c r="E64" t="s">
         <v>621</v>
       </c>
       <c r="F64" t="s">
-        <v>1100</v>
+        <v>1127</v>
       </c>
       <c r="G64" t="s">
-        <v>1101</v>
+        <v>1128</v>
       </c>
       <c r="H64" t="s">
         <v>161</v>
@@ -17208,7 +17567,7 @@
         <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>1076</v>
+        <v>1103</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
@@ -17225,7 +17584,7 @@
         <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>1102</v>
+        <v>1129</v>
       </c>
       <c r="C65" t="s">
         <v>161</v>
@@ -17284,19 +17643,19 @@
         <v>701001</v>
       </c>
       <c r="C66" t="s">
-        <v>1103</v>
+        <v>1130</v>
       </c>
       <c r="D66" t="s">
-        <v>1104</v>
+        <v>1131</v>
       </c>
       <c r="E66" t="s">
         <v>621</v>
       </c>
       <c r="F66" t="s">
-        <v>1105</v>
+        <v>1132</v>
       </c>
       <c r="G66" t="s">
-        <v>1019</v>
+        <v>1046</v>
       </c>
       <c r="H66" t="s">
         <v>161</v>
@@ -17320,7 +17679,7 @@
         <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>1081</v>
+        <v>1108</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
@@ -17359,7 +17718,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{0e754b0f-c854-4e58-9394-75f0f32f6700}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{29744a69-728b-45fe-9b11-3be186d116ba}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -17378,10 +17737,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="14.0833333333333" customWidth="1"/>
@@ -17398,19 +17757,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="D1" t="s">
-        <v>1107</v>
+        <v>1134</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>883</v>
+        <v>910</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1108</v>
+        <v>1135</v>
       </c>
       <c r="G1" t="s">
-        <v>1109</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -17467,13 +17826,13 @@
         <v>556</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1110</v>
+        <v>1137</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1111</v>
+        <v>1138</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1112</v>
+        <v>1139</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>596</v>
@@ -17496,13 +17855,13 @@
         <v>199999</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1113</v>
+        <v>1140</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>597</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>1114</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6" ht="52.2" spans="1:7">
@@ -17519,335 +17878,326 @@
         <v>299999</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1116</v>
+        <v>1143</v>
       </c>
       <c r="G6" t="s">
-        <v>1117</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="7" ht="87" spans="1:7">
-      <c r="A7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B7">
+      <c r="A7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="9">
         <v>1003</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="9">
         <v>201000</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="9">
         <v>229999</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="8" ht="34.8" spans="1:7">
-      <c r="A8" t="s">
-        <v>161</v>
-      </c>
+      <c r="E7" s="10" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="8" ht="84" customHeight="1" spans="1:7">
       <c r="B8">
+        <v>1003</v>
+      </c>
+      <c r="C8">
+        <v>201000</v>
+      </c>
+      <c r="D8">
+        <v>209999</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1" spans="1:7">
+      <c r="A9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9">
         <v>1004</v>
       </c>
-      <c r="C8">
-        <v>230000</v>
-      </c>
-      <c r="D8">
+      <c r="C9">
+        <v>210000</v>
+      </c>
+      <c r="D9">
         <v>299999</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="9" ht="69.6" spans="1:7">
-      <c r="A9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9">
+      <c r="E9" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="10" ht="69.6" spans="1:7">
+      <c r="A10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="9">
         <v>1005</v>
       </c>
-      <c r="C9">
+      <c r="C10" s="9">
         <v>300000</v>
       </c>
-      <c r="D9">
+      <c r="D10" s="9">
         <v>399999</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="10" ht="34.8" spans="1:7">
-      <c r="A10" t="s">
-        <v>161</v>
-      </c>
-      <c r="B10">
+      <c r="E10" s="10" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="11" ht="67" customHeight="1" spans="1:7">
+      <c r="B11">
+        <v>1005</v>
+      </c>
+      <c r="C11">
+        <v>300000</v>
+      </c>
+      <c r="D11">
+        <v>399999</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="12" ht="34.8" spans="1:7">
+      <c r="A12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="9">
         <v>1006</v>
       </c>
-      <c r="C10">
+      <c r="C12" s="9">
         <v>301000</v>
       </c>
-      <c r="D10">
+      <c r="D12" s="9">
         <v>301999</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="11" ht="34.8" spans="1:7">
-      <c r="A11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B11">
+      <c r="E12" s="10" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:7">
+      <c r="B13">
+        <v>1006</v>
+      </c>
+      <c r="C13">
+        <v>301000</v>
+      </c>
+      <c r="D13">
+        <v>301999</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="14" ht="34.8" spans="1:7">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14">
         <v>1007</v>
       </c>
-      <c r="C11">
+      <c r="C14">
         <v>302000</v>
       </c>
-      <c r="D11">
+      <c r="D14">
         <v>302999</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>1130</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="G11" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="12" ht="34.8" spans="1:7">
-      <c r="A12" t="s">
-        <v>161</v>
-      </c>
-      <c r="B12">
+      <c r="E14" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="15" ht="34.8" spans="1:7">
+      <c r="A15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15">
         <v>1008</v>
       </c>
-      <c r="C12">
+      <c r="C15">
         <v>303000</v>
       </c>
-      <c r="D12">
+      <c r="D15">
         <v>399999</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="13" ht="87" spans="1:7">
-      <c r="A13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B13">
+      <c r="E15" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="16" ht="87" spans="1:7">
+      <c r="A16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16">
         <v>1009</v>
       </c>
-      <c r="C13">
+      <c r="C16">
         <v>400000</v>
       </c>
-      <c r="D13">
+      <c r="D16">
         <v>499999</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>1136</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>1137</v>
-      </c>
-      <c r="G13" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="14" ht="52.2" spans="1:7">
-      <c r="A14" t="s">
-        <v>161</v>
-      </c>
-      <c r="B14">
+      <c r="E16" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="17" ht="52.2" spans="1:7">
+      <c r="A17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17">
         <v>1010</v>
       </c>
-      <c r="C14">
+      <c r="C17">
         <v>400000</v>
       </c>
-      <c r="D14">
+      <c r="D17">
         <v>409999</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>1140</v>
-      </c>
-      <c r="G14" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="15" ht="52.2" spans="1:7">
-      <c r="A15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B15">
+      <c r="E17" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="18" ht="52.2" spans="1:7">
+      <c r="A18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18">
         <v>1011</v>
       </c>
-      <c r="C15">
+      <c r="C18">
         <v>410000</v>
       </c>
-      <c r="D15">
+      <c r="D18">
         <v>499999</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>1143</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="16" ht="52.2" spans="1:7">
-      <c r="A16" t="s">
-        <v>161</v>
-      </c>
-      <c r="B16">
+      <c r="E18" s="6" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="19" ht="52.2" spans="1:7">
+      <c r="A19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19">
         <v>1012</v>
       </c>
-      <c r="C16">
+      <c r="C19">
         <v>500000</v>
-      </c>
-      <c r="D16">
-        <v>599999</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>1145</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="17" ht="34.8" spans="1:7">
-      <c r="A17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B17">
-        <v>1013</v>
-      </c>
-      <c r="C17">
-        <v>501000</v>
-      </c>
-      <c r="D17">
-        <v>501999</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>1148</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>1149</v>
-      </c>
-      <c r="G17" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="18" ht="34.8" spans="1:7">
-      <c r="A18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B18">
-        <v>1014</v>
-      </c>
-      <c r="C18">
-        <v>502000</v>
-      </c>
-      <c r="D18">
-        <v>502999</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>1152</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="19" ht="34.8" spans="1:7">
-      <c r="A19" t="s">
-        <v>161</v>
-      </c>
-      <c r="B19">
-        <v>1015</v>
-      </c>
-      <c r="C19">
-        <v>503000</v>
       </c>
       <c r="D19">
         <v>599999</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1154</v>
+        <v>1179</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1155</v>
+        <v>1180</v>
       </c>
       <c r="G19" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="20" ht="87" spans="1:7">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="20" ht="34.8" spans="1:7">
       <c r="A20" t="s">
         <v>161</v>
       </c>
       <c r="B20">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="C20">
-        <v>600000</v>
+        <v>501000</v>
       </c>
       <c r="D20">
-        <v>699999</v>
+        <v>501999</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1157</v>
+        <v>1182</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1158</v>
+        <v>1183</v>
       </c>
       <c r="G20" t="s">
-        <v>1159</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="21" ht="34.8" spans="1:7">
@@ -17855,22 +18205,22 @@
         <v>161</v>
       </c>
       <c r="B21">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C21">
-        <v>601000</v>
+        <v>502000</v>
       </c>
       <c r="D21">
-        <v>601999</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>1160</v>
+        <v>502999</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>1185</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1161</v>
+        <v>1186</v>
       </c>
       <c r="G21" t="s">
-        <v>1162</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="22" ht="34.8" spans="1:7">
@@ -17878,45 +18228,45 @@
         <v>161</v>
       </c>
       <c r="B22">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C22">
-        <v>602000</v>
+        <v>503000</v>
       </c>
       <c r="D22">
-        <v>602999</v>
+        <v>599999</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>1163</v>
+        <v>1188</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1164</v>
+        <v>1189</v>
       </c>
       <c r="G22" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="23" ht="34.8" spans="1:7">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="23" ht="87" spans="1:7">
       <c r="A23" t="s">
         <v>161</v>
       </c>
       <c r="B23">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="C23">
-        <v>603000</v>
+        <v>600000</v>
       </c>
       <c r="D23">
-        <v>603999</v>
+        <v>699999</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1166</v>
+        <v>1191</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1167</v>
+        <v>1192</v>
       </c>
       <c r="G23" t="s">
-        <v>1168</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="24" ht="34.8" spans="1:7">
@@ -17924,22 +18274,22 @@
         <v>161</v>
       </c>
       <c r="B24">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="C24">
-        <v>604000</v>
+        <v>601000</v>
       </c>
       <c r="D24">
-        <v>699999</v>
+        <v>601999</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1169</v>
+        <v>1194</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1170</v>
+        <v>1195</v>
       </c>
       <c r="G24" t="s">
-        <v>1171</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="25" ht="34.8" spans="1:7">
@@ -17947,45 +18297,45 @@
         <v>161</v>
       </c>
       <c r="B25">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="C25">
-        <v>700000</v>
+        <v>602000</v>
       </c>
       <c r="D25">
-        <v>799999</v>
+        <v>602999</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1172</v>
+        <v>1197</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1173</v>
+        <v>1198</v>
       </c>
       <c r="G25" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="26" ht="52.2" spans="1:7">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="26" ht="34.8" spans="1:7">
       <c r="A26" t="s">
         <v>161</v>
       </c>
       <c r="B26">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="C26">
-        <v>700000</v>
+        <v>603000</v>
       </c>
       <c r="D26">
-        <v>709999</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>1175</v>
+        <v>603999</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>1200</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1176</v>
+        <v>1201</v>
       </c>
       <c r="G26" t="s">
-        <v>1177</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="27" ht="34.8" spans="1:7">
@@ -17993,22 +18343,22 @@
         <v>161</v>
       </c>
       <c r="B27">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="C27">
-        <v>700000</v>
+        <v>604000</v>
       </c>
       <c r="D27">
-        <v>700999</v>
+        <v>699999</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>1178</v>
+        <v>1203</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1179</v>
+        <v>1204</v>
       </c>
       <c r="G27" t="s">
-        <v>1180</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="28" ht="34.8" spans="1:7">
@@ -18016,154 +18366,347 @@
         <v>161</v>
       </c>
       <c r="B28">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="C28">
-        <v>701000</v>
+        <v>700000</v>
       </c>
       <c r="D28">
-        <v>701999</v>
+        <v>799999</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>1181</v>
+        <v>1206</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1182</v>
+        <v>1207</v>
       </c>
       <c r="G28" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="29" ht="34.8" spans="1:7">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="29" ht="52.2" spans="1:7">
       <c r="A29" t="s">
         <v>161</v>
       </c>
       <c r="B29">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="C29">
-        <v>702000</v>
+        <v>700000</v>
       </c>
       <c r="D29">
         <v>709999</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>1184</v>
+      <c r="E29" s="1" t="s">
+        <v>1209</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1185</v>
+        <v>1210</v>
       </c>
       <c r="G29" t="s">
-        <v>1186</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="30" ht="34.8" spans="1:7">
-      <c r="A30" t="s">
-        <v>161</v>
-      </c>
-      <c r="B30">
+      <c r="A30" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="9">
+        <v>1023</v>
+      </c>
+      <c r="C30" s="9">
+        <v>700000</v>
+      </c>
+      <c r="D30" s="9">
+        <v>700999</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>1213</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="31" ht="52.2" spans="1:7">
+      <c r="B31">
+        <v>1023</v>
+      </c>
+      <c r="C31">
+        <v>700000</v>
+      </c>
+      <c r="D31">
+        <v>700999</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="32" ht="34.8" spans="1:7">
+      <c r="B32">
+        <v>1029</v>
+      </c>
+      <c r="C32">
+        <v>700000</v>
+      </c>
+      <c r="D32">
+        <v>700099</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="33" ht="34.8" spans="1:7">
+      <c r="B33">
+        <v>1030</v>
+      </c>
+      <c r="C33">
+        <v>700100</v>
+      </c>
+      <c r="D33">
+        <v>700999</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="34" ht="34.8" spans="1:7">
+      <c r="A34" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="9">
+        <v>1024</v>
+      </c>
+      <c r="C34" s="9">
+        <v>701000</v>
+      </c>
+      <c r="D34" s="9">
+        <v>701999</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="35" ht="71" customHeight="1" spans="1:7">
+      <c r="B35">
+        <v>1024</v>
+      </c>
+      <c r="C35">
+        <v>701000</v>
+      </c>
+      <c r="D35">
+        <v>701999</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="36" ht="71" customHeight="1" spans="1:7">
+      <c r="B36">
+        <v>1031</v>
+      </c>
+      <c r="C36">
+        <v>701000</v>
+      </c>
+      <c r="D36">
+        <v>701099</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="37" ht="71" customHeight="1" spans="1:7">
+      <c r="B37">
+        <v>1032</v>
+      </c>
+      <c r="C37">
+        <v>701100</v>
+      </c>
+      <c r="D37">
+        <v>701999</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="38" ht="34.8" spans="1:7">
+      <c r="A38" t="s">
+        <v>161</v>
+      </c>
+      <c r="B38">
+        <v>1025</v>
+      </c>
+      <c r="C38">
+        <v>702000</v>
+      </c>
+      <c r="D38">
+        <v>709999</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="39" ht="34.8" spans="1:7">
+      <c r="A39" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39">
         <v>1026</v>
       </c>
-      <c r="C30">
+      <c r="C39">
         <v>710000</v>
       </c>
-      <c r="D30">
+      <c r="D39">
         <v>799999</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>1187</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="G30" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="31" ht="34.8" spans="1:7">
-      <c r="A31" t="s">
-        <v>161</v>
-      </c>
-      <c r="B31">
+      <c r="E39" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="40" ht="34.8" spans="1:7">
+      <c r="A40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B40">
         <v>1027</v>
       </c>
-      <c r="C31">
+      <c r="C40">
         <v>800000</v>
       </c>
-      <c r="D31">
+      <c r="D40">
         <v>999999</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="E40" s="6" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G40" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="32" ht="34.8" spans="1:7">
-      <c r="A32" t="s">
-        <v>161</v>
-      </c>
-      <c r="B32">
+    <row r="41" ht="34.8" spans="1:7">
+      <c r="A41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41">
         <v>1028</v>
       </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32">
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
         <v>99999</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>1192</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>1193</v>
-      </c>
-      <c r="G32" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="33" spans="5:5">
-      <c r="E33" s="6"/>
-    </row>
-    <row r="35" spans="5:5">
-      <c r="E35" s="6"/>
-    </row>
-    <row r="36" spans="5:5">
-      <c r="E36" s="6"/>
-    </row>
-    <row r="37" spans="5:5">
-      <c r="E37" s="6"/>
-    </row>
-    <row r="38" spans="5:5">
-      <c r="E38" s="6"/>
-    </row>
-    <row r="39" spans="5:5">
-      <c r="E39" s="6"/>
-    </row>
-    <row r="40" spans="5:5">
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" spans="5:5">
-      <c r="E41" s="6"/>
-    </row>
-    <row r="43" spans="5:5">
-      <c r="E43" s="6"/>
-    </row>
-    <row r="44" spans="5:5">
-      <c r="E44" s="6"/>
-    </row>
-    <row r="45" spans="5:5">
-      <c r="E45" s="6"/>
-    </row>
-    <row r="47" spans="5:5">
+      <c r="E41" s="6" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="E42" s="2"/>
+      <c r="F42"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="F43"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="F44"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="F45"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="F46"/>
+    </row>
+    <row r="47" spans="1:7">
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="5:5">
+    <row r="48" spans="1:7">
       <c r="E48" s="6"/>
+    </row>
+    <row r="49" spans="5:5">
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" spans="5:5">
+      <c r="E50" s="6"/>
+    </row>
+    <row r="52" spans="5:5">
+      <c r="E52" s="6"/>
+    </row>
+    <row r="53" spans="5:5">
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" spans="5:5">
+      <c r="E54" s="6"/>
+    </row>
+    <row r="56" spans="5:5">
+      <c r="E56" s="6"/>
+    </row>
+    <row r="57" spans="5:5">
+      <c r="E57" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18184,35 +18727,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="20" t="s">
         <v>512</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="16" t="s">
         <v>513</v>
       </c>
       <c r="E2" t="s">
@@ -18221,130 +18764,130 @@
       <c r="F2" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11" t="s">
+      <c r="G2" s="16"/>
+      <c r="H2" s="16" t="s">
         <v>515</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="J2" s="11">
-        <v>1</v>
-      </c>
-      <c r="K2" s="11" t="s">
+      <c r="J2" s="16">
+        <v>1</v>
+      </c>
+      <c r="K2" s="16" t="s">
         <v>516</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="16" t="s">
         <v>517</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="16" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="16" t="s">
         <v>519</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="16" t="s">
         <v>520</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11" t="s">
+      <c r="G3" s="16"/>
+      <c r="H3" s="16" t="s">
         <v>521</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="16" t="s">
         <v>522</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="16">
         <v>2</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="16" t="s">
         <v>523</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="16" t="s">
         <v>524</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="16" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="16" t="s">
         <v>526</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="16" t="s">
         <v>527</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11" t="s">
+      <c r="G4" s="16"/>
+      <c r="H4" s="16" t="s">
         <v>528</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="16" t="s">
         <v>529</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="16">
         <v>4</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="16" t="s">
         <v>530</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="16" t="s">
         <v>531</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P4" s="16" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="16" t="s">
         <v>533</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11" t="s">
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
         <v>535</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="16" t="s">
         <v>536</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="16">
         <v>8</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="16" t="s">
         <v>537</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="16" t="s">
         <v>538</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="P5" s="16" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="16" t="s">
         <v>540</v>
       </c>
       <c r="E6" t="s">
@@ -18353,278 +18896,278 @@
       <c r="F6" t="s">
         <v>140</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11" t="s">
+      <c r="G6" s="16"/>
+      <c r="H6" s="16" t="s">
         <v>542</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="16" t="s">
         <v>543</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="16">
         <v>16</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="P6" s="11" t="s">
+      <c r="P6" s="16" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="16" t="s">
         <v>547</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="16" t="s">
         <v>548</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11" t="s">
+      <c r="G7" s="16"/>
+      <c r="H7" s="16" t="s">
         <v>549</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="16">
         <v>32</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="16" t="s">
         <v>551</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="16" t="s">
         <v>552</v>
       </c>
-      <c r="P7" s="11" t="s">
+      <c r="P7" s="16" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="8" spans="1:21">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="16" t="s">
         <v>554</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="16" t="s">
         <v>555</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="16" t="s">
         <v>507</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="16" t="s">
         <v>556</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="16" t="s">
         <v>557</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="16">
         <v>64</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="16" t="s">
         <v>558</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="16" t="s">
         <v>559</v>
       </c>
-      <c r="P8" s="11" t="s">
+      <c r="P8" s="16" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="9" spans="1:21">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="16" t="s">
         <v>392</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="16" t="s">
         <v>561</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="16" t="s">
         <v>562</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="16" t="s">
         <v>563</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="16" t="s">
         <v>564</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="16" t="s">
         <v>565</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="16">
         <v>128</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="16" t="s">
         <v>566</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="16" t="s">
         <v>567</v>
       </c>
-      <c r="P9" s="11" t="s">
+      <c r="P9" s="16" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="16" t="s">
         <v>569</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="16" t="s">
         <v>570</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="16" t="s">
         <v>571</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="16">
         <v>256</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="16" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="16" t="s">
         <v>485</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="16" t="s">
         <v>573</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="16" t="s">
         <v>574</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="16" t="s">
         <v>575</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="16">
         <v>512</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="16" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="16" t="s">
         <v>490</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="16" t="s">
         <v>577</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="16" t="s">
         <v>578</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="16" t="s">
         <v>579</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="16">
         <v>1024</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="16" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="16" t="s">
         <v>581</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="16" t="s">
         <v>582</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="16" t="s">
         <v>583</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="16">
         <v>2048</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="16" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="16" t="s">
         <v>585</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="16" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="16" t="s">
         <v>586</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="16" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="16" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="21" spans="1:21">
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="16" t="s">
         <v>588</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="16" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="16" t="s">
         <v>589</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="16" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="16" t="s">
         <v>591</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="16" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="20" t="s">
         <v>593</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="15"/>
-      <c r="S32" s="15"/>
-      <c r="T32" s="15"/>
-      <c r="U32" s="15"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="20"/>
     </row>
     <row r="34" s="5" customFormat="1" spans="1:2">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="24" t="s">
         <v>594</v>
       </c>
       <c r="B34" s="5" t="s">
@@ -18632,7 +19175,7 @@
       </c>
     </row>
     <row r="35" s="5" customFormat="1" spans="1:2">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="24" t="s">
         <v>596</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -18651,7 +19194,7 @@
       <c r="A37" s="8"/>
     </row>
     <row r="38" s="5" customFormat="1" spans="1:2">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="24" t="s">
         <v>594</v>
       </c>
       <c r="B38" s="5" t="s">
@@ -18659,7 +19202,7 @@
       </c>
     </row>
     <row r="39" s="5" customFormat="1" spans="1:2">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="24" t="s">
         <v>596</v>
       </c>
       <c r="B39" s="5" t="s">
@@ -18667,7 +19210,7 @@
       </c>
     </row>
     <row r="40" s="5" customFormat="1" spans="1:2">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="24" t="s">
         <v>602</v>
       </c>
       <c r="B40" s="5" t="s">
@@ -18675,7 +19218,7 @@
       </c>
     </row>
     <row r="41" s="5" customFormat="1" spans="1:2">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="24" t="s">
         <v>598</v>
       </c>
       <c r="B41" s="5" t="s">
@@ -18692,7 +19235,7 @@
     </row>
     <row r="43" s="5" customFormat="1"/>
     <row r="44" s="5" customFormat="1" spans="1:2">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="24" t="s">
         <v>594</v>
       </c>
       <c r="B44" s="5" t="s">
@@ -18700,7 +19243,7 @@
       </c>
     </row>
     <row r="45" s="5" customFormat="1" spans="1:2">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="24" t="s">
         <v>596</v>
       </c>
       <c r="B45" s="5" t="s">
@@ -18716,7 +19259,7 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="24" t="s">
         <v>594</v>
       </c>
       <c r="B48" s="5" t="s">
@@ -18724,11 +19267,11 @@
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="7"/>
+      <c r="A49" s="24"/>
       <c r="B49" s="5"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="24" t="s">
         <v>594</v>
       </c>
       <c r="B50" s="5" t="s">
@@ -18739,14 +19282,14 @@
       <c r="G50" s="5"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="7"/>
+      <c r="A51" s="24"/>
       <c r="B51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="24" t="s">
         <v>594</v>
       </c>
       <c r="B52" s="5" t="s">
@@ -18755,7 +19298,7 @@
       <c r="G52" s="5"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="24" t="s">
         <v>596</v>
       </c>
       <c r="B53" s="5" t="s">
@@ -18773,7 +19316,7 @@
       <c r="G54" s="5"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="24" t="s">
         <v>594</v>
       </c>
       <c r="B56" s="5" t="s">
@@ -18781,7 +19324,7 @@
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="24" t="s">
         <v>596</v>
       </c>
       <c r="B57" s="5" t="s">
@@ -18800,7 +19343,7 @@
       <c r="C58" s="5"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="24" t="s">
         <v>594</v>
       </c>
       <c r="B60" s="5" t="s">
@@ -18808,7 +19351,7 @@
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="24" t="s">
         <v>596</v>
       </c>
       <c r="B61" s="5" t="s">
@@ -18824,7 +19367,7 @@
       </c>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="24" t="s">
         <v>594</v>
       </c>
       <c r="B64" s="5" t="s">
@@ -18832,7 +19375,7 @@
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="24" t="s">
         <v>596</v>
       </c>
       <c r="B65" s="5" t="s">
@@ -18840,7 +19383,7 @@
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="24" t="s">
         <v>602</v>
       </c>
       <c r="B66" s="5" t="s">
@@ -18849,7 +19392,7 @@
       <c r="C66" s="5"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="24" t="s">
         <v>602</v>
       </c>
       <c r="B67" s="5" t="s">
@@ -18858,7 +19401,7 @@
       <c r="C67" s="5"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="24" t="s">
         <v>602</v>
       </c>
       <c r="B68" s="5" t="s">
@@ -18867,7 +19410,7 @@
       <c r="C68" s="5"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="24" t="s">
         <v>602</v>
       </c>
       <c r="B69" t="s">
@@ -18875,7 +19418,7 @@
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="24" t="s">
         <v>602</v>
       </c>
       <c r="B70" t="s">
@@ -18887,7 +19430,7 @@
       <c r="F71" s="5"/>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="24" t="s">
         <v>594</v>
       </c>
       <c r="B72" s="5" t="s">
@@ -18895,7 +19438,7 @@
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="24" t="s">
         <v>596</v>
       </c>
       <c r="B73" s="5" t="s">
@@ -18912,7 +19455,7 @@
       <c r="C74" s="5"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="24" t="s">
         <v>594</v>
       </c>
       <c r="B76" t="s">
@@ -18920,7 +19463,7 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="7" t="s">
+      <c r="A77" s="24" t="s">
         <v>596</v>
       </c>
       <c r="B77" t="s">
@@ -19138,10 +19681,10 @@
       <c r="C5" t="s">
         <v>670</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="16" t="s">
         <v>671</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="16" t="s">
         <v>672</v>
       </c>
       <c r="F5">
@@ -19179,10 +19722,10 @@
       <c r="C6" t="s">
         <v>675</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="16" t="s">
         <v>676</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="16" t="s">
         <v>672</v>
       </c>
       <c r="F6">
@@ -19220,10 +19763,10 @@
       <c r="C7" t="s">
         <v>677</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="16" t="s">
         <v>677</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="16" t="s">
         <v>672</v>
       </c>
       <c r="F7">
@@ -19264,7 +19807,7 @@
       <c r="D8" t="s">
         <v>679</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="16" t="s">
         <v>680</v>
       </c>
       <c r="F8">
@@ -19302,10 +19845,10 @@
       <c r="C9" t="s">
         <v>682</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="16" t="s">
         <v>671</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="16" t="s">
         <v>672</v>
       </c>
       <c r="F9">
@@ -19337,13 +19880,13 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="E15" s="11"/>
+      <c r="E15" s="16"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="E16" s="11"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="11"/>
+      <c r="E17" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20072,7 +20615,7 @@
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="7.25" customWidth="1"/>
     <col min="5" max="5" width="11.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="11.0833333333333" style="12" customWidth="1"/>
+    <col min="6" max="6" width="11.0833333333333" style="17" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20132,7 +20675,7 @@
       <c r="E3" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="F3" s="13"/>
+      <c r="F3" s="18"/>
       <c r="G3" s="2" t="s">
         <v>667</v>
       </c>
@@ -20173,7 +20716,7 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="17">
         <f>E5/10000</f>
         <v>0</v>
       </c>
@@ -20194,7 +20737,7 @@
       <c r="E6">
         <v>6700</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="17">
         <f>E6/10000</f>
         <v>0.67</v>
       </c>
@@ -20215,7 +20758,7 @@
       <c r="E7">
         <v>2200</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="17">
         <f t="shared" ref="F7:F17" si="0">E7/10000</f>
         <v>0.22</v>
       </c>
@@ -20233,10 +20776,10 @@
       <c r="D8" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="19">
         <v>900</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="17">
         <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
@@ -20254,10 +20797,10 @@
       <c r="D9" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="19">
         <v>180</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="17">
         <f t="shared" si="0"/>
         <v>0.018</v>
       </c>
@@ -20278,7 +20821,7 @@
       <c r="E10">
         <v>20</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="17">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -20290,7 +20833,7 @@
       <c r="A11" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="17">
         <f>SUM(F5:F10)</f>
         <v>1</v>
       </c>
@@ -20308,7 +20851,7 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -20329,7 +20872,7 @@
       <c r="E13">
         <v>3700</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="17">
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
@@ -20353,7 +20896,7 @@
       <c r="E14">
         <v>4200</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="17">
         <f t="shared" si="0"/>
         <v>0.42</v>
       </c>
@@ -20374,7 +20917,7 @@
       <c r="E15">
         <v>1700</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="17">
         <f t="shared" si="0"/>
         <v>0.17</v>
       </c>
@@ -20395,7 +20938,7 @@
       <c r="E16">
         <v>380</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="17">
         <f t="shared" si="0"/>
         <v>0.038</v>
       </c>
@@ -20416,7 +20959,7 @@
       <c r="E17">
         <v>20</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="17">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
@@ -20428,7 +20971,7 @@
       <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="17">
         <f>SUM(F12:F17)</f>
         <v>1</v>
       </c>
@@ -20596,7 +21139,7 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="17">
         <f t="shared" ref="F28:F33" si="1">E28/10000</f>
         <v>0</v>
       </c>
@@ -20620,7 +21163,7 @@
       <c r="E29">
         <v>6700</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="17">
         <f t="shared" si="1"/>
         <v>0.67</v>
       </c>
@@ -20641,7 +21184,7 @@
       <c r="E30">
         <v>2200</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="17">
         <f t="shared" si="1"/>
         <v>0.22</v>
       </c>
@@ -20659,10 +21202,10 @@
       <c r="D31" t="s">
         <v>105</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="19">
         <v>900</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="17">
         <f t="shared" si="1"/>
         <v>0.09</v>
       </c>
@@ -20680,10 +21223,10 @@
       <c r="D32" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="19">
         <v>180</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="17">
         <f t="shared" si="1"/>
         <v>0.018</v>
       </c>
@@ -20704,7 +21247,7 @@
       <c r="E33">
         <v>20</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="17">
         <f t="shared" si="1"/>
         <v>0.002</v>
       </c>
@@ -20713,7 +21256,7 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="F34" s="12">
+      <c r="F34" s="17">
         <f>SUM(F28:F33)</f>
         <v>1</v>
       </c>
@@ -22041,10 +22584,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="16" t="s">
         <v>520</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="16" t="s">
         <v>110</v>
       </c>
       <c r="E6" t="s">
@@ -22064,10 +22607,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="16" t="s">
         <v>527</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="16" t="s">
         <v>105</v>
       </c>
       <c r="E7" t="s">
@@ -22087,10 +22630,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="16" t="s">
         <v>121</v>
       </c>
       <c r="E8" t="s">
@@ -22110,10 +22653,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="16" t="s">
         <v>541</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="16" t="s">
         <v>140</v>
       </c>
       <c r="E9" t="s">
@@ -22133,10 +22676,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="16" t="s">
         <v>548</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="16" t="s">
         <v>92</v>
       </c>
       <c r="E10" t="s">
@@ -22156,10 +22699,10 @@
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="16" t="s">
         <v>555</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="16" t="s">
         <v>507</v>
       </c>
       <c r="E11" t="s">
@@ -22179,10 +22722,10 @@
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="16" t="s">
         <v>562</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="16" t="s">
         <v>563</v>
       </c>
       <c r="E12" t="s">
@@ -22205,6 +22748,481 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="17.9166666666667" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="12.0833333333333" customWidth="1"/>
+    <col min="6" max="6" width="20.8333333333333" customWidth="1"/>
+    <col min="7" max="7" width="20.0833333333333" customWidth="1"/>
+    <col min="8" max="8" width="19.9166666666667" customWidth="1"/>
+    <col min="9" max="9" width="13.1666666666667" customWidth="1"/>
+    <col min="10" max="10" width="12.0833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>794</v>
+      </c>
+      <c r="C1" t="s">
+        <v>795</v>
+      </c>
+      <c r="D1" t="s">
+        <v>796</v>
+      </c>
+      <c r="F1" t="s">
+        <v>797</v>
+      </c>
+      <c r="G1" t="s">
+        <v>798</v>
+      </c>
+      <c r="H1" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>802</v>
+      </c>
+      <c r="F2" t="s">
+        <v>646</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="198" customHeight="1" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>810</v>
+      </c>
+      <c r="C4" t="s">
+        <v>811</v>
+      </c>
+      <c r="D4" t="s">
+        <v>812</v>
+      </c>
+      <c r="E4" t="s">
+        <v>813</v>
+      </c>
+      <c r="F4" t="s">
+        <v>814</v>
+      </c>
+      <c r="G4" t="s">
+        <v>815</v>
+      </c>
+      <c r="H4" t="s">
+        <v>816</v>
+      </c>
+      <c r="I4" t="s">
+        <v>817</v>
+      </c>
+      <c r="J4" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6">
+        <v>9001</v>
+      </c>
+      <c r="C6">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>818</v>
+      </c>
+      <c r="E6" t="str">
+        <f>LOOKUP(B6,Item!B:B,Item!H:H)</f>
+        <v>史诗</v>
+      </c>
+      <c r="F6">
+        <v>0.9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>819</v>
+      </c>
+      <c r="H6" t="s">
+        <v>820</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" t="str">
+        <f>LOOKUP(B6,Item!B:B,Item!D:D)</f>
+        <v>红茶</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7">
+        <v>9002</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>818</v>
+      </c>
+      <c r="E7" t="str">
+        <f>LOOKUP(B7,Item!B:B,Item!H:H)</f>
+        <v>稀有</v>
+      </c>
+      <c r="F7">
+        <v>0.8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>819</v>
+      </c>
+      <c r="H7" t="s">
+        <v>820</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="str">
+        <f>LOOKUP(B7,Item!B:B,Item!D:D)</f>
+        <v>波尔多</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8">
+        <v>9003</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>818</v>
+      </c>
+      <c r="E8" t="str">
+        <f>LOOKUP(B8,Item!B:B,Item!H:H)</f>
+        <v>稀有</v>
+      </c>
+      <c r="F8">
+        <v>0.8</v>
+      </c>
+      <c r="G8" t="s">
+        <v>819</v>
+      </c>
+      <c r="H8" t="s">
+        <v>820</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="str">
+        <f>LOOKUP(B8,Item!B:B,Item!D:D)</f>
+        <v>勃艮第</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9">
+        <v>9004</v>
+      </c>
+      <c r="C9">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>818</v>
+      </c>
+      <c r="E9" t="str">
+        <f>LOOKUP(B9,Item!B:B,Item!H:H)</f>
+        <v>史诗</v>
+      </c>
+      <c r="F9">
+        <v>0.9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>819</v>
+      </c>
+      <c r="H9" t="s">
+        <v>820</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="str">
+        <f>LOOKUP(B9,Item!B:B,Item!D:D)</f>
+        <v>霞多丽</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10">
+        <v>9005</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>818</v>
+      </c>
+      <c r="E10" t="str">
+        <f>LOOKUP(B10,Item!B:B,Item!H:H)</f>
+        <v>稀有</v>
+      </c>
+      <c r="F10">
+        <v>0.8</v>
+      </c>
+      <c r="G10" t="s">
+        <v>819</v>
+      </c>
+      <c r="H10" t="s">
+        <v>820</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="str">
+        <f>LOOKUP(B10,Item!B:B,Item!D:D)</f>
+        <v>子弹杯</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11">
+        <v>9006</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>818</v>
+      </c>
+      <c r="E11" t="str">
+        <f>LOOKUP(B11,Item!B:B,Item!H:H)</f>
+        <v>稀有</v>
+      </c>
+      <c r="F11">
+        <v>0.8</v>
+      </c>
+      <c r="G11" t="s">
+        <v>819</v>
+      </c>
+      <c r="H11" t="s">
+        <v>820</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="str">
+        <f>LOOKUP(B11,Item!B:B,Item!D:D)</f>
+        <v>郁金香杯</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12">
+        <v>9007</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>818</v>
+      </c>
+      <c r="E12" t="str">
+        <f>LOOKUP(B12,Item!B:B,Item!H:H)</f>
+        <v>稀有</v>
+      </c>
+      <c r="F12">
+        <v>0.8</v>
+      </c>
+      <c r="G12" t="s">
+        <v>819</v>
+      </c>
+      <c r="H12" t="s">
+        <v>820</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="str">
+        <f>LOOKUP(B12,Item!B:B,Item!D:D)</f>
+        <v>平底杯</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13">
+        <v>9008</v>
+      </c>
+      <c r="C13">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>818</v>
+      </c>
+      <c r="E13" t="str">
+        <f>LOOKUP(B13,Item!B:B,Item!H:H)</f>
+        <v>史诗</v>
+      </c>
+      <c r="F13">
+        <v>0.9</v>
+      </c>
+      <c r="G13" t="s">
+        <v>819</v>
+      </c>
+      <c r="H13" t="s">
+        <v>820</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="str">
+        <f>LOOKUP(B13,Item!B:B,Item!D:D)</f>
+        <v>年份酒</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14">
+        <v>9009</v>
+      </c>
+      <c r="C14">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>818</v>
+      </c>
+      <c r="E14" t="str">
+        <f>LOOKUP(B14,Item!B:B,Item!H:H)</f>
+        <v>优秀</v>
+      </c>
+      <c r="F14">
+        <v>0.7</v>
+      </c>
+      <c r="G14" t="s">
+        <v>819</v>
+      </c>
+      <c r="H14" t="s">
+        <v>820</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="str">
+        <f>LOOKUP(B14,Item!B:B,Item!D:D)</f>
+        <v>凉白开</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15">
+        <v>9010</v>
+      </c>
+      <c r="C15">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>818</v>
+      </c>
+      <c r="E15" t="str">
+        <f>LOOKUP(B15,Item!B:B,Item!H:H)</f>
+        <v>史诗</v>
+      </c>
+      <c r="F15">
+        <v>0.9</v>
+      </c>
+      <c r="G15" t="s">
+        <v>819</v>
+      </c>
+      <c r="H15" t="s">
+        <v>820</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="str">
+        <f>LOOKUP(B15,Item!B:B,Item!D:D)</f>
+        <v>威士忌</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16">
+        <v>9011</v>
+      </c>
+      <c r="C16">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>818</v>
+      </c>
+      <c r="E16" t="str">
+        <f>LOOKUP(B16,Item!B:B,Item!H:H)</f>
+        <v>传说</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>819</v>
+      </c>
+      <c r="H16" t="s">
+        <v>820</v>
+      </c>
+      <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16" t="str">
+        <f>LOOKUP(B16,Item!B:B,Item!D:D)</f>
+        <v>威士忌雪茄</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E31"/>
@@ -22223,10 +23241,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>794</v>
+        <v>821</v>
       </c>
       <c r="D1" t="s">
-        <v>795</v>
+        <v>822</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -22243,7 +23261,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>796</v>
+        <v>823</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -22260,10 +23278,10 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="E3" t="s">
-        <v>798</v>
+        <v>825</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -22285,7 +23303,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>799</v>
+        <v>826</v>
       </c>
       <c r="D5" t="s">
         <v>139</v>
@@ -22299,7 +23317,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>800</v>
+        <v>827</v>
       </c>
       <c r="D6" t="s">
         <v>190</v>
@@ -22313,7 +23331,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>801</v>
+        <v>828</v>
       </c>
       <c r="D7" t="s">
         <v>392</v>
@@ -22337,7 +23355,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>802</v>
+        <v>829</v>
       </c>
       <c r="D10" t="s">
         <v>270</v>
@@ -22381,216 +23399,42 @@
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="11"/>
+      <c r="C22" s="16"/>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="11"/>
+      <c r="C23" s="16"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
-    <col min="2" max="2" width="14.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="13.25" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>803</v>
-      </c>
-      <c r="D1" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>805</v>
-      </c>
-      <c r="D3" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="B5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="B6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="B7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="B8" t="s">
-        <v>211</v>
-      </c>
-      <c r="C8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>4003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="B9" t="s">
-        <v>392</v>
-      </c>
-      <c r="C9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="B10" t="s">
-        <v>237</v>
-      </c>
-      <c r="C10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="B11" t="s">
-        <v>270</v>
-      </c>
-      <c r="C11" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>6001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="B12" t="s">
-        <v>315</v>
-      </c>
-      <c r="C12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>7004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="B13" t="s">
-        <v>437</v>
-      </c>
-      <c r="C13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="B14" t="s">
-        <v>485</v>
-      </c>
-      <c r="C14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="B15" t="s">
-        <v>490</v>
-      </c>
-      <c r="C15" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>11002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="B16" t="s">
-        <v>499</v>
-      </c>
-      <c r="C16" t="b">
-        <v>1</v>
-      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/bak/xlsx/Items.xlsx
+++ b/luban-excels/bak/xlsx/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="12"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="812" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="1246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="1272">
   <si>
     <t>##var</t>
   </si>
@@ -2146,12 +2146,6 @@
     <t>IsEnabled</t>
   </si>
   <si>
-    <t>SteamOpenCostItemDefId</t>
-  </si>
-  <si>
-    <t>SteamExchangeTargetItemDefId</t>
-  </si>
-  <si>
     <t>EBlindBoxType</t>
   </si>
   <si>
@@ -2193,12 +2187,6 @@
     <t>临时开关</t>
   </si>
   <si>
-    <t>调用 Steam ExchangeItems 开启该盲盒时，作为交换材料消耗的 Steam ItemDef ID；填 0 表示不使用 Steam 库存物品作为开箱成本。</t>
-  </si>
-  <si>
-    <t>调用 Steam ExchangeItems 开启该盲盒时，请求生成的目标 Steam ItemDef ID。通常指向 Generator；Steam 完成交换后会展开 Generator 并返回最终奖励物品。</t>
-  </si>
-  <si>
     <t>奖励盒ID</t>
   </si>
   <si>
@@ -2229,12 +2217,6 @@
     <t>是否启用</t>
   </si>
   <si>
-    <t>Steam开箱消耗物品DefID</t>
-  </si>
-  <si>
-    <t>Steam交换目标物品DefID</t>
-  </si>
-  <si>
     <t>标准盲盒</t>
   </si>
   <si>
@@ -2271,7 +2253,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>新手盲盒招待券专用，后续招待券需新建ID</t>
+    <t>Old盲盒招待券专用（归档）</t>
   </si>
   <si>
     <t>UI\BlindBox\HintIcon_Common_Ticket.png</t>
@@ -2280,9 +2262,6 @@
     <t>BlindBoxId</t>
   </si>
   <si>
-    <t>VoucherUpgradeBlindBoxIds</t>
-  </si>
-  <si>
     <t>IsLoopTrack</t>
   </si>
   <si>
@@ -2292,9 +2271,6 @@
     <t>IntervalSeconds</t>
   </si>
   <si>
-    <t>EndSeconds</t>
-  </si>
-  <si>
     <t>MaxGrantCount</t>
   </si>
   <si>
@@ -2307,31 +2283,25 @@
     <t>SteamDropMaxPerWindow</t>
   </si>
   <si>
-    <t>(list#sep=|),int</t>
+    <t>CostChipsOverride</t>
   </si>
   <si>
     <t>对应 BlindBox.Id</t>
   </si>
   <si>
-    <t>按优先级填写可使用票券升级为的 BlindBox.Id。展示本行盲盒时，客户端按列表顺序检查对应盲盒的开箱票券，首个票券充足的盲盒将替代本行配置的 BlindBoxId；均不可用时仍展示原盲盒。留空表示不允许升级。</t>
-  </si>
-  <si>
-    <t>TRUE 表示正常阶段循环装扮券生产行</t>
+    <t>TRUE 表示正常阶段循环装扮奖励准备行</t>
   </si>
   <si>
     <t>按玩家调度时钟计算的最早生效时间</t>
   </si>
   <si>
-    <t>非循环行为相对上次领取间隔；循环行为 Steam 装扮券掉落间隔</t>
-  </si>
-  <si>
-    <t>结束时间；无限循环填 -1</t>
+    <t>非循环行为相对上次领取间隔；循环行为 Steam 直接奖励掉落间隔</t>
   </si>
   <si>
     <t>最多发放次数；不限填 -1</t>
   </si>
   <si>
-    <t>通过 TriggerItemDrop 请求的 Steam PlaytimeGenerator ItemDef ID；本地消耗品填 0</t>
+    <t>通过 TriggerItemDrop 请求的 Steam PlaytimeGenerator ItemDef ID；该定义直接生成最终装扮；本地消耗品填 0</t>
   </si>
   <si>
     <t>Steam 掉落窗口基础秒数；乘等待倍率后转为分钟；0 表示不启用</t>
@@ -2340,10 +2310,7 @@
     <t>Steam 掉落窗口内最多发放次数；未启用窗口时填 0</t>
   </si>
   <si>
-    <t>前 12 条控制新手顺序；正常阶段只保留一条循环装扮券生产行</t>
-  </si>
-  <si>
-    <t>可升级票券盲盒列表</t>
+    <t>&gt;0 本次展示覆盖 BlindBox 默认筹码成本；=0 表示继承，&lt;0 表示免费并显示其绝对值的字符串并添加删除线，注意配置中的倍率</t>
   </si>
   <si>
     <t>是循环生效的</t>
@@ -2355,7 +2322,10 @@
     <t>间隔秒数</t>
   </si>
   <si>
-    <t>结束秒数</t>
+    <t>分钟</t>
+  </si>
+  <si>
+    <t>累计分钟</t>
   </si>
   <si>
     <t>最多发放次数</t>
@@ -2370,64 +2340,28 @@
     <t>Steam窗口最大发放数</t>
   </si>
   <si>
+    <t>本次筹码成本覆盖</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>id无实际意义01与稀有读无关</t>
+  </si>
+  <si>
+    <t>先抽品质时命中的品质</t>
+  </si>
+  <si>
+    <t>品质权重，0 或禁用表示不参与</t>
+  </si>
+  <si>
+    <t>权重</t>
+  </si>
+  <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>新手期固定：5 分钟装扮盲盒，开发阶段时间为十分之一，下同</t>
-  </si>
-  <si>
-    <t>新手期固定：15 分钟新手礼盒</t>
-  </si>
-  <si>
-    <t>新手期固定：25 分钟消耗品盲盒</t>
-  </si>
-  <si>
-    <t>新手期固定：35 分钟装扮盲盒</t>
-  </si>
-  <si>
-    <t>新手期固定：45 分钟新手礼盒</t>
-  </si>
-  <si>
-    <t>新手期固定：55 分钟消耗品盲盒</t>
-  </si>
-  <si>
-    <t>新手期固定：65 分钟装扮盲盒</t>
-  </si>
-  <si>
-    <t>新手期固定：75 分钟新手礼盒</t>
-  </si>
-  <si>
-    <t>新手期固定：85 分钟消耗品盲盒</t>
-  </si>
-  <si>
-    <t>新手期固定：95 分钟装扮盲盒</t>
-  </si>
-  <si>
-    <t>新手期固定：105 分钟新手礼盒</t>
-  </si>
-  <si>
-    <t>新手期固定：115 分钟消耗品盲盒</t>
-  </si>
-  <si>
-    <t>正常阶段：第 12 个奖励入账后启动；正式倍率下每 30 分钟生产装扮券，60 分钟窗口最多 2 张</t>
-  </si>
-  <si>
-    <t>Rarity</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>id无实际意义01与稀有读无关</t>
-  </si>
-  <si>
-    <t>先抽品质时命中的品质</t>
-  </si>
-  <si>
-    <t>品质权重，0 或禁用表示不参与</t>
-  </si>
-  <si>
-    <t>权重</t>
   </si>
   <si>
     <t>新手盲盒概率会高一点</t>
@@ -3458,6 +3392,21 @@
     <t>NewbieBlindBoxV1GeneratorOfficial</t>
   </si>
   <si>
+    <t>正式新手阶段回执</t>
+  </si>
+  <si>
+    <t>NewbieScheduleStart</t>
+  </si>
+  <si>
+    <t>新手调度直接奖励开始</t>
+  </si>
+  <si>
+    <t>NewbieScheduleEnd</t>
+  </si>
+  <si>
+    <t>新手调度直接奖励结束</t>
+  </si>
+  <si>
     <t>正式 LinkTree 永久回执</t>
   </si>
   <si>
@@ -3512,124 +3461,244 @@
     <t>501004x1;191012x1</t>
   </si>
   <si>
+    <t>Old新手一次性游玩投放</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1001PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1001游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1001 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1001.</t>
+  </si>
+  <si>
+    <t>204001x1</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1002PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1002游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1002 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1002.</t>
+  </si>
+  <si>
+    <t>201002x1</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1004PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1004游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1004 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1004.</t>
+  </si>
+  <si>
+    <t>201001x1</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1005PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1005游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1005 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1005.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1007PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1007游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1007 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1007.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1008PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1008游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1008 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1008.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1010PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1010游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1010 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1010.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1011PlaytimeDrop</t>
+  </si>
+  <si>
+    <t>新手调度1011游玩投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1011 Playtime Drop</t>
+  </si>
+  <si>
+    <t>Grants the blind box item configured by newbie schedule 1011.</t>
+  </si>
+  <si>
     <t>正式新手一次性游玩投放</t>
   </si>
   <si>
-    <t>NewbieSchedule1001PlaytimeDrop</t>
-  </si>
-  <si>
-    <t>新手调度1001游玩投放</t>
-  </si>
-  <si>
-    <t>Newbie Schedule 1001 Playtime Drop</t>
-  </si>
-  <si>
-    <t>Grants the blind box item configured by newbie schedule 1001.</t>
-  </si>
-  <si>
-    <t>204001x1</t>
-  </si>
-  <si>
-    <t>NewbieSchedule1002PlaytimeDrop</t>
-  </si>
-  <si>
-    <t>新手调度1002游玩投放</t>
-  </si>
-  <si>
-    <t>Newbie Schedule 1002 Playtime Drop</t>
-  </si>
-  <si>
-    <t>Grants the blind box item configured by newbie schedule 1002.</t>
-  </si>
-  <si>
-    <t>201002x1</t>
-  </si>
-  <si>
-    <t>NewbieSchedule1004PlaytimeDrop</t>
-  </si>
-  <si>
-    <t>新手调度1004游玩投放</t>
-  </si>
-  <si>
-    <t>Newbie Schedule 1004 Playtime Drop</t>
-  </si>
-  <si>
-    <t>Grants the blind box item configured by newbie schedule 1004.</t>
-  </si>
-  <si>
-    <t>201001x1</t>
-  </si>
-  <si>
-    <t>NewbieSchedule1005PlaytimeDrop</t>
-  </si>
-  <si>
-    <t>新手调度1005游玩投放</t>
-  </si>
-  <si>
-    <t>Newbie Schedule 1005 Playtime Drop</t>
-  </si>
-  <si>
-    <t>Grants the blind box item configured by newbie schedule 1005.</t>
-  </si>
-  <si>
-    <t>NewbieSchedule1007PlaytimeDrop</t>
-  </si>
-  <si>
-    <t>新手调度1007游玩投放</t>
-  </si>
-  <si>
-    <t>Newbie Schedule 1007 Playtime Drop</t>
-  </si>
-  <si>
-    <t>Grants the blind box item configured by newbie schedule 1007.</t>
-  </si>
-  <si>
-    <t>NewbieSchedule1008PlaytimeDrop</t>
-  </si>
-  <si>
-    <t>新手调度1008游玩投放</t>
-  </si>
-  <si>
-    <t>Newbie Schedule 1008 Playtime Drop</t>
-  </si>
-  <si>
-    <t>Grants the blind box item configured by newbie schedule 1008.</t>
-  </si>
-  <si>
-    <t>NewbieSchedule1010PlaytimeDrop</t>
-  </si>
-  <si>
-    <t>新手调度1010游玩投放</t>
-  </si>
-  <si>
-    <t>Newbie Schedule 1010 Playtime Drop</t>
-  </si>
-  <si>
-    <t>Grants the blind box item configured by newbie schedule 1010.</t>
-  </si>
-  <si>
-    <t>NewbieSchedule1011PlaytimeDrop</t>
-  </si>
-  <si>
-    <t>新手调度1011游玩投放</t>
-  </si>
-  <si>
-    <t>Newbie Schedule 1011 Playtime Drop</t>
-  </si>
-  <si>
-    <t>Grants the blind box item configured by newbie schedule 1011.</t>
+    <t>NewbieSchedule1001DirectReward</t>
+  </si>
+  <si>
+    <t>新手调度1001直接奖励投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1001 Direct Reward</t>
+  </si>
+  <si>
+    <t>Generates one standard decoration reward for newbie schedule 1001.</t>
+  </si>
+  <si>
+    <t>301001x1</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1002DirectReward</t>
+  </si>
+  <si>
+    <t>新手调度1002直接奖励投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1002 Direct Reward</t>
+  </si>
+  <si>
+    <t>Generates one newbie decoration reward for newbie schedule 1002.</t>
+  </si>
+  <si>
+    <t>301002x1</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1004DirectReward</t>
+  </si>
+  <si>
+    <t>新手调度1004直接奖励投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1004 Direct Reward</t>
+  </si>
+  <si>
+    <t>Generates one standard decoration reward for newbie schedule 1004.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1005DirectReward</t>
+  </si>
+  <si>
+    <t>新手调度1005直接奖励投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1005 Direct Reward</t>
+  </si>
+  <si>
+    <t>Generates one newbie decoration reward for newbie schedule 1005.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1007DirectReward</t>
+  </si>
+  <si>
+    <t>新手调度1007直接奖励投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1007 Direct Reward</t>
+  </si>
+  <si>
+    <t>Generates one standard decoration reward for newbie schedule 1007.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1008DirectReward</t>
+  </si>
+  <si>
+    <t>新手调度1008直接奖励投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1008 Direct Reward</t>
+  </si>
+  <si>
+    <t>Generates one newbie decoration reward for newbie schedule 1008.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1010DirectReward</t>
+  </si>
+  <si>
+    <t>新手调度1010直接奖励投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1010 Direct Reward</t>
+  </si>
+  <si>
+    <t>Generates one standard decoration reward for newbie schedule 1010.</t>
+  </si>
+  <si>
+    <t>NewbieSchedule1011DirectReward</t>
+  </si>
+  <si>
+    <t>新手调度1011直接奖励投放</t>
+  </si>
+  <si>
+    <t>Newbie Schedule 1011 Direct Reward</t>
+  </si>
+  <si>
+    <t>Generates one newbie decoration reward for newbie schedule 1011.</t>
+  </si>
+  <si>
+    <t>Old长期循环游玩投放</t>
+  </si>
+  <si>
+    <t>RecurringDecorationBlindBoxDrop</t>
+  </si>
+  <si>
+    <t>循环装扮盲盒券投放</t>
+  </si>
+  <si>
+    <t>Recurring Decoration Blind Box Drop</t>
   </si>
   <si>
     <t>正式长期循环游玩投放</t>
   </si>
   <si>
-    <t>RecurringDecorationBlindBoxDrop</t>
-  </si>
-  <si>
-    <t>循环装扮盲盒券投放</t>
-  </si>
-  <si>
-    <t>Recurring Decoration Blind Box Drop</t>
+    <t>RecurringDecorationDirectReward</t>
+  </si>
+  <si>
+    <t>循环装扮直接奖励投放</t>
+  </si>
+  <si>
+    <t>Recurring Decoration Direct Reward</t>
+  </si>
+  <si>
+    <t>Generates one recurring standard decoration reward under the Steam playtime drop window.</t>
   </si>
   <si>
     <t>StartItemDefId</t>
@@ -3777,6 +3846,15 @@
   </si>
   <si>
     <t>501xxx LinkTree、502xxx 补偿中心</t>
+  </si>
+  <si>
+    <t>新手状态永久回执字段</t>
+  </si>
+  <si>
+    <t>记录一些可获得奖励的新手状态，避免玩家重复走领奖流程</t>
+  </si>
+  <si>
+    <t>500001，新手盲盒阶段开始，500012，新手盲盒阶段走完</t>
   </si>
   <si>
     <t>LinkTree 永久回执子段。</t>
@@ -13540,10 +13618,10 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>830</v>
+        <v>808</v>
       </c>
       <c r="D1" t="s">
-        <v>831</v>
+        <v>809</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -13568,10 +13646,10 @@
         <v>59</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>832</v>
+        <v>810</v>
       </c>
       <c r="D3" t="s">
-        <v>833</v>
+        <v>811</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -13729,55 +13807,55 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>834</v>
+        <v>812</v>
       </c>
       <c r="D1" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>835</v>
+        <v>813</v>
       </c>
       <c r="F1" t="s">
         <v>640</v>
       </c>
       <c r="G1" t="s">
-        <v>836</v>
+        <v>814</v>
       </c>
       <c r="H1" t="s">
-        <v>837</v>
+        <v>815</v>
       </c>
       <c r="I1" t="s">
-        <v>838</v>
+        <v>816</v>
       </c>
       <c r="J1" t="s">
-        <v>839</v>
+        <v>817</v>
       </c>
       <c r="K1" t="s">
-        <v>840</v>
+        <v>818</v>
       </c>
       <c r="L1" t="s">
-        <v>841</v>
+        <v>819</v>
       </c>
       <c r="M1" t="s">
-        <v>842</v>
+        <v>820</v>
       </c>
       <c r="N1" t="s">
-        <v>843</v>
+        <v>821</v>
       </c>
       <c r="O1" t="s">
-        <v>844</v>
+        <v>822</v>
       </c>
       <c r="P1" t="s">
-        <v>845</v>
+        <v>823</v>
       </c>
       <c r="Q1" t="s">
-        <v>846</v>
+        <v>824</v>
       </c>
       <c r="R1" t="s">
-        <v>847</v>
+        <v>825</v>
       </c>
       <c r="S1" t="s">
-        <v>848</v>
+        <v>826</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -13815,10 +13893,10 @@
         <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>849</v>
+        <v>827</v>
       </c>
       <c r="M2" t="s">
-        <v>850</v>
+        <v>828</v>
       </c>
       <c r="N2" t="s">
         <v>30</v>
@@ -13844,58 +13922,58 @@
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>851</v>
+        <v>829</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>852</v>
+        <v>830</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>853</v>
+        <v>831</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>854</v>
+        <v>832</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>855</v>
+        <v>833</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>856</v>
+        <v>834</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>857</v>
+        <v>835</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>858</v>
+        <v>836</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>859</v>
+        <v>837</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>860</v>
+        <v>838</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>861</v>
+        <v>839</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>862</v>
+        <v>840</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>863</v>
+        <v>841</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>864</v>
+        <v>842</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>865</v>
+        <v>843</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>866</v>
+        <v>844</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>867</v>
+        <v>845</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>868</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -13903,58 +13981,58 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>869</v>
+        <v>847</v>
       </c>
       <c r="C4" t="s">
-        <v>870</v>
+        <v>848</v>
       </c>
       <c r="D4" t="s">
-        <v>871</v>
+        <v>849</v>
       </c>
       <c r="E4" t="s">
-        <v>872</v>
+        <v>850</v>
       </c>
       <c r="F4" t="s">
-        <v>873</v>
+        <v>851</v>
       </c>
       <c r="G4" t="s">
-        <v>874</v>
+        <v>852</v>
       </c>
       <c r="H4" t="s">
-        <v>875</v>
+        <v>853</v>
       </c>
       <c r="I4" t="s">
-        <v>876</v>
+        <v>854</v>
       </c>
       <c r="J4" t="s">
-        <v>877</v>
+        <v>855</v>
       </c>
       <c r="K4" t="s">
-        <v>878</v>
+        <v>856</v>
       </c>
       <c r="L4" t="s">
-        <v>879</v>
+        <v>857</v>
       </c>
       <c r="M4" t="s">
-        <v>880</v>
+        <v>858</v>
       </c>
       <c r="N4" t="s">
-        <v>881</v>
+        <v>859</v>
       </c>
       <c r="O4" t="s">
-        <v>882</v>
+        <v>860</v>
       </c>
       <c r="P4" t="s">
-        <v>883</v>
+        <v>861</v>
       </c>
       <c r="Q4" t="s">
-        <v>884</v>
+        <v>862</v>
       </c>
       <c r="R4" t="s">
-        <v>885</v>
+        <v>863</v>
       </c>
       <c r="S4" t="s">
-        <v>886</v>
+        <v>864</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -13962,7 +14040,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>887</v>
+        <v>865</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -13974,25 +14052,25 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="H5" t="s">
-        <v>889</v>
+        <v>867</v>
       </c>
       <c r="I5" t="s">
-        <v>890</v>
+        <v>868</v>
       </c>
       <c r="J5" t="s">
-        <v>891</v>
+        <v>869</v>
       </c>
       <c r="K5" t="s">
-        <v>892</v>
+        <v>870</v>
       </c>
       <c r="L5" t="s">
-        <v>893</v>
+        <v>871</v>
       </c>
       <c r="M5" t="s">
-        <v>894</v>
+        <v>872</v>
       </c>
       <c r="N5">
         <v>92005</v>
@@ -14012,7 +14090,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>895</v>
+        <v>873</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -14024,25 +14102,25 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>896</v>
+        <v>874</v>
       </c>
       <c r="H6" t="s">
-        <v>897</v>
+        <v>875</v>
       </c>
       <c r="I6" t="s">
-        <v>890</v>
+        <v>868</v>
       </c>
       <c r="J6" t="s">
-        <v>898</v>
+        <v>876</v>
       </c>
       <c r="K6" t="s">
-        <v>898</v>
+        <v>876</v>
       </c>
       <c r="L6" t="s">
-        <v>893</v>
+        <v>871</v>
       </c>
       <c r="M6" t="s">
-        <v>899</v>
+        <v>877</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -14062,7 +14140,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>900</v>
+        <v>878</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -14074,25 +14152,25 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>901</v>
+        <v>879</v>
       </c>
       <c r="H7" t="s">
-        <v>902</v>
+        <v>880</v>
       </c>
       <c r="I7" t="s">
-        <v>890</v>
+        <v>868</v>
       </c>
       <c r="J7" t="s">
-        <v>903</v>
+        <v>881</v>
       </c>
       <c r="K7" t="s">
-        <v>904</v>
+        <v>882</v>
       </c>
       <c r="L7" t="s">
-        <v>893</v>
+        <v>871</v>
       </c>
       <c r="M7" t="s">
-        <v>899</v>
+        <v>877</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -14112,7 +14190,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>905</v>
+        <v>883</v>
       </c>
       <c r="D8">
         <v>40</v>
@@ -14124,25 +14202,25 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>906</v>
+        <v>884</v>
       </c>
       <c r="H8" t="s">
-        <v>907</v>
+        <v>885</v>
       </c>
       <c r="I8" t="s">
-        <v>890</v>
+        <v>868</v>
       </c>
       <c r="J8" t="s">
-        <v>908</v>
+        <v>886</v>
       </c>
       <c r="K8" t="s">
-        <v>908</v>
+        <v>886</v>
       </c>
       <c r="L8" t="s">
-        <v>893</v>
+        <v>871</v>
       </c>
       <c r="M8" t="s">
-        <v>894</v>
+        <v>872</v>
       </c>
       <c r="N8">
         <v>91012</v>
@@ -14162,7 +14240,7 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>887</v>
+        <v>865</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -14174,25 +14252,25 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="H9" t="s">
-        <v>889</v>
+        <v>867</v>
       </c>
       <c r="I9" t="s">
-        <v>890</v>
+        <v>868</v>
       </c>
       <c r="J9" t="s">
-        <v>891</v>
+        <v>869</v>
       </c>
       <c r="K9" t="s">
-        <v>892</v>
+        <v>870</v>
       </c>
       <c r="L9" t="s">
-        <v>893</v>
+        <v>871</v>
       </c>
       <c r="M9" t="s">
-        <v>894</v>
+        <v>872</v>
       </c>
       <c r="N9">
         <v>92005</v>
@@ -14215,7 +14293,7 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>895</v>
+        <v>873</v>
       </c>
       <c r="D10">
         <v>80</v>
@@ -14227,25 +14305,25 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>896</v>
+        <v>874</v>
       </c>
       <c r="H10" t="s">
-        <v>897</v>
+        <v>875</v>
       </c>
       <c r="I10" t="s">
-        <v>890</v>
+        <v>868</v>
       </c>
       <c r="J10" t="s">
-        <v>898</v>
+        <v>876</v>
       </c>
       <c r="K10" t="s">
-        <v>898</v>
+        <v>876</v>
       </c>
       <c r="L10" t="s">
-        <v>893</v>
+        <v>871</v>
       </c>
       <c r="M10" t="s">
-        <v>899</v>
+        <v>877</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -14268,7 +14346,7 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>900</v>
+        <v>878</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -14280,25 +14358,25 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>901</v>
+        <v>879</v>
       </c>
       <c r="H11" t="s">
-        <v>902</v>
+        <v>880</v>
       </c>
       <c r="I11" t="s">
-        <v>890</v>
+        <v>868</v>
       </c>
       <c r="J11" t="s">
-        <v>903</v>
+        <v>881</v>
       </c>
       <c r="K11" t="s">
-        <v>904</v>
+        <v>882</v>
       </c>
       <c r="L11" t="s">
-        <v>893</v>
+        <v>871</v>
       </c>
       <c r="M11" t="s">
-        <v>899</v>
+        <v>877</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -14321,7 +14399,7 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>905</v>
+        <v>883</v>
       </c>
       <c r="D12">
         <v>120</v>
@@ -14333,25 +14411,25 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>906</v>
+        <v>884</v>
       </c>
       <c r="H12" t="s">
-        <v>907</v>
+        <v>885</v>
       </c>
       <c r="I12" t="s">
-        <v>890</v>
+        <v>868</v>
       </c>
       <c r="J12" t="s">
-        <v>908</v>
+        <v>886</v>
       </c>
       <c r="K12" t="s">
-        <v>908</v>
+        <v>886</v>
       </c>
       <c r="L12" t="s">
-        <v>893</v>
+        <v>871</v>
       </c>
       <c r="M12" t="s">
-        <v>894</v>
+        <v>872</v>
       </c>
       <c r="N12">
         <v>91012</v>
@@ -14378,7 +14456,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R66"/>
+  <dimension ref="A1:R80"/>
   <sheetFormatPr defaultColWidth="27" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -14408,49 +14486,49 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>834</v>
+        <v>812</v>
       </c>
       <c r="E1" t="s">
-        <v>909</v>
+        <v>887</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>910</v>
+        <v>888</v>
       </c>
       <c r="H1" t="s">
-        <v>911</v>
+        <v>889</v>
       </c>
       <c r="I1" t="s">
-        <v>912</v>
+        <v>890</v>
       </c>
       <c r="J1" t="s">
-        <v>913</v>
+        <v>891</v>
       </c>
       <c r="K1" t="s">
-        <v>914</v>
+        <v>892</v>
       </c>
       <c r="L1" t="s">
-        <v>915</v>
+        <v>893</v>
       </c>
       <c r="M1" t="s">
-        <v>916</v>
+        <v>894</v>
       </c>
       <c r="N1" t="s">
-        <v>917</v>
+        <v>895</v>
       </c>
       <c r="O1" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="P1" t="s">
         <v>640</v>
       </c>
       <c r="Q1" t="s">
-        <v>919</v>
+        <v>897</v>
       </c>
       <c r="R1" t="s">
-        <v>920</v>
+        <v>898</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -14511,52 +14589,52 @@
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>921</v>
+        <v>899</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>922</v>
+        <v>900</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>923</v>
+        <v>901</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>924</v>
+        <v>902</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>925</v>
+        <v>903</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>926</v>
+        <v>904</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>927</v>
+        <v>905</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>928</v>
+        <v>906</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>929</v>
+        <v>907</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>930</v>
+        <v>908</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>931</v>
+        <v>909</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>932</v>
+        <v>910</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>933</v>
+        <v>911</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>934</v>
+        <v>912</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>935</v>
+        <v>913</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -14564,55 +14642,55 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>936</v>
+        <v>914</v>
       </c>
       <c r="C4" t="s">
-        <v>870</v>
+        <v>848</v>
       </c>
       <c r="D4" t="s">
-        <v>937</v>
+        <v>915</v>
       </c>
       <c r="E4" t="s">
-        <v>938</v>
+        <v>916</v>
       </c>
       <c r="F4" t="s">
-        <v>939</v>
+        <v>917</v>
       </c>
       <c r="G4" t="s">
         <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>940</v>
+        <v>918</v>
       </c>
       <c r="I4" t="s">
-        <v>941</v>
+        <v>919</v>
       </c>
       <c r="J4" t="s">
         <v>81</v>
       </c>
       <c r="K4" t="s">
-        <v>942</v>
+        <v>920</v>
       </c>
       <c r="L4" t="s">
-        <v>943</v>
+        <v>921</v>
       </c>
       <c r="M4" t="s">
-        <v>944</v>
+        <v>922</v>
       </c>
       <c r="N4" t="s">
         <v>83</v>
       </c>
       <c r="O4" t="s">
-        <v>945</v>
+        <v>923</v>
       </c>
       <c r="P4" t="s">
-        <v>873</v>
+        <v>851</v>
       </c>
       <c r="Q4" t="s">
-        <v>946</v>
+        <v>924</v>
       </c>
       <c r="R4" t="s">
-        <v>947</v>
+        <v>925</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -14623,22 +14701,22 @@
         <v>401001</v>
       </c>
       <c r="C5" t="s">
-        <v>948</v>
+        <v>926</v>
       </c>
       <c r="D5" t="s">
-        <v>949</v>
+        <v>927</v>
       </c>
       <c r="E5" t="s">
         <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>950</v>
+        <v>928</v>
       </c>
       <c r="G5" t="s">
-        <v>951</v>
+        <v>929</v>
       </c>
       <c r="H5" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -14679,22 +14757,22 @@
         <v>401002</v>
       </c>
       <c r="C6" t="s">
-        <v>953</v>
+        <v>931</v>
       </c>
       <c r="D6" t="s">
-        <v>954</v>
+        <v>932</v>
       </c>
       <c r="E6" t="s">
         <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>955</v>
+        <v>933</v>
       </c>
       <c r="G6" t="s">
-        <v>956</v>
+        <v>934</v>
       </c>
       <c r="H6" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -14735,22 +14813,22 @@
         <v>401003</v>
       </c>
       <c r="C7" t="s">
-        <v>957</v>
+        <v>935</v>
       </c>
       <c r="D7" t="s">
-        <v>958</v>
+        <v>936</v>
       </c>
       <c r="E7" t="s">
         <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>959</v>
+        <v>937</v>
       </c>
       <c r="G7" t="s">
-        <v>960</v>
+        <v>938</v>
       </c>
       <c r="H7" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -14791,22 +14869,22 @@
         <v>401004</v>
       </c>
       <c r="C8" t="s">
-        <v>961</v>
+        <v>939</v>
       </c>
       <c r="D8" t="s">
-        <v>962</v>
+        <v>940</v>
       </c>
       <c r="E8" t="s">
         <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>963</v>
+        <v>941</v>
       </c>
       <c r="G8" t="s">
-        <v>964</v>
+        <v>942</v>
       </c>
       <c r="H8" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -14847,22 +14925,22 @@
         <v>401005</v>
       </c>
       <c r="C9" t="s">
-        <v>965</v>
+        <v>943</v>
       </c>
       <c r="D9" t="s">
-        <v>966</v>
+        <v>944</v>
       </c>
       <c r="E9" t="s">
         <v>96</v>
       </c>
       <c r="F9" t="s">
-        <v>950</v>
+        <v>928</v>
       </c>
       <c r="G9" t="s">
-        <v>951</v>
+        <v>929</v>
       </c>
       <c r="H9" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -14903,22 +14981,22 @@
         <v>401006</v>
       </c>
       <c r="C10" t="s">
-        <v>967</v>
+        <v>945</v>
       </c>
       <c r="D10" t="s">
-        <v>968</v>
+        <v>946</v>
       </c>
       <c r="E10" t="s">
         <v>96</v>
       </c>
       <c r="F10" t="s">
-        <v>955</v>
+        <v>933</v>
       </c>
       <c r="G10" t="s">
-        <v>956</v>
+        <v>934</v>
       </c>
       <c r="H10" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -14959,22 +15037,22 @@
         <v>401007</v>
       </c>
       <c r="C11" t="s">
-        <v>969</v>
+        <v>947</v>
       </c>
       <c r="D11" t="s">
-        <v>970</v>
+        <v>948</v>
       </c>
       <c r="E11" t="s">
         <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>959</v>
+        <v>937</v>
       </c>
       <c r="G11" t="s">
-        <v>960</v>
+        <v>938</v>
       </c>
       <c r="H11" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -15015,22 +15093,22 @@
         <v>401008</v>
       </c>
       <c r="C12" t="s">
-        <v>971</v>
+        <v>949</v>
       </c>
       <c r="D12" t="s">
-        <v>972</v>
+        <v>950</v>
       </c>
       <c r="E12" t="s">
         <v>96</v>
       </c>
       <c r="F12" t="s">
-        <v>963</v>
+        <v>941</v>
       </c>
       <c r="G12" t="s">
-        <v>964</v>
+        <v>942</v>
       </c>
       <c r="H12" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -15068,7 +15146,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>973</v>
+        <v>951</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -15079,19 +15157,19 @@
         <v>402001</v>
       </c>
       <c r="C14" t="s">
-        <v>974</v>
+        <v>952</v>
       </c>
       <c r="D14" t="s">
-        <v>975</v>
+        <v>953</v>
       </c>
       <c r="E14" t="s">
         <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>976</v>
+        <v>954</v>
       </c>
       <c r="G14" t="s">
-        <v>977</v>
+        <v>955</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -15129,19 +15207,19 @@
         <v>402002</v>
       </c>
       <c r="C15" t="s">
-        <v>978</v>
+        <v>956</v>
       </c>
       <c r="D15" t="s">
-        <v>979</v>
+        <v>957</v>
       </c>
       <c r="E15" t="s">
         <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="G15" t="s">
-        <v>981</v>
+        <v>959</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -15176,19 +15254,19 @@
         <v>402003</v>
       </c>
       <c r="C16" t="s">
-        <v>982</v>
+        <v>960</v>
       </c>
       <c r="D16" t="s">
-        <v>983</v>
+        <v>961</v>
       </c>
       <c r="E16" t="s">
         <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>984</v>
+        <v>962</v>
       </c>
       <c r="G16" t="s">
-        <v>985</v>
+        <v>963</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -15223,7 +15301,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>986</v>
+        <v>964</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -15234,19 +15312,19 @@
         <v>403001</v>
       </c>
       <c r="C18" t="s">
-        <v>987</v>
+        <v>965</v>
       </c>
       <c r="D18" t="s">
-        <v>988</v>
+        <v>966</v>
       </c>
       <c r="E18" t="s">
-        <v>989</v>
+        <v>967</v>
       </c>
       <c r="F18" t="s">
-        <v>990</v>
+        <v>968</v>
       </c>
       <c r="G18" t="s">
-        <v>991</v>
+        <v>969</v>
       </c>
       <c r="H18" t="s">
         <v>161</v>
@@ -15270,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>992</v>
+        <v>970</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
@@ -15287,19 +15365,19 @@
         <v>403002</v>
       </c>
       <c r="C19" t="s">
-        <v>993</v>
+        <v>971</v>
       </c>
       <c r="D19" t="s">
-        <v>994</v>
+        <v>972</v>
       </c>
       <c r="E19" t="s">
-        <v>989</v>
+        <v>967</v>
       </c>
       <c r="F19" t="s">
-        <v>995</v>
+        <v>973</v>
       </c>
       <c r="G19" t="s">
-        <v>996</v>
+        <v>974</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -15320,7 +15398,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>997</v>
+        <v>975</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
@@ -15337,19 +15415,19 @@
         <v>403003</v>
       </c>
       <c r="C20" t="s">
-        <v>998</v>
+        <v>976</v>
       </c>
       <c r="D20" t="s">
-        <v>999</v>
+        <v>977</v>
       </c>
       <c r="E20" t="s">
-        <v>989</v>
+        <v>967</v>
       </c>
       <c r="F20" t="s">
-        <v>1000</v>
+        <v>978</v>
       </c>
       <c r="G20" t="s">
-        <v>1001</v>
+        <v>979</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -15370,7 +15448,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>997</v>
+        <v>975</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
@@ -15387,7 +15465,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>1002</v>
+        <v>980</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -15395,19 +15473,19 @@
         <v>404001</v>
       </c>
       <c r="C22" t="s">
-        <v>1003</v>
+        <v>981</v>
       </c>
       <c r="D22" t="s">
-        <v>1004</v>
+        <v>982</v>
       </c>
       <c r="E22" t="s">
         <v>621</v>
       </c>
       <c r="F22" t="s">
-        <v>1005</v>
+        <v>983</v>
       </c>
       <c r="G22" t="s">
-        <v>1006</v>
+        <v>984</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -15428,7 +15506,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>1007</v>
+        <v>985</v>
       </c>
       <c r="P22" t="b">
         <v>1</v>
@@ -15445,19 +15523,19 @@
         <v>404002</v>
       </c>
       <c r="C23" t="s">
-        <v>1008</v>
+        <v>986</v>
       </c>
       <c r="D23" t="s">
-        <v>1009</v>
+        <v>987</v>
       </c>
       <c r="E23" t="s">
         <v>621</v>
       </c>
       <c r="F23" t="s">
-        <v>1010</v>
+        <v>988</v>
       </c>
       <c r="G23" t="s">
-        <v>1011</v>
+        <v>989</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -15478,7 +15556,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>1012</v>
+        <v>990</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
@@ -15495,19 +15573,19 @@
         <v>404004</v>
       </c>
       <c r="C24" t="s">
-        <v>1013</v>
+        <v>991</v>
       </c>
       <c r="D24" t="s">
-        <v>1014</v>
+        <v>992</v>
       </c>
       <c r="E24" t="s">
         <v>621</v>
       </c>
       <c r="F24" t="s">
-        <v>1015</v>
+        <v>993</v>
       </c>
       <c r="G24" t="s">
-        <v>1016</v>
+        <v>994</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -15528,7 +15606,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
@@ -15545,19 +15623,19 @@
         <v>404005</v>
       </c>
       <c r="C25" t="s">
-        <v>1018</v>
+        <v>996</v>
       </c>
       <c r="D25" t="s">
-        <v>1019</v>
+        <v>997</v>
       </c>
       <c r="E25" t="s">
         <v>621</v>
       </c>
       <c r="F25" t="s">
-        <v>1020</v>
+        <v>998</v>
       </c>
       <c r="G25" t="s">
-        <v>1021</v>
+        <v>999</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -15578,7 +15656,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>1012</v>
+        <v>990</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
@@ -15595,19 +15673,19 @@
         <v>404007</v>
       </c>
       <c r="C26" t="s">
-        <v>1022</v>
+        <v>1000</v>
       </c>
       <c r="D26" t="s">
-        <v>1023</v>
+        <v>1001</v>
       </c>
       <c r="E26" t="s">
         <v>621</v>
       </c>
       <c r="F26" t="s">
-        <v>1024</v>
+        <v>1002</v>
       </c>
       <c r="G26" t="s">
-        <v>1025</v>
+        <v>1003</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -15628,7 +15706,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="P26" t="b">
         <v>1</v>
@@ -15645,19 +15723,19 @@
         <v>404008</v>
       </c>
       <c r="C27" t="s">
-        <v>1026</v>
+        <v>1004</v>
       </c>
       <c r="D27" t="s">
-        <v>1027</v>
+        <v>1005</v>
       </c>
       <c r="E27" t="s">
         <v>621</v>
       </c>
       <c r="F27" t="s">
-        <v>1028</v>
+        <v>1006</v>
       </c>
       <c r="G27" t="s">
-        <v>1029</v>
+        <v>1007</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -15678,7 +15756,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>1012</v>
+        <v>990</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -15695,19 +15773,19 @@
         <v>404010</v>
       </c>
       <c r="C28" t="s">
-        <v>1030</v>
+        <v>1008</v>
       </c>
       <c r="D28" t="s">
-        <v>1031</v>
+        <v>1009</v>
       </c>
       <c r="E28" t="s">
         <v>621</v>
       </c>
       <c r="F28" t="s">
-        <v>1032</v>
+        <v>1010</v>
       </c>
       <c r="G28" t="s">
-        <v>1033</v>
+        <v>1011</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -15728,7 +15806,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
@@ -15745,19 +15823,19 @@
         <v>404011</v>
       </c>
       <c r="C29" t="s">
-        <v>1034</v>
+        <v>1012</v>
       </c>
       <c r="D29" t="s">
-        <v>1035</v>
+        <v>1013</v>
       </c>
       <c r="E29" t="s">
         <v>621</v>
       </c>
       <c r="F29" t="s">
-        <v>1036</v>
+        <v>1014</v>
       </c>
       <c r="G29" t="s">
-        <v>1037</v>
+        <v>1015</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -15778,7 +15856,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>1012</v>
+        <v>990</v>
       </c>
       <c r="P29" t="b">
         <v>1</v>
@@ -15795,19 +15873,19 @@
         <v>404013</v>
       </c>
       <c r="C30" t="s">
-        <v>1038</v>
+        <v>1016</v>
       </c>
       <c r="D30" t="s">
-        <v>1039</v>
+        <v>1017</v>
       </c>
       <c r="E30" t="s">
         <v>621</v>
       </c>
       <c r="F30" t="s">
-        <v>1040</v>
+        <v>1018</v>
       </c>
       <c r="G30" t="s">
-        <v>1041</v>
+        <v>1019</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -15828,7 +15906,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -15845,7 +15923,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>1042</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -15853,19 +15931,19 @@
         <v>405001</v>
       </c>
       <c r="C32" t="s">
-        <v>1043</v>
+        <v>1021</v>
       </c>
       <c r="D32" t="s">
-        <v>1044</v>
+        <v>1022</v>
       </c>
       <c r="E32" t="s">
         <v>621</v>
       </c>
       <c r="F32" t="s">
-        <v>1045</v>
+        <v>1023</v>
       </c>
       <c r="G32" t="s">
-        <v>1046</v>
+        <v>1024</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -15886,7 +15964,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
       <c r="P32" t="b">
         <v>1</v>
@@ -15903,7 +15981,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>1047</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -15911,22 +15989,22 @@
         <v>406005</v>
       </c>
       <c r="C34" t="s">
-        <v>1048</v>
+        <v>1026</v>
       </c>
       <c r="D34" t="s">
-        <v>1049</v>
+        <v>1027</v>
       </c>
       <c r="E34" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="F34" t="s">
-        <v>1050</v>
+        <v>1028</v>
       </c>
       <c r="G34" t="s">
-        <v>1051</v>
+        <v>1029</v>
       </c>
       <c r="H34" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I34" t="b">
         <v>1</v>
@@ -15947,7 +16025,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>1052</v>
+        <v>1030</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -15964,22 +16042,22 @@
         <v>406006</v>
       </c>
       <c r="C35" t="s">
-        <v>1053</v>
+        <v>1031</v>
       </c>
       <c r="D35" t="s">
-        <v>1054</v>
+        <v>1032</v>
       </c>
       <c r="E35" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="F35" t="s">
-        <v>1055</v>
+        <v>1033</v>
       </c>
       <c r="G35" t="s">
-        <v>1056</v>
+        <v>1034</v>
       </c>
       <c r="H35" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I35" t="b">
         <v>1</v>
@@ -16000,7 +16078,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="s">
-        <v>1057</v>
+        <v>1035</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -16017,22 +16095,22 @@
         <v>406007</v>
       </c>
       <c r="C36" t="s">
-        <v>1058</v>
+        <v>1036</v>
       </c>
       <c r="D36" t="s">
-        <v>1059</v>
+        <v>1037</v>
       </c>
       <c r="E36" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="F36" t="s">
-        <v>1060</v>
+        <v>1038</v>
       </c>
       <c r="G36" t="s">
-        <v>1061</v>
+        <v>1039</v>
       </c>
       <c r="H36" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -16053,7 +16131,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>1062</v>
+        <v>1040</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -16070,22 +16148,22 @@
         <v>406008</v>
       </c>
       <c r="C37" t="s">
-        <v>1063</v>
+        <v>1041</v>
       </c>
       <c r="D37" t="s">
-        <v>1064</v>
+        <v>1042</v>
       </c>
       <c r="E37" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="F37" t="s">
-        <v>1065</v>
+        <v>1043</v>
       </c>
       <c r="G37" t="s">
-        <v>1066</v>
+        <v>1044</v>
       </c>
       <c r="H37" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
@@ -16106,7 +16184,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>1067</v>
+        <v>1045</v>
       </c>
       <c r="P37" t="b">
         <v>1</v>
@@ -16128,7 +16206,7 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>1068</v>
+        <v>1046</v>
       </c>
       <c r="C39" t="s">
         <v>161</v>
@@ -16187,19 +16265,19 @@
         <v>201001</v>
       </c>
       <c r="C40" t="s">
-        <v>1069</v>
+        <v>1047</v>
       </c>
       <c r="D40" t="s">
-        <v>979</v>
+        <v>957</v>
       </c>
       <c r="E40" t="s">
         <v>96</v>
       </c>
       <c r="F40" t="s">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="G40" t="s">
-        <v>981</v>
+        <v>959</v>
       </c>
       <c r="H40" t="s">
         <v>161</v>
@@ -16243,19 +16321,19 @@
         <v>201002</v>
       </c>
       <c r="C41" t="s">
-        <v>1070</v>
+        <v>1048</v>
       </c>
       <c r="D41" t="s">
-        <v>983</v>
+        <v>961</v>
       </c>
       <c r="E41" t="s">
         <v>96</v>
       </c>
       <c r="F41" t="s">
-        <v>984</v>
+        <v>962</v>
       </c>
       <c r="G41" t="s">
-        <v>985</v>
+        <v>963</v>
       </c>
       <c r="H41" t="s">
         <v>161</v>
@@ -16299,19 +16377,19 @@
         <v>204001</v>
       </c>
       <c r="C42" t="s">
-        <v>1071</v>
+        <v>1049</v>
       </c>
       <c r="D42" t="s">
-        <v>975</v>
+        <v>953</v>
       </c>
       <c r="E42" t="s">
         <v>96</v>
       </c>
       <c r="F42" t="s">
-        <v>976</v>
+        <v>954</v>
       </c>
       <c r="G42" t="s">
-        <v>977</v>
+        <v>955</v>
       </c>
       <c r="H42" t="s">
         <v>161</v>
@@ -16352,7 +16430,7 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>1072</v>
+        <v>1050</v>
       </c>
       <c r="C43" t="s">
         <v>161</v>
@@ -16411,19 +16489,19 @@
         <v>301001</v>
       </c>
       <c r="C44" t="s">
-        <v>1073</v>
+        <v>1051</v>
       </c>
       <c r="D44" t="s">
-        <v>994</v>
+        <v>972</v>
       </c>
       <c r="E44" t="s">
-        <v>989</v>
+        <v>967</v>
       </c>
       <c r="F44" t="s">
-        <v>995</v>
+        <v>973</v>
       </c>
       <c r="G44" t="s">
-        <v>996</v>
+        <v>974</v>
       </c>
       <c r="H44" t="s">
         <v>161</v>
@@ -16447,7 +16525,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="s">
-        <v>997</v>
+        <v>975</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -16467,19 +16545,19 @@
         <v>301002</v>
       </c>
       <c r="C45" t="s">
-        <v>1074</v>
+        <v>1052</v>
       </c>
       <c r="D45" t="s">
-        <v>999</v>
+        <v>977</v>
       </c>
       <c r="E45" t="s">
-        <v>989</v>
+        <v>967</v>
       </c>
       <c r="F45" t="s">
-        <v>1000</v>
+        <v>978</v>
       </c>
       <c r="G45" t="s">
-        <v>1001</v>
+        <v>979</v>
       </c>
       <c r="H45" t="s">
         <v>161</v>
@@ -16503,7 +16581,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>997</v>
+        <v>975</v>
       </c>
       <c r="P45" t="b">
         <v>1</v>
@@ -16520,223 +16598,103 @@
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C46" t="s">
-        <v>161</v>
-      </c>
-      <c r="D46" t="s">
-        <v>161</v>
-      </c>
-      <c r="E46" t="s">
-        <v>161</v>
-      </c>
-      <c r="F46" t="s">
-        <v>161</v>
-      </c>
-      <c r="G46" t="s">
-        <v>161</v>
-      </c>
-      <c r="H46" t="s">
-        <v>161</v>
-      </c>
-      <c r="I46" t="s">
-        <v>161</v>
-      </c>
-      <c r="J46" t="s">
-        <v>161</v>
-      </c>
-      <c r="K46" t="s">
-        <v>161</v>
-      </c>
-      <c r="L46" t="s">
-        <v>161</v>
-      </c>
-      <c r="M46" t="s">
-        <v>161</v>
-      </c>
-      <c r="N46" t="s">
-        <v>161</v>
-      </c>
-      <c r="O46" t="s">
-        <v>161</v>
-      </c>
-      <c r="P46" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>161</v>
-      </c>
-      <c r="R46" t="s">
-        <v>161</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="47" spans="1:18">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>39</v>
       </c>
       <c r="B47">
-        <v>501001</v>
+        <v>500001</v>
       </c>
       <c r="C47" t="s">
-        <v>1076</v>
+        <v>1054</v>
       </c>
       <c r="D47" t="s">
-        <v>1077</v>
+        <v>1055</v>
       </c>
       <c r="E47" t="s">
         <v>96</v>
       </c>
       <c r="F47" t="s">
-        <v>950</v>
-      </c>
-      <c r="G47" t="s">
-        <v>951</v>
-      </c>
-      <c r="H47" t="s">
-        <v>952</v>
-      </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" t="b">
-        <v>1</v>
-      </c>
-      <c r="M47" t="b">
-        <v>1</v>
-      </c>
-      <c r="N47" t="b">
-        <v>0</v>
-      </c>
-      <c r="O47" t="s">
-        <v>161</v>
-      </c>
-      <c r="P47" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="b">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>161</v>
+        <v>39</v>
       </c>
       <c r="B48">
-        <v>501002</v>
+        <v>500012</v>
       </c>
       <c r="C48" t="s">
-        <v>1078</v>
+        <v>1056</v>
       </c>
       <c r="D48" t="s">
-        <v>1079</v>
+        <v>1057</v>
       </c>
       <c r="E48" t="s">
         <v>96</v>
       </c>
       <c r="F48" t="s">
-        <v>955</v>
-      </c>
-      <c r="G48" t="s">
-        <v>956</v>
-      </c>
-      <c r="H48" t="s">
-        <v>952</v>
-      </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" t="b">
-        <v>1</v>
-      </c>
-      <c r="M48" t="b">
-        <v>1</v>
-      </c>
-      <c r="N48" t="b">
-        <v>0</v>
-      </c>
-      <c r="O48" t="s">
-        <v>161</v>
-      </c>
-      <c r="P48" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q48" t="b">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="49" spans="1:18">
       <c r="A49" t="s">
-        <v>161</v>
-      </c>
-      <c r="B49">
-        <v>501003</v>
+        <v>39</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1058</v>
       </c>
       <c r="C49" t="s">
-        <v>1080</v>
+        <v>161</v>
       </c>
       <c r="D49" t="s">
-        <v>1081</v>
+        <v>161</v>
       </c>
       <c r="E49" t="s">
-        <v>96</v>
+        <v>161</v>
       </c>
       <c r="F49" t="s">
-        <v>959</v>
+        <v>161</v>
       </c>
       <c r="G49" t="s">
-        <v>960</v>
+        <v>161</v>
       </c>
       <c r="H49" t="s">
-        <v>952</v>
-      </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" t="b">
-        <v>1</v>
-      </c>
-      <c r="M49" t="b">
-        <v>1</v>
-      </c>
-      <c r="N49" t="b">
-        <v>0</v>
+        <v>161</v>
+      </c>
+      <c r="I49" t="s">
+        <v>161</v>
+      </c>
+      <c r="J49" t="s">
+        <v>161</v>
+      </c>
+      <c r="K49" t="s">
+        <v>161</v>
+      </c>
+      <c r="L49" t="s">
+        <v>161</v>
+      </c>
+      <c r="M49" t="s">
+        <v>161</v>
+      </c>
+      <c r="N49" t="s">
+        <v>161</v>
       </c>
       <c r="O49" t="s">
         <v>161</v>
       </c>
-      <c r="P49" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q49" t="b">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
+      <c r="P49" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>161</v>
+      </c>
+      <c r="R49" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:18">
@@ -16744,25 +16702,25 @@
         <v>161</v>
       </c>
       <c r="B50">
-        <v>501004</v>
+        <v>501001</v>
       </c>
       <c r="C50" t="s">
-        <v>1082</v>
+        <v>1059</v>
       </c>
       <c r="D50" t="s">
-        <v>1083</v>
+        <v>1060</v>
       </c>
       <c r="E50" t="s">
         <v>96</v>
       </c>
       <c r="F50" t="s">
-        <v>963</v>
+        <v>928</v>
       </c>
       <c r="G50" t="s">
-        <v>964</v>
+        <v>929</v>
       </c>
       <c r="H50" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I50" t="b">
         <v>1</v>
@@ -16797,58 +16755,58 @@
     </row>
     <row r="51" spans="1:18">
       <c r="A51" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1084</v>
+        <v>161</v>
+      </c>
+      <c r="B51">
+        <v>501002</v>
       </c>
       <c r="C51" t="s">
-        <v>161</v>
+        <v>1061</v>
       </c>
       <c r="D51" t="s">
-        <v>161</v>
+        <v>1062</v>
       </c>
       <c r="E51" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="F51" t="s">
-        <v>161</v>
+        <v>933</v>
       </c>
       <c r="G51" t="s">
-        <v>161</v>
+        <v>934</v>
       </c>
       <c r="H51" t="s">
-        <v>161</v>
-      </c>
-      <c r="I51" t="s">
-        <v>161</v>
-      </c>
-      <c r="J51" t="s">
-        <v>161</v>
-      </c>
-      <c r="K51" t="s">
-        <v>161</v>
-      </c>
-      <c r="L51" t="s">
-        <v>161</v>
-      </c>
-      <c r="M51" t="s">
-        <v>161</v>
-      </c>
-      <c r="N51" t="s">
-        <v>161</v>
+        <v>930</v>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
+      <c r="M51" t="b">
+        <v>1</v>
+      </c>
+      <c r="N51" t="b">
+        <v>0</v>
       </c>
       <c r="O51" t="s">
         <v>161</v>
       </c>
-      <c r="P51" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>161</v>
-      </c>
-      <c r="R51" t="s">
-        <v>161</v>
+      <c r="P51" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="b">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:18">
@@ -16856,25 +16814,25 @@
         <v>161</v>
       </c>
       <c r="B52">
-        <v>601001</v>
+        <v>501003</v>
       </c>
       <c r="C52" t="s">
-        <v>1085</v>
+        <v>1063</v>
       </c>
       <c r="D52" t="s">
-        <v>1049</v>
+        <v>1064</v>
       </c>
       <c r="E52" t="s">
-        <v>918</v>
+        <v>96</v>
       </c>
       <c r="F52" t="s">
-        <v>1050</v>
+        <v>937</v>
       </c>
       <c r="G52" t="s">
-        <v>1051</v>
+        <v>938</v>
       </c>
       <c r="H52" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
@@ -16895,7 +16853,7 @@
         <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>1086</v>
+        <v>161</v>
       </c>
       <c r="P52" t="b">
         <v>1</v>
@@ -16912,25 +16870,25 @@
         <v>161</v>
       </c>
       <c r="B53">
-        <v>601002</v>
+        <v>501004</v>
       </c>
       <c r="C53" t="s">
-        <v>1087</v>
+        <v>1065</v>
       </c>
       <c r="D53" t="s">
-        <v>1054</v>
+        <v>1066</v>
       </c>
       <c r="E53" t="s">
-        <v>918</v>
+        <v>96</v>
       </c>
       <c r="F53" t="s">
-        <v>1055</v>
+        <v>941</v>
       </c>
       <c r="G53" t="s">
-        <v>1056</v>
+        <v>942</v>
       </c>
       <c r="H53" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I53" t="b">
         <v>1</v>
@@ -16951,7 +16909,7 @@
         <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>1088</v>
+        <v>161</v>
       </c>
       <c r="P53" t="b">
         <v>1</v>
@@ -16965,58 +16923,58 @@
     </row>
     <row r="54" spans="1:18">
       <c r="A54" t="s">
-        <v>161</v>
-      </c>
-      <c r="B54">
-        <v>601003</v>
+        <v>39</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1067</v>
       </c>
       <c r="C54" t="s">
-        <v>1089</v>
+        <v>161</v>
       </c>
       <c r="D54" t="s">
-        <v>1059</v>
+        <v>161</v>
       </c>
       <c r="E54" t="s">
-        <v>918</v>
+        <v>161</v>
       </c>
       <c r="F54" t="s">
-        <v>1060</v>
+        <v>161</v>
       </c>
       <c r="G54" t="s">
-        <v>1061</v>
+        <v>161</v>
       </c>
       <c r="H54" t="s">
-        <v>952</v>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="b">
-        <v>0</v>
-      </c>
-      <c r="L54" t="b">
-        <v>1</v>
-      </c>
-      <c r="M54" t="b">
-        <v>1</v>
-      </c>
-      <c r="N54" t="b">
-        <v>0</v>
+        <v>161</v>
+      </c>
+      <c r="I54" t="s">
+        <v>161</v>
+      </c>
+      <c r="J54" t="s">
+        <v>161</v>
+      </c>
+      <c r="K54" t="s">
+        <v>161</v>
+      </c>
+      <c r="L54" t="s">
+        <v>161</v>
+      </c>
+      <c r="M54" t="s">
+        <v>161</v>
+      </c>
+      <c r="N54" t="s">
+        <v>161</v>
       </c>
       <c r="O54" t="s">
-        <v>1090</v>
-      </c>
-      <c r="P54" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q54" t="b">
-        <v>0</v>
-      </c>
-      <c r="R54">
-        <v>0</v>
+        <v>161</v>
+      </c>
+      <c r="P54" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>161</v>
+      </c>
+      <c r="R54" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -17024,25 +16982,25 @@
         <v>161</v>
       </c>
       <c r="B55">
-        <v>601004</v>
+        <v>601001</v>
       </c>
       <c r="C55" t="s">
-        <v>1091</v>
+        <v>1068</v>
       </c>
       <c r="D55" t="s">
-        <v>1064</v>
+        <v>1027</v>
       </c>
       <c r="E55" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
       <c r="F55" t="s">
-        <v>1065</v>
+        <v>1028</v>
       </c>
       <c r="G55" t="s">
-        <v>1066</v>
+        <v>1029</v>
       </c>
       <c r="H55" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
@@ -17063,7 +17021,7 @@
         <v>0</v>
       </c>
       <c r="O55" t="s">
-        <v>1092</v>
+        <v>1069</v>
       </c>
       <c r="P55" t="b">
         <v>1</v>
@@ -17077,58 +17035,58 @@
     </row>
     <row r="56" spans="1:18">
       <c r="A56" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1093</v>
+        <v>161</v>
+      </c>
+      <c r="B56">
+        <v>601002</v>
       </c>
       <c r="C56" t="s">
-        <v>161</v>
+        <v>1070</v>
       </c>
       <c r="D56" t="s">
-        <v>161</v>
+        <v>1032</v>
       </c>
       <c r="E56" t="s">
-        <v>161</v>
+        <v>896</v>
       </c>
       <c r="F56" t="s">
-        <v>161</v>
+        <v>1033</v>
       </c>
       <c r="G56" t="s">
-        <v>161</v>
+        <v>1034</v>
       </c>
       <c r="H56" t="s">
-        <v>161</v>
-      </c>
-      <c r="I56" t="s">
-        <v>161</v>
-      </c>
-      <c r="J56" t="s">
-        <v>161</v>
-      </c>
-      <c r="K56" t="s">
-        <v>161</v>
-      </c>
-      <c r="L56" t="s">
-        <v>161</v>
-      </c>
-      <c r="M56" t="s">
-        <v>161</v>
-      </c>
-      <c r="N56" t="s">
-        <v>161</v>
+        <v>930</v>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="b">
+        <v>1</v>
+      </c>
+      <c r="M56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N56" t="b">
+        <v>0</v>
       </c>
       <c r="O56" t="s">
-        <v>161</v>
-      </c>
-      <c r="P56" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>161</v>
-      </c>
-      <c r="R56" t="s">
-        <v>161</v>
+        <v>1071</v>
+      </c>
+      <c r="P56" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="b">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:18">
@@ -17136,28 +17094,28 @@
         <v>161</v>
       </c>
       <c r="B57">
-        <v>700001</v>
+        <v>601003</v>
       </c>
       <c r="C57" t="s">
-        <v>1094</v>
+        <v>1072</v>
       </c>
       <c r="D57" t="s">
-        <v>1095</v>
+        <v>1037</v>
       </c>
       <c r="E57" t="s">
-        <v>621</v>
+        <v>896</v>
       </c>
       <c r="F57" t="s">
-        <v>1096</v>
+        <v>1038</v>
       </c>
       <c r="G57" t="s">
-        <v>1097</v>
+        <v>1039</v>
       </c>
       <c r="H57" t="s">
-        <v>161</v>
+        <v>930</v>
       </c>
       <c r="I57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
@@ -17175,7 +17133,7 @@
         <v>0</v>
       </c>
       <c r="O57" t="s">
-        <v>1098</v>
+        <v>1073</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
@@ -17192,28 +17150,28 @@
         <v>161</v>
       </c>
       <c r="B58">
-        <v>700002</v>
+        <v>601004</v>
       </c>
       <c r="C58" t="s">
-        <v>1099</v>
+        <v>1074</v>
       </c>
       <c r="D58" t="s">
-        <v>1100</v>
+        <v>1042</v>
       </c>
       <c r="E58" t="s">
-        <v>621</v>
+        <v>896</v>
       </c>
       <c r="F58" t="s">
-        <v>1101</v>
+        <v>1043</v>
       </c>
       <c r="G58" t="s">
-        <v>1102</v>
+        <v>1044</v>
       </c>
       <c r="H58" t="s">
-        <v>161</v>
+        <v>930</v>
       </c>
       <c r="I58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
@@ -17231,7 +17189,7 @@
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>1103</v>
+        <v>1075</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -17245,58 +17203,58 @@
     </row>
     <row r="59" spans="1:18">
       <c r="A59" t="s">
-        <v>161</v>
-      </c>
-      <c r="B59">
-        <v>700004</v>
+        <v>39</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1076</v>
       </c>
       <c r="C59" t="s">
-        <v>1104</v>
+        <v>161</v>
       </c>
       <c r="D59" t="s">
-        <v>1105</v>
+        <v>161</v>
       </c>
       <c r="E59" t="s">
-        <v>621</v>
+        <v>161</v>
       </c>
       <c r="F59" t="s">
-        <v>1106</v>
+        <v>161</v>
       </c>
       <c r="G59" t="s">
-        <v>1107</v>
+        <v>161</v>
       </c>
       <c r="H59" t="s">
         <v>161</v>
       </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" t="b">
-        <v>1</v>
-      </c>
-      <c r="M59" t="b">
-        <v>1</v>
-      </c>
-      <c r="N59" t="b">
-        <v>0</v>
+      <c r="I59" t="s">
+        <v>161</v>
+      </c>
+      <c r="J59" t="s">
+        <v>161</v>
+      </c>
+      <c r="K59" t="s">
+        <v>161</v>
+      </c>
+      <c r="L59" t="s">
+        <v>161</v>
+      </c>
+      <c r="M59" t="s">
+        <v>161</v>
+      </c>
+      <c r="N59" t="s">
+        <v>161</v>
       </c>
       <c r="O59" t="s">
-        <v>1108</v>
-      </c>
-      <c r="P59" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q59" t="b">
-        <v>0</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
+        <v>161</v>
+      </c>
+      <c r="P59" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>161</v>
+      </c>
+      <c r="R59" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:18">
@@ -17304,22 +17262,22 @@
         <v>161</v>
       </c>
       <c r="B60">
-        <v>700005</v>
+        <v>700001</v>
       </c>
       <c r="C60" t="s">
-        <v>1109</v>
+        <v>1077</v>
       </c>
       <c r="D60" t="s">
-        <v>1110</v>
+        <v>1078</v>
       </c>
       <c r="E60" t="s">
         <v>621</v>
       </c>
       <c r="F60" t="s">
-        <v>1111</v>
+        <v>1079</v>
       </c>
       <c r="G60" t="s">
-        <v>1112</v>
+        <v>1080</v>
       </c>
       <c r="H60" t="s">
         <v>161</v>
@@ -17343,13 +17301,13 @@
         <v>0</v>
       </c>
       <c r="O60" t="s">
-        <v>1103</v>
+        <v>1081</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -17360,22 +17318,22 @@
         <v>161</v>
       </c>
       <c r="B61">
-        <v>700007</v>
+        <v>700002</v>
       </c>
       <c r="C61" t="s">
-        <v>1113</v>
+        <v>1082</v>
       </c>
       <c r="D61" t="s">
-        <v>1114</v>
+        <v>1083</v>
       </c>
       <c r="E61" t="s">
         <v>621</v>
       </c>
       <c r="F61" t="s">
-        <v>1115</v>
+        <v>1084</v>
       </c>
       <c r="G61" t="s">
-        <v>1116</v>
+        <v>1085</v>
       </c>
       <c r="H61" t="s">
         <v>161</v>
@@ -17399,13 +17357,13 @@
         <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>1108</v>
+        <v>1086</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61">
         <v>0</v>
@@ -17416,22 +17374,22 @@
         <v>161</v>
       </c>
       <c r="B62">
-        <v>700008</v>
+        <v>700004</v>
       </c>
       <c r="C62" t="s">
-        <v>1117</v>
+        <v>1087</v>
       </c>
       <c r="D62" t="s">
-        <v>1118</v>
+        <v>1088</v>
       </c>
       <c r="E62" t="s">
         <v>621</v>
       </c>
       <c r="F62" t="s">
-        <v>1119</v>
+        <v>1089</v>
       </c>
       <c r="G62" t="s">
-        <v>1120</v>
+        <v>1090</v>
       </c>
       <c r="H62" t="s">
         <v>161</v>
@@ -17455,13 +17413,13 @@
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62">
         <v>0</v>
@@ -17472,22 +17430,22 @@
         <v>161</v>
       </c>
       <c r="B63">
-        <v>700010</v>
+        <v>700005</v>
       </c>
       <c r="C63" t="s">
-        <v>1121</v>
+        <v>1092</v>
       </c>
       <c r="D63" t="s">
-        <v>1122</v>
+        <v>1093</v>
       </c>
       <c r="E63" t="s">
         <v>621</v>
       </c>
       <c r="F63" t="s">
-        <v>1123</v>
+        <v>1094</v>
       </c>
       <c r="G63" t="s">
-        <v>1124</v>
+        <v>1095</v>
       </c>
       <c r="H63" t="s">
         <v>161</v>
@@ -17511,13 +17469,13 @@
         <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>1108</v>
+        <v>1086</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -17528,22 +17486,22 @@
         <v>161</v>
       </c>
       <c r="B64">
-        <v>700011</v>
+        <v>700007</v>
       </c>
       <c r="C64" t="s">
-        <v>1125</v>
+        <v>1096</v>
       </c>
       <c r="D64" t="s">
-        <v>1126</v>
+        <v>1097</v>
       </c>
       <c r="E64" t="s">
         <v>621</v>
       </c>
       <c r="F64" t="s">
-        <v>1127</v>
+        <v>1098</v>
       </c>
       <c r="G64" t="s">
-        <v>1128</v>
+        <v>1099</v>
       </c>
       <c r="H64" t="s">
         <v>161</v>
@@ -17567,13 +17525,13 @@
         <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64">
         <v>0</v>
@@ -17581,58 +17539,58 @@
     </row>
     <row r="65" spans="1:18">
       <c r="A65" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1129</v>
+        <v>161</v>
+      </c>
+      <c r="B65">
+        <v>700008</v>
       </c>
       <c r="C65" t="s">
-        <v>161</v>
+        <v>1100</v>
       </c>
       <c r="D65" t="s">
-        <v>161</v>
+        <v>1101</v>
       </c>
       <c r="E65" t="s">
-        <v>161</v>
+        <v>621</v>
       </c>
       <c r="F65" t="s">
-        <v>161</v>
+        <v>1102</v>
       </c>
       <c r="G65" t="s">
-        <v>161</v>
+        <v>1103</v>
       </c>
       <c r="H65" t="s">
         <v>161</v>
       </c>
-      <c r="I65" t="s">
-        <v>161</v>
-      </c>
-      <c r="J65" t="s">
-        <v>161</v>
-      </c>
-      <c r="K65" t="s">
-        <v>161</v>
-      </c>
-      <c r="L65" t="s">
-        <v>161</v>
-      </c>
-      <c r="M65" t="s">
-        <v>161</v>
-      </c>
-      <c r="N65" t="s">
-        <v>161</v>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" t="b">
+        <v>1</v>
+      </c>
+      <c r="M65" t="b">
+        <v>1</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>161</v>
-      </c>
-      <c r="P65" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>161</v>
-      </c>
-      <c r="R65" t="s">
-        <v>161</v>
+        <v>1086</v>
+      </c>
+      <c r="P65" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="b">
+        <v>1</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:18">
@@ -17640,54 +17598,715 @@
         <v>161</v>
       </c>
       <c r="B66">
-        <v>701001</v>
+        <v>700010</v>
       </c>
       <c r="C66" t="s">
-        <v>1130</v>
+        <v>1104</v>
       </c>
       <c r="D66" t="s">
-        <v>1131</v>
+        <v>1105</v>
       </c>
       <c r="E66" t="s">
         <v>621</v>
       </c>
       <c r="F66" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H66" t="s">
+        <v>161</v>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="b">
+        <v>1</v>
+      </c>
+      <c r="M66" t="b">
+        <v>1</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" t="s">
+        <v>1091</v>
+      </c>
+      <c r="P66" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="b">
+        <v>1</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
+      <c r="A67" t="s">
+        <v>161</v>
+      </c>
+      <c r="B67">
+        <v>700011</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E67" t="s">
+        <v>621</v>
+      </c>
+      <c r="F67" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H67" t="s">
+        <v>161</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" t="b">
+        <v>1</v>
+      </c>
+      <c r="M67" t="b">
+        <v>1</v>
+      </c>
+      <c r="N67" t="b">
+        <v>0</v>
+      </c>
+      <c r="O67" t="s">
+        <v>1086</v>
+      </c>
+      <c r="P67" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="b">
+        <v>1</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18">
+      <c r="A68" t="s">
+        <v>39</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18">
+      <c r="B69">
+        <v>700101</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E69" t="s">
+        <v>621</v>
+      </c>
+      <c r="F69" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G69" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H69" t="s">
+        <v>161</v>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" t="b">
+        <v>1</v>
+      </c>
+      <c r="M69" t="b">
+        <v>1</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" t="s">
+        <v>1117</v>
+      </c>
+      <c r="P69" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="b">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
+      <c r="B70">
+        <v>700102</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D70" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E70" t="s">
+        <v>621</v>
+      </c>
+      <c r="F70" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G70" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H70" t="s">
+        <v>161</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" t="b">
+        <v>1</v>
+      </c>
+      <c r="M70" t="b">
+        <v>1</v>
+      </c>
+      <c r="N70" t="b">
+        <v>0</v>
+      </c>
+      <c r="O70" t="s">
+        <v>1122</v>
+      </c>
+      <c r="P70" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="b">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
+      <c r="B71">
+        <v>700104</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E71" t="s">
+        <v>621</v>
+      </c>
+      <c r="F71" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G71" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H71" t="s">
+        <v>161</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" t="b">
+        <v>1</v>
+      </c>
+      <c r="M71" t="b">
+        <v>1</v>
+      </c>
+      <c r="N71" t="b">
+        <v>0</v>
+      </c>
+      <c r="O71" t="s">
+        <v>1117</v>
+      </c>
+      <c r="P71" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="b">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
+      <c r="B72">
+        <v>700105</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D72" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E72" t="s">
+        <v>621</v>
+      </c>
+      <c r="F72" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G72" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H72" t="s">
+        <v>161</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="b">
+        <v>1</v>
+      </c>
+      <c r="M72" t="b">
+        <v>1</v>
+      </c>
+      <c r="N72" t="b">
+        <v>0</v>
+      </c>
+      <c r="O72" t="s">
+        <v>1122</v>
+      </c>
+      <c r="P72" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="b">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
+      <c r="B73">
+        <v>700107</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D73" t="s">
         <v>1132</v>
       </c>
-      <c r="G66" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H66" t="s">
-        <v>161</v>
-      </c>
-      <c r="I66" t="b">
-        <v>0</v>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66" t="b">
-        <v>1</v>
-      </c>
-      <c r="M66" t="b">
-        <v>1</v>
-      </c>
-      <c r="N66" t="b">
-        <v>0</v>
-      </c>
-      <c r="O66" t="s">
-        <v>1108</v>
-      </c>
-      <c r="P66" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q66" t="b">
-        <v>0</v>
-      </c>
-      <c r="R66">
+      <c r="E73" t="s">
+        <v>621</v>
+      </c>
+      <c r="F73" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H73" t="s">
+        <v>161</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="b">
+        <v>1</v>
+      </c>
+      <c r="M73" t="b">
+        <v>1</v>
+      </c>
+      <c r="N73" t="b">
+        <v>0</v>
+      </c>
+      <c r="O73" t="s">
+        <v>1117</v>
+      </c>
+      <c r="P73" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="b">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
+      <c r="B74">
+        <v>700108</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D74" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E74" t="s">
+        <v>621</v>
+      </c>
+      <c r="F74" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G74" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H74" t="s">
+        <v>161</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="b">
+        <v>1</v>
+      </c>
+      <c r="M74" t="b">
+        <v>1</v>
+      </c>
+      <c r="N74" t="b">
+        <v>0</v>
+      </c>
+      <c r="O74" t="s">
+        <v>1122</v>
+      </c>
+      <c r="P74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="b">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
+      <c r="B75">
+        <v>700110</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E75" t="s">
+        <v>621</v>
+      </c>
+      <c r="F75" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G75" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H75" t="s">
+        <v>161</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="b">
+        <v>1</v>
+      </c>
+      <c r="M75" t="b">
+        <v>1</v>
+      </c>
+      <c r="N75" t="b">
+        <v>0</v>
+      </c>
+      <c r="O75" t="s">
+        <v>1117</v>
+      </c>
+      <c r="P75" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="b">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
+      <c r="B76">
+        <v>700111</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E76" t="s">
+        <v>621</v>
+      </c>
+      <c r="F76" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G76" t="s">
+        <v>1146</v>
+      </c>
+      <c r="H76" t="s">
+        <v>161</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="b">
+        <v>1</v>
+      </c>
+      <c r="M76" t="b">
+        <v>1</v>
+      </c>
+      <c r="N76" t="b">
+        <v>0</v>
+      </c>
+      <c r="O76" t="s">
+        <v>1122</v>
+      </c>
+      <c r="P76" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="b">
+        <v>0</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
+      <c r="A77" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C77" t="s">
+        <v>161</v>
+      </c>
+      <c r="D77" t="s">
+        <v>161</v>
+      </c>
+      <c r="E77" t="s">
+        <v>161</v>
+      </c>
+      <c r="F77" t="s">
+        <v>161</v>
+      </c>
+      <c r="G77" t="s">
+        <v>161</v>
+      </c>
+      <c r="H77" t="s">
+        <v>161</v>
+      </c>
+      <c r="I77" t="s">
+        <v>161</v>
+      </c>
+      <c r="J77" t="s">
+        <v>161</v>
+      </c>
+      <c r="K77" t="s">
+        <v>161</v>
+      </c>
+      <c r="L77" t="s">
+        <v>161</v>
+      </c>
+      <c r="M77" t="s">
+        <v>161</v>
+      </c>
+      <c r="N77" t="s">
+        <v>161</v>
+      </c>
+      <c r="O77" t="s">
+        <v>161</v>
+      </c>
+      <c r="P77" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>161</v>
+      </c>
+      <c r="R77" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
+      <c r="A78" t="s">
+        <v>161</v>
+      </c>
+      <c r="B78">
+        <v>701001</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D78" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E78" t="s">
+        <v>621</v>
+      </c>
+      <c r="F78" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G78" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H78" t="s">
+        <v>161</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" t="b">
+        <v>1</v>
+      </c>
+      <c r="M78" t="b">
+        <v>1</v>
+      </c>
+      <c r="N78" t="b">
+        <v>0</v>
+      </c>
+      <c r="O78" t="s">
+        <v>1091</v>
+      </c>
+      <c r="P78" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="b">
+        <v>1</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18">
+      <c r="A79" t="s">
+        <v>39</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18">
+      <c r="B80">
+        <v>701101</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D80" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E80" t="s">
+        <v>621</v>
+      </c>
+      <c r="F80" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G80" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H80" t="s">
+        <v>161</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" t="b">
+        <v>1</v>
+      </c>
+      <c r="M80" t="b">
+        <v>1</v>
+      </c>
+      <c r="N80" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" t="s">
+        <v>1117</v>
+      </c>
+      <c r="P80" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="b">
+        <v>0</v>
+      </c>
+      <c r="R80">
         <v>0</v>
       </c>
     </row>
@@ -17718,7 +18337,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{29744a69-728b-45fe-9b11-3be186d116ba}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{782ddc8a-1aa0-448e-bd41-535a16a934e8}">
             <xm:f>NOT(ISERROR(SEARCH(FALSE,L1)))</xm:f>
             <xm:f>FALSE</xm:f>
             <x14:dxf>
@@ -17740,7 +18359,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="14.0833333333333" customWidth="1"/>
@@ -17757,19 +18376,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1133</v>
+        <v>1156</v>
       </c>
       <c r="D1" t="s">
-        <v>1134</v>
+        <v>1157</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>910</v>
+        <v>888</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1135</v>
+        <v>1158</v>
       </c>
       <c r="G1" t="s">
-        <v>1136</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -17826,13 +18445,13 @@
         <v>556</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1137</v>
+        <v>1160</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1138</v>
+        <v>1161</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1139</v>
+        <v>1162</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>596</v>
@@ -17855,13 +18474,13 @@
         <v>199999</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1140</v>
+        <v>1163</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>597</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>1141</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="6" ht="52.2" spans="1:7">
@@ -17878,13 +18497,13 @@
         <v>299999</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1142</v>
+        <v>1165</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1143</v>
+        <v>1166</v>
       </c>
       <c r="G6" t="s">
-        <v>1144</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="7" ht="87" spans="1:7">
@@ -17901,13 +18520,13 @@
         <v>229999</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>1145</v>
+        <v>1168</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>1146</v>
+        <v>1169</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>1147</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="8" ht="84" customHeight="1" spans="1:7">
@@ -17921,13 +18540,13 @@
         <v>209999</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1148</v>
+        <v>1171</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1149</v>
+        <v>1172</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>1150</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="9" ht="65" customHeight="1" spans="1:7">
@@ -17944,13 +18563,13 @@
         <v>299999</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1151</v>
+        <v>1174</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1152</v>
+        <v>1175</v>
       </c>
       <c r="G9" t="s">
-        <v>1153</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="10" ht="69.6" spans="1:7">
@@ -17967,13 +18586,13 @@
         <v>399999</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>1154</v>
+        <v>1177</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>1155</v>
+        <v>1178</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>1156</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="11" ht="67" customHeight="1" spans="1:7">
@@ -17987,13 +18606,13 @@
         <v>399999</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1157</v>
+        <v>1180</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1158</v>
+        <v>1181</v>
       </c>
       <c r="G11" t="s">
-        <v>1156</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="12" ht="34.8" spans="1:7">
@@ -18010,13 +18629,13 @@
         <v>301999</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>1159</v>
+        <v>1182</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>1160</v>
+        <v>1183</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>1161</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1" spans="1:7">
@@ -18030,13 +18649,13 @@
         <v>301999</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1162</v>
+        <v>1185</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1163</v>
+        <v>1186</v>
       </c>
       <c r="G13" t="s">
-        <v>1161</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="14" ht="34.8" spans="1:7">
@@ -18053,13 +18672,13 @@
         <v>302999</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1164</v>
+        <v>1187</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1165</v>
+        <v>1188</v>
       </c>
       <c r="G14" t="s">
-        <v>1166</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="15" ht="34.8" spans="1:7">
@@ -18076,13 +18695,13 @@
         <v>399999</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1167</v>
+        <v>1190</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1168</v>
+        <v>1191</v>
       </c>
       <c r="G15" t="s">
-        <v>1169</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="16" ht="87" spans="1:7">
@@ -18099,13 +18718,13 @@
         <v>499999</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1170</v>
+        <v>1193</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1171</v>
+        <v>1194</v>
       </c>
       <c r="G16" t="s">
-        <v>1172</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="17" ht="52.2" spans="1:7">
@@ -18122,13 +18741,13 @@
         <v>409999</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1173</v>
+        <v>1196</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1174</v>
+        <v>1197</v>
       </c>
       <c r="G17" t="s">
-        <v>1175</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="18" ht="52.2" spans="1:7">
@@ -18145,13 +18764,13 @@
         <v>499999</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>1176</v>
+        <v>1199</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1177</v>
+        <v>1200</v>
       </c>
       <c r="G18" t="s">
-        <v>1178</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="19" ht="52.2" spans="1:7">
@@ -18168,36 +18787,33 @@
         <v>599999</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1180</v>
+        <v>1203</v>
       </c>
       <c r="G19" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="20" ht="34.8" spans="1:7">
-      <c r="A20" t="s">
-        <v>161</v>
-      </c>
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="20" ht="52.2" spans="1:7">
       <c r="B20">
-        <v>1013</v>
+        <v>1033</v>
       </c>
       <c r="C20">
-        <v>501000</v>
+        <v>500001</v>
       </c>
       <c r="D20">
-        <v>501999</v>
+        <v>500999</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="G20" t="s">
-        <v>1184</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="21" ht="34.8" spans="1:7">
@@ -18205,22 +18821,22 @@
         <v>161</v>
       </c>
       <c r="B21">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C21">
-        <v>502000</v>
+        <v>501000</v>
       </c>
       <c r="D21">
-        <v>502999</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>1185</v>
+        <v>501999</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>1208</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1186</v>
+        <v>1209</v>
       </c>
       <c r="G21" t="s">
-        <v>1187</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="22" ht="34.8" spans="1:7">
@@ -18228,68 +18844,68 @@
         <v>161</v>
       </c>
       <c r="B22">
+        <v>1014</v>
+      </c>
+      <c r="C22">
+        <v>502000</v>
+      </c>
+      <c r="D22">
+        <v>502999</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="23" ht="34.8" spans="1:7">
+      <c r="A23" t="s">
+        <v>161</v>
+      </c>
+      <c r="B23">
         <v>1015</v>
       </c>
-      <c r="C22">
+      <c r="C23">
         <v>503000</v>
       </c>
-      <c r="D22">
+      <c r="D23">
         <v>599999</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>1188</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>1189</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="23" ht="87" spans="1:7">
-      <c r="A23" t="s">
-        <v>161</v>
-      </c>
-      <c r="B23">
+      <c r="E23" s="6" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="24" ht="87" spans="1:7">
+      <c r="A24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24">
         <v>1016</v>
       </c>
-      <c r="C23">
+      <c r="C24">
         <v>600000</v>
       </c>
-      <c r="D23">
+      <c r="D24">
         <v>699999</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>1191</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G23" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="24" ht="34.8" spans="1:7">
-      <c r="A24" t="s">
-        <v>161</v>
-      </c>
-      <c r="B24">
-        <v>1017</v>
-      </c>
-      <c r="C24">
-        <v>601000</v>
-      </c>
-      <c r="D24">
-        <v>601999</v>
-      </c>
       <c r="E24" s="6" t="s">
-        <v>1194</v>
+        <v>1217</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1195</v>
+        <v>1218</v>
       </c>
       <c r="G24" t="s">
-        <v>1196</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="25" ht="34.8" spans="1:7">
@@ -18297,22 +18913,22 @@
         <v>161</v>
       </c>
       <c r="B25">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C25">
-        <v>602000</v>
+        <v>601000</v>
       </c>
       <c r="D25">
-        <v>602999</v>
+        <v>601999</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1197</v>
+        <v>1220</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>1198</v>
+        <v>1221</v>
       </c>
       <c r="G25" t="s">
-        <v>1199</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="26" ht="34.8" spans="1:7">
@@ -18320,22 +18936,22 @@
         <v>161</v>
       </c>
       <c r="B26">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C26">
-        <v>603000</v>
+        <v>602000</v>
       </c>
       <c r="D26">
-        <v>603999</v>
+        <v>602999</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>1200</v>
+        <v>1223</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1201</v>
+        <v>1224</v>
       </c>
       <c r="G26" t="s">
-        <v>1202</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="27" ht="34.8" spans="1:7">
@@ -18343,22 +18959,22 @@
         <v>161</v>
       </c>
       <c r="B27">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C27">
-        <v>604000</v>
+        <v>603000</v>
       </c>
       <c r="D27">
-        <v>699999</v>
+        <v>603999</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>1203</v>
+        <v>1226</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1204</v>
+        <v>1227</v>
       </c>
       <c r="G27" t="s">
-        <v>1205</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="28" ht="34.8" spans="1:7">
@@ -18366,234 +18982,234 @@
         <v>161</v>
       </c>
       <c r="B28">
+        <v>1020</v>
+      </c>
+      <c r="C28">
+        <v>604000</v>
+      </c>
+      <c r="D28">
+        <v>699999</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="29" ht="34.8" spans="1:7">
+      <c r="A29" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29">
         <v>1021</v>
-      </c>
-      <c r="C28">
-        <v>700000</v>
-      </c>
-      <c r="D28">
-        <v>799999</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>1206</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>1207</v>
-      </c>
-      <c r="G28" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="29" ht="52.2" spans="1:7">
-      <c r="A29" t="s">
-        <v>161</v>
-      </c>
-      <c r="B29">
-        <v>1022</v>
       </c>
       <c r="C29">
         <v>700000</v>
       </c>
       <c r="D29">
+        <v>799999</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="30" ht="52.2" spans="1:7">
+      <c r="A30" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30">
+        <v>1022</v>
+      </c>
+      <c r="C30">
+        <v>700000</v>
+      </c>
+      <c r="D30">
         <v>709999</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>1210</v>
-      </c>
-      <c r="G29" t="s">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="30" ht="34.8" spans="1:7">
-      <c r="A30" s="9" t="s">
+      <c r="E30" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="31" ht="34.8" spans="1:7">
+      <c r="A31" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B31" s="9">
         <v>1023</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C31" s="9">
         <v>700000</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D31" s="9">
         <v>700999</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>1212</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="31" ht="52.2" spans="1:7">
-      <c r="B31">
+      <c r="E31" s="13" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="32" ht="52.2" spans="1:7">
+      <c r="B32">
         <v>1023</v>
-      </c>
-      <c r="C31">
-        <v>700000</v>
-      </c>
-      <c r="D31">
-        <v>700999</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>1215</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>1216</v>
-      </c>
-      <c r="G31" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="32" ht="34.8" spans="1:7">
-      <c r="B32">
-        <v>1029</v>
       </c>
       <c r="C32">
         <v>700000</v>
       </c>
       <c r="D32">
-        <v>700099</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>1218</v>
+        <v>700999</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>1241</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1219</v>
+        <v>1242</v>
       </c>
       <c r="G32" t="s">
-        <v>1220</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="33" ht="34.8" spans="1:7">
       <c r="B33">
+        <v>1029</v>
+      </c>
+      <c r="C33">
+        <v>700000</v>
+      </c>
+      <c r="D33">
+        <v>700099</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="34" ht="34.8" spans="1:7">
+      <c r="B34">
         <v>1030</v>
       </c>
-      <c r="C33">
+      <c r="C34">
         <v>700100</v>
       </c>
-      <c r="D33">
+      <c r="D34">
         <v>700999</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>1222</v>
-      </c>
-      <c r="G33" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="34" ht="34.8" spans="1:7">
-      <c r="A34" s="9" t="s">
+      <c r="E34" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="35" ht="34.8" spans="1:7">
+      <c r="A35" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B35" s="9">
         <v>1024</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C35" s="9">
         <v>701000</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D35" s="9">
         <v>701999</v>
       </c>
-      <c r="E34" s="13" t="s">
-        <v>1224</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>1225</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="35" ht="71" customHeight="1" spans="1:7">
-      <c r="B35">
-        <v>1024</v>
-      </c>
-      <c r="C35">
-        <v>701000</v>
-      </c>
-      <c r="D35">
-        <v>701999</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>1227</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>1228</v>
-      </c>
-      <c r="G35" t="s">
-        <v>1229</v>
+      <c r="E35" s="13" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>1252</v>
       </c>
     </row>
     <row r="36" ht="71" customHeight="1" spans="1:7">
       <c r="B36">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="C36">
         <v>701000</v>
       </c>
       <c r="D36">
-        <v>701099</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>1230</v>
+        <v>701999</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>1253</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>1231</v>
+        <v>1254</v>
       </c>
       <c r="G36" t="s">
-        <v>1232</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="37" ht="71" customHeight="1" spans="1:7">
       <c r="B37">
+        <v>1031</v>
+      </c>
+      <c r="C37">
+        <v>701000</v>
+      </c>
+      <c r="D37">
+        <v>701099</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="38" ht="71" customHeight="1" spans="1:7">
+      <c r="B38">
         <v>1032</v>
       </c>
-      <c r="C37">
+      <c r="C38">
         <v>701100</v>
       </c>
-      <c r="D37">
+      <c r="D38">
         <v>701999</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>1225</v>
-      </c>
-      <c r="G37" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="38" ht="34.8" spans="1:7">
-      <c r="A38" t="s">
-        <v>161</v>
-      </c>
-      <c r="B38">
-        <v>1025</v>
-      </c>
-      <c r="C38">
-        <v>702000</v>
-      </c>
-      <c r="D38">
-        <v>709999</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>1235</v>
+      <c r="E38" s="2" t="s">
+        <v>1259</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>1236</v>
+        <v>1251</v>
       </c>
       <c r="G38" t="s">
-        <v>1237</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="39" ht="34.8" spans="1:7">
@@ -18601,22 +19217,22 @@
         <v>161</v>
       </c>
       <c r="B39">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C39">
-        <v>710000</v>
+        <v>702000</v>
       </c>
       <c r="D39">
-        <v>799999</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>1238</v>
+        <v>709999</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>1261</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>1239</v>
+        <v>1262</v>
       </c>
       <c r="G39" t="s">
-        <v>1240</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="40" ht="34.8" spans="1:7">
@@ -18624,22 +19240,22 @@
         <v>161</v>
       </c>
       <c r="B40">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C40">
-        <v>800000</v>
+        <v>710000</v>
       </c>
       <c r="D40">
-        <v>999999</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>1241</v>
+        <v>799999</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>1264</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>1242</v>
+        <v>1265</v>
       </c>
       <c r="G40" t="s">
-        <v>629</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="41" ht="34.8" spans="1:7">
@@ -18647,29 +19263,49 @@
         <v>161</v>
       </c>
       <c r="B41">
+        <v>1027</v>
+      </c>
+      <c r="C41">
+        <v>800000</v>
+      </c>
+      <c r="D41">
+        <v>999999</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G41" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="42" ht="34.8" spans="1:7">
+      <c r="A42" t="s">
+        <v>161</v>
+      </c>
+      <c r="B42">
         <v>1028</v>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41">
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
         <v>99999</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>1243</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>1244</v>
-      </c>
-      <c r="G41" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="E42" s="2"/>
-      <c r="F42"/>
+      <c r="E42" s="6" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1271</v>
+      </c>
     </row>
     <row r="43" spans="1:7">
+      <c r="E43" s="2"/>
       <c r="F43"/>
     </row>
     <row r="44" spans="1:7">
@@ -18682,7 +19318,7 @@
       <c r="F46"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="E47" s="6"/>
+      <c r="F47"/>
     </row>
     <row r="48" spans="1:7">
       <c r="E48" s="6"/>
@@ -18693,8 +19329,8 @@
     <row r="50" spans="5:5">
       <c r="E50" s="6"/>
     </row>
-    <row r="52" spans="5:5">
-      <c r="E52" s="6"/>
+    <row r="51" spans="5:5">
+      <c r="E51" s="6"/>
     </row>
     <row r="53" spans="5:5">
       <c r="E53" s="6"/>
@@ -18702,11 +19338,14 @@
     <row r="54" spans="5:5">
       <c r="E54" s="6"/>
     </row>
-    <row r="56" spans="5:5">
-      <c r="E56" s="6"/>
+    <row r="55" spans="5:5">
+      <c r="E55" s="6"/>
     </row>
     <row r="57" spans="5:5">
-      <c r="E57" s="2"/>
+      <c r="E57" s="6"/>
+    </row>
+    <row r="58" spans="5:5">
+      <c r="E58" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19482,7 +20121,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
@@ -19501,7 +20140,7 @@
     <col min="14" max="14" width="28.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -19538,14 +20177,8 @@
       <c r="L1" t="s">
         <v>640</v>
       </c>
-      <c r="M1" t="s">
-        <v>641</v>
-      </c>
-      <c r="N1" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
@@ -19556,22 +20189,22 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F2" t="s">
         <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H2" t="s">
         <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="J2" t="s">
         <v>31</v>
@@ -19582,116 +20215,101 @@
       <c r="L2" t="s">
         <v>35</v>
       </c>
-      <c r="M2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="109" customHeight="1" spans="1:14">
+    </row>
+    <row r="3" s="2" customFormat="1" ht="109" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>653</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>75</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="4" s="5" customFormat="1" spans="1:14">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="4" s="5" customFormat="1" spans="1:12">
       <c r="A4" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>658</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>659</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>661</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>662</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>665</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>75</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>667</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>668</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="F5">
         <v>1000</v>
       </c>
       <c r="G5" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -19700,7 +20318,7 @@
         <v>3</v>
       </c>
       <c r="J5" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -19708,31 +20326,25 @@
       <c r="L5" t="b">
         <v>1</v>
       </c>
-      <c r="M5">
-        <v>201001</v>
-      </c>
-      <c r="N5">
-        <v>301001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+    </row>
+    <row r="6" spans="1:12">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="F6">
         <v>1000</v>
       </c>
       <c r="G6" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -19741,7 +20353,7 @@
         <v>3</v>
       </c>
       <c r="J6" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -19749,31 +20361,25 @@
       <c r="L6" t="b">
         <v>1</v>
       </c>
-      <c r="M6">
-        <v>201002</v>
-      </c>
-      <c r="N6">
-        <v>301002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+    </row>
+    <row r="7" spans="1:12">
       <c r="B7">
         <v>2001</v>
       </c>
       <c r="C7" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="F7">
         <v>1000</v>
       </c>
       <c r="G7" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="H7">
         <v>3</v>
@@ -19782,7 +20388,7 @@
         <v>3</v>
       </c>
       <c r="J7" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -19790,31 +20396,25 @@
       <c r="L7" t="b">
         <v>1</v>
       </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+    </row>
+    <row r="8" spans="1:12">
       <c r="B8">
         <v>3001</v>
       </c>
       <c r="C8" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="D8" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -19823,7 +20423,7 @@
         <v>3</v>
       </c>
       <c r="J8" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -19831,31 +20431,25 @@
       <c r="L8" t="b">
         <v>1</v>
       </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+    </row>
+    <row r="9" spans="1:12">
       <c r="B9">
         <v>4001</v>
       </c>
       <c r="C9" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="H9">
         <v>3</v>
@@ -19864,25 +20458,19 @@
         <v>3</v>
       </c>
       <c r="J9" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
       </c>
-      <c r="L9" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>204001</v>
-      </c>
-      <c r="N9">
-        <v>301001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="L9" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="E15" s="16"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:12">
       <c r="E16" s="16"/>
     </row>
     <row r="17" spans="5:5">
@@ -19897,27 +20485,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.16666666666667" customWidth="1"/>
-    <col min="3" max="3" width="10.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="18.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="10.8333333333333" customWidth="1"/>
-    <col min="6" max="6" width="13.4166666666667" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="14.5" customWidth="1"/>
-    <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="13.1666666666667" customWidth="1"/>
-    <col min="11" max="11" width="10.25" customWidth="1"/>
-    <col min="12" max="12" width="18.6666666666667" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="30.8333333333333" customWidth="1"/>
-    <col min="15" max="15" width="45.25" customWidth="1"/>
+    <col min="3" max="4" width="10.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.4166666666667" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="9" width="7.83333333333333" customWidth="1"/>
+    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="11" max="11" width="13.1666666666667" customWidth="1"/>
+    <col min="12" max="12" width="10.25" customWidth="1"/>
+    <col min="13" max="13" width="18.6666666666667" customWidth="1"/>
+    <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="15" max="15" width="8.75" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -19925,40 +20511,41 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D1" t="s">
+        <v>679</v>
+      </c>
+      <c r="E1" t="s">
+        <v>680</v>
+      </c>
+      <c r="F1" t="s">
+        <v>681</v>
+      </c>
+      <c r="G1"/>
+      <c r="J1" t="s">
+        <v>682</v>
+      </c>
+      <c r="K1" t="s">
+        <v>640</v>
+      </c>
+      <c r="L1" t="s">
+        <v>683</v>
+      </c>
+      <c r="M1" t="s">
         <v>684</v>
       </c>
-      <c r="D1" t="s">
+      <c r="N1" t="s">
         <v>685</v>
       </c>
-      <c r="E1" t="s">
+      <c r="O1" t="s">
+        <v>161</v>
+      </c>
+      <c r="P1" t="s">
         <v>686</v>
       </c>
-      <c r="F1" t="s">
-        <v>687</v>
-      </c>
-      <c r="G1" t="s">
-        <v>688</v>
-      </c>
-      <c r="H1" t="s">
-        <v>689</v>
-      </c>
-      <c r="I1" t="s">
-        <v>690</v>
-      </c>
-      <c r="J1" t="s">
-        <v>640</v>
-      </c>
-      <c r="K1" t="s">
-        <v>691</v>
-      </c>
-      <c r="L1" t="s">
-        <v>692</v>
-      </c>
-      <c r="M1" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
         <v>29</v>
       </c>
@@ -19969,28 +20556,20 @@
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>694</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2"/>
+      <c r="J2" t="s">
         <v>30</v>
       </c>
-      <c r="H2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>35</v>
-      </c>
-      <c r="K2" t="s">
-        <v>30</v>
       </c>
       <c r="L2" t="s">
         <v>30</v>
@@ -19998,50 +20577,57 @@
       <c r="M2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="128" customHeight="1" spans="1:14">
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>161</v>
+      </c>
+      <c r="P2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="128" customHeight="1" spans="1:16">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>161</v>
+      </c>
       <c r="C3" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
@@ -20049,148 +20635,178 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D4" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="E4" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="F4" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="G4" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="H4" t="s">
-        <v>710</v>
-      </c>
-      <c r="I4" t="s">
-        <v>711</v>
+        <v>700</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
       </c>
       <c r="J4" t="s">
-        <v>667</v>
+        <v>701</v>
       </c>
       <c r="K4" t="s">
-        <v>712</v>
+        <v>663</v>
       </c>
       <c r="L4" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="M4" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="N4" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>704</v>
+      </c>
+      <c r="O4"/>
+      <c r="P4" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5">
-        <v>4001</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
+        <v>1001</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>SUM($F$5:F5)</f>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>30</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <f>F5*10/60</f>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>30</v>
+        <f>E5*10/60</f>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>700001</v>
+        <f>F5*$I$4/60</f>
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>700101</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6">
         <v>1002</v>
       </c>
-      <c r="E6" t="b">
-        <v>0</v>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>SUM($F$5:F6)</f>
+        <v>66</v>
       </c>
       <c r="F6">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>60</v>
+        <f t="shared" ref="G6:G16" si="0">F6*10/60</f>
+        <v>6</v>
       </c>
       <c r="H6">
-        <v>90</v>
+        <f t="shared" ref="H6:H16" si="1">E6*10/60</f>
+        <v>11</v>
       </c>
       <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>700002</v>
+        <f t="shared" ref="I6:I16" si="2">F6*$I$4/60</f>
+        <v>2.4</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>700102</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7">
         <v>2001</v>
       </c>
-      <c r="D7">
-        <v>4001</v>
-      </c>
-      <c r="E7" t="b">
-        <v>0</v>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>SUM($F$5:F7)</f>
+        <v>114</v>
       </c>
       <c r="F7">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>150</v>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>3.2</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -20198,116 +20814,146 @@
       <c r="M7">
         <v>0</v>
       </c>
-      <c r="N7" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7"/>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8">
         <v>1001</v>
       </c>
-      <c r="E8" t="b">
-        <v>0</v>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f>SUM($F$5:F8)</f>
+        <v>162</v>
       </c>
       <c r="F8">
-        <v>210</v>
+        <v>48</v>
       </c>
       <c r="G8">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="H8">
-        <v>210</v>
+        <f t="shared" si="1"/>
+        <v>27</v>
       </c>
       <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>700004</v>
+        <f t="shared" si="2"/>
+        <v>3.2</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>700104</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8"/>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9">
         <v>1002</v>
       </c>
-      <c r="E9" t="b">
-        <v>0</v>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f>SUM($F$5:F9)</f>
+        <v>222</v>
       </c>
       <c r="F9">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="H9">
-        <v>270</v>
+        <f t="shared" si="1"/>
+        <v>37</v>
       </c>
       <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>700005</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>700105</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9"/>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10">
         <v>2001</v>
       </c>
-      <c r="D10">
-        <v>4001</v>
-      </c>
-      <c r="E10" t="b">
-        <v>0</v>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <f>SUM($F$5:F10)</f>
+        <v>282</v>
       </c>
       <c r="F10">
-        <v>330</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="H10">
-        <v>330</v>
+        <f t="shared" si="1"/>
+        <v>47</v>
       </c>
       <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -20315,116 +20961,146 @@
       <c r="M10">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10"/>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11">
         <v>1001</v>
       </c>
-      <c r="E11" t="b">
-        <v>0</v>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <f>SUM($F$5:F11)</f>
+        <v>354</v>
       </c>
       <c r="F11">
-        <v>390</v>
+        <v>72</v>
       </c>
       <c r="G11">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="H11">
-        <v>390</v>
+        <f t="shared" si="1"/>
+        <v>59</v>
       </c>
       <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11">
-        <v>700007</v>
+        <f t="shared" si="2"/>
+        <v>4.8</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>700107</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12">
         <v>1002</v>
       </c>
-      <c r="E12" t="b">
-        <v>0</v>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f>SUM($F$5:F12)</f>
+        <v>426</v>
       </c>
       <c r="F12">
-        <v>450</v>
+        <v>72</v>
       </c>
       <c r="G12">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="H12">
-        <v>450</v>
+        <f t="shared" si="1"/>
+        <v>71</v>
       </c>
       <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <v>700008</v>
+        <f t="shared" si="2"/>
+        <v>4.8</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>700108</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
-      <c r="N12" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12"/>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13">
         <v>2001</v>
       </c>
-      <c r="D13">
-        <v>4001</v>
-      </c>
-      <c r="E13" t="b">
-        <v>0</v>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f>SUM($F$5:F13)</f>
+        <v>516</v>
       </c>
       <c r="F13">
-        <v>510</v>
+        <v>90</v>
       </c>
       <c r="G13">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="H13">
-        <v>510</v>
+        <f t="shared" si="1"/>
+        <v>86</v>
       </c>
       <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -20432,116 +21108,146 @@
       <c r="M13">
         <v>0</v>
       </c>
-      <c r="N13" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13"/>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14">
         <v>1001</v>
       </c>
-      <c r="E14" t="b">
-        <v>0</v>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f>SUM($F$5:F14)</f>
+        <v>606</v>
       </c>
       <c r="F14">
-        <v>570</v>
+        <v>90</v>
       </c>
       <c r="G14">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="H14">
-        <v>570</v>
+        <f t="shared" si="1"/>
+        <v>101</v>
       </c>
       <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>700010</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>700110</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
-      <c r="N14" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15">
         <v>1002</v>
       </c>
-      <c r="E15" t="b">
-        <v>0</v>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f>SUM($F$5:F15)</f>
+        <v>696</v>
       </c>
       <c r="F15">
-        <v>630</v>
+        <v>90</v>
       </c>
       <c r="G15">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="H15">
-        <v>630</v>
+        <f t="shared" si="1"/>
+        <v>116</v>
       </c>
       <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>700011</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>700111</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16">
         <v>2001</v>
       </c>
-      <c r="D16">
-        <v>4001</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f>SUM($F$5:F16)</f>
+        <v>786</v>
       </c>
       <c r="F16">
-        <v>690</v>
+        <v>90</v>
       </c>
       <c r="G16">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="H16">
-        <v>690</v>
+        <f t="shared" si="1"/>
+        <v>131</v>
       </c>
       <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -20549,54 +21255,89 @@
       <c r="M16">
         <v>0</v>
       </c>
-      <c r="N16" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16"/>
+      <c r="P16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="B17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" t="s">
+        <v>161</v>
+      </c>
+      <c r="E17" t="s">
+        <v>161</v>
+      </c>
+      <c r="F17" t="s">
+        <v>161</v>
+      </c>
+      <c r="G17"/>
+      <c r="J17" t="s">
+        <v>161</v>
+      </c>
+      <c r="K17" t="s">
+        <v>161</v>
+      </c>
+      <c r="L17" t="s">
+        <v>161</v>
+      </c>
+      <c r="M17" t="s">
+        <v>161</v>
+      </c>
+      <c r="N17" t="s">
+        <v>161</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="B18">
         <v>2001</v>
       </c>
       <c r="C18">
         <v>1001</v>
       </c>
-      <c r="D18">
-        <v>4001</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>780</v>
       </c>
       <c r="F18">
-        <v>780</v>
-      </c>
-      <c r="G18">
         <v>180</v>
       </c>
-      <c r="H18">
+      <c r="G18"/>
+      <c r="J18">
         <v>-1</v>
       </c>
-      <c r="I18">
-        <v>-1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>701001</v>
+      <c r="K18" t="b">
+        <v>1</v>
       </c>
       <c r="L18">
+        <v>701101</v>
+      </c>
+      <c r="M18">
         <v>360</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>2</v>
       </c>
-      <c r="N18" t="s">
-        <v>728</v>
+      <c r="O18"/>
+      <c r="P18">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -20627,13 +21368,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="D1" t="s">
-        <v>729</v>
+        <v>706</v>
       </c>
       <c r="E1" t="s">
-        <v>730</v>
+        <v>707</v>
       </c>
       <c r="G1" t="s">
         <v>640</v>
@@ -20664,20 +21405,20 @@
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>731</v>
+        <v>708</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>732</v>
+        <v>709</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>733</v>
+        <v>710</v>
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -20688,19 +21429,19 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D4" t="s">
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>734</v>
+        <v>711</v>
       </c>
       <c r="G4" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="H4" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -20880,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>735</v>
+        <v>713</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -21118,7 +21859,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>736</v>
+        <v>714</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -21147,7 +21888,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>737</v>
+        <v>715</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -21293,28 +22034,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>738</v>
+        <v>716</v>
       </c>
       <c r="D1" t="s">
-        <v>730</v>
+        <v>707</v>
       </c>
       <c r="E1" t="s">
-        <v>739</v>
+        <v>717</v>
       </c>
       <c r="F1" t="s">
-        <v>740</v>
+        <v>718</v>
       </c>
       <c r="G1" t="s">
-        <v>741</v>
+        <v>719</v>
       </c>
       <c r="H1" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="I1" t="s">
         <v>640</v>
       </c>
       <c r="J1" t="s">
-        <v>743</v>
+        <v>721</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -21357,28 +22098,28 @@
         <v>161</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>744</v>
+        <v>722</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>745</v>
+        <v>723</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>746</v>
+        <v>724</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>747</v>
+        <v>725</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>747</v>
+        <v>725</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>748</v>
+        <v>726</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>749</v>
+        <v>727</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -21389,31 +22130,31 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>750</v>
+        <v>728</v>
       </c>
       <c r="D4" t="s">
-        <v>751</v>
+        <v>729</v>
       </c>
       <c r="E4" t="s">
-        <v>752</v>
+        <v>730</v>
       </c>
       <c r="F4" t="s">
-        <v>753</v>
+        <v>731</v>
       </c>
       <c r="G4" t="s">
-        <v>753</v>
+        <v>731</v>
       </c>
       <c r="H4" t="s">
-        <v>754</v>
+        <v>732</v>
       </c>
       <c r="I4" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="J4" t="s">
-        <v>755</v>
+        <v>733</v>
       </c>
       <c r="K4" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -21829,7 +22570,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>756</v>
+        <v>734</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -21864,7 +22605,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>756</v>
+        <v>734</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -21963,7 +22704,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>756</v>
+        <v>734</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -21998,7 +22739,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>756</v>
+        <v>734</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -22161,7 +22902,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>756</v>
+        <v>734</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -22196,7 +22937,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>756</v>
+        <v>734</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -22231,7 +22972,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>756</v>
+        <v>734</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -22438,25 +23179,25 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>757</v>
+        <v>735</v>
       </c>
       <c r="F1" t="s">
-        <v>758</v>
+        <v>736</v>
       </c>
       <c r="G1" t="s">
-        <v>759</v>
+        <v>737</v>
       </c>
       <c r="H1" t="s">
-        <v>760</v>
+        <v>738</v>
       </c>
       <c r="I1" t="s">
-        <v>761</v>
+        <v>739</v>
       </c>
       <c r="K1" t="s">
-        <v>762</v>
+        <v>740</v>
       </c>
       <c r="L1" t="s">
-        <v>763</v>
+        <v>741</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -22500,23 +23241,23 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>764</v>
+        <v>742</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>765</v>
+        <v>743</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>766</v>
+        <v>744</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>767</v>
+        <v>745</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>766</v>
+        <v>744</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>768</v>
+        <v>746</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -22533,28 +23274,28 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>769</v>
+        <v>747</v>
       </c>
       <c r="F4" t="s">
-        <v>770</v>
+        <v>748</v>
       </c>
       <c r="G4" t="s">
-        <v>771</v>
+        <v>749</v>
       </c>
       <c r="H4" t="s">
-        <v>772</v>
+        <v>750</v>
       </c>
       <c r="I4" t="s">
-        <v>773</v>
+        <v>751</v>
       </c>
       <c r="J4" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="K4" t="s">
-        <v>774</v>
+        <v>752</v>
       </c>
       <c r="L4" t="s">
-        <v>775</v>
+        <v>753</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -22568,16 +23309,16 @@
         <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>776</v>
+        <v>754</v>
       </c>
       <c r="F5" t="s">
-        <v>777</v>
+        <v>755</v>
       </c>
       <c r="H5" t="s">
-        <v>778</v>
+        <v>756</v>
       </c>
       <c r="K5" t="s">
-        <v>779</v>
+        <v>757</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -22591,16 +23332,16 @@
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>780</v>
+        <v>758</v>
       </c>
       <c r="F6" t="s">
-        <v>777</v>
+        <v>755</v>
       </c>
       <c r="H6" t="s">
-        <v>781</v>
+        <v>759</v>
       </c>
       <c r="K6" t="s">
-        <v>782</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -22614,16 +23355,16 @@
         <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>783</v>
+        <v>761</v>
       </c>
       <c r="F7" t="s">
-        <v>777</v>
+        <v>755</v>
       </c>
       <c r="H7" t="s">
-        <v>784</v>
+        <v>762</v>
       </c>
       <c r="K7" t="s">
-        <v>785</v>
+        <v>763</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -22637,16 +23378,16 @@
         <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>786</v>
+        <v>764</v>
       </c>
       <c r="F8" t="s">
-        <v>777</v>
+        <v>755</v>
       </c>
       <c r="H8" t="s">
-        <v>787</v>
+        <v>765</v>
       </c>
       <c r="K8" t="s">
-        <v>788</v>
+        <v>766</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -22660,16 +23401,16 @@
         <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>789</v>
+        <v>767</v>
       </c>
       <c r="F9" t="s">
-        <v>777</v>
+        <v>755</v>
       </c>
       <c r="H9" t="s">
-        <v>790</v>
+        <v>768</v>
       </c>
       <c r="K9" t="s">
-        <v>779</v>
+        <v>757</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -22683,16 +23424,16 @@
         <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>791</v>
+        <v>769</v>
       </c>
       <c r="F10" t="s">
-        <v>777</v>
+        <v>755</v>
       </c>
       <c r="H10" t="s">
-        <v>792</v>
+        <v>770</v>
       </c>
       <c r="K10" t="s">
-        <v>782</v>
+        <v>760</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -22706,16 +23447,16 @@
         <v>507</v>
       </c>
       <c r="E11" t="s">
-        <v>791</v>
+        <v>769</v>
       </c>
       <c r="F11" t="s">
-        <v>777</v>
+        <v>755</v>
       </c>
       <c r="H11" t="s">
-        <v>792</v>
+        <v>770</v>
       </c>
       <c r="J11" t="s">
-        <v>793</v>
+        <v>771</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -22729,16 +23470,16 @@
         <v>563</v>
       </c>
       <c r="E12" t="s">
-        <v>791</v>
+        <v>769</v>
       </c>
       <c r="F12" t="s">
-        <v>777</v>
+        <v>755</v>
       </c>
       <c r="H12" t="s">
-        <v>792</v>
+        <v>770</v>
       </c>
       <c r="J12" t="s">
-        <v>793</v>
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -22770,25 +23511,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>794</v>
+        <v>772</v>
       </c>
       <c r="C1" t="s">
-        <v>795</v>
+        <v>773</v>
       </c>
       <c r="D1" t="s">
-        <v>796</v>
+        <v>774</v>
       </c>
       <c r="F1" t="s">
-        <v>797</v>
+        <v>775</v>
       </c>
       <c r="G1" t="s">
-        <v>798</v>
+        <v>776</v>
       </c>
       <c r="H1" t="s">
-        <v>799</v>
+        <v>777</v>
       </c>
       <c r="I1" t="s">
-        <v>800</v>
+        <v>778</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -22796,16 +23537,16 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>801</v>
+        <v>779</v>
       </c>
       <c r="C2" t="s">
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>802</v>
+        <v>780</v>
       </c>
       <c r="F2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G2" t="s">
         <v>31</v>
@@ -22822,25 +23563,25 @@
         <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>803</v>
+        <v>781</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>804</v>
+        <v>782</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>805</v>
+        <v>783</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>806</v>
+        <v>784</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>807</v>
+        <v>785</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>808</v>
+        <v>786</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>809</v>
+        <v>787</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -22848,31 +23589,31 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>810</v>
+        <v>788</v>
       </c>
       <c r="C4" t="s">
-        <v>811</v>
+        <v>789</v>
       </c>
       <c r="D4" t="s">
-        <v>812</v>
+        <v>790</v>
       </c>
       <c r="E4" t="s">
-        <v>813</v>
+        <v>791</v>
       </c>
       <c r="F4" t="s">
-        <v>814</v>
+        <v>792</v>
       </c>
       <c r="G4" t="s">
-        <v>815</v>
+        <v>793</v>
       </c>
       <c r="H4" t="s">
-        <v>816</v>
+        <v>794</v>
       </c>
       <c r="I4" t="s">
-        <v>817</v>
+        <v>795</v>
       </c>
       <c r="J4" t="s">
-        <v>813</v>
+        <v>791</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -22883,7 +23624,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="E6" t="str">
         <f>LOOKUP(B6,Item!B:B,Item!H:H)</f>
@@ -22893,10 +23634,10 @@
         <v>0.9</v>
       </c>
       <c r="G6" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
       <c r="H6" t="s">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -22914,7 +23655,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="E7" t="str">
         <f>LOOKUP(B7,Item!B:B,Item!H:H)</f>
@@ -22924,10 +23665,10 @@
         <v>0.8</v>
       </c>
       <c r="G7" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
       <c r="H7" t="s">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -22945,7 +23686,7 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="E8" t="str">
         <f>LOOKUP(B8,Item!B:B,Item!H:H)</f>
@@ -22955,10 +23696,10 @@
         <v>0.8</v>
       </c>
       <c r="G8" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
       <c r="H8" t="s">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -22976,7 +23717,7 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="E9" t="str">
         <f>LOOKUP(B9,Item!B:B,Item!H:H)</f>
@@ -22986,10 +23727,10 @@
         <v>0.9</v>
       </c>
       <c r="G9" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
       <c r="H9" t="s">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -23007,7 +23748,7 @@
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="E10" t="str">
         <f>LOOKUP(B10,Item!B:B,Item!H:H)</f>
@@ -23017,10 +23758,10 @@
         <v>0.8</v>
       </c>
       <c r="G10" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
       <c r="H10" t="s">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -23038,7 +23779,7 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="E11" t="str">
         <f>LOOKUP(B11,Item!B:B,Item!H:H)</f>
@@ -23048,10 +23789,10 @@
         <v>0.8</v>
       </c>
       <c r="G11" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
       <c r="H11" t="s">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -23069,7 +23810,7 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="E12" t="str">
         <f>LOOKUP(B12,Item!B:B,Item!H:H)</f>
@@ -23079,10 +23820,10 @@
         <v>0.8</v>
       </c>
       <c r="G12" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
       <c r="H12" t="s">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -23100,7 +23841,7 @@
         <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="E13" t="str">
         <f>LOOKUP(B13,Item!B:B,Item!H:H)</f>
@@ -23110,10 +23851,10 @@
         <v>0.9</v>
       </c>
       <c r="G13" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
       <c r="H13" t="s">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -23131,7 +23872,7 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="E14" t="str">
         <f>LOOKUP(B14,Item!B:B,Item!H:H)</f>
@@ -23141,10 +23882,10 @@
         <v>0.7</v>
       </c>
       <c r="G14" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
       <c r="H14" t="s">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -23162,7 +23903,7 @@
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="E15" t="str">
         <f>LOOKUP(B15,Item!B:B,Item!H:H)</f>
@@ -23172,10 +23913,10 @@
         <v>0.9</v>
       </c>
       <c r="G15" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
       <c r="H15" t="s">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -23193,7 +23934,7 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="E16" t="str">
         <f>LOOKUP(B16,Item!B:B,Item!H:H)</f>
@@ -23203,10 +23944,10 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
       <c r="H16" t="s">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -23241,10 +23982,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>821</v>
+        <v>799</v>
       </c>
       <c r="D1" t="s">
-        <v>822</v>
+        <v>800</v>
       </c>
       <c r="E1" t="s">
         <v>7</v>
@@ -23261,7 +24002,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>823</v>
+        <v>801</v>
       </c>
       <c r="E2" t="s">
         <v>30</v>
@@ -23278,10 +24019,10 @@
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>824</v>
+        <v>802</v>
       </c>
       <c r="E3" t="s">
-        <v>825</v>
+        <v>803</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -23303,7 +24044,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>826</v>
+        <v>804</v>
       </c>
       <c r="D5" t="s">
         <v>139</v>
@@ -23317,7 +24058,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>827</v>
+        <v>805</v>
       </c>
       <c r="D6" t="s">
         <v>190</v>
@@ -23331,7 +24072,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>828</v>
+        <v>806</v>
       </c>
       <c r="D7" t="s">
         <v>392</v>
@@ -23355,7 +24096,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>829</v>
+        <v>807</v>
       </c>
       <c r="D10" t="s">
         <v>270</v>
